--- a/data/bitacora.xlsx
+++ b/data/bitacora.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29819"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29825"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://grupokaufmann-my.sharepoint.com/personal/samuel_sanchez_grupokaufmann_com/Documents/Documentos/Dev/bitacora_diaria/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="335" documentId="8_{4616FF0F-C10E-4DFE-8F27-869B9C60E0F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7ACB77ED-ACC9-43BA-A194-CDEBA9184811}"/>
+  <xr:revisionPtr revIDLastSave="344" documentId="8_{4616FF0F-C10E-4DFE-8F27-869B9C60E0F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E977F3E9-7E0D-4C1E-A20A-8DCF42B2E71A}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{A9E3F017-9040-47A2-B586-0486128F3261}"/>
   </bookViews>
@@ -1641,17 +1641,7 @@
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{40364ABC-409D-4532-8E14-9D155F80C509}" name="Tabla1" displayName="Tabla1" ref="A1:J205" totalsRowShown="0">
-  <autoFilter ref="A1:J205" xr:uid="{40364ABC-409D-4532-8E14-9D155F80C509}">
-    <filterColumn colId="4">
-      <filters blank="1">
-        <filter val="ALEJANDRO ALBERTO VILLAGRA ORÓSTEGUI"/>
-        <filter val="ARTURO ANDRÉS SILVA ESPERGUE"/>
-        <filter val="BORIS ISRAEL CRUCES MARTÍNEZ"/>
-        <filter val="RODRIGO ANDRÉS INZUNZA LABRA"/>
-        <filter val="SERGIO ALBERTO ORELLANA VEGA"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
+  <autoFilter ref="A1:J205" xr:uid="{40364ABC-409D-4532-8E14-9D155F80C509}"/>
   <tableColumns count="10">
     <tableColumn id="1" xr3:uid="{0A7C6585-5C8B-46BF-ABA0-2DA806D161DC}" name="FLOTA" dataDxfId="9"/>
     <tableColumn id="2" xr3:uid="{EB7792BB-219D-496F-9F16-84F6805E0CB0}" name="VIN CON PROBLEMAS" dataDxfId="8"/>
@@ -2032,7 +2022,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:12" ht="14.45" hidden="1">
+    <row r="2" spans="1:12" ht="14.45">
       <c r="A2" s="7" t="s">
         <v>10</v>
       </c>
@@ -2055,7 +2045,7 @@
       <c r="H2" s="12"/>
       <c r="I2" s="12"/>
     </row>
-    <row r="3" spans="1:12" ht="14.45" hidden="1">
+    <row r="3" spans="1:12" ht="14.45">
       <c r="A3" s="7" t="s">
         <v>10</v>
       </c>
@@ -2078,7 +2068,7 @@
       <c r="H3" s="12"/>
       <c r="I3" s="12"/>
     </row>
-    <row r="4" spans="1:12" ht="14.45" hidden="1">
+    <row r="4" spans="1:12" ht="14.45">
       <c r="A4" s="7" t="s">
         <v>10</v>
       </c>
@@ -2101,7 +2091,7 @@
       <c r="H4" s="12"/>
       <c r="I4" s="12"/>
     </row>
-    <row r="5" spans="1:12" ht="14.45" hidden="1">
+    <row r="5" spans="1:12" ht="14.45">
       <c r="A5" s="7" t="s">
         <v>10</v>
       </c>
@@ -2124,7 +2114,7 @@
       <c r="H5" s="12"/>
       <c r="I5" s="12"/>
     </row>
-    <row r="6" spans="1:12" ht="14.45" hidden="1">
+    <row r="6" spans="1:12" ht="14.45">
       <c r="A6" s="7" t="s">
         <v>10</v>
       </c>
@@ -2147,7 +2137,7 @@
       <c r="H6" s="12"/>
       <c r="I6" s="12"/>
     </row>
-    <row r="7" spans="1:12" ht="14.45" hidden="1">
+    <row r="7" spans="1:12" ht="14.45">
       <c r="A7" s="7" t="s">
         <v>10</v>
       </c>
@@ -2170,7 +2160,7 @@
       <c r="H7" s="24"/>
       <c r="I7" s="24"/>
     </row>
-    <row r="8" spans="1:12" ht="14.45" hidden="1">
+    <row r="8" spans="1:12" ht="14.45">
       <c r="A8" s="7" t="s">
         <v>10</v>
       </c>
@@ -2193,7 +2183,7 @@
       <c r="H8" s="24"/>
       <c r="I8" s="24"/>
     </row>
-    <row r="9" spans="1:12" ht="14.45" hidden="1">
+    <row r="9" spans="1:12" ht="14.45">
       <c r="A9" s="7" t="s">
         <v>10</v>
       </c>
@@ -2216,7 +2206,7 @@
       <c r="H9" s="12"/>
       <c r="I9" s="12"/>
     </row>
-    <row r="10" spans="1:12" ht="14.45" hidden="1">
+    <row r="10" spans="1:12" ht="14.45">
       <c r="A10" s="7" t="s">
         <v>10</v>
       </c>
@@ -2239,7 +2229,7 @@
       <c r="H10" s="12"/>
       <c r="I10" s="12"/>
     </row>
-    <row r="11" spans="1:12" ht="14.45" hidden="1">
+    <row r="11" spans="1:12" ht="14.45">
       <c r="A11" s="7" t="s">
         <v>10</v>
       </c>
@@ -2683,7 +2673,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="30" spans="1:9" ht="14.45" hidden="1">
+    <row r="30" spans="1:9" ht="14.45">
       <c r="A30" s="7" t="s">
         <v>80</v>
       </c>
@@ -2706,7 +2696,7 @@
       <c r="H30" s="12"/>
       <c r="I30" s="12"/>
     </row>
-    <row r="31" spans="1:9" ht="14.45" hidden="1">
+    <row r="31" spans="1:9" ht="14.45">
       <c r="A31" s="7" t="s">
         <v>80</v>
       </c>
@@ -2729,7 +2719,7 @@
       <c r="H31" s="12"/>
       <c r="I31" s="12"/>
     </row>
-    <row r="32" spans="1:9" ht="14.45" hidden="1">
+    <row r="32" spans="1:9" ht="14.45">
       <c r="A32" s="7" t="s">
         <v>80</v>
       </c>
@@ -2752,7 +2742,7 @@
       <c r="H32" s="12"/>
       <c r="I32" s="12"/>
     </row>
-    <row r="33" spans="1:9" ht="14.45" hidden="1">
+    <row r="33" spans="1:9" ht="14.45">
       <c r="A33" s="7" t="s">
         <v>80</v>
       </c>
@@ -2775,7 +2765,7 @@
       <c r="H33" s="12"/>
       <c r="I33" s="12"/>
     </row>
-    <row r="34" spans="1:9" ht="14.45" hidden="1">
+    <row r="34" spans="1:9" ht="14.45">
       <c r="A34" s="7" t="s">
         <v>80</v>
       </c>
@@ -2798,7 +2788,7 @@
       <c r="H34" s="12"/>
       <c r="I34" s="12"/>
     </row>
-    <row r="35" spans="1:9" ht="14.45" hidden="1">
+    <row r="35" spans="1:9" ht="14.45">
       <c r="A35" s="7" t="s">
         <v>80</v>
       </c>
@@ -2821,7 +2811,7 @@
       <c r="H35" s="12"/>
       <c r="I35" s="12"/>
     </row>
-    <row r="36" spans="1:9" ht="14.45" hidden="1">
+    <row r="36" spans="1:9" ht="14.45">
       <c r="A36" s="7" t="s">
         <v>80</v>
       </c>
@@ -3768,7 +3758,7 @@
       <c r="H72" s="12"/>
       <c r="I72" s="12"/>
     </row>
-    <row r="73" spans="1:9" ht="14.45" hidden="1">
+    <row r="73" spans="1:9" ht="14.45">
       <c r="A73" s="7" t="s">
         <v>172</v>
       </c>
@@ -3791,7 +3781,7 @@
       <c r="H73" s="12"/>
       <c r="I73" s="12"/>
     </row>
-    <row r="74" spans="1:9" ht="14.45" hidden="1">
+    <row r="74" spans="1:9" ht="14.45">
       <c r="A74" s="7" t="s">
         <v>172</v>
       </c>
@@ -4182,7 +4172,7 @@
       <c r="H90" s="12"/>
       <c r="I90" s="12"/>
     </row>
-    <row r="91" spans="1:9" ht="14.45" hidden="1">
+    <row r="91" spans="1:9" ht="14.45">
       <c r="A91" s="7" t="s">
         <v>210</v>
       </c>
@@ -4205,7 +4195,7 @@
       <c r="H91" s="12"/>
       <c r="I91" s="12"/>
     </row>
-    <row r="92" spans="1:9" ht="14.45" hidden="1">
+    <row r="92" spans="1:9" ht="14.45">
       <c r="A92" s="7" t="s">
         <v>210</v>
       </c>
@@ -4228,7 +4218,7 @@
       <c r="H92" s="12"/>
       <c r="I92" s="12"/>
     </row>
-    <row r="93" spans="1:9" ht="14.45" hidden="1">
+    <row r="93" spans="1:9" ht="14.45">
       <c r="A93" s="7" t="s">
         <v>210</v>
       </c>
@@ -4956,7 +4946,7 @@
       <c r="H123" s="12"/>
       <c r="I123" s="12"/>
     </row>
-    <row r="124" spans="1:9" ht="14.45" hidden="1">
+    <row r="124" spans="1:9" ht="14.45">
       <c r="A124" s="7" t="s">
         <v>287</v>
       </c>
@@ -4979,7 +4969,7 @@
       <c r="H124" s="12"/>
       <c r="I124" s="12"/>
     </row>
-    <row r="125" spans="1:9" ht="14.45" hidden="1">
+    <row r="125" spans="1:9" ht="14.45">
       <c r="A125" s="7" t="s">
         <v>287</v>
       </c>
@@ -5002,7 +4992,7 @@
       <c r="H125" s="12"/>
       <c r="I125" s="12"/>
     </row>
-    <row r="126" spans="1:9" ht="14.45" hidden="1">
+    <row r="126" spans="1:9" ht="14.45">
       <c r="A126" s="7" t="s">
         <v>287</v>
       </c>
@@ -6576,6 +6566,15 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x010100027709BF533FA442AFC4A8B2C0110727" ma:contentTypeVersion="15" ma:contentTypeDescription="Crear nuevo documento." ma:contentTypeScope="" ma:versionID="a37fc0d7c302f7619d355a49e1f175a4">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="3e53c16e-6636-411e-b1c4-e9eeb71b3b2a" xmlns:ns4="bda9c1ec-c4e2-44f9-929c-ca399fe36c88" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="01250a30c504a808427f15ccf149ee4d" ns3:_="" ns4:_="">
     <xsd:import namespace="3e53c16e-6636-411e-b1c4-e9eeb71b3b2a"/>
@@ -6808,7 +6807,7 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <_activity xmlns="3e53c16e-6636-411e-b1c4-e9eeb71b3b2a" xsi:nil="true"/>
@@ -6816,23 +6815,14 @@
 </p:properties>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3C8123E5-81FD-4C24-91F1-33BC079967E9}"/>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4794C7E6-B89D-4081-9A67-B8D500EF1EE4}"/>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D9861A25-610F-425F-BC6A-AC52D4971411}"/>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3C8123E5-81FD-4C24-91F1-33BC079967E9}"/>
 </file>
--- a/data/bitacora.xlsx
+++ b/data/bitacora.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://grupokaufmann-my.sharepoint.com/personal/samuel_sanchez_grupokaufmann_com/Documents/Documentos/Dev/bitacora_diaria/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="344" documentId="8_{4616FF0F-C10E-4DFE-8F27-869B9C60E0F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E977F3E9-7E0D-4C1E-A20A-8DCF42B2E71A}"/>
+  <xr:revisionPtr revIDLastSave="346" documentId="8_{4616FF0F-C10E-4DFE-8F27-869B9C60E0F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{195D0159-75E2-4678-8C7E-7E1B57B3EDDA}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{A9E3F017-9040-47A2-B586-0486128F3261}"/>
   </bookViews>
@@ -6566,6 +6566,14 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_activity xmlns="3e53c16e-6636-411e-b1c4-e9eeb71b3b2a" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
   <Display>DocumentLibraryForm</Display>
@@ -6574,7 +6582,7 @@
 </FormTemplates>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x010100027709BF533FA442AFC4A8B2C0110727" ma:contentTypeVersion="15" ma:contentTypeDescription="Crear nuevo documento." ma:contentTypeScope="" ma:versionID="a37fc0d7c302f7619d355a49e1f175a4">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="3e53c16e-6636-411e-b1c4-e9eeb71b3b2a" xmlns:ns4="bda9c1ec-c4e2-44f9-929c-ca399fe36c88" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="01250a30c504a808427f15ccf149ee4d" ns3:_="" ns4:_="">
     <xsd:import namespace="3e53c16e-6636-411e-b1c4-e9eeb71b3b2a"/>
@@ -6807,22 +6815,14 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_activity xmlns="3e53c16e-6636-411e-b1c4-e9eeb71b3b2a" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D9861A25-610F-425F-BC6A-AC52D4971411}"/>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3C8123E5-81FD-4C24-91F1-33BC079967E9}"/>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4794C7E6-B89D-4081-9A67-B8D500EF1EE4}"/>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D9861A25-610F-425F-BC6A-AC52D4971411}"/>
 </file>
--- a/data/bitacora.xlsx
+++ b/data/bitacora.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29825"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://grupokaufmann-my.sharepoint.com/personal/samuel_sanchez_grupokaufmann_com/Documents/Documentos/Dev/bitacora_diaria/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="346" documentId="8_{4616FF0F-C10E-4DFE-8F27-869B9C60E0F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{195D0159-75E2-4678-8C7E-7E1B57B3EDDA}"/>
+  <xr:revisionPtr revIDLastSave="348" documentId="8_{4616FF0F-C10E-4DFE-8F27-869B9C60E0F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1C18D249-8141-4783-AC41-8C4A3919858E}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{A9E3F017-9040-47A2-B586-0486128F3261}"/>
+    <workbookView xWindow="-28920" yWindow="-1155" windowWidth="29040" windowHeight="15720" xr2:uid="{A9E3F017-9040-47A2-B586-0486128F3261}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -19,7 +19,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Hoja1!$A$1:$F$127</definedName>
   </definedNames>
-  <calcPr calcId="191028" calcCompleted="0"/>
+  <calcPr calcId="191028"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -1087,7 +1087,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1639,9 +1639,24 @@
 </styleSheet>
 </file>
 
+<file path=xl/namedSheetViews/namedSheetView1.xml><?xml version="1.0" encoding="utf-8"?>
+<namedSheetViews xmlns="http://schemas.microsoft.com/office/spreadsheetml/2019/namedsheetviews" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14"/>
+</file>
+
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{40364ABC-409D-4532-8E14-9D155F80C509}" name="Tabla1" displayName="Tabla1" ref="A1:J205" totalsRowShown="0">
-  <autoFilter ref="A1:J205" xr:uid="{40364ABC-409D-4532-8E14-9D155F80C509}"/>
+  <autoFilter ref="A1:J205" xr:uid="{40364ABC-409D-4532-8E14-9D155F80C509}">
+    <filterColumn colId="0">
+      <filters>
+        <filter val="SACYR"/>
+      </filters>
+    </filterColumn>
+    <filterColumn colId="5">
+      <filters>
+        <filter val="No revisada"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <tableColumns count="10">
     <tableColumn id="1" xr3:uid="{0A7C6585-5C8B-46BF-ABA0-2DA806D161DC}" name="FLOTA" dataDxfId="9"/>
     <tableColumn id="2" xr3:uid="{EB7792BB-219D-496F-9F16-84F6805E0CB0}" name="VIN CON PROBLEMAS" dataDxfId="8"/>
@@ -1975,22 +1990,22 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EDA66EBA-6B88-4C75-8217-0B7E221D898D}">
-  <dimension ref="A1:L204"/>
-  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" customHeight="1"/>
+  <dimension ref="A1:L205"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.453125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="43" style="6" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="22.7109375" style="6" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.28515625" style="43" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="22.7265625" style="6" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.26953125" style="43" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="25" style="6" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="40.28515625" style="6" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="27.5703125" style="6" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="18.85546875" style="16" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="20.140625" style="16" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="40.26953125" style="6" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="27.54296875" style="6" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="18.81640625" style="16" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="20.1796875" style="16" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="79" style="6" bestFit="1" customWidth="1"/>
-    <col min="11" max="16384" width="11.42578125" style="6"/>
+    <col min="11" max="16384" width="11.453125" style="6"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="14.45">
+    <row r="1" spans="1:12" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A1" s="17" t="s">
         <v>0</v>
       </c>
@@ -2022,7 +2037,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:12" ht="14.45">
+    <row r="2" spans="1:12" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A2" s="7" t="s">
         <v>10</v>
       </c>
@@ -2045,7 +2060,7 @@
       <c r="H2" s="12"/>
       <c r="I2" s="12"/>
     </row>
-    <row r="3" spans="1:12" ht="14.45">
+    <row r="3" spans="1:12" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A3" s="7" t="s">
         <v>10</v>
       </c>
@@ -2068,7 +2083,7 @@
       <c r="H3" s="12"/>
       <c r="I3" s="12"/>
     </row>
-    <row r="4" spans="1:12" ht="14.45">
+    <row r="4" spans="1:12" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A4" s="7" t="s">
         <v>10</v>
       </c>
@@ -2091,7 +2106,7 @@
       <c r="H4" s="12"/>
       <c r="I4" s="12"/>
     </row>
-    <row r="5" spans="1:12" ht="14.45">
+    <row r="5" spans="1:12" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A5" s="7" t="s">
         <v>10</v>
       </c>
@@ -2114,7 +2129,7 @@
       <c r="H5" s="12"/>
       <c r="I5" s="12"/>
     </row>
-    <row r="6" spans="1:12" ht="14.45">
+    <row r="6" spans="1:12" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A6" s="7" t="s">
         <v>10</v>
       </c>
@@ -2137,7 +2152,7 @@
       <c r="H6" s="12"/>
       <c r="I6" s="12"/>
     </row>
-    <row r="7" spans="1:12" ht="14.45">
+    <row r="7" spans="1:12" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A7" s="7" t="s">
         <v>10</v>
       </c>
@@ -2160,7 +2175,7 @@
       <c r="H7" s="24"/>
       <c r="I7" s="24"/>
     </row>
-    <row r="8" spans="1:12" ht="14.45">
+    <row r="8" spans="1:12" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A8" s="7" t="s">
         <v>10</v>
       </c>
@@ -2183,7 +2198,7 @@
       <c r="H8" s="24"/>
       <c r="I8" s="24"/>
     </row>
-    <row r="9" spans="1:12" ht="14.45">
+    <row r="9" spans="1:12" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A9" s="7" t="s">
         <v>10</v>
       </c>
@@ -2206,7 +2221,7 @@
       <c r="H9" s="12"/>
       <c r="I9" s="12"/>
     </row>
-    <row r="10" spans="1:12" ht="14.45">
+    <row r="10" spans="1:12" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A10" s="7" t="s">
         <v>10</v>
       </c>
@@ -2229,7 +2244,7 @@
       <c r="H10" s="12"/>
       <c r="I10" s="12"/>
     </row>
-    <row r="11" spans="1:12" ht="14.45">
+    <row r="11" spans="1:12" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A11" s="7" t="s">
         <v>10</v>
       </c>
@@ -2252,7 +2267,7 @@
       <c r="H11" s="12"/>
       <c r="I11" s="12"/>
     </row>
-    <row r="12" spans="1:12" ht="14.45">
+    <row r="12" spans="1:12" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A12" s="7" t="s">
         <v>33</v>
       </c>
@@ -2276,7 +2291,7 @@
       <c r="I12" s="12"/>
       <c r="L12" s="26"/>
     </row>
-    <row r="13" spans="1:12" ht="14.45">
+    <row r="13" spans="1:12" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A13" s="7" t="s">
         <v>33</v>
       </c>
@@ -2299,7 +2314,7 @@
       <c r="H13" s="12"/>
       <c r="I13" s="12"/>
     </row>
-    <row r="14" spans="1:12" ht="14.45">
+    <row r="14" spans="1:12" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A14" s="7" t="s">
         <v>33</v>
       </c>
@@ -2322,7 +2337,7 @@
       <c r="H14" s="12"/>
       <c r="I14" s="12"/>
     </row>
-    <row r="15" spans="1:12" ht="14.45">
+    <row r="15" spans="1:12" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A15" s="7" t="s">
         <v>33</v>
       </c>
@@ -2345,7 +2360,7 @@
       <c r="H15" s="12"/>
       <c r="I15" s="12"/>
     </row>
-    <row r="16" spans="1:12" ht="14.45">
+    <row r="16" spans="1:12" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A16" s="7" t="s">
         <v>33</v>
       </c>
@@ -2368,7 +2383,7 @@
       <c r="H16" s="12"/>
       <c r="I16" s="12"/>
     </row>
-    <row r="17" spans="1:9" ht="14.45">
+    <row r="17" spans="1:9" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A17" s="7" t="s">
         <v>33</v>
       </c>
@@ -2391,7 +2406,7 @@
       <c r="H17" s="12"/>
       <c r="I17" s="12"/>
     </row>
-    <row r="18" spans="1:9" ht="14.45">
+    <row r="18" spans="1:9" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A18" s="7" t="s">
         <v>33</v>
       </c>
@@ -2414,7 +2429,7 @@
       <c r="H18" s="12"/>
       <c r="I18" s="12"/>
     </row>
-    <row r="19" spans="1:9" ht="14.45">
+    <row r="19" spans="1:9" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A19" s="7" t="s">
         <v>33</v>
       </c>
@@ -2437,7 +2452,7 @@
       <c r="H19" s="12"/>
       <c r="I19" s="12"/>
     </row>
-    <row r="20" spans="1:9" ht="14.45">
+    <row r="20" spans="1:9" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A20" s="7" t="s">
         <v>51</v>
       </c>
@@ -2460,7 +2475,7 @@
       <c r="H20" s="12"/>
       <c r="I20" s="12"/>
     </row>
-    <row r="21" spans="1:9" ht="14.45">
+    <row r="21" spans="1:9" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A21" s="7" t="s">
         <v>51</v>
       </c>
@@ -2483,7 +2498,7 @@
       <c r="H21" s="12"/>
       <c r="I21" s="12"/>
     </row>
-    <row r="22" spans="1:9" ht="14.45">
+    <row r="22" spans="1:9" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A22" s="7" t="s">
         <v>51</v>
       </c>
@@ -2506,7 +2521,7 @@
       <c r="H22" s="12"/>
       <c r="I22" s="12"/>
     </row>
-    <row r="23" spans="1:9" ht="14.45">
+    <row r="23" spans="1:9" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A23" s="7" t="s">
         <v>59</v>
       </c>
@@ -2529,7 +2544,7 @@
       <c r="H23" s="12"/>
       <c r="I23" s="12"/>
     </row>
-    <row r="24" spans="1:9" ht="14.45">
+    <row r="24" spans="1:9" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A24" s="7" t="s">
         <v>59</v>
       </c>
@@ -2552,7 +2567,7 @@
       <c r="H24" s="12"/>
       <c r="I24" s="12"/>
     </row>
-    <row r="25" spans="1:9" ht="14.45">
+    <row r="25" spans="1:9" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A25" s="7" t="s">
         <v>65</v>
       </c>
@@ -2575,7 +2590,7 @@
       <c r="H25" s="12"/>
       <c r="I25" s="12"/>
     </row>
-    <row r="26" spans="1:9" ht="14.45">
+    <row r="26" spans="1:9" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A26" s="7" t="s">
         <v>65</v>
       </c>
@@ -2598,7 +2613,7 @@
       <c r="H26" s="12"/>
       <c r="I26" s="12"/>
     </row>
-    <row r="27" spans="1:9" ht="14.45">
+    <row r="27" spans="1:9" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A27" s="7" t="s">
         <v>65</v>
       </c>
@@ -2621,7 +2636,7 @@
       <c r="H27" s="12"/>
       <c r="I27" s="12"/>
     </row>
-    <row r="28" spans="1:9" ht="14.45">
+    <row r="28" spans="1:9" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A28" s="7" t="s">
         <v>65</v>
       </c>
@@ -2644,7 +2659,7 @@
       <c r="H28" s="12"/>
       <c r="I28" s="12"/>
     </row>
-    <row r="29" spans="1:9" ht="14.45">
+    <row r="29" spans="1:9" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A29" s="7" t="s">
         <v>65</v>
       </c>
@@ -2673,7 +2688,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="30" spans="1:9" ht="14.45">
+    <row r="30" spans="1:9" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A30" s="7" t="s">
         <v>80</v>
       </c>
@@ -2696,7 +2711,7 @@
       <c r="H30" s="12"/>
       <c r="I30" s="12"/>
     </row>
-    <row r="31" spans="1:9" ht="14.45">
+    <row r="31" spans="1:9" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A31" s="7" t="s">
         <v>80</v>
       </c>
@@ -2719,7 +2734,7 @@
       <c r="H31" s="12"/>
       <c r="I31" s="12"/>
     </row>
-    <row r="32" spans="1:9" ht="14.45">
+    <row r="32" spans="1:9" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A32" s="7" t="s">
         <v>80</v>
       </c>
@@ -2742,7 +2757,7 @@
       <c r="H32" s="12"/>
       <c r="I32" s="12"/>
     </row>
-    <row r="33" spans="1:9" ht="14.45">
+    <row r="33" spans="1:9" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A33" s="7" t="s">
         <v>80</v>
       </c>
@@ -2765,7 +2780,7 @@
       <c r="H33" s="12"/>
       <c r="I33" s="12"/>
     </row>
-    <row r="34" spans="1:9" ht="14.45">
+    <row r="34" spans="1:9" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A34" s="7" t="s">
         <v>80</v>
       </c>
@@ -2788,7 +2803,7 @@
       <c r="H34" s="12"/>
       <c r="I34" s="12"/>
     </row>
-    <row r="35" spans="1:9" ht="14.45">
+    <row r="35" spans="1:9" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A35" s="7" t="s">
         <v>80</v>
       </c>
@@ -2811,7 +2826,7 @@
       <c r="H35" s="12"/>
       <c r="I35" s="12"/>
     </row>
-    <row r="36" spans="1:9" ht="14.45">
+    <row r="36" spans="1:9" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A36" s="7" t="s">
         <v>80</v>
       </c>
@@ -2834,7 +2849,7 @@
       <c r="H36" s="12"/>
       <c r="I36" s="12"/>
     </row>
-    <row r="37" spans="1:9" ht="14.45">
+    <row r="37" spans="1:9" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A37" s="7" t="s">
         <v>95</v>
       </c>
@@ -2863,7 +2878,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="38" spans="1:9" ht="14.45">
+    <row r="38" spans="1:9" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A38" s="7" t="s">
         <v>95</v>
       </c>
@@ -2892,7 +2907,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="39" spans="1:9" ht="14.45">
+    <row r="39" spans="1:9" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A39" s="7" t="s">
         <v>95</v>
       </c>
@@ -2915,7 +2930,7 @@
       <c r="H39" s="12"/>
       <c r="I39" s="12"/>
     </row>
-    <row r="40" spans="1:9" ht="14.45">
+    <row r="40" spans="1:9" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A40" s="7" t="s">
         <v>95</v>
       </c>
@@ -2944,7 +2959,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="41" spans="1:9" ht="14.45">
+    <row r="41" spans="1:9" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A41" s="7" t="s">
         <v>95</v>
       </c>
@@ -2973,7 +2988,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="42" spans="1:9" ht="14.45">
+    <row r="42" spans="1:9" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A42" s="7" t="s">
         <v>95</v>
       </c>
@@ -2996,7 +3011,7 @@
       <c r="H42" s="12"/>
       <c r="I42" s="12"/>
     </row>
-    <row r="43" spans="1:9" ht="14.45">
+    <row r="43" spans="1:9" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A43" s="7" t="s">
         <v>95</v>
       </c>
@@ -3019,7 +3034,7 @@
       <c r="H43" s="12"/>
       <c r="I43" s="12"/>
     </row>
-    <row r="44" spans="1:9" ht="14.45">
+    <row r="44" spans="1:9" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A44" s="7" t="s">
         <v>95</v>
       </c>
@@ -3042,7 +3057,7 @@
       <c r="H44" s="12"/>
       <c r="I44" s="12"/>
     </row>
-    <row r="45" spans="1:9" ht="14.45">
+    <row r="45" spans="1:9" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A45" s="7" t="s">
         <v>95</v>
       </c>
@@ -3065,7 +3080,7 @@
       <c r="H45" s="12"/>
       <c r="I45" s="12"/>
     </row>
-    <row r="46" spans="1:9" ht="14.45">
+    <row r="46" spans="1:9" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A46" s="7" t="s">
         <v>95</v>
       </c>
@@ -3094,7 +3109,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="47" spans="1:9" ht="14.45">
+    <row r="47" spans="1:9" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A47" s="7" t="s">
         <v>95</v>
       </c>
@@ -3123,7 +3138,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="48" spans="1:9" ht="14.45">
+    <row r="48" spans="1:9" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A48" s="7" t="s">
         <v>95</v>
       </c>
@@ -3152,7 +3167,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="49" spans="1:9" ht="14.45">
+    <row r="49" spans="1:9" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A49" s="7" t="s">
         <v>95</v>
       </c>
@@ -3181,7 +3196,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="50" spans="1:9" ht="14.45">
+    <row r="50" spans="1:9" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A50" s="7" t="s">
         <v>95</v>
       </c>
@@ -3204,7 +3219,7 @@
       <c r="H50" s="12"/>
       <c r="I50" s="12"/>
     </row>
-    <row r="51" spans="1:9" ht="14.45">
+    <row r="51" spans="1:9" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A51" s="7" t="s">
         <v>95</v>
       </c>
@@ -3227,7 +3242,7 @@
       <c r="H51" s="12"/>
       <c r="I51" s="12"/>
     </row>
-    <row r="52" spans="1:9" ht="14.45">
+    <row r="52" spans="1:9" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A52" s="7" t="s">
         <v>95</v>
       </c>
@@ -3250,7 +3265,7 @@
       <c r="H52" s="12"/>
       <c r="I52" s="12"/>
     </row>
-    <row r="53" spans="1:9" ht="14.45">
+    <row r="53" spans="1:9" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A53" s="7" t="s">
         <v>95</v>
       </c>
@@ -3279,7 +3294,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="54" spans="1:9" ht="14.45">
+    <row r="54" spans="1:9" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A54" s="7" t="s">
         <v>95</v>
       </c>
@@ -3302,7 +3317,7 @@
       <c r="H54" s="12"/>
       <c r="I54" s="12"/>
     </row>
-    <row r="55" spans="1:9" ht="14.45">
+    <row r="55" spans="1:9" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A55" s="7" t="s">
         <v>95</v>
       </c>
@@ -3331,7 +3346,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="56" spans="1:9" ht="14.45">
+    <row r="56" spans="1:9" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A56" s="7" t="s">
         <v>95</v>
       </c>
@@ -3360,7 +3375,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="57" spans="1:9" ht="14.45">
+    <row r="57" spans="1:9" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A57" s="7" t="s">
         <v>95</v>
       </c>
@@ -3389,7 +3404,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="58" spans="1:9" ht="14.45">
+    <row r="58" spans="1:9" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A58" s="7" t="s">
         <v>95</v>
       </c>
@@ -3412,7 +3427,7 @@
       <c r="H58" s="12"/>
       <c r="I58" s="12"/>
     </row>
-    <row r="59" spans="1:9" ht="14.45">
+    <row r="59" spans="1:9" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A59" s="7" t="s">
         <v>95</v>
       </c>
@@ -3441,7 +3456,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="60" spans="1:9" ht="14.45">
+    <row r="60" spans="1:9" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A60" s="7" t="s">
         <v>95</v>
       </c>
@@ -3464,7 +3479,7 @@
       <c r="H60" s="12"/>
       <c r="I60" s="12"/>
     </row>
-    <row r="61" spans="1:9" ht="14.45">
+    <row r="61" spans="1:9" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A61" s="7" t="s">
         <v>95</v>
       </c>
@@ -3487,7 +3502,7 @@
       <c r="H61" s="12"/>
       <c r="I61" s="12"/>
     </row>
-    <row r="62" spans="1:9" ht="14.45">
+    <row r="62" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A62" s="7" t="s">
         <v>149</v>
       </c>
@@ -3510,7 +3525,7 @@
       <c r="H62" s="12"/>
       <c r="I62" s="12"/>
     </row>
-    <row r="63" spans="1:9" ht="14.45">
+    <row r="63" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A63" s="7" t="s">
         <v>149</v>
       </c>
@@ -3533,7 +3548,7 @@
       <c r="H63" s="12"/>
       <c r="I63" s="12"/>
     </row>
-    <row r="64" spans="1:9" ht="14.45">
+    <row r="64" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A64" s="7" t="s">
         <v>149</v>
       </c>
@@ -3556,7 +3571,7 @@
       <c r="H64" s="12"/>
       <c r="I64" s="12"/>
     </row>
-    <row r="65" spans="1:9" ht="14.45">
+    <row r="65" spans="1:9" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A65" s="7" t="s">
         <v>149</v>
       </c>
@@ -3585,7 +3600,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="66" spans="1:9" ht="14.45">
+    <row r="66" spans="1:9" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A66" s="7" t="s">
         <v>149</v>
       </c>
@@ -3614,7 +3629,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="67" spans="1:9" ht="14.45">
+    <row r="67" spans="1:9" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A67" s="7" t="s">
         <v>149</v>
       </c>
@@ -3643,7 +3658,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="68" spans="1:9" ht="14.45">
+    <row r="68" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A68" s="7" t="s">
         <v>149</v>
       </c>
@@ -3666,7 +3681,7 @@
       <c r="H68" s="12"/>
       <c r="I68" s="12"/>
     </row>
-    <row r="69" spans="1:9" ht="14.45">
+    <row r="69" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A69" s="7" t="s">
         <v>149</v>
       </c>
@@ -3689,7 +3704,7 @@
       <c r="H69" s="12"/>
       <c r="I69" s="12"/>
     </row>
-    <row r="70" spans="1:9" ht="14.45">
+    <row r="70" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A70" s="7" t="s">
         <v>149</v>
       </c>
@@ -3712,7 +3727,7 @@
       <c r="H70" s="12"/>
       <c r="I70" s="12"/>
     </row>
-    <row r="71" spans="1:9" ht="14.45">
+    <row r="71" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A71" s="7" t="s">
         <v>149</v>
       </c>
@@ -3735,7 +3750,7 @@
       <c r="H71" s="12"/>
       <c r="I71" s="12"/>
     </row>
-    <row r="72" spans="1:9" ht="14.45">
+    <row r="72" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A72" s="7" t="s">
         <v>149</v>
       </c>
@@ -3758,7 +3773,7 @@
       <c r="H72" s="12"/>
       <c r="I72" s="12"/>
     </row>
-    <row r="73" spans="1:9" ht="14.45">
+    <row r="73" spans="1:9" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A73" s="7" t="s">
         <v>172</v>
       </c>
@@ -3781,7 +3796,7 @@
       <c r="H73" s="12"/>
       <c r="I73" s="12"/>
     </row>
-    <row r="74" spans="1:9" ht="14.45">
+    <row r="74" spans="1:9" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A74" s="7" t="s">
         <v>172</v>
       </c>
@@ -3804,7 +3819,7 @@
       <c r="H74" s="12"/>
       <c r="I74" s="12"/>
     </row>
-    <row r="75" spans="1:9" ht="14.45">
+    <row r="75" spans="1:9" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A75" s="7" t="s">
         <v>177</v>
       </c>
@@ -3827,7 +3842,7 @@
       <c r="H75" s="12"/>
       <c r="I75" s="12"/>
     </row>
-    <row r="76" spans="1:9" ht="14.45">
+    <row r="76" spans="1:9" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A76" s="7" t="s">
         <v>177</v>
       </c>
@@ -3850,7 +3865,7 @@
       <c r="H76" s="12"/>
       <c r="I76" s="12"/>
     </row>
-    <row r="77" spans="1:9" ht="14.45">
+    <row r="77" spans="1:9" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A77" s="7" t="s">
         <v>177</v>
       </c>
@@ -3873,7 +3888,7 @@
       <c r="H77" s="12"/>
       <c r="I77" s="12"/>
     </row>
-    <row r="78" spans="1:9" ht="14.45">
+    <row r="78" spans="1:9" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A78" s="7" t="s">
         <v>177</v>
       </c>
@@ -3896,7 +3911,7 @@
       <c r="H78" s="12"/>
       <c r="I78" s="12"/>
     </row>
-    <row r="79" spans="1:9" ht="14.45">
+    <row r="79" spans="1:9" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A79" s="7" t="s">
         <v>177</v>
       </c>
@@ -3919,7 +3934,7 @@
       <c r="H79" s="12"/>
       <c r="I79" s="12"/>
     </row>
-    <row r="80" spans="1:9" ht="14.45">
+    <row r="80" spans="1:9" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A80" s="7" t="s">
         <v>177</v>
       </c>
@@ -3942,7 +3957,7 @@
       <c r="H80" s="12"/>
       <c r="I80" s="12"/>
     </row>
-    <row r="81" spans="1:9" ht="14.45">
+    <row r="81" spans="1:9" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A81" s="7" t="s">
         <v>177</v>
       </c>
@@ -3965,7 +3980,7 @@
       <c r="H81" s="12"/>
       <c r="I81" s="12"/>
     </row>
-    <row r="82" spans="1:9" ht="14.45">
+    <row r="82" spans="1:9" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A82" s="7" t="s">
         <v>177</v>
       </c>
@@ -3988,7 +4003,7 @@
       <c r="H82" s="12"/>
       <c r="I82" s="12"/>
     </row>
-    <row r="83" spans="1:9" ht="14.45">
+    <row r="83" spans="1:9" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A83" s="7" t="s">
         <v>177</v>
       </c>
@@ -4011,7 +4026,7 @@
       <c r="H83" s="12"/>
       <c r="I83" s="12"/>
     </row>
-    <row r="84" spans="1:9" ht="14.45">
+    <row r="84" spans="1:9" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A84" s="7" t="s">
         <v>177</v>
       </c>
@@ -4034,7 +4049,7 @@
       <c r="H84" s="12"/>
       <c r="I84" s="12"/>
     </row>
-    <row r="85" spans="1:9" ht="14.45">
+    <row r="85" spans="1:9" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A85" s="7" t="s">
         <v>177</v>
       </c>
@@ -4057,7 +4072,7 @@
       <c r="H85" s="12"/>
       <c r="I85" s="12"/>
     </row>
-    <row r="86" spans="1:9" ht="14.45">
+    <row r="86" spans="1:9" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A86" s="7" t="s">
         <v>177</v>
       </c>
@@ -4080,7 +4095,7 @@
       <c r="H86" s="12"/>
       <c r="I86" s="12"/>
     </row>
-    <row r="87" spans="1:9" ht="14.45">
+    <row r="87" spans="1:9" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A87" s="7" t="s">
         <v>177</v>
       </c>
@@ -4103,7 +4118,7 @@
       <c r="H87" s="12"/>
       <c r="I87" s="12"/>
     </row>
-    <row r="88" spans="1:9" ht="14.45">
+    <row r="88" spans="1:9" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A88" s="7" t="s">
         <v>177</v>
       </c>
@@ -4126,7 +4141,7 @@
       <c r="H88" s="12"/>
       <c r="I88" s="12"/>
     </row>
-    <row r="89" spans="1:9" ht="14.45">
+    <row r="89" spans="1:9" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A89" s="7" t="s">
         <v>177</v>
       </c>
@@ -4149,7 +4164,7 @@
       <c r="H89" s="12"/>
       <c r="I89" s="12"/>
     </row>
-    <row r="90" spans="1:9" ht="14.45">
+    <row r="90" spans="1:9" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A90" s="7" t="s">
         <v>177</v>
       </c>
@@ -4172,7 +4187,7 @@
       <c r="H90" s="12"/>
       <c r="I90" s="12"/>
     </row>
-    <row r="91" spans="1:9" ht="14.45">
+    <row r="91" spans="1:9" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A91" s="7" t="s">
         <v>210</v>
       </c>
@@ -4195,7 +4210,7 @@
       <c r="H91" s="12"/>
       <c r="I91" s="12"/>
     </row>
-    <row r="92" spans="1:9" ht="14.45">
+    <row r="92" spans="1:9" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A92" s="7" t="s">
         <v>210</v>
       </c>
@@ -4218,7 +4233,7 @@
       <c r="H92" s="12"/>
       <c r="I92" s="12"/>
     </row>
-    <row r="93" spans="1:9" ht="14.45">
+    <row r="93" spans="1:9" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A93" s="7" t="s">
         <v>210</v>
       </c>
@@ -4241,7 +4256,7 @@
       <c r="H93" s="12"/>
       <c r="I93" s="12"/>
     </row>
-    <row r="94" spans="1:9" ht="14.45">
+    <row r="94" spans="1:9" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A94" s="7" t="s">
         <v>217</v>
       </c>
@@ -4270,7 +4285,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="95" spans="1:9" ht="14.45">
+    <row r="95" spans="1:9" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A95" s="7" t="s">
         <v>217</v>
       </c>
@@ -4293,7 +4308,7 @@
       <c r="H95" s="12"/>
       <c r="I95" s="12"/>
     </row>
-    <row r="96" spans="1:9" ht="14.45">
+    <row r="96" spans="1:9" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A96" s="7" t="s">
         <v>217</v>
       </c>
@@ -4316,7 +4331,7 @@
       <c r="H96" s="12"/>
       <c r="I96" s="12"/>
     </row>
-    <row r="97" spans="1:10" ht="14.45">
+    <row r="97" spans="1:10" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A97" s="7" t="s">
         <v>217</v>
       </c>
@@ -4339,7 +4354,7 @@
       <c r="H97" s="12"/>
       <c r="I97" s="12"/>
     </row>
-    <row r="98" spans="1:10" ht="14.45">
+    <row r="98" spans="1:10" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A98" s="7" t="s">
         <v>225</v>
       </c>
@@ -4368,7 +4383,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="99" spans="1:10" ht="14.45">
+    <row r="99" spans="1:10" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A99" s="7" t="s">
         <v>225</v>
       </c>
@@ -4391,7 +4406,7 @@
       <c r="H99" s="12"/>
       <c r="I99" s="12"/>
     </row>
-    <row r="100" spans="1:10" ht="14.45">
+    <row r="100" spans="1:10" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A100" s="7" t="s">
         <v>231</v>
       </c>
@@ -4414,7 +4429,7 @@
       <c r="H100" s="12"/>
       <c r="I100" s="12"/>
     </row>
-    <row r="101" spans="1:10" ht="14.45">
+    <row r="101" spans="1:10" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A101" s="7" t="s">
         <v>231</v>
       </c>
@@ -4440,7 +4455,7 @@
         <v>237</v>
       </c>
     </row>
-    <row r="102" spans="1:10" ht="14.45">
+    <row r="102" spans="1:10" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A102" s="7" t="s">
         <v>238</v>
       </c>
@@ -4463,7 +4478,7 @@
       <c r="H102" s="12"/>
       <c r="I102" s="12"/>
     </row>
-    <row r="103" spans="1:10" ht="14.45">
+    <row r="103" spans="1:10" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A103" s="7" t="s">
         <v>238</v>
       </c>
@@ -4486,7 +4501,7 @@
       <c r="H103" s="12"/>
       <c r="I103" s="12"/>
     </row>
-    <row r="104" spans="1:10" ht="14.45">
+    <row r="104" spans="1:10" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A104" s="7" t="s">
         <v>238</v>
       </c>
@@ -4509,7 +4524,7 @@
       <c r="H104" s="12"/>
       <c r="I104" s="12"/>
     </row>
-    <row r="105" spans="1:10" ht="14.45">
+    <row r="105" spans="1:10" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A105" s="7" t="s">
         <v>238</v>
       </c>
@@ -4532,7 +4547,7 @@
       <c r="H105" s="12"/>
       <c r="I105" s="12"/>
     </row>
-    <row r="106" spans="1:10" ht="14.45">
+    <row r="106" spans="1:10" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A106" s="7" t="s">
         <v>238</v>
       </c>
@@ -4555,7 +4570,7 @@
       <c r="H106" s="12"/>
       <c r="I106" s="12"/>
     </row>
-    <row r="107" spans="1:10" ht="14.45">
+    <row r="107" spans="1:10" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A107" s="7" t="s">
         <v>238</v>
       </c>
@@ -4578,7 +4593,7 @@
       <c r="H107" s="12"/>
       <c r="I107" s="12"/>
     </row>
-    <row r="108" spans="1:10" ht="14.45">
+    <row r="108" spans="1:10" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A108" s="7" t="s">
         <v>238</v>
       </c>
@@ -4601,7 +4616,7 @@
       <c r="H108" s="12"/>
       <c r="I108" s="12"/>
     </row>
-    <row r="109" spans="1:10" ht="14.45">
+    <row r="109" spans="1:10" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A109" s="7" t="s">
         <v>238</v>
       </c>
@@ -4624,7 +4639,7 @@
       <c r="H109" s="12"/>
       <c r="I109" s="12"/>
     </row>
-    <row r="110" spans="1:10" ht="14.45">
+    <row r="110" spans="1:10" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A110" s="7" t="s">
         <v>238</v>
       </c>
@@ -4647,7 +4662,7 @@
       <c r="H110" s="12"/>
       <c r="I110" s="12"/>
     </row>
-    <row r="111" spans="1:10" ht="14.45">
+    <row r="111" spans="1:10" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A111" s="7" t="s">
         <v>238</v>
       </c>
@@ -4670,7 +4685,7 @@
       <c r="H111" s="12"/>
       <c r="I111" s="12"/>
     </row>
-    <row r="112" spans="1:10" ht="14.45">
+    <row r="112" spans="1:10" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A112" s="7" t="s">
         <v>238</v>
       </c>
@@ -4693,7 +4708,7 @@
       <c r="H112" s="12"/>
       <c r="I112" s="12"/>
     </row>
-    <row r="113" spans="1:9" ht="14.45">
+    <row r="113" spans="1:9" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A113" s="7" t="s">
         <v>238</v>
       </c>
@@ -4716,7 +4731,7 @@
       <c r="H113" s="12"/>
       <c r="I113" s="12"/>
     </row>
-    <row r="114" spans="1:9" ht="14.45">
+    <row r="114" spans="1:9" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A114" s="7" t="s">
         <v>238</v>
       </c>
@@ -4739,7 +4754,7 @@
       <c r="H114" s="12"/>
       <c r="I114" s="12"/>
     </row>
-    <row r="115" spans="1:9" ht="14.45">
+    <row r="115" spans="1:9" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A115" s="7" t="s">
         <v>238</v>
       </c>
@@ -4762,7 +4777,7 @@
       <c r="H115" s="12"/>
       <c r="I115" s="12"/>
     </row>
-    <row r="116" spans="1:9" ht="14.45">
+    <row r="116" spans="1:9" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A116" s="7" t="s">
         <v>238</v>
       </c>
@@ -4785,7 +4800,7 @@
       <c r="H116" s="12"/>
       <c r="I116" s="12"/>
     </row>
-    <row r="117" spans="1:9" ht="14.45">
+    <row r="117" spans="1:9" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A117" s="7" t="s">
         <v>238</v>
       </c>
@@ -4808,7 +4823,7 @@
       <c r="H117" s="12"/>
       <c r="I117" s="12"/>
     </row>
-    <row r="118" spans="1:9" ht="14.45">
+    <row r="118" spans="1:9" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A118" s="7" t="s">
         <v>238</v>
       </c>
@@ -4831,7 +4846,7 @@
       <c r="H118" s="12"/>
       <c r="I118" s="12"/>
     </row>
-    <row r="119" spans="1:9" ht="14.45">
+    <row r="119" spans="1:9" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A119" s="7" t="s">
         <v>238</v>
       </c>
@@ -4854,7 +4869,7 @@
       <c r="H119" s="12"/>
       <c r="I119" s="12"/>
     </row>
-    <row r="120" spans="1:9" ht="14.45">
+    <row r="120" spans="1:9" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A120" s="7" t="s">
         <v>276</v>
       </c>
@@ -4877,7 +4892,7 @@
       <c r="H120" s="12"/>
       <c r="I120" s="12"/>
     </row>
-    <row r="121" spans="1:9" ht="14.45">
+    <row r="121" spans="1:9" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A121" s="7" t="s">
         <v>276</v>
       </c>
@@ -4900,7 +4915,7 @@
       <c r="H121" s="12"/>
       <c r="I121" s="12"/>
     </row>
-    <row r="122" spans="1:9" ht="14.45">
+    <row r="122" spans="1:9" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A122" s="7" t="s">
         <v>276</v>
       </c>
@@ -4923,7 +4938,7 @@
       <c r="H122" s="12"/>
       <c r="I122" s="12"/>
     </row>
-    <row r="123" spans="1:9" ht="14.45">
+    <row r="123" spans="1:9" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A123" s="7" t="s">
         <v>284</v>
       </c>
@@ -4946,7 +4961,7 @@
       <c r="H123" s="12"/>
       <c r="I123" s="12"/>
     </row>
-    <row r="124" spans="1:9" ht="14.45">
+    <row r="124" spans="1:9" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A124" s="7" t="s">
         <v>287</v>
       </c>
@@ -4969,7 +4984,7 @@
       <c r="H124" s="12"/>
       <c r="I124" s="12"/>
     </row>
-    <row r="125" spans="1:9" ht="14.45">
+    <row r="125" spans="1:9" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A125" s="7" t="s">
         <v>287</v>
       </c>
@@ -4992,7 +5007,7 @@
       <c r="H125" s="12"/>
       <c r="I125" s="12"/>
     </row>
-    <row r="126" spans="1:9" ht="14.45">
+    <row r="126" spans="1:9" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A126" s="7" t="s">
         <v>287</v>
       </c>
@@ -5015,7 +5030,7 @@
       <c r="H126" s="15"/>
       <c r="I126" s="15"/>
     </row>
-    <row r="127" spans="1:9" ht="14.45">
+    <row r="127" spans="1:9" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A127" s="7" t="s">
         <v>294</v>
       </c>
@@ -5038,7 +5053,7 @@
       <c r="H127" s="12"/>
       <c r="I127" s="12"/>
     </row>
-    <row r="128" spans="1:9" ht="14.45">
+    <row r="128" spans="1:9" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A128" t="s">
         <v>297</v>
       </c>
@@ -5065,7 +5080,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="129" spans="1:10" ht="14.45">
+    <row r="129" spans="1:10" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A129" t="s">
         <v>297</v>
       </c>
@@ -5090,7 +5105,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="130" spans="1:10" ht="15" customHeight="1">
+    <row r="130" spans="1:10" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A130" s="33" t="s">
         <v>303</v>
       </c>
@@ -5115,7 +5130,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="131" spans="1:10" ht="15" customHeight="1">
+    <row r="131" spans="1:10" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A131" s="33" t="s">
         <v>307</v>
       </c>
@@ -5140,7 +5155,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="132" spans="1:10" ht="15" customHeight="1">
+    <row r="132" spans="1:10" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A132" s="33" t="s">
         <v>65</v>
       </c>
@@ -5165,7 +5180,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="133" spans="1:10" ht="15" customHeight="1">
+    <row r="133" spans="1:10" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A133" s="33" t="s">
         <v>313</v>
       </c>
@@ -5190,7 +5205,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="134" spans="1:10" ht="15" customHeight="1">
+    <row r="134" spans="1:10" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A134" s="33" t="s">
         <v>313</v>
       </c>
@@ -5215,7 +5230,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="135" spans="1:10" ht="15" customHeight="1">
+    <row r="135" spans="1:10" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A135" s="33" t="s">
         <v>276</v>
       </c>
@@ -5240,7 +5255,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="136" spans="1:10" ht="15" customHeight="1">
+    <row r="136" spans="1:10" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A136" s="33" t="s">
         <v>320</v>
       </c>
@@ -5266,7 +5281,7 @@
       </c>
       <c r="J136" s="38"/>
     </row>
-    <row r="137" spans="1:10" ht="15" customHeight="1">
+    <row r="137" spans="1:10" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A137" s="33" t="s">
         <v>324</v>
       </c>
@@ -5292,7 +5307,7 @@
       </c>
       <c r="J137" s="38"/>
     </row>
-    <row r="138" spans="1:10" ht="15" customHeight="1">
+    <row r="138" spans="1:10" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A138" s="7" t="s">
         <v>329</v>
       </c>
@@ -5316,7 +5331,7 @@
       </c>
       <c r="J138" s="37"/>
     </row>
-    <row r="139" spans="1:10" ht="15" customHeight="1">
+    <row r="139" spans="1:10" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A139" s="7" t="s">
         <v>329</v>
       </c>
@@ -5340,7 +5355,7 @@
       </c>
       <c r="J139" s="38"/>
     </row>
-    <row r="140" spans="1:10" ht="15" customHeight="1">
+    <row r="140" spans="1:10" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A140" s="7" t="s">
         <v>329</v>
       </c>
@@ -5364,7 +5379,7 @@
       </c>
       <c r="J140" s="38"/>
     </row>
-    <row r="141" spans="1:10" ht="15" customHeight="1">
+    <row r="141" spans="1:10" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A141" s="33" t="s">
         <v>333</v>
       </c>
@@ -5390,7 +5405,7 @@
       </c>
       <c r="J141" s="38"/>
     </row>
-    <row r="142" spans="1:10" ht="15" customHeight="1">
+    <row r="142" spans="1:10" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A142" s="33" t="s">
         <v>313</v>
       </c>
@@ -5415,7 +5430,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="143" spans="1:10" ht="15" customHeight="1">
+    <row r="143" spans="1:10" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A143" s="7" t="s">
         <v>336</v>
       </c>
@@ -5440,7 +5455,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="144" spans="1:10" ht="15" customHeight="1">
+    <row r="144" spans="1:10" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A144" s="33" t="s">
         <v>339</v>
       </c>
@@ -5465,7 +5480,7 @@
         <v>342</v>
       </c>
     </row>
-    <row r="145" spans="1:9" ht="15" customHeight="1">
+    <row r="145" spans="1:9" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A145" s="7" t="s">
         <v>65</v>
       </c>
@@ -5490,7 +5505,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="146" spans="1:9" ht="15" customHeight="1">
+    <row r="146" spans="1:9" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A146" s="7"/>
       <c r="B146" s="8"/>
       <c r="C146" s="40"/>
@@ -5501,7 +5516,7 @@
       <c r="H146" s="12"/>
       <c r="I146" s="12"/>
     </row>
-    <row r="147" spans="1:9" ht="15" customHeight="1">
+    <row r="147" spans="1:9" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A147" s="7"/>
       <c r="B147" s="8"/>
       <c r="C147" s="40"/>
@@ -5512,7 +5527,7 @@
       <c r="H147" s="12"/>
       <c r="I147" s="12"/>
     </row>
-    <row r="148" spans="1:9" ht="15" customHeight="1">
+    <row r="148" spans="1:9" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A148" s="7"/>
       <c r="B148" s="8"/>
       <c r="C148" s="40"/>
@@ -5523,7 +5538,7 @@
       <c r="H148" s="12"/>
       <c r="I148" s="12"/>
     </row>
-    <row r="149" spans="1:9" ht="15" customHeight="1">
+    <row r="149" spans="1:9" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A149" s="7"/>
       <c r="B149" s="8"/>
       <c r="C149" s="40"/>
@@ -5534,7 +5549,7 @@
       <c r="H149" s="12"/>
       <c r="I149" s="12"/>
     </row>
-    <row r="150" spans="1:9" ht="15" customHeight="1">
+    <row r="150" spans="1:9" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A150" s="7"/>
       <c r="B150" s="8"/>
       <c r="C150" s="40"/>
@@ -5545,7 +5560,7 @@
       <c r="H150" s="12"/>
       <c r="I150" s="12"/>
     </row>
-    <row r="151" spans="1:9" ht="15" customHeight="1">
+    <row r="151" spans="1:9" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A151" s="7"/>
       <c r="B151" s="8"/>
       <c r="C151" s="40"/>
@@ -5556,7 +5571,7 @@
       <c r="H151" s="12"/>
       <c r="I151" s="12"/>
     </row>
-    <row r="152" spans="1:9" ht="15" customHeight="1">
+    <row r="152" spans="1:9" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A152" s="7"/>
       <c r="B152" s="8"/>
       <c r="C152" s="40"/>
@@ -5567,7 +5582,7 @@
       <c r="H152" s="12"/>
       <c r="I152" s="12"/>
     </row>
-    <row r="153" spans="1:9" ht="15" customHeight="1">
+    <row r="153" spans="1:9" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A153" s="7"/>
       <c r="B153" s="8"/>
       <c r="C153" s="40"/>
@@ -5578,7 +5593,7 @@
       <c r="H153" s="12"/>
       <c r="I153" s="12"/>
     </row>
-    <row r="154" spans="1:9" ht="15" customHeight="1">
+    <row r="154" spans="1:9" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A154" s="7"/>
       <c r="B154" s="8"/>
       <c r="C154" s="40"/>
@@ -5589,7 +5604,7 @@
       <c r="H154" s="12"/>
       <c r="I154" s="12"/>
     </row>
-    <row r="155" spans="1:9" ht="15" customHeight="1">
+    <row r="155" spans="1:9" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A155" s="7"/>
       <c r="B155" s="8"/>
       <c r="C155" s="40"/>
@@ -5600,7 +5615,7 @@
       <c r="H155" s="12"/>
       <c r="I155" s="12"/>
     </row>
-    <row r="156" spans="1:9" ht="15" customHeight="1">
+    <row r="156" spans="1:9" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A156" s="7"/>
       <c r="B156" s="8"/>
       <c r="C156" s="40"/>
@@ -5611,7 +5626,7 @@
       <c r="H156" s="12"/>
       <c r="I156" s="12"/>
     </row>
-    <row r="157" spans="1:9" ht="15" customHeight="1">
+    <row r="157" spans="1:9" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A157" s="7"/>
       <c r="B157" s="8"/>
       <c r="C157" s="40"/>
@@ -5622,7 +5637,7 @@
       <c r="H157" s="12"/>
       <c r="I157" s="12"/>
     </row>
-    <row r="158" spans="1:9" ht="15" customHeight="1">
+    <row r="158" spans="1:9" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A158" s="7"/>
       <c r="B158" s="8"/>
       <c r="C158" s="40"/>
@@ -5633,7 +5648,7 @@
       <c r="H158" s="12"/>
       <c r="I158" s="12"/>
     </row>
-    <row r="159" spans="1:9" ht="15" customHeight="1">
+    <row r="159" spans="1:9" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A159" s="7"/>
       <c r="B159" s="8"/>
       <c r="C159" s="40"/>
@@ -5644,7 +5659,7 @@
       <c r="H159" s="12"/>
       <c r="I159" s="12"/>
     </row>
-    <row r="160" spans="1:9" ht="15" customHeight="1">
+    <row r="160" spans="1:9" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A160" s="7"/>
       <c r="B160" s="8"/>
       <c r="C160" s="40"/>
@@ -5655,7 +5670,7 @@
       <c r="H160" s="12"/>
       <c r="I160" s="12"/>
     </row>
-    <row r="161" spans="1:9" ht="15" customHeight="1">
+    <row r="161" spans="1:9" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A161" s="7"/>
       <c r="B161" s="8"/>
       <c r="C161" s="40"/>
@@ -5666,7 +5681,7 @@
       <c r="H161" s="12"/>
       <c r="I161" s="12"/>
     </row>
-    <row r="162" spans="1:9" ht="15" customHeight="1">
+    <row r="162" spans="1:9" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A162" s="7"/>
       <c r="B162" s="8"/>
       <c r="C162" s="40"/>
@@ -5677,7 +5692,7 @@
       <c r="H162" s="12"/>
       <c r="I162" s="12"/>
     </row>
-    <row r="163" spans="1:9" ht="15" customHeight="1">
+    <row r="163" spans="1:9" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A163" s="7"/>
       <c r="B163" s="8"/>
       <c r="C163" s="40"/>
@@ -5688,7 +5703,7 @@
       <c r="H163" s="12"/>
       <c r="I163" s="12"/>
     </row>
-    <row r="164" spans="1:9" ht="15" customHeight="1">
+    <row r="164" spans="1:9" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A164" s="7"/>
       <c r="B164" s="8"/>
       <c r="C164" s="40"/>
@@ -5699,7 +5714,7 @@
       <c r="H164" s="12"/>
       <c r="I164" s="12"/>
     </row>
-    <row r="165" spans="1:9" ht="15" customHeight="1">
+    <row r="165" spans="1:9" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A165" s="7"/>
       <c r="B165" s="8"/>
       <c r="C165" s="40"/>
@@ -5710,7 +5725,7 @@
       <c r="H165" s="12"/>
       <c r="I165" s="12"/>
     </row>
-    <row r="166" spans="1:9" ht="15" customHeight="1">
+    <row r="166" spans="1:9" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A166" s="7"/>
       <c r="B166" s="8"/>
       <c r="C166" s="40"/>
@@ -5721,7 +5736,7 @@
       <c r="H166" s="12"/>
       <c r="I166" s="12"/>
     </row>
-    <row r="167" spans="1:9" ht="15" customHeight="1">
+    <row r="167" spans="1:9" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A167" s="7"/>
       <c r="B167" s="8"/>
       <c r="C167" s="40"/>
@@ -5732,7 +5747,7 @@
       <c r="H167" s="12"/>
       <c r="I167" s="12"/>
     </row>
-    <row r="168" spans="1:9" ht="15" customHeight="1">
+    <row r="168" spans="1:9" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A168" s="7"/>
       <c r="B168" s="8"/>
       <c r="C168" s="40"/>
@@ -5743,7 +5758,7 @@
       <c r="H168" s="12"/>
       <c r="I168" s="12"/>
     </row>
-    <row r="169" spans="1:9" ht="15" customHeight="1">
+    <row r="169" spans="1:9" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A169" s="7"/>
       <c r="B169" s="8"/>
       <c r="C169" s="40"/>
@@ -5754,7 +5769,7 @@
       <c r="H169" s="12"/>
       <c r="I169" s="12"/>
     </row>
-    <row r="170" spans="1:9" ht="15" customHeight="1">
+    <row r="170" spans="1:9" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A170" s="7"/>
       <c r="B170" s="8"/>
       <c r="C170" s="40"/>
@@ -5765,7 +5780,7 @@
       <c r="H170" s="12"/>
       <c r="I170" s="12"/>
     </row>
-    <row r="171" spans="1:9" ht="15" customHeight="1">
+    <row r="171" spans="1:9" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A171" s="7"/>
       <c r="B171" s="8"/>
       <c r="C171" s="40"/>
@@ -5776,7 +5791,7 @@
       <c r="H171" s="12"/>
       <c r="I171" s="12"/>
     </row>
-    <row r="172" spans="1:9" ht="15" customHeight="1">
+    <row r="172" spans="1:9" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A172" s="7"/>
       <c r="B172" s="8"/>
       <c r="C172" s="40"/>
@@ -5787,7 +5802,7 @@
       <c r="H172" s="12"/>
       <c r="I172" s="12"/>
     </row>
-    <row r="173" spans="1:9" ht="15" customHeight="1">
+    <row r="173" spans="1:9" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A173" s="7"/>
       <c r="B173" s="8"/>
       <c r="C173" s="40"/>
@@ -5798,7 +5813,7 @@
       <c r="H173" s="12"/>
       <c r="I173" s="12"/>
     </row>
-    <row r="174" spans="1:9" ht="15" customHeight="1">
+    <row r="174" spans="1:9" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A174" s="7"/>
       <c r="B174" s="8"/>
       <c r="C174" s="40"/>
@@ -5809,7 +5824,7 @@
       <c r="H174" s="12"/>
       <c r="I174" s="12"/>
     </row>
-    <row r="175" spans="1:9" ht="15" customHeight="1">
+    <row r="175" spans="1:9" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A175" s="7"/>
       <c r="B175" s="8"/>
       <c r="C175" s="40"/>
@@ -5820,7 +5835,7 @@
       <c r="H175" s="12"/>
       <c r="I175" s="12"/>
     </row>
-    <row r="176" spans="1:9" ht="15" customHeight="1">
+    <row r="176" spans="1:9" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A176" s="7"/>
       <c r="B176" s="8"/>
       <c r="C176" s="40"/>
@@ -5831,7 +5846,7 @@
       <c r="H176" s="12"/>
       <c r="I176" s="12"/>
     </row>
-    <row r="177" spans="1:9" ht="15" customHeight="1">
+    <row r="177" spans="1:9" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A177" s="7"/>
       <c r="B177" s="8"/>
       <c r="C177" s="40"/>
@@ -5842,7 +5857,7 @@
       <c r="H177" s="12"/>
       <c r="I177" s="12"/>
     </row>
-    <row r="178" spans="1:9" ht="15" customHeight="1">
+    <row r="178" spans="1:9" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A178" s="7"/>
       <c r="B178" s="8"/>
       <c r="C178" s="40"/>
@@ -5853,7 +5868,7 @@
       <c r="H178" s="12"/>
       <c r="I178" s="12"/>
     </row>
-    <row r="179" spans="1:9" ht="15" customHeight="1">
+    <row r="179" spans="1:9" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A179" s="7"/>
       <c r="B179" s="8"/>
       <c r="C179" s="40"/>
@@ -5864,7 +5879,7 @@
       <c r="H179" s="12"/>
       <c r="I179" s="12"/>
     </row>
-    <row r="180" spans="1:9" ht="15" customHeight="1">
+    <row r="180" spans="1:9" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A180" s="7"/>
       <c r="B180" s="8"/>
       <c r="C180" s="40"/>
@@ -5875,7 +5890,7 @@
       <c r="H180" s="12"/>
       <c r="I180" s="12"/>
     </row>
-    <row r="181" spans="1:9" ht="15" customHeight="1">
+    <row r="181" spans="1:9" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A181" s="7"/>
       <c r="B181" s="8"/>
       <c r="C181" s="40"/>
@@ -5886,7 +5901,7 @@
       <c r="H181" s="12"/>
       <c r="I181" s="12"/>
     </row>
-    <row r="182" spans="1:9" ht="15" customHeight="1">
+    <row r="182" spans="1:9" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A182" s="7"/>
       <c r="B182" s="8"/>
       <c r="C182" s="40"/>
@@ -5897,7 +5912,7 @@
       <c r="H182" s="12"/>
       <c r="I182" s="12"/>
     </row>
-    <row r="183" spans="1:9" ht="15" customHeight="1">
+    <row r="183" spans="1:9" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A183" s="7"/>
       <c r="B183" s="8"/>
       <c r="C183" s="40"/>
@@ -5908,7 +5923,7 @@
       <c r="H183" s="12"/>
       <c r="I183" s="12"/>
     </row>
-    <row r="184" spans="1:9" ht="15" customHeight="1">
+    <row r="184" spans="1:9" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A184" s="7"/>
       <c r="B184" s="8"/>
       <c r="C184" s="40"/>
@@ -5919,7 +5934,7 @@
       <c r="H184" s="12"/>
       <c r="I184" s="12"/>
     </row>
-    <row r="185" spans="1:9" ht="15" customHeight="1">
+    <row r="185" spans="1:9" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A185" s="7"/>
       <c r="B185" s="8"/>
       <c r="C185" s="40"/>
@@ -5930,7 +5945,7 @@
       <c r="H185" s="12"/>
       <c r="I185" s="12"/>
     </row>
-    <row r="186" spans="1:9" ht="15" customHeight="1">
+    <row r="186" spans="1:9" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A186" s="7"/>
       <c r="B186" s="8"/>
       <c r="C186" s="40"/>
@@ -5941,7 +5956,7 @@
       <c r="H186" s="12"/>
       <c r="I186" s="12"/>
     </row>
-    <row r="187" spans="1:9" ht="15" customHeight="1">
+    <row r="187" spans="1:9" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A187" s="7"/>
       <c r="B187" s="8"/>
       <c r="C187" s="40"/>
@@ -5952,7 +5967,7 @@
       <c r="H187" s="12"/>
       <c r="I187" s="12"/>
     </row>
-    <row r="188" spans="1:9" ht="15" customHeight="1">
+    <row r="188" spans="1:9" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A188" s="7"/>
       <c r="B188" s="8"/>
       <c r="C188" s="40"/>
@@ -5963,7 +5978,7 @@
       <c r="H188" s="12"/>
       <c r="I188" s="12"/>
     </row>
-    <row r="189" spans="1:9" ht="15" customHeight="1">
+    <row r="189" spans="1:9" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A189" s="7"/>
       <c r="B189" s="8"/>
       <c r="C189" s="40"/>
@@ -5974,7 +5989,7 @@
       <c r="H189" s="12"/>
       <c r="I189" s="12"/>
     </row>
-    <row r="190" spans="1:9" ht="15" customHeight="1">
+    <row r="190" spans="1:9" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A190" s="7"/>
       <c r="B190" s="8"/>
       <c r="C190" s="40"/>
@@ -5985,7 +6000,7 @@
       <c r="H190" s="12"/>
       <c r="I190" s="12"/>
     </row>
-    <row r="191" spans="1:9" ht="15" customHeight="1">
+    <row r="191" spans="1:9" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A191" s="7"/>
       <c r="B191" s="8"/>
       <c r="C191" s="40"/>
@@ -5996,7 +6011,7 @@
       <c r="H191" s="12"/>
       <c r="I191" s="12"/>
     </row>
-    <row r="192" spans="1:9" ht="15" customHeight="1">
+    <row r="192" spans="1:9" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A192" s="7"/>
       <c r="B192" s="8"/>
       <c r="C192" s="40"/>
@@ -6007,7 +6022,7 @@
       <c r="H192" s="12"/>
       <c r="I192" s="12"/>
     </row>
-    <row r="193" spans="1:9" ht="15" customHeight="1">
+    <row r="193" spans="1:9" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A193" s="7"/>
       <c r="B193" s="8"/>
       <c r="C193" s="40"/>
@@ -6018,7 +6033,7 @@
       <c r="H193" s="12"/>
       <c r="I193" s="12"/>
     </row>
-    <row r="194" spans="1:9" ht="15" customHeight="1">
+    <row r="194" spans="1:9" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A194" s="7"/>
       <c r="B194" s="8"/>
       <c r="C194" s="40"/>
@@ -6029,7 +6044,7 @@
       <c r="H194" s="12"/>
       <c r="I194" s="12"/>
     </row>
-    <row r="195" spans="1:9" ht="15" customHeight="1">
+    <row r="195" spans="1:9" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A195" s="7"/>
       <c r="B195" s="8"/>
       <c r="C195" s="40"/>
@@ -6040,7 +6055,7 @@
       <c r="H195" s="12"/>
       <c r="I195" s="12"/>
     </row>
-    <row r="196" spans="1:9" ht="15" customHeight="1">
+    <row r="196" spans="1:9" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A196" s="7"/>
       <c r="B196" s="8"/>
       <c r="C196" s="40"/>
@@ -6051,7 +6066,7 @@
       <c r="H196" s="12"/>
       <c r="I196" s="12"/>
     </row>
-    <row r="197" spans="1:9" ht="15" customHeight="1">
+    <row r="197" spans="1:9" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A197" s="7"/>
       <c r="B197" s="8"/>
       <c r="C197" s="40"/>
@@ -6062,7 +6077,7 @@
       <c r="H197" s="12"/>
       <c r="I197" s="12"/>
     </row>
-    <row r="198" spans="1:9" ht="15" customHeight="1">
+    <row r="198" spans="1:9" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A198" s="7"/>
       <c r="B198" s="8"/>
       <c r="C198" s="40"/>
@@ -6073,7 +6088,7 @@
       <c r="H198" s="12"/>
       <c r="I198" s="12"/>
     </row>
-    <row r="199" spans="1:9" ht="15" customHeight="1">
+    <row r="199" spans="1:9" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A199" s="7"/>
       <c r="B199" s="8"/>
       <c r="C199" s="40"/>
@@ -6084,7 +6099,7 @@
       <c r="H199" s="12"/>
       <c r="I199" s="12"/>
     </row>
-    <row r="200" spans="1:9" ht="15" customHeight="1">
+    <row r="200" spans="1:9" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A200" s="7"/>
       <c r="B200" s="8"/>
       <c r="C200" s="40"/>
@@ -6095,7 +6110,7 @@
       <c r="H200" s="12"/>
       <c r="I200" s="12"/>
     </row>
-    <row r="201" spans="1:9" ht="15" customHeight="1">
+    <row r="201" spans="1:9" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A201" s="7"/>
       <c r="B201" s="8"/>
       <c r="C201" s="40"/>
@@ -6106,7 +6121,7 @@
       <c r="H201" s="12"/>
       <c r="I201" s="12"/>
     </row>
-    <row r="202" spans="1:9" ht="15" customHeight="1">
+    <row r="202" spans="1:9" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A202" s="7"/>
       <c r="B202" s="8"/>
       <c r="C202" s="40"/>
@@ -6117,7 +6132,7 @@
       <c r="H202" s="12"/>
       <c r="I202" s="12"/>
     </row>
-    <row r="203" spans="1:9" ht="15" customHeight="1">
+    <row r="203" spans="1:9" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A203" s="7"/>
       <c r="B203" s="8"/>
       <c r="C203" s="40"/>
@@ -6128,7 +6143,7 @@
       <c r="H203" s="12"/>
       <c r="I203" s="12"/>
     </row>
-    <row r="204" spans="1:9" ht="15" customHeight="1">
+    <row r="204" spans="1:9" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A204" s="7"/>
       <c r="B204" s="8"/>
       <c r="C204" s="40"/>
@@ -6139,6 +6154,7 @@
       <c r="H204" s="12"/>
       <c r="I204" s="12"/>
     </row>
+    <row r="205" spans="1:9" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
@@ -6150,29 +6166,29 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4E144160-55E5-40A6-9A8E-E41DA7F6726D}">
   <dimension ref="D2:N92"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="14.45"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="12" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="60.28515625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="58.85546875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="12.5703125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="11.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="60.26953125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="58.81640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.54296875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.26953125" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="16" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="22.5703125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="22.54296875" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="10" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="42" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="54" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="40.28515625" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="35.42578125" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="9.42578125" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="8.42578125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="40.26953125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="35.453125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="9.453125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="8.453125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="4:14">
+    <row r="2" spans="4:14" x14ac:dyDescent="0.35">
       <c r="M2" s="5"/>
       <c r="N2" s="5"/>
     </row>
-    <row r="3" spans="4:14">
+    <row r="3" spans="4:14" x14ac:dyDescent="0.35">
       <c r="D3" s="1">
         <v>868589060374017</v>
       </c>
@@ -6190,7 +6206,7 @@
         <v>46043</v>
       </c>
     </row>
-    <row r="4" spans="4:14">
+    <row r="4" spans="4:14" x14ac:dyDescent="0.35">
       <c r="D4" s="1">
         <v>868589060674226</v>
       </c>
@@ -6208,355 +6224,355 @@
         <v>46043</v>
       </c>
     </row>
-    <row r="5" spans="4:14">
+    <row r="5" spans="4:14" x14ac:dyDescent="0.35">
       <c r="M5" s="5"/>
       <c r="N5" s="5"/>
     </row>
-    <row r="6" spans="4:14">
+    <row r="6" spans="4:14" x14ac:dyDescent="0.35">
       <c r="M6" s="5"/>
       <c r="N6" s="5"/>
     </row>
-    <row r="7" spans="4:14">
+    <row r="7" spans="4:14" x14ac:dyDescent="0.35">
       <c r="M7" s="5"/>
       <c r="N7" s="5"/>
     </row>
-    <row r="8" spans="4:14">
+    <row r="8" spans="4:14" x14ac:dyDescent="0.35">
       <c r="M8" s="5"/>
       <c r="N8" s="5"/>
     </row>
-    <row r="9" spans="4:14">
+    <row r="9" spans="4:14" x14ac:dyDescent="0.35">
       <c r="M9" s="5"/>
       <c r="N9" s="5"/>
     </row>
-    <row r="10" spans="4:14">
+    <row r="10" spans="4:14" x14ac:dyDescent="0.35">
       <c r="M10" s="5"/>
       <c r="N10" s="5"/>
     </row>
-    <row r="11" spans="4:14">
+    <row r="11" spans="4:14" x14ac:dyDescent="0.35">
       <c r="M11" s="5"/>
       <c r="N11" s="5"/>
     </row>
-    <row r="12" spans="4:14">
+    <row r="12" spans="4:14" x14ac:dyDescent="0.35">
       <c r="M12" s="5"/>
       <c r="N12" s="5"/>
     </row>
-    <row r="13" spans="4:14">
+    <row r="13" spans="4:14" x14ac:dyDescent="0.35">
       <c r="M13" s="5"/>
       <c r="N13" s="5"/>
     </row>
-    <row r="14" spans="4:14">
+    <row r="14" spans="4:14" x14ac:dyDescent="0.35">
       <c r="M14" s="5"/>
       <c r="N14" s="5"/>
     </row>
-    <row r="15" spans="4:14">
+    <row r="15" spans="4:14" x14ac:dyDescent="0.35">
       <c r="M15" s="5"/>
       <c r="N15" s="5"/>
     </row>
-    <row r="16" spans="4:14">
+    <row r="16" spans="4:14" x14ac:dyDescent="0.35">
       <c r="M16" s="5"/>
       <c r="N16" s="5"/>
     </row>
-    <row r="17" spans="13:14">
+    <row r="17" spans="13:14" x14ac:dyDescent="0.35">
       <c r="M17" s="5"/>
       <c r="N17" s="5"/>
     </row>
-    <row r="18" spans="13:14">
+    <row r="18" spans="13:14" x14ac:dyDescent="0.35">
       <c r="M18" s="5"/>
       <c r="N18" s="5"/>
     </row>
-    <row r="19" spans="13:14">
+    <row r="19" spans="13:14" x14ac:dyDescent="0.35">
       <c r="M19" s="5"/>
       <c r="N19" s="5"/>
     </row>
-    <row r="20" spans="13:14">
+    <row r="20" spans="13:14" x14ac:dyDescent="0.35">
       <c r="M20" s="5"/>
       <c r="N20" s="5"/>
     </row>
-    <row r="21" spans="13:14">
+    <row r="21" spans="13:14" x14ac:dyDescent="0.35">
       <c r="M21" s="5"/>
       <c r="N21" s="5"/>
     </row>
-    <row r="22" spans="13:14">
+    <row r="22" spans="13:14" x14ac:dyDescent="0.35">
       <c r="M22" s="5"/>
       <c r="N22" s="5"/>
     </row>
-    <row r="23" spans="13:14">
+    <row r="23" spans="13:14" x14ac:dyDescent="0.35">
       <c r="M23" s="5"/>
       <c r="N23" s="5"/>
     </row>
-    <row r="24" spans="13:14">
+    <row r="24" spans="13:14" x14ac:dyDescent="0.35">
       <c r="M24" s="5"/>
       <c r="N24" s="5"/>
     </row>
-    <row r="25" spans="13:14">
+    <row r="25" spans="13:14" x14ac:dyDescent="0.35">
       <c r="M25" s="5"/>
       <c r="N25" s="5"/>
     </row>
-    <row r="26" spans="13:14">
+    <row r="26" spans="13:14" x14ac:dyDescent="0.35">
       <c r="M26" s="5"/>
       <c r="N26" s="5"/>
     </row>
-    <row r="27" spans="13:14">
+    <row r="27" spans="13:14" x14ac:dyDescent="0.35">
       <c r="M27" s="5"/>
       <c r="N27" s="5"/>
     </row>
-    <row r="28" spans="13:14">
+    <row r="28" spans="13:14" x14ac:dyDescent="0.35">
       <c r="M28" s="5"/>
       <c r="N28" s="5"/>
     </row>
-    <row r="29" spans="13:14">
+    <row r="29" spans="13:14" x14ac:dyDescent="0.35">
       <c r="M29" s="5"/>
       <c r="N29" s="5"/>
     </row>
-    <row r="30" spans="13:14">
+    <row r="30" spans="13:14" x14ac:dyDescent="0.35">
       <c r="M30" s="5"/>
       <c r="N30" s="5"/>
     </row>
-    <row r="31" spans="13:14">
+    <row r="31" spans="13:14" x14ac:dyDescent="0.35">
       <c r="M31" s="5"/>
       <c r="N31" s="5"/>
     </row>
-    <row r="32" spans="13:14">
+    <row r="32" spans="13:14" x14ac:dyDescent="0.35">
       <c r="M32" s="5"/>
       <c r="N32" s="5"/>
     </row>
-    <row r="33" spans="13:14">
+    <row r="33" spans="13:14" x14ac:dyDescent="0.35">
       <c r="M33" s="5"/>
       <c r="N33" s="5"/>
     </row>
-    <row r="34" spans="13:14">
+    <row r="34" spans="13:14" x14ac:dyDescent="0.35">
       <c r="M34" s="5"/>
       <c r="N34" s="5"/>
     </row>
-    <row r="35" spans="13:14">
+    <row r="35" spans="13:14" x14ac:dyDescent="0.35">
       <c r="M35" s="5"/>
       <c r="N35" s="5"/>
     </row>
-    <row r="36" spans="13:14">
+    <row r="36" spans="13:14" x14ac:dyDescent="0.35">
       <c r="M36" s="5"/>
       <c r="N36" s="5"/>
     </row>
-    <row r="37" spans="13:14">
+    <row r="37" spans="13:14" x14ac:dyDescent="0.35">
       <c r="M37" s="5"/>
       <c r="N37" s="5"/>
     </row>
-    <row r="38" spans="13:14">
+    <row r="38" spans="13:14" x14ac:dyDescent="0.35">
       <c r="M38" s="5"/>
       <c r="N38" s="5"/>
     </row>
-    <row r="39" spans="13:14">
+    <row r="39" spans="13:14" x14ac:dyDescent="0.35">
       <c r="M39" s="5"/>
       <c r="N39" s="5"/>
     </row>
-    <row r="40" spans="13:14">
+    <row r="40" spans="13:14" x14ac:dyDescent="0.35">
       <c r="M40" s="5"/>
       <c r="N40" s="5"/>
     </row>
-    <row r="41" spans="13:14">
+    <row r="41" spans="13:14" x14ac:dyDescent="0.35">
       <c r="M41" s="5"/>
       <c r="N41" s="5"/>
     </row>
-    <row r="42" spans="13:14">
+    <row r="42" spans="13:14" x14ac:dyDescent="0.35">
       <c r="M42" s="5"/>
       <c r="N42" s="5"/>
     </row>
-    <row r="43" spans="13:14">
+    <row r="43" spans="13:14" x14ac:dyDescent="0.35">
       <c r="M43" s="5"/>
       <c r="N43" s="5"/>
     </row>
-    <row r="44" spans="13:14">
+    <row r="44" spans="13:14" x14ac:dyDescent="0.35">
       <c r="M44" s="5"/>
       <c r="N44" s="5"/>
     </row>
-    <row r="45" spans="13:14">
+    <row r="45" spans="13:14" x14ac:dyDescent="0.35">
       <c r="M45" s="5"/>
       <c r="N45" s="5"/>
     </row>
-    <row r="46" spans="13:14">
+    <row r="46" spans="13:14" x14ac:dyDescent="0.35">
       <c r="M46" s="5"/>
       <c r="N46" s="5"/>
     </row>
-    <row r="47" spans="13:14">
+    <row r="47" spans="13:14" x14ac:dyDescent="0.35">
       <c r="M47" s="5"/>
       <c r="N47" s="5"/>
     </row>
-    <row r="48" spans="13:14">
+    <row r="48" spans="13:14" x14ac:dyDescent="0.35">
       <c r="M48" s="5"/>
       <c r="N48" s="5"/>
     </row>
-    <row r="49" spans="13:14">
+    <row r="49" spans="13:14" x14ac:dyDescent="0.35">
       <c r="M49" s="5"/>
       <c r="N49" s="5"/>
     </row>
-    <row r="50" spans="13:14">
+    <row r="50" spans="13:14" x14ac:dyDescent="0.35">
       <c r="M50" s="5"/>
       <c r="N50" s="5"/>
     </row>
-    <row r="51" spans="13:14">
+    <row r="51" spans="13:14" x14ac:dyDescent="0.35">
       <c r="M51" s="5"/>
       <c r="N51" s="5"/>
     </row>
-    <row r="52" spans="13:14">
+    <row r="52" spans="13:14" x14ac:dyDescent="0.35">
       <c r="M52" s="5"/>
       <c r="N52" s="5"/>
     </row>
-    <row r="53" spans="13:14">
+    <row r="53" spans="13:14" x14ac:dyDescent="0.35">
       <c r="M53" s="5"/>
       <c r="N53" s="5"/>
     </row>
-    <row r="54" spans="13:14">
+    <row r="54" spans="13:14" x14ac:dyDescent="0.35">
       <c r="M54" s="5"/>
       <c r="N54" s="5"/>
     </row>
-    <row r="55" spans="13:14">
+    <row r="55" spans="13:14" x14ac:dyDescent="0.35">
       <c r="M55" s="5"/>
       <c r="N55" s="5"/>
     </row>
-    <row r="56" spans="13:14">
+    <row r="56" spans="13:14" x14ac:dyDescent="0.35">
       <c r="M56" s="5"/>
       <c r="N56" s="5"/>
     </row>
-    <row r="57" spans="13:14">
+    <row r="57" spans="13:14" x14ac:dyDescent="0.35">
       <c r="M57" s="5"/>
       <c r="N57" s="5"/>
     </row>
-    <row r="58" spans="13:14">
+    <row r="58" spans="13:14" x14ac:dyDescent="0.35">
       <c r="M58" s="5"/>
       <c r="N58" s="5"/>
     </row>
-    <row r="59" spans="13:14">
+    <row r="59" spans="13:14" x14ac:dyDescent="0.35">
       <c r="M59" s="5"/>
       <c r="N59" s="5"/>
     </row>
-    <row r="60" spans="13:14">
+    <row r="60" spans="13:14" x14ac:dyDescent="0.35">
       <c r="M60" s="5"/>
       <c r="N60" s="5"/>
     </row>
-    <row r="61" spans="13:14">
+    <row r="61" spans="13:14" x14ac:dyDescent="0.35">
       <c r="M61" s="5"/>
       <c r="N61" s="5"/>
     </row>
-    <row r="62" spans="13:14">
+    <row r="62" spans="13:14" x14ac:dyDescent="0.35">
       <c r="M62" s="5"/>
       <c r="N62" s="5"/>
     </row>
-    <row r="63" spans="13:14">
+    <row r="63" spans="13:14" x14ac:dyDescent="0.35">
       <c r="M63" s="5"/>
       <c r="N63" s="5"/>
     </row>
-    <row r="64" spans="13:14">
+    <row r="64" spans="13:14" x14ac:dyDescent="0.35">
       <c r="M64" s="5"/>
       <c r="N64" s="5"/>
     </row>
-    <row r="65" spans="13:14">
+    <row r="65" spans="13:14" x14ac:dyDescent="0.35">
       <c r="M65" s="5"/>
       <c r="N65" s="5"/>
     </row>
-    <row r="66" spans="13:14">
+    <row r="66" spans="13:14" x14ac:dyDescent="0.35">
       <c r="M66" s="5"/>
       <c r="N66" s="5"/>
     </row>
-    <row r="67" spans="13:14">
+    <row r="67" spans="13:14" x14ac:dyDescent="0.35">
       <c r="M67" s="5"/>
       <c r="N67" s="5"/>
     </row>
-    <row r="68" spans="13:14">
+    <row r="68" spans="13:14" x14ac:dyDescent="0.35">
       <c r="M68" s="5"/>
       <c r="N68" s="5"/>
     </row>
-    <row r="69" spans="13:14">
+    <row r="69" spans="13:14" x14ac:dyDescent="0.35">
       <c r="M69" s="5"/>
       <c r="N69" s="5"/>
     </row>
-    <row r="70" spans="13:14">
+    <row r="70" spans="13:14" x14ac:dyDescent="0.35">
       <c r="M70" s="5"/>
       <c r="N70" s="5"/>
     </row>
-    <row r="71" spans="13:14">
+    <row r="71" spans="13:14" x14ac:dyDescent="0.35">
       <c r="M71" s="5"/>
       <c r="N71" s="5"/>
     </row>
-    <row r="72" spans="13:14">
+    <row r="72" spans="13:14" x14ac:dyDescent="0.35">
       <c r="M72" s="5"/>
       <c r="N72" s="5"/>
     </row>
-    <row r="73" spans="13:14">
+    <row r="73" spans="13:14" x14ac:dyDescent="0.35">
       <c r="M73" s="5"/>
       <c r="N73" s="5"/>
     </row>
-    <row r="74" spans="13:14">
+    <row r="74" spans="13:14" x14ac:dyDescent="0.35">
       <c r="M74" s="5"/>
       <c r="N74" s="5"/>
     </row>
-    <row r="75" spans="13:14">
+    <row r="75" spans="13:14" x14ac:dyDescent="0.35">
       <c r="M75" s="5"/>
       <c r="N75" s="5"/>
     </row>
-    <row r="76" spans="13:14">
+    <row r="76" spans="13:14" x14ac:dyDescent="0.35">
       <c r="M76" s="5"/>
       <c r="N76" s="5"/>
     </row>
-    <row r="77" spans="13:14">
+    <row r="77" spans="13:14" x14ac:dyDescent="0.35">
       <c r="M77" s="5"/>
       <c r="N77" s="5"/>
     </row>
-    <row r="78" spans="13:14">
+    <row r="78" spans="13:14" x14ac:dyDescent="0.35">
       <c r="M78" s="5"/>
       <c r="N78" s="5"/>
     </row>
-    <row r="79" spans="13:14">
+    <row r="79" spans="13:14" x14ac:dyDescent="0.35">
       <c r="M79" s="5"/>
       <c r="N79" s="5"/>
     </row>
-    <row r="80" spans="13:14">
+    <row r="80" spans="13:14" x14ac:dyDescent="0.35">
       <c r="M80" s="5"/>
       <c r="N80" s="5"/>
     </row>
-    <row r="81" spans="13:14">
+    <row r="81" spans="13:14" x14ac:dyDescent="0.35">
       <c r="M81" s="5"/>
       <c r="N81" s="5"/>
     </row>
-    <row r="82" spans="13:14">
+    <row r="82" spans="13:14" x14ac:dyDescent="0.35">
       <c r="M82" s="5"/>
       <c r="N82" s="5"/>
     </row>
-    <row r="83" spans="13:14">
+    <row r="83" spans="13:14" x14ac:dyDescent="0.35">
       <c r="M83" s="5"/>
       <c r="N83" s="5"/>
     </row>
-    <row r="84" spans="13:14">
+    <row r="84" spans="13:14" x14ac:dyDescent="0.35">
       <c r="M84" s="5"/>
       <c r="N84" s="5"/>
     </row>
-    <row r="85" spans="13:14">
+    <row r="85" spans="13:14" x14ac:dyDescent="0.35">
       <c r="M85" s="5"/>
       <c r="N85" s="5"/>
     </row>
-    <row r="86" spans="13:14">
+    <row r="86" spans="13:14" x14ac:dyDescent="0.35">
       <c r="M86" s="5"/>
       <c r="N86" s="5"/>
     </row>
-    <row r="87" spans="13:14">
+    <row r="87" spans="13:14" x14ac:dyDescent="0.35">
       <c r="M87" s="5"/>
       <c r="N87" s="5"/>
     </row>
-    <row r="88" spans="13:14">
+    <row r="88" spans="13:14" x14ac:dyDescent="0.35">
       <c r="M88" s="5"/>
       <c r="N88" s="5"/>
     </row>
-    <row r="89" spans="13:14">
+    <row r="89" spans="13:14" x14ac:dyDescent="0.35">
       <c r="M89" s="5"/>
       <c r="N89" s="5"/>
     </row>
-    <row r="90" spans="13:14">
+    <row r="90" spans="13:14" x14ac:dyDescent="0.35">
       <c r="M90" s="5"/>
       <c r="N90" s="5"/>
     </row>
-    <row r="91" spans="13:14">
+    <row r="91" spans="13:14" x14ac:dyDescent="0.35">
       <c r="M91" s="5"/>
       <c r="N91" s="5"/>
     </row>
-    <row r="92" spans="13:14">
+    <row r="92" spans="13:14" x14ac:dyDescent="0.35">
       <c r="M92" s="5"/>
       <c r="N92" s="5"/>
     </row>
@@ -6566,14 +6582,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_activity xmlns="3e53c16e-6636-411e-b1c4-e9eeb71b3b2a" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
   <Display>DocumentLibraryForm</Display>
@@ -6582,7 +6590,7 @@
 </FormTemplates>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x010100027709BF533FA442AFC4A8B2C0110727" ma:contentTypeVersion="15" ma:contentTypeDescription="Crear nuevo documento." ma:contentTypeScope="" ma:versionID="a37fc0d7c302f7619d355a49e1f175a4">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="3e53c16e-6636-411e-b1c4-e9eeb71b3b2a" xmlns:ns4="bda9c1ec-c4e2-44f9-929c-ca399fe36c88" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="01250a30c504a808427f15ccf149ee4d" ns3:_="" ns4:_="">
     <xsd:import namespace="3e53c16e-6636-411e-b1c4-e9eeb71b3b2a"/>
@@ -6815,14 +6823,47 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_activity xmlns="3e53c16e-6636-411e-b1c4-e9eeb71b3b2a" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D9861A25-610F-425F-BC6A-AC52D4971411}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3C8123E5-81FD-4C24-91F1-33BC079967E9}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3C8123E5-81FD-4C24-91F1-33BC079967E9}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4794C7E6-B89D-4081-9A67-B8D500EF1EE4}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="3e53c16e-6636-411e-b1c4-e9eeb71b3b2a"/>
+    <ds:schemaRef ds:uri="bda9c1ec-c4e2-44f9-929c-ca399fe36c88"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4794C7E6-B89D-4081-9A67-B8D500EF1EE4}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D9861A25-610F-425F-BC6A-AC52D4971411}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="3e53c16e-6636-411e-b1c4-e9eeb71b3b2a"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/data/bitacora.xlsx
+++ b/data/bitacora.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://grupokaufmann-my.sharepoint.com/personal/samuel_sanchez_grupokaufmann_com/Documents/Documentos/Dev/bitacora_diaria/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="348" documentId="8_{4616FF0F-C10E-4DFE-8F27-869B9C60E0F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1C18D249-8141-4783-AC41-8C4A3919858E}"/>
+  <xr:revisionPtr revIDLastSave="357" documentId="8_{4616FF0F-C10E-4DFE-8F27-869B9C60E0F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D5D1F434-0134-47BB-ACB8-D6A94FE006B9}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-1155" windowWidth="29040" windowHeight="15720" xr2:uid="{A9E3F017-9040-47A2-B586-0486128F3261}"/>
+    <workbookView minimized="1" xWindow="-26520" yWindow="1035" windowWidth="14400" windowHeight="8175" xr2:uid="{A9E3F017-9040-47A2-B586-0486128F3261}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -19,7 +19,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Hoja1!$A$1:$F$127</definedName>
   </definedNames>
-  <calcPr calcId="191028"/>
+  <calcPr calcId="191028" calcCompleted="0"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="788" uniqueCount="347">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="791" uniqueCount="350">
   <si>
     <t>FLOTA</t>
   </si>
@@ -1081,6 +1081,15 @@
   </si>
   <si>
     <t>Revisado</t>
+  </si>
+  <si>
+    <t>TFLF99</t>
+  </si>
+  <si>
+    <t>TFLF98</t>
+  </si>
+  <si>
+    <t>TFHD90</t>
   </si>
 </sst>
 </file>
@@ -1639,24 +1648,9 @@
 </styleSheet>
 </file>
 
-<file path=xl/namedSheetViews/namedSheetView1.xml><?xml version="1.0" encoding="utf-8"?>
-<namedSheetViews xmlns="http://schemas.microsoft.com/office/spreadsheetml/2019/namedsheetviews" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14"/>
-</file>
-
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{40364ABC-409D-4532-8E14-9D155F80C509}" name="Tabla1" displayName="Tabla1" ref="A1:J205" totalsRowShown="0">
-  <autoFilter ref="A1:J205" xr:uid="{40364ABC-409D-4532-8E14-9D155F80C509}">
-    <filterColumn colId="0">
-      <filters>
-        <filter val="SACYR"/>
-      </filters>
-    </filterColumn>
-    <filterColumn colId="5">
-      <filters>
-        <filter val="No revisada"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
+  <autoFilter ref="A1:J205" xr:uid="{40364ABC-409D-4532-8E14-9D155F80C509}"/>
   <tableColumns count="10">
     <tableColumn id="1" xr3:uid="{0A7C6585-5C8B-46BF-ABA0-2DA806D161DC}" name="FLOTA" dataDxfId="9"/>
     <tableColumn id="2" xr3:uid="{EB7792BB-219D-496F-9F16-84F6805E0CB0}" name="VIN CON PROBLEMAS" dataDxfId="8"/>
@@ -1990,7 +1984,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EDA66EBA-6B88-4C75-8217-0B7E221D898D}">
-  <dimension ref="A1:L205"/>
+  <dimension ref="A1:L204"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.453125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="43" style="6" bestFit="1" customWidth="1"/>
@@ -2037,7 +2031,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:12" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:12" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A2" s="7" t="s">
         <v>10</v>
       </c>
@@ -2060,7 +2054,7 @@
       <c r="H2" s="12"/>
       <c r="I2" s="12"/>
     </row>
-    <row r="3" spans="1:12" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:12" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A3" s="7" t="s">
         <v>10</v>
       </c>
@@ -2083,7 +2077,7 @@
       <c r="H3" s="12"/>
       <c r="I3" s="12"/>
     </row>
-    <row r="4" spans="1:12" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:12" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A4" s="7" t="s">
         <v>10</v>
       </c>
@@ -2106,7 +2100,7 @@
       <c r="H4" s="12"/>
       <c r="I4" s="12"/>
     </row>
-    <row r="5" spans="1:12" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:12" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A5" s="7" t="s">
         <v>10</v>
       </c>
@@ -2129,7 +2123,7 @@
       <c r="H5" s="12"/>
       <c r="I5" s="12"/>
     </row>
-    <row r="6" spans="1:12" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:12" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A6" s="7" t="s">
         <v>10</v>
       </c>
@@ -2152,7 +2146,7 @@
       <c r="H6" s="12"/>
       <c r="I6" s="12"/>
     </row>
-    <row r="7" spans="1:12" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:12" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A7" s="7" t="s">
         <v>10</v>
       </c>
@@ -2175,7 +2169,7 @@
       <c r="H7" s="24"/>
       <c r="I7" s="24"/>
     </row>
-    <row r="8" spans="1:12" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:12" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A8" s="7" t="s">
         <v>10</v>
       </c>
@@ -2198,7 +2192,7 @@
       <c r="H8" s="24"/>
       <c r="I8" s="24"/>
     </row>
-    <row r="9" spans="1:12" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:12" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A9" s="7" t="s">
         <v>10</v>
       </c>
@@ -2221,7 +2215,7 @@
       <c r="H9" s="12"/>
       <c r="I9" s="12"/>
     </row>
-    <row r="10" spans="1:12" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:12" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A10" s="7" t="s">
         <v>10</v>
       </c>
@@ -2244,7 +2238,7 @@
       <c r="H10" s="12"/>
       <c r="I10" s="12"/>
     </row>
-    <row r="11" spans="1:12" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:12" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A11" s="7" t="s">
         <v>10</v>
       </c>
@@ -2267,7 +2261,7 @@
       <c r="H11" s="12"/>
       <c r="I11" s="12"/>
     </row>
-    <row r="12" spans="1:12" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:12" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A12" s="7" t="s">
         <v>33</v>
       </c>
@@ -2291,7 +2285,7 @@
       <c r="I12" s="12"/>
       <c r="L12" s="26"/>
     </row>
-    <row r="13" spans="1:12" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:12" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A13" s="7" t="s">
         <v>33</v>
       </c>
@@ -2314,7 +2308,7 @@
       <c r="H13" s="12"/>
       <c r="I13" s="12"/>
     </row>
-    <row r="14" spans="1:12" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:12" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A14" s="7" t="s">
         <v>33</v>
       </c>
@@ -2337,7 +2331,7 @@
       <c r="H14" s="12"/>
       <c r="I14" s="12"/>
     </row>
-    <row r="15" spans="1:12" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:12" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A15" s="7" t="s">
         <v>33</v>
       </c>
@@ -2360,7 +2354,7 @@
       <c r="H15" s="12"/>
       <c r="I15" s="12"/>
     </row>
-    <row r="16" spans="1:12" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:12" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A16" s="7" t="s">
         <v>33</v>
       </c>
@@ -2383,7 +2377,7 @@
       <c r="H16" s="12"/>
       <c r="I16" s="12"/>
     </row>
-    <row r="17" spans="1:9" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A17" s="7" t="s">
         <v>33</v>
       </c>
@@ -2406,7 +2400,7 @@
       <c r="H17" s="12"/>
       <c r="I17" s="12"/>
     </row>
-    <row r="18" spans="1:9" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A18" s="7" t="s">
         <v>33</v>
       </c>
@@ -2429,7 +2423,7 @@
       <c r="H18" s="12"/>
       <c r="I18" s="12"/>
     </row>
-    <row r="19" spans="1:9" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A19" s="7" t="s">
         <v>33</v>
       </c>
@@ -2452,7 +2446,7 @@
       <c r="H19" s="12"/>
       <c r="I19" s="12"/>
     </row>
-    <row r="20" spans="1:9" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A20" s="7" t="s">
         <v>51</v>
       </c>
@@ -2475,7 +2469,7 @@
       <c r="H20" s="12"/>
       <c r="I20" s="12"/>
     </row>
-    <row r="21" spans="1:9" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A21" s="7" t="s">
         <v>51</v>
       </c>
@@ -2498,7 +2492,7 @@
       <c r="H21" s="12"/>
       <c r="I21" s="12"/>
     </row>
-    <row r="22" spans="1:9" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A22" s="7" t="s">
         <v>51</v>
       </c>
@@ -2521,7 +2515,7 @@
       <c r="H22" s="12"/>
       <c r="I22" s="12"/>
     </row>
-    <row r="23" spans="1:9" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A23" s="7" t="s">
         <v>59</v>
       </c>
@@ -2544,7 +2538,7 @@
       <c r="H23" s="12"/>
       <c r="I23" s="12"/>
     </row>
-    <row r="24" spans="1:9" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A24" s="7" t="s">
         <v>59</v>
       </c>
@@ -2567,7 +2561,7 @@
       <c r="H24" s="12"/>
       <c r="I24" s="12"/>
     </row>
-    <row r="25" spans="1:9" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A25" s="7" t="s">
         <v>65</v>
       </c>
@@ -2590,7 +2584,7 @@
       <c r="H25" s="12"/>
       <c r="I25" s="12"/>
     </row>
-    <row r="26" spans="1:9" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A26" s="7" t="s">
         <v>65</v>
       </c>
@@ -2613,7 +2607,7 @@
       <c r="H26" s="12"/>
       <c r="I26" s="12"/>
     </row>
-    <row r="27" spans="1:9" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A27" s="7" t="s">
         <v>65</v>
       </c>
@@ -2636,7 +2630,7 @@
       <c r="H27" s="12"/>
       <c r="I27" s="12"/>
     </row>
-    <row r="28" spans="1:9" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A28" s="7" t="s">
         <v>65</v>
       </c>
@@ -2659,7 +2653,7 @@
       <c r="H28" s="12"/>
       <c r="I28" s="12"/>
     </row>
-    <row r="29" spans="1:9" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A29" s="7" t="s">
         <v>65</v>
       </c>
@@ -2688,7 +2682,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="30" spans="1:9" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A30" s="7" t="s">
         <v>80</v>
       </c>
@@ -2711,7 +2705,7 @@
       <c r="H30" s="12"/>
       <c r="I30" s="12"/>
     </row>
-    <row r="31" spans="1:9" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A31" s="7" t="s">
         <v>80</v>
       </c>
@@ -2734,7 +2728,7 @@
       <c r="H31" s="12"/>
       <c r="I31" s="12"/>
     </row>
-    <row r="32" spans="1:9" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A32" s="7" t="s">
         <v>80</v>
       </c>
@@ -2757,7 +2751,7 @@
       <c r="H32" s="12"/>
       <c r="I32" s="12"/>
     </row>
-    <row r="33" spans="1:9" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A33" s="7" t="s">
         <v>80</v>
       </c>
@@ -2780,7 +2774,7 @@
       <c r="H33" s="12"/>
       <c r="I33" s="12"/>
     </row>
-    <row r="34" spans="1:9" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A34" s="7" t="s">
         <v>80</v>
       </c>
@@ -2803,7 +2797,7 @@
       <c r="H34" s="12"/>
       <c r="I34" s="12"/>
     </row>
-    <row r="35" spans="1:9" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A35" s="7" t="s">
         <v>80</v>
       </c>
@@ -2826,7 +2820,7 @@
       <c r="H35" s="12"/>
       <c r="I35" s="12"/>
     </row>
-    <row r="36" spans="1:9" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A36" s="7" t="s">
         <v>80</v>
       </c>
@@ -2849,7 +2843,7 @@
       <c r="H36" s="12"/>
       <c r="I36" s="12"/>
     </row>
-    <row r="37" spans="1:9" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A37" s="7" t="s">
         <v>95</v>
       </c>
@@ -2878,7 +2872,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="38" spans="1:9" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A38" s="7" t="s">
         <v>95</v>
       </c>
@@ -2907,7 +2901,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="39" spans="1:9" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A39" s="7" t="s">
         <v>95</v>
       </c>
@@ -2930,7 +2924,7 @@
       <c r="H39" s="12"/>
       <c r="I39" s="12"/>
     </row>
-    <row r="40" spans="1:9" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A40" s="7" t="s">
         <v>95</v>
       </c>
@@ -2959,7 +2953,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="41" spans="1:9" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A41" s="7" t="s">
         <v>95</v>
       </c>
@@ -2988,7 +2982,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="42" spans="1:9" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A42" s="7" t="s">
         <v>95</v>
       </c>
@@ -3011,7 +3005,7 @@
       <c r="H42" s="12"/>
       <c r="I42" s="12"/>
     </row>
-    <row r="43" spans="1:9" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A43" s="7" t="s">
         <v>95</v>
       </c>
@@ -3034,7 +3028,7 @@
       <c r="H43" s="12"/>
       <c r="I43" s="12"/>
     </row>
-    <row r="44" spans="1:9" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A44" s="7" t="s">
         <v>95</v>
       </c>
@@ -3057,7 +3051,7 @@
       <c r="H44" s="12"/>
       <c r="I44" s="12"/>
     </row>
-    <row r="45" spans="1:9" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A45" s="7" t="s">
         <v>95</v>
       </c>
@@ -3080,7 +3074,7 @@
       <c r="H45" s="12"/>
       <c r="I45" s="12"/>
     </row>
-    <row r="46" spans="1:9" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A46" s="7" t="s">
         <v>95</v>
       </c>
@@ -3109,7 +3103,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="47" spans="1:9" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A47" s="7" t="s">
         <v>95</v>
       </c>
@@ -3138,7 +3132,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="48" spans="1:9" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A48" s="7" t="s">
         <v>95</v>
       </c>
@@ -3167,7 +3161,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="49" spans="1:9" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A49" s="7" t="s">
         <v>95</v>
       </c>
@@ -3196,7 +3190,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="50" spans="1:9" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A50" s="7" t="s">
         <v>95</v>
       </c>
@@ -3219,7 +3213,7 @@
       <c r="H50" s="12"/>
       <c r="I50" s="12"/>
     </row>
-    <row r="51" spans="1:9" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A51" s="7" t="s">
         <v>95</v>
       </c>
@@ -3242,7 +3236,7 @@
       <c r="H51" s="12"/>
       <c r="I51" s="12"/>
     </row>
-    <row r="52" spans="1:9" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A52" s="7" t="s">
         <v>95</v>
       </c>
@@ -3265,7 +3259,7 @@
       <c r="H52" s="12"/>
       <c r="I52" s="12"/>
     </row>
-    <row r="53" spans="1:9" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A53" s="7" t="s">
         <v>95</v>
       </c>
@@ -3294,7 +3288,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="54" spans="1:9" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A54" s="7" t="s">
         <v>95</v>
       </c>
@@ -3317,7 +3311,7 @@
       <c r="H54" s="12"/>
       <c r="I54" s="12"/>
     </row>
-    <row r="55" spans="1:9" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A55" s="7" t="s">
         <v>95</v>
       </c>
@@ -3346,7 +3340,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="56" spans="1:9" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A56" s="7" t="s">
         <v>95</v>
       </c>
@@ -3375,7 +3369,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="57" spans="1:9" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A57" s="7" t="s">
         <v>95</v>
       </c>
@@ -3404,7 +3398,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="58" spans="1:9" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A58" s="7" t="s">
         <v>95</v>
       </c>
@@ -3427,7 +3421,7 @@
       <c r="H58" s="12"/>
       <c r="I58" s="12"/>
     </row>
-    <row r="59" spans="1:9" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A59" s="7" t="s">
         <v>95</v>
       </c>
@@ -3456,7 +3450,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="60" spans="1:9" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A60" s="7" t="s">
         <v>95</v>
       </c>
@@ -3479,7 +3473,7 @@
       <c r="H60" s="12"/>
       <c r="I60" s="12"/>
     </row>
-    <row r="61" spans="1:9" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A61" s="7" t="s">
         <v>95</v>
       </c>
@@ -3571,7 +3565,7 @@
       <c r="H64" s="12"/>
       <c r="I64" s="12"/>
     </row>
-    <row r="65" spans="1:9" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A65" s="7" t="s">
         <v>149</v>
       </c>
@@ -3600,7 +3594,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="66" spans="1:9" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A66" s="7" t="s">
         <v>149</v>
       </c>
@@ -3629,7 +3623,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="67" spans="1:9" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A67" s="7" t="s">
         <v>149</v>
       </c>
@@ -3773,7 +3767,7 @@
       <c r="H72" s="12"/>
       <c r="I72" s="12"/>
     </row>
-    <row r="73" spans="1:9" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A73" s="7" t="s">
         <v>172</v>
       </c>
@@ -3796,7 +3790,7 @@
       <c r="H73" s="12"/>
       <c r="I73" s="12"/>
     </row>
-    <row r="74" spans="1:9" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A74" s="7" t="s">
         <v>172</v>
       </c>
@@ -3819,7 +3813,7 @@
       <c r="H74" s="12"/>
       <c r="I74" s="12"/>
     </row>
-    <row r="75" spans="1:9" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A75" s="7" t="s">
         <v>177</v>
       </c>
@@ -3842,7 +3836,7 @@
       <c r="H75" s="12"/>
       <c r="I75" s="12"/>
     </row>
-    <row r="76" spans="1:9" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A76" s="7" t="s">
         <v>177</v>
       </c>
@@ -3865,7 +3859,7 @@
       <c r="H76" s="12"/>
       <c r="I76" s="12"/>
     </row>
-    <row r="77" spans="1:9" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A77" s="7" t="s">
         <v>177</v>
       </c>
@@ -3888,7 +3882,7 @@
       <c r="H77" s="12"/>
       <c r="I77" s="12"/>
     </row>
-    <row r="78" spans="1:9" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A78" s="7" t="s">
         <v>177</v>
       </c>
@@ -3911,7 +3905,7 @@
       <c r="H78" s="12"/>
       <c r="I78" s="12"/>
     </row>
-    <row r="79" spans="1:9" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A79" s="7" t="s">
         <v>177</v>
       </c>
@@ -3934,7 +3928,7 @@
       <c r="H79" s="12"/>
       <c r="I79" s="12"/>
     </row>
-    <row r="80" spans="1:9" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A80" s="7" t="s">
         <v>177</v>
       </c>
@@ -3957,7 +3951,7 @@
       <c r="H80" s="12"/>
       <c r="I80" s="12"/>
     </row>
-    <row r="81" spans="1:9" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A81" s="7" t="s">
         <v>177</v>
       </c>
@@ -3980,7 +3974,7 @@
       <c r="H81" s="12"/>
       <c r="I81" s="12"/>
     </row>
-    <row r="82" spans="1:9" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="82" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A82" s="7" t="s">
         <v>177</v>
       </c>
@@ -4003,7 +3997,7 @@
       <c r="H82" s="12"/>
       <c r="I82" s="12"/>
     </row>
-    <row r="83" spans="1:9" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A83" s="7" t="s">
         <v>177</v>
       </c>
@@ -4026,7 +4020,7 @@
       <c r="H83" s="12"/>
       <c r="I83" s="12"/>
     </row>
-    <row r="84" spans="1:9" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="84" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A84" s="7" t="s">
         <v>177</v>
       </c>
@@ -4049,7 +4043,7 @@
       <c r="H84" s="12"/>
       <c r="I84" s="12"/>
     </row>
-    <row r="85" spans="1:9" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="85" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A85" s="7" t="s">
         <v>177</v>
       </c>
@@ -4072,7 +4066,7 @@
       <c r="H85" s="12"/>
       <c r="I85" s="12"/>
     </row>
-    <row r="86" spans="1:9" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="86" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A86" s="7" t="s">
         <v>177</v>
       </c>
@@ -4095,7 +4089,7 @@
       <c r="H86" s="12"/>
       <c r="I86" s="12"/>
     </row>
-    <row r="87" spans="1:9" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="87" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A87" s="7" t="s">
         <v>177</v>
       </c>
@@ -4118,7 +4112,7 @@
       <c r="H87" s="12"/>
       <c r="I87" s="12"/>
     </row>
-    <row r="88" spans="1:9" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="88" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A88" s="7" t="s">
         <v>177</v>
       </c>
@@ -4141,7 +4135,7 @@
       <c r="H88" s="12"/>
       <c r="I88" s="12"/>
     </row>
-    <row r="89" spans="1:9" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="89" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A89" s="7" t="s">
         <v>177</v>
       </c>
@@ -4164,7 +4158,7 @@
       <c r="H89" s="12"/>
       <c r="I89" s="12"/>
     </row>
-    <row r="90" spans="1:9" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="90" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A90" s="7" t="s">
         <v>177</v>
       </c>
@@ -4187,7 +4181,7 @@
       <c r="H90" s="12"/>
       <c r="I90" s="12"/>
     </row>
-    <row r="91" spans="1:9" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="91" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A91" s="7" t="s">
         <v>210</v>
       </c>
@@ -4210,7 +4204,7 @@
       <c r="H91" s="12"/>
       <c r="I91" s="12"/>
     </row>
-    <row r="92" spans="1:9" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="92" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A92" s="7" t="s">
         <v>210</v>
       </c>
@@ -4233,7 +4227,7 @@
       <c r="H92" s="12"/>
       <c r="I92" s="12"/>
     </row>
-    <row r="93" spans="1:9" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="93" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A93" s="7" t="s">
         <v>210</v>
       </c>
@@ -4256,7 +4250,7 @@
       <c r="H93" s="12"/>
       <c r="I93" s="12"/>
     </row>
-    <row r="94" spans="1:9" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="94" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A94" s="7" t="s">
         <v>217</v>
       </c>
@@ -4285,7 +4279,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="95" spans="1:9" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="95" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A95" s="7" t="s">
         <v>217</v>
       </c>
@@ -4308,7 +4302,7 @@
       <c r="H95" s="12"/>
       <c r="I95" s="12"/>
     </row>
-    <row r="96" spans="1:9" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="96" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A96" s="7" t="s">
         <v>217</v>
       </c>
@@ -4331,7 +4325,7 @@
       <c r="H96" s="12"/>
       <c r="I96" s="12"/>
     </row>
-    <row r="97" spans="1:10" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="97" spans="1:10" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A97" s="7" t="s">
         <v>217</v>
       </c>
@@ -4354,7 +4348,7 @@
       <c r="H97" s="12"/>
       <c r="I97" s="12"/>
     </row>
-    <row r="98" spans="1:10" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="98" spans="1:10" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A98" s="7" t="s">
         <v>225</v>
       </c>
@@ -4383,7 +4377,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="99" spans="1:10" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="99" spans="1:10" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A99" s="7" t="s">
         <v>225</v>
       </c>
@@ -4406,7 +4400,7 @@
       <c r="H99" s="12"/>
       <c r="I99" s="12"/>
     </row>
-    <row r="100" spans="1:10" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="100" spans="1:10" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A100" s="7" t="s">
         <v>231</v>
       </c>
@@ -4429,7 +4423,7 @@
       <c r="H100" s="12"/>
       <c r="I100" s="12"/>
     </row>
-    <row r="101" spans="1:10" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="101" spans="1:10" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A101" s="7" t="s">
         <v>231</v>
       </c>
@@ -4455,7 +4449,7 @@
         <v>237</v>
       </c>
     </row>
-    <row r="102" spans="1:10" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="102" spans="1:10" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A102" s="7" t="s">
         <v>238</v>
       </c>
@@ -4478,7 +4472,7 @@
       <c r="H102" s="12"/>
       <c r="I102" s="12"/>
     </row>
-    <row r="103" spans="1:10" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="103" spans="1:10" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A103" s="7" t="s">
         <v>238</v>
       </c>
@@ -4501,7 +4495,7 @@
       <c r="H103" s="12"/>
       <c r="I103" s="12"/>
     </row>
-    <row r="104" spans="1:10" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="104" spans="1:10" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A104" s="7" t="s">
         <v>238</v>
       </c>
@@ -4524,7 +4518,7 @@
       <c r="H104" s="12"/>
       <c r="I104" s="12"/>
     </row>
-    <row r="105" spans="1:10" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="105" spans="1:10" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A105" s="7" t="s">
         <v>238</v>
       </c>
@@ -4547,7 +4541,7 @@
       <c r="H105" s="12"/>
       <c r="I105" s="12"/>
     </row>
-    <row r="106" spans="1:10" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="106" spans="1:10" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A106" s="7" t="s">
         <v>238</v>
       </c>
@@ -4570,7 +4564,7 @@
       <c r="H106" s="12"/>
       <c r="I106" s="12"/>
     </row>
-    <row r="107" spans="1:10" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="107" spans="1:10" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A107" s="7" t="s">
         <v>238</v>
       </c>
@@ -4593,7 +4587,7 @@
       <c r="H107" s="12"/>
       <c r="I107" s="12"/>
     </row>
-    <row r="108" spans="1:10" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="108" spans="1:10" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A108" s="7" t="s">
         <v>238</v>
       </c>
@@ -4616,7 +4610,7 @@
       <c r="H108" s="12"/>
       <c r="I108" s="12"/>
     </row>
-    <row r="109" spans="1:10" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="109" spans="1:10" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A109" s="7" t="s">
         <v>238</v>
       </c>
@@ -4639,7 +4633,7 @@
       <c r="H109" s="12"/>
       <c r="I109" s="12"/>
     </row>
-    <row r="110" spans="1:10" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="110" spans="1:10" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A110" s="7" t="s">
         <v>238</v>
       </c>
@@ -4662,7 +4656,7 @@
       <c r="H110" s="12"/>
       <c r="I110" s="12"/>
     </row>
-    <row r="111" spans="1:10" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="111" spans="1:10" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A111" s="7" t="s">
         <v>238</v>
       </c>
@@ -4685,7 +4679,7 @@
       <c r="H111" s="12"/>
       <c r="I111" s="12"/>
     </row>
-    <row r="112" spans="1:10" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="112" spans="1:10" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A112" s="7" t="s">
         <v>238</v>
       </c>
@@ -4708,7 +4702,7 @@
       <c r="H112" s="12"/>
       <c r="I112" s="12"/>
     </row>
-    <row r="113" spans="1:9" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="113" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A113" s="7" t="s">
         <v>238</v>
       </c>
@@ -4731,7 +4725,7 @@
       <c r="H113" s="12"/>
       <c r="I113" s="12"/>
     </row>
-    <row r="114" spans="1:9" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="114" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A114" s="7" t="s">
         <v>238</v>
       </c>
@@ -4754,7 +4748,7 @@
       <c r="H114" s="12"/>
       <c r="I114" s="12"/>
     </row>
-    <row r="115" spans="1:9" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="115" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A115" s="7" t="s">
         <v>238</v>
       </c>
@@ -4777,7 +4771,7 @@
       <c r="H115" s="12"/>
       <c r="I115" s="12"/>
     </row>
-    <row r="116" spans="1:9" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="116" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A116" s="7" t="s">
         <v>238</v>
       </c>
@@ -4800,7 +4794,7 @@
       <c r="H116" s="12"/>
       <c r="I116" s="12"/>
     </row>
-    <row r="117" spans="1:9" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="117" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A117" s="7" t="s">
         <v>238</v>
       </c>
@@ -4823,7 +4817,7 @@
       <c r="H117" s="12"/>
       <c r="I117" s="12"/>
     </row>
-    <row r="118" spans="1:9" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="118" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A118" s="7" t="s">
         <v>238</v>
       </c>
@@ -4846,7 +4840,7 @@
       <c r="H118" s="12"/>
       <c r="I118" s="12"/>
     </row>
-    <row r="119" spans="1:9" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="119" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A119" s="7" t="s">
         <v>238</v>
       </c>
@@ -4869,7 +4863,7 @@
       <c r="H119" s="12"/>
       <c r="I119" s="12"/>
     </row>
-    <row r="120" spans="1:9" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="120" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A120" s="7" t="s">
         <v>276</v>
       </c>
@@ -4892,7 +4886,7 @@
       <c r="H120" s="12"/>
       <c r="I120" s="12"/>
     </row>
-    <row r="121" spans="1:9" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="121" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A121" s="7" t="s">
         <v>276</v>
       </c>
@@ -4915,7 +4909,7 @@
       <c r="H121" s="12"/>
       <c r="I121" s="12"/>
     </row>
-    <row r="122" spans="1:9" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="122" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A122" s="7" t="s">
         <v>276</v>
       </c>
@@ -4938,7 +4932,7 @@
       <c r="H122" s="12"/>
       <c r="I122" s="12"/>
     </row>
-    <row r="123" spans="1:9" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="123" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A123" s="7" t="s">
         <v>284</v>
       </c>
@@ -4961,7 +4955,7 @@
       <c r="H123" s="12"/>
       <c r="I123" s="12"/>
     </row>
-    <row r="124" spans="1:9" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="124" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A124" s="7" t="s">
         <v>287</v>
       </c>
@@ -4984,7 +4978,7 @@
       <c r="H124" s="12"/>
       <c r="I124" s="12"/>
     </row>
-    <row r="125" spans="1:9" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="125" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A125" s="7" t="s">
         <v>287</v>
       </c>
@@ -5007,7 +5001,7 @@
       <c r="H125" s="12"/>
       <c r="I125" s="12"/>
     </row>
-    <row r="126" spans="1:9" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="126" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A126" s="7" t="s">
         <v>287</v>
       </c>
@@ -5030,7 +5024,7 @@
       <c r="H126" s="15"/>
       <c r="I126" s="15"/>
     </row>
-    <row r="127" spans="1:9" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="127" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A127" s="7" t="s">
         <v>294</v>
       </c>
@@ -5053,7 +5047,7 @@
       <c r="H127" s="12"/>
       <c r="I127" s="12"/>
     </row>
-    <row r="128" spans="1:9" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="128" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A128" t="s">
         <v>297</v>
       </c>
@@ -5080,7 +5074,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="129" spans="1:10" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="129" spans="1:10" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A129" t="s">
         <v>297</v>
       </c>
@@ -5105,7 +5099,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="130" spans="1:10" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="130" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A130" s="33" t="s">
         <v>303</v>
       </c>
@@ -5130,7 +5124,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="131" spans="1:10" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="131" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A131" s="33" t="s">
         <v>307</v>
       </c>
@@ -5155,7 +5149,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="132" spans="1:10" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="132" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A132" s="33" t="s">
         <v>65</v>
       </c>
@@ -5180,7 +5174,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="133" spans="1:10" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="133" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A133" s="33" t="s">
         <v>313</v>
       </c>
@@ -5205,7 +5199,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="134" spans="1:10" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="134" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A134" s="33" t="s">
         <v>313</v>
       </c>
@@ -5230,7 +5224,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="135" spans="1:10" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="135" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A135" s="33" t="s">
         <v>276</v>
       </c>
@@ -5255,7 +5249,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="136" spans="1:10" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="136" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A136" s="33" t="s">
         <v>320</v>
       </c>
@@ -5281,7 +5275,7 @@
       </c>
       <c r="J136" s="38"/>
     </row>
-    <row r="137" spans="1:10" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="137" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A137" s="33" t="s">
         <v>324</v>
       </c>
@@ -5307,7 +5301,7 @@
       </c>
       <c r="J137" s="38"/>
     </row>
-    <row r="138" spans="1:10" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="138" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A138" s="7" t="s">
         <v>329</v>
       </c>
@@ -5331,7 +5325,7 @@
       </c>
       <c r="J138" s="37"/>
     </row>
-    <row r="139" spans="1:10" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="139" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A139" s="7" t="s">
         <v>329</v>
       </c>
@@ -5355,7 +5349,7 @@
       </c>
       <c r="J139" s="38"/>
     </row>
-    <row r="140" spans="1:10" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="140" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A140" s="7" t="s">
         <v>329</v>
       </c>
@@ -5379,7 +5373,7 @@
       </c>
       <c r="J140" s="38"/>
     </row>
-    <row r="141" spans="1:10" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="141" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A141" s="33" t="s">
         <v>333</v>
       </c>
@@ -5405,7 +5399,7 @@
       </c>
       <c r="J141" s="38"/>
     </row>
-    <row r="142" spans="1:10" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="142" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A142" s="33" t="s">
         <v>313</v>
       </c>
@@ -5430,7 +5424,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="143" spans="1:10" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="143" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A143" s="7" t="s">
         <v>336</v>
       </c>
@@ -5455,7 +5449,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="144" spans="1:10" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="144" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A144" s="33" t="s">
         <v>339</v>
       </c>
@@ -5480,7 +5474,7 @@
         <v>342</v>
       </c>
     </row>
-    <row r="145" spans="1:9" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="145" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A145" s="7" t="s">
         <v>65</v>
       </c>
@@ -5505,21 +5499,28 @@
         <v>79</v>
       </c>
     </row>
-    <row r="146" spans="1:9" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="146" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A146" s="7"/>
       <c r="B146" s="8"/>
-      <c r="C146" s="40"/>
+      <c r="C146" t="s">
+        <v>347</v>
+      </c>
       <c r="D146" s="9"/>
       <c r="E146" s="8"/>
       <c r="F146" s="10"/>
       <c r="G146" s="13"/>
       <c r="H146" s="12"/>
       <c r="I146" s="12"/>
-    </row>
-    <row r="147" spans="1:9" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="J146" s="6">
+        <v>863457051708251</v>
+      </c>
+    </row>
+    <row r="147" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A147" s="7"/>
       <c r="B147" s="8"/>
-      <c r="C147" s="40"/>
+      <c r="C147" t="s">
+        <v>348</v>
+      </c>
       <c r="D147" s="9"/>
       <c r="E147" s="8"/>
       <c r="F147" s="10"/>
@@ -5527,10 +5528,12 @@
       <c r="H147" s="12"/>
       <c r="I147" s="12"/>
     </row>
-    <row r="148" spans="1:9" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="148" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A148" s="7"/>
       <c r="B148" s="8"/>
-      <c r="C148" s="40"/>
+      <c r="C148" t="s">
+        <v>349</v>
+      </c>
       <c r="D148" s="9"/>
       <c r="E148" s="8"/>
       <c r="F148" s="10"/>
@@ -5538,7 +5541,7 @@
       <c r="H148" s="12"/>
       <c r="I148" s="12"/>
     </row>
-    <row r="149" spans="1:9" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="149" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A149" s="7"/>
       <c r="B149" s="8"/>
       <c r="C149" s="40"/>
@@ -5549,7 +5552,7 @@
       <c r="H149" s="12"/>
       <c r="I149" s="12"/>
     </row>
-    <row r="150" spans="1:9" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="150" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A150" s="7"/>
       <c r="B150" s="8"/>
       <c r="C150" s="40"/>
@@ -5560,7 +5563,7 @@
       <c r="H150" s="12"/>
       <c r="I150" s="12"/>
     </row>
-    <row r="151" spans="1:9" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="151" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A151" s="7"/>
       <c r="B151" s="8"/>
       <c r="C151" s="40"/>
@@ -5571,7 +5574,7 @@
       <c r="H151" s="12"/>
       <c r="I151" s="12"/>
     </row>
-    <row r="152" spans="1:9" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="152" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A152" s="7"/>
       <c r="B152" s="8"/>
       <c r="C152" s="40"/>
@@ -5582,7 +5585,7 @@
       <c r="H152" s="12"/>
       <c r="I152" s="12"/>
     </row>
-    <row r="153" spans="1:9" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="153" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A153" s="7"/>
       <c r="B153" s="8"/>
       <c r="C153" s="40"/>
@@ -5593,7 +5596,7 @@
       <c r="H153" s="12"/>
       <c r="I153" s="12"/>
     </row>
-    <row r="154" spans="1:9" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="154" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A154" s="7"/>
       <c r="B154" s="8"/>
       <c r="C154" s="40"/>
@@ -5604,7 +5607,7 @@
       <c r="H154" s="12"/>
       <c r="I154" s="12"/>
     </row>
-    <row r="155" spans="1:9" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="155" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A155" s="7"/>
       <c r="B155" s="8"/>
       <c r="C155" s="40"/>
@@ -5615,7 +5618,7 @@
       <c r="H155" s="12"/>
       <c r="I155" s="12"/>
     </row>
-    <row r="156" spans="1:9" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="156" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A156" s="7"/>
       <c r="B156" s="8"/>
       <c r="C156" s="40"/>
@@ -5626,7 +5629,7 @@
       <c r="H156" s="12"/>
       <c r="I156" s="12"/>
     </row>
-    <row r="157" spans="1:9" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="157" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A157" s="7"/>
       <c r="B157" s="8"/>
       <c r="C157" s="40"/>
@@ -5637,7 +5640,7 @@
       <c r="H157" s="12"/>
       <c r="I157" s="12"/>
     </row>
-    <row r="158" spans="1:9" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="158" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A158" s="7"/>
       <c r="B158" s="8"/>
       <c r="C158" s="40"/>
@@ -5648,7 +5651,7 @@
       <c r="H158" s="12"/>
       <c r="I158" s="12"/>
     </row>
-    <row r="159" spans="1:9" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="159" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A159" s="7"/>
       <c r="B159" s="8"/>
       <c r="C159" s="40"/>
@@ -5659,7 +5662,7 @@
       <c r="H159" s="12"/>
       <c r="I159" s="12"/>
     </row>
-    <row r="160" spans="1:9" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="160" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A160" s="7"/>
       <c r="B160" s="8"/>
       <c r="C160" s="40"/>
@@ -5670,7 +5673,7 @@
       <c r="H160" s="12"/>
       <c r="I160" s="12"/>
     </row>
-    <row r="161" spans="1:9" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="161" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A161" s="7"/>
       <c r="B161" s="8"/>
       <c r="C161" s="40"/>
@@ -5681,7 +5684,7 @@
       <c r="H161" s="12"/>
       <c r="I161" s="12"/>
     </row>
-    <row r="162" spans="1:9" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="162" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A162" s="7"/>
       <c r="B162" s="8"/>
       <c r="C162" s="40"/>
@@ -5692,7 +5695,7 @@
       <c r="H162" s="12"/>
       <c r="I162" s="12"/>
     </row>
-    <row r="163" spans="1:9" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="163" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A163" s="7"/>
       <c r="B163" s="8"/>
       <c r="C163" s="40"/>
@@ -5703,7 +5706,7 @@
       <c r="H163" s="12"/>
       <c r="I163" s="12"/>
     </row>
-    <row r="164" spans="1:9" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="164" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A164" s="7"/>
       <c r="B164" s="8"/>
       <c r="C164" s="40"/>
@@ -5714,7 +5717,7 @@
       <c r="H164" s="12"/>
       <c r="I164" s="12"/>
     </row>
-    <row r="165" spans="1:9" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="165" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A165" s="7"/>
       <c r="B165" s="8"/>
       <c r="C165" s="40"/>
@@ -5725,7 +5728,7 @@
       <c r="H165" s="12"/>
       <c r="I165" s="12"/>
     </row>
-    <row r="166" spans="1:9" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="166" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A166" s="7"/>
       <c r="B166" s="8"/>
       <c r="C166" s="40"/>
@@ -5736,7 +5739,7 @@
       <c r="H166" s="12"/>
       <c r="I166" s="12"/>
     </row>
-    <row r="167" spans="1:9" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="167" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A167" s="7"/>
       <c r="B167" s="8"/>
       <c r="C167" s="40"/>
@@ -5747,7 +5750,7 @@
       <c r="H167" s="12"/>
       <c r="I167" s="12"/>
     </row>
-    <row r="168" spans="1:9" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="168" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A168" s="7"/>
       <c r="B168" s="8"/>
       <c r="C168" s="40"/>
@@ -5758,7 +5761,7 @@
       <c r="H168" s="12"/>
       <c r="I168" s="12"/>
     </row>
-    <row r="169" spans="1:9" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="169" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A169" s="7"/>
       <c r="B169" s="8"/>
       <c r="C169" s="40"/>
@@ -5769,7 +5772,7 @@
       <c r="H169" s="12"/>
       <c r="I169" s="12"/>
     </row>
-    <row r="170" spans="1:9" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="170" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A170" s="7"/>
       <c r="B170" s="8"/>
       <c r="C170" s="40"/>
@@ -5780,7 +5783,7 @@
       <c r="H170" s="12"/>
       <c r="I170" s="12"/>
     </row>
-    <row r="171" spans="1:9" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="171" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A171" s="7"/>
       <c r="B171" s="8"/>
       <c r="C171" s="40"/>
@@ -5791,7 +5794,7 @@
       <c r="H171" s="12"/>
       <c r="I171" s="12"/>
     </row>
-    <row r="172" spans="1:9" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="172" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A172" s="7"/>
       <c r="B172" s="8"/>
       <c r="C172" s="40"/>
@@ -5802,7 +5805,7 @@
       <c r="H172" s="12"/>
       <c r="I172" s="12"/>
     </row>
-    <row r="173" spans="1:9" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="173" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A173" s="7"/>
       <c r="B173" s="8"/>
       <c r="C173" s="40"/>
@@ -5813,7 +5816,7 @@
       <c r="H173" s="12"/>
       <c r="I173" s="12"/>
     </row>
-    <row r="174" spans="1:9" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="174" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A174" s="7"/>
       <c r="B174" s="8"/>
       <c r="C174" s="40"/>
@@ -5824,7 +5827,7 @@
       <c r="H174" s="12"/>
       <c r="I174" s="12"/>
     </row>
-    <row r="175" spans="1:9" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="175" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A175" s="7"/>
       <c r="B175" s="8"/>
       <c r="C175" s="40"/>
@@ -5835,7 +5838,7 @@
       <c r="H175" s="12"/>
       <c r="I175" s="12"/>
     </row>
-    <row r="176" spans="1:9" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="176" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A176" s="7"/>
       <c r="B176" s="8"/>
       <c r="C176" s="40"/>
@@ -5846,7 +5849,7 @@
       <c r="H176" s="12"/>
       <c r="I176" s="12"/>
     </row>
-    <row r="177" spans="1:9" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="177" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A177" s="7"/>
       <c r="B177" s="8"/>
       <c r="C177" s="40"/>
@@ -5857,7 +5860,7 @@
       <c r="H177" s="12"/>
       <c r="I177" s="12"/>
     </row>
-    <row r="178" spans="1:9" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="178" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A178" s="7"/>
       <c r="B178" s="8"/>
       <c r="C178" s="40"/>
@@ -5868,7 +5871,7 @@
       <c r="H178" s="12"/>
       <c r="I178" s="12"/>
     </row>
-    <row r="179" spans="1:9" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="179" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A179" s="7"/>
       <c r="B179" s="8"/>
       <c r="C179" s="40"/>
@@ -5879,7 +5882,7 @@
       <c r="H179" s="12"/>
       <c r="I179" s="12"/>
     </row>
-    <row r="180" spans="1:9" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="180" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A180" s="7"/>
       <c r="B180" s="8"/>
       <c r="C180" s="40"/>
@@ -5890,7 +5893,7 @@
       <c r="H180" s="12"/>
       <c r="I180" s="12"/>
     </row>
-    <row r="181" spans="1:9" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="181" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A181" s="7"/>
       <c r="B181" s="8"/>
       <c r="C181" s="40"/>
@@ -5901,7 +5904,7 @@
       <c r="H181" s="12"/>
       <c r="I181" s="12"/>
     </row>
-    <row r="182" spans="1:9" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="182" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A182" s="7"/>
       <c r="B182" s="8"/>
       <c r="C182" s="40"/>
@@ -5912,7 +5915,7 @@
       <c r="H182" s="12"/>
       <c r="I182" s="12"/>
     </row>
-    <row r="183" spans="1:9" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="183" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A183" s="7"/>
       <c r="B183" s="8"/>
       <c r="C183" s="40"/>
@@ -5923,7 +5926,7 @@
       <c r="H183" s="12"/>
       <c r="I183" s="12"/>
     </row>
-    <row r="184" spans="1:9" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="184" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A184" s="7"/>
       <c r="B184" s="8"/>
       <c r="C184" s="40"/>
@@ -5934,7 +5937,7 @@
       <c r="H184" s="12"/>
       <c r="I184" s="12"/>
     </row>
-    <row r="185" spans="1:9" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="185" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A185" s="7"/>
       <c r="B185" s="8"/>
       <c r="C185" s="40"/>
@@ -5945,7 +5948,7 @@
       <c r="H185" s="12"/>
       <c r="I185" s="12"/>
     </row>
-    <row r="186" spans="1:9" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="186" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A186" s="7"/>
       <c r="B186" s="8"/>
       <c r="C186" s="40"/>
@@ -5956,7 +5959,7 @@
       <c r="H186" s="12"/>
       <c r="I186" s="12"/>
     </row>
-    <row r="187" spans="1:9" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="187" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A187" s="7"/>
       <c r="B187" s="8"/>
       <c r="C187" s="40"/>
@@ -5967,7 +5970,7 @@
       <c r="H187" s="12"/>
       <c r="I187" s="12"/>
     </row>
-    <row r="188" spans="1:9" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="188" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A188" s="7"/>
       <c r="B188" s="8"/>
       <c r="C188" s="40"/>
@@ -5978,7 +5981,7 @@
       <c r="H188" s="12"/>
       <c r="I188" s="12"/>
     </row>
-    <row r="189" spans="1:9" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="189" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A189" s="7"/>
       <c r="B189" s="8"/>
       <c r="C189" s="40"/>
@@ -5989,7 +5992,7 @@
       <c r="H189" s="12"/>
       <c r="I189" s="12"/>
     </row>
-    <row r="190" spans="1:9" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="190" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A190" s="7"/>
       <c r="B190" s="8"/>
       <c r="C190" s="40"/>
@@ -6000,7 +6003,7 @@
       <c r="H190" s="12"/>
       <c r="I190" s="12"/>
     </row>
-    <row r="191" spans="1:9" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="191" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A191" s="7"/>
       <c r="B191" s="8"/>
       <c r="C191" s="40"/>
@@ -6011,7 +6014,7 @@
       <c r="H191" s="12"/>
       <c r="I191" s="12"/>
     </row>
-    <row r="192" spans="1:9" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="192" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A192" s="7"/>
       <c r="B192" s="8"/>
       <c r="C192" s="40"/>
@@ -6022,7 +6025,7 @@
       <c r="H192" s="12"/>
       <c r="I192" s="12"/>
     </row>
-    <row r="193" spans="1:9" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="193" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A193" s="7"/>
       <c r="B193" s="8"/>
       <c r="C193" s="40"/>
@@ -6033,7 +6036,7 @@
       <c r="H193" s="12"/>
       <c r="I193" s="12"/>
     </row>
-    <row r="194" spans="1:9" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="194" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A194" s="7"/>
       <c r="B194" s="8"/>
       <c r="C194" s="40"/>
@@ -6044,7 +6047,7 @@
       <c r="H194" s="12"/>
       <c r="I194" s="12"/>
     </row>
-    <row r="195" spans="1:9" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="195" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A195" s="7"/>
       <c r="B195" s="8"/>
       <c r="C195" s="40"/>
@@ -6055,7 +6058,7 @@
       <c r="H195" s="12"/>
       <c r="I195" s="12"/>
     </row>
-    <row r="196" spans="1:9" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="196" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A196" s="7"/>
       <c r="B196" s="8"/>
       <c r="C196" s="40"/>
@@ -6066,7 +6069,7 @@
       <c r="H196" s="12"/>
       <c r="I196" s="12"/>
     </row>
-    <row r="197" spans="1:9" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="197" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A197" s="7"/>
       <c r="B197" s="8"/>
       <c r="C197" s="40"/>
@@ -6077,7 +6080,7 @@
       <c r="H197" s="12"/>
       <c r="I197" s="12"/>
     </row>
-    <row r="198" spans="1:9" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="198" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A198" s="7"/>
       <c r="B198" s="8"/>
       <c r="C198" s="40"/>
@@ -6088,7 +6091,7 @@
       <c r="H198" s="12"/>
       <c r="I198" s="12"/>
     </row>
-    <row r="199" spans="1:9" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="199" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A199" s="7"/>
       <c r="B199" s="8"/>
       <c r="C199" s="40"/>
@@ -6099,7 +6102,7 @@
       <c r="H199" s="12"/>
       <c r="I199" s="12"/>
     </row>
-    <row r="200" spans="1:9" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="200" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A200" s="7"/>
       <c r="B200" s="8"/>
       <c r="C200" s="40"/>
@@ -6110,7 +6113,7 @@
       <c r="H200" s="12"/>
       <c r="I200" s="12"/>
     </row>
-    <row r="201" spans="1:9" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="201" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A201" s="7"/>
       <c r="B201" s="8"/>
       <c r="C201" s="40"/>
@@ -6121,7 +6124,7 @@
       <c r="H201" s="12"/>
       <c r="I201" s="12"/>
     </row>
-    <row r="202" spans="1:9" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="202" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A202" s="7"/>
       <c r="B202" s="8"/>
       <c r="C202" s="40"/>
@@ -6132,7 +6135,7 @@
       <c r="H202" s="12"/>
       <c r="I202" s="12"/>
     </row>
-    <row r="203" spans="1:9" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="203" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A203" s="7"/>
       <c r="B203" s="8"/>
       <c r="C203" s="40"/>
@@ -6143,7 +6146,7 @@
       <c r="H203" s="12"/>
       <c r="I203" s="12"/>
     </row>
-    <row r="204" spans="1:9" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="204" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A204" s="7"/>
       <c r="B204" s="8"/>
       <c r="C204" s="40"/>
@@ -6154,7 +6157,6 @@
       <c r="H204" s="12"/>
       <c r="I204" s="12"/>
     </row>
-    <row r="205" spans="1:9" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
@@ -6582,15 +6584,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x010100027709BF533FA442AFC4A8B2C0110727" ma:contentTypeVersion="15" ma:contentTypeDescription="Crear nuevo documento." ma:contentTypeScope="" ma:versionID="a37fc0d7c302f7619d355a49e1f175a4">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="3e53c16e-6636-411e-b1c4-e9eeb71b3b2a" xmlns:ns4="bda9c1ec-c4e2-44f9-929c-ca399fe36c88" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="01250a30c504a808427f15ccf149ee4d" ns3:_="" ns4:_="">
     <xsd:import namespace="3e53c16e-6636-411e-b1c4-e9eeb71b3b2a"/>
@@ -6823,6 +6816,15 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
@@ -6832,14 +6834,6 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3C8123E5-81FD-4C24-91F1-33BC079967E9}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4794C7E6-B89D-4081-9A67-B8D500EF1EE4}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -6858,6 +6852,14 @@
 </ds:datastoreItem>
 </file>
 
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3C8123E5-81FD-4C24-91F1-33BC079967E9}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D9861A25-610F-425F-BC6A-AC52D4971411}">
   <ds:schemaRefs>

--- a/data/bitacora.xlsx
+++ b/data/bitacora.xlsx
@@ -1,7 +1,7 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29910"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
@@ -1077,26 +1077,26 @@
     <t>PDCT73</t>
   </si>
   <si>
+    <t>TFLF99</t>
+  </si>
+  <si>
+    <t>TFLF98</t>
+  </si>
+  <si>
+    <t>TFHD90</t>
+  </si>
+  <si>
     <t>IMEI</t>
   </si>
   <si>
     <t>Revisado</t>
-  </si>
-  <si>
-    <t>TFLF99</t>
-  </si>
-  <si>
-    <t>TFLF98</t>
-  </si>
-  <si>
-    <t>TFHD90</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="3">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1985,21 +1985,21 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EDA66EBA-6B88-4C75-8217-0B7E221D898D}">
   <dimension ref="A1:L204"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.453125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="43" style="6" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="22.7265625" style="6" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.26953125" style="43" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="22.7109375" style="6" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.28515625" style="43" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="25" style="6" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="40.26953125" style="6" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="27.54296875" style="6" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="18.81640625" style="16" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="20.1796875" style="16" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="40.28515625" style="6" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="27.5703125" style="6" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="18.85546875" style="16" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="20.140625" style="16" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="79" style="6" bestFit="1" customWidth="1"/>
-    <col min="11" max="16384" width="11.453125" style="6"/>
+    <col min="11" max="16384" width="11.42578125" style="6"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:12" ht="14.45">
       <c r="A1" s="17" t="s">
         <v>0</v>
       </c>
@@ -2031,7 +2031,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:12" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:12" ht="14.45">
       <c r="A2" s="7" t="s">
         <v>10</v>
       </c>
@@ -2054,7 +2054,7 @@
       <c r="H2" s="12"/>
       <c r="I2" s="12"/>
     </row>
-    <row r="3" spans="1:12" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:12" ht="14.45">
       <c r="A3" s="7" t="s">
         <v>10</v>
       </c>
@@ -2077,7 +2077,7 @@
       <c r="H3" s="12"/>
       <c r="I3" s="12"/>
     </row>
-    <row r="4" spans="1:12" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:12" ht="14.45">
       <c r="A4" s="7" t="s">
         <v>10</v>
       </c>
@@ -2100,7 +2100,7 @@
       <c r="H4" s="12"/>
       <c r="I4" s="12"/>
     </row>
-    <row r="5" spans="1:12" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:12" ht="14.45">
       <c r="A5" s="7" t="s">
         <v>10</v>
       </c>
@@ -2123,7 +2123,7 @@
       <c r="H5" s="12"/>
       <c r="I5" s="12"/>
     </row>
-    <row r="6" spans="1:12" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:12" ht="14.45">
       <c r="A6" s="7" t="s">
         <v>10</v>
       </c>
@@ -2146,7 +2146,7 @@
       <c r="H6" s="12"/>
       <c r="I6" s="12"/>
     </row>
-    <row r="7" spans="1:12" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:12" ht="14.45">
       <c r="A7" s="7" t="s">
         <v>10</v>
       </c>
@@ -2169,7 +2169,7 @@
       <c r="H7" s="24"/>
       <c r="I7" s="24"/>
     </row>
-    <row r="8" spans="1:12" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:12" ht="14.45">
       <c r="A8" s="7" t="s">
         <v>10</v>
       </c>
@@ -2192,7 +2192,7 @@
       <c r="H8" s="24"/>
       <c r="I8" s="24"/>
     </row>
-    <row r="9" spans="1:12" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:12" ht="14.45">
       <c r="A9" s="7" t="s">
         <v>10</v>
       </c>
@@ -2215,7 +2215,7 @@
       <c r="H9" s="12"/>
       <c r="I9" s="12"/>
     </row>
-    <row r="10" spans="1:12" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:12" ht="14.45">
       <c r="A10" s="7" t="s">
         <v>10</v>
       </c>
@@ -2238,7 +2238,7 @@
       <c r="H10" s="12"/>
       <c r="I10" s="12"/>
     </row>
-    <row r="11" spans="1:12" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:12" ht="14.45">
       <c r="A11" s="7" t="s">
         <v>10</v>
       </c>
@@ -2261,7 +2261,7 @@
       <c r="H11" s="12"/>
       <c r="I11" s="12"/>
     </row>
-    <row r="12" spans="1:12" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:12" ht="14.45">
       <c r="A12" s="7" t="s">
         <v>33</v>
       </c>
@@ -2285,7 +2285,7 @@
       <c r="I12" s="12"/>
       <c r="L12" s="26"/>
     </row>
-    <row r="13" spans="1:12" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:12" ht="14.45">
       <c r="A13" s="7" t="s">
         <v>33</v>
       </c>
@@ -2308,7 +2308,7 @@
       <c r="H13" s="12"/>
       <c r="I13" s="12"/>
     </row>
-    <row r="14" spans="1:12" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:12" ht="14.45">
       <c r="A14" s="7" t="s">
         <v>33</v>
       </c>
@@ -2331,7 +2331,7 @@
       <c r="H14" s="12"/>
       <c r="I14" s="12"/>
     </row>
-    <row r="15" spans="1:12" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:12" ht="14.45">
       <c r="A15" s="7" t="s">
         <v>33</v>
       </c>
@@ -2354,7 +2354,7 @@
       <c r="H15" s="12"/>
       <c r="I15" s="12"/>
     </row>
-    <row r="16" spans="1:12" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:12" ht="14.45">
       <c r="A16" s="7" t="s">
         <v>33</v>
       </c>
@@ -2377,7 +2377,7 @@
       <c r="H16" s="12"/>
       <c r="I16" s="12"/>
     </row>
-    <row r="17" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:9" ht="14.45">
       <c r="A17" s="7" t="s">
         <v>33</v>
       </c>
@@ -2400,7 +2400,7 @@
       <c r="H17" s="12"/>
       <c r="I17" s="12"/>
     </row>
-    <row r="18" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:9" ht="14.45">
       <c r="A18" s="7" t="s">
         <v>33</v>
       </c>
@@ -2423,7 +2423,7 @@
       <c r="H18" s="12"/>
       <c r="I18" s="12"/>
     </row>
-    <row r="19" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:9" ht="14.45">
       <c r="A19" s="7" t="s">
         <v>33</v>
       </c>
@@ -2446,7 +2446,7 @@
       <c r="H19" s="12"/>
       <c r="I19" s="12"/>
     </row>
-    <row r="20" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:9" ht="14.45">
       <c r="A20" s="7" t="s">
         <v>51</v>
       </c>
@@ -2469,7 +2469,7 @@
       <c r="H20" s="12"/>
       <c r="I20" s="12"/>
     </row>
-    <row r="21" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:9" ht="14.45">
       <c r="A21" s="7" t="s">
         <v>51</v>
       </c>
@@ -2492,7 +2492,7 @@
       <c r="H21" s="12"/>
       <c r="I21" s="12"/>
     </row>
-    <row r="22" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:9" ht="14.45">
       <c r="A22" s="7" t="s">
         <v>51</v>
       </c>
@@ -2515,7 +2515,7 @@
       <c r="H22" s="12"/>
       <c r="I22" s="12"/>
     </row>
-    <row r="23" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:9" ht="14.45">
       <c r="A23" s="7" t="s">
         <v>59</v>
       </c>
@@ -2538,7 +2538,7 @@
       <c r="H23" s="12"/>
       <c r="I23" s="12"/>
     </row>
-    <row r="24" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:9" ht="14.45">
       <c r="A24" s="7" t="s">
         <v>59</v>
       </c>
@@ -2561,7 +2561,7 @@
       <c r="H24" s="12"/>
       <c r="I24" s="12"/>
     </row>
-    <row r="25" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:9" ht="14.45">
       <c r="A25" s="7" t="s">
         <v>65</v>
       </c>
@@ -2584,7 +2584,7 @@
       <c r="H25" s="12"/>
       <c r="I25" s="12"/>
     </row>
-    <row r="26" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:9" ht="14.45">
       <c r="A26" s="7" t="s">
         <v>65</v>
       </c>
@@ -2607,7 +2607,7 @@
       <c r="H26" s="12"/>
       <c r="I26" s="12"/>
     </row>
-    <row r="27" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:9" ht="14.45">
       <c r="A27" s="7" t="s">
         <v>65</v>
       </c>
@@ -2630,7 +2630,7 @@
       <c r="H27" s="12"/>
       <c r="I27" s="12"/>
     </row>
-    <row r="28" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:9" ht="14.45">
       <c r="A28" s="7" t="s">
         <v>65</v>
       </c>
@@ -2653,7 +2653,7 @@
       <c r="H28" s="12"/>
       <c r="I28" s="12"/>
     </row>
-    <row r="29" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:9" ht="14.45">
       <c r="A29" s="7" t="s">
         <v>65</v>
       </c>
@@ -2682,7 +2682,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="30" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:9" ht="14.45">
       <c r="A30" s="7" t="s">
         <v>80</v>
       </c>
@@ -2705,7 +2705,7 @@
       <c r="H30" s="12"/>
       <c r="I30" s="12"/>
     </row>
-    <row r="31" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:9" ht="14.45">
       <c r="A31" s="7" t="s">
         <v>80</v>
       </c>
@@ -2728,7 +2728,7 @@
       <c r="H31" s="12"/>
       <c r="I31" s="12"/>
     </row>
-    <row r="32" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:9" ht="14.45">
       <c r="A32" s="7" t="s">
         <v>80</v>
       </c>
@@ -2751,7 +2751,7 @@
       <c r="H32" s="12"/>
       <c r="I32" s="12"/>
     </row>
-    <row r="33" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:9" ht="14.45">
       <c r="A33" s="7" t="s">
         <v>80</v>
       </c>
@@ -2774,7 +2774,7 @@
       <c r="H33" s="12"/>
       <c r="I33" s="12"/>
     </row>
-    <row r="34" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:9" ht="14.45">
       <c r="A34" s="7" t="s">
         <v>80</v>
       </c>
@@ -2797,7 +2797,7 @@
       <c r="H34" s="12"/>
       <c r="I34" s="12"/>
     </row>
-    <row r="35" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:9" ht="14.45">
       <c r="A35" s="7" t="s">
         <v>80</v>
       </c>
@@ -2820,7 +2820,7 @@
       <c r="H35" s="12"/>
       <c r="I35" s="12"/>
     </row>
-    <row r="36" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:9" ht="14.45">
       <c r="A36" s="7" t="s">
         <v>80</v>
       </c>
@@ -2843,7 +2843,7 @@
       <c r="H36" s="12"/>
       <c r="I36" s="12"/>
     </row>
-    <row r="37" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:9" ht="14.45">
       <c r="A37" s="7" t="s">
         <v>95</v>
       </c>
@@ -2872,7 +2872,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="38" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:9" ht="14.45">
       <c r="A38" s="7" t="s">
         <v>95</v>
       </c>
@@ -2901,7 +2901,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="39" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:9" ht="14.45">
       <c r="A39" s="7" t="s">
         <v>95</v>
       </c>
@@ -2924,7 +2924,7 @@
       <c r="H39" s="12"/>
       <c r="I39" s="12"/>
     </row>
-    <row r="40" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:9" ht="14.45">
       <c r="A40" s="7" t="s">
         <v>95</v>
       </c>
@@ -2953,7 +2953,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="41" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:9" ht="14.45">
       <c r="A41" s="7" t="s">
         <v>95</v>
       </c>
@@ -2982,7 +2982,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="42" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:9" ht="14.45">
       <c r="A42" s="7" t="s">
         <v>95</v>
       </c>
@@ -3005,7 +3005,7 @@
       <c r="H42" s="12"/>
       <c r="I42" s="12"/>
     </row>
-    <row r="43" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:9" ht="14.45">
       <c r="A43" s="7" t="s">
         <v>95</v>
       </c>
@@ -3028,7 +3028,7 @@
       <c r="H43" s="12"/>
       <c r="I43" s="12"/>
     </row>
-    <row r="44" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:9" ht="14.45">
       <c r="A44" s="7" t="s">
         <v>95</v>
       </c>
@@ -3051,7 +3051,7 @@
       <c r="H44" s="12"/>
       <c r="I44" s="12"/>
     </row>
-    <row r="45" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:9" ht="14.45">
       <c r="A45" s="7" t="s">
         <v>95</v>
       </c>
@@ -3074,7 +3074,7 @@
       <c r="H45" s="12"/>
       <c r="I45" s="12"/>
     </row>
-    <row r="46" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:9" ht="14.45">
       <c r="A46" s="7" t="s">
         <v>95</v>
       </c>
@@ -3103,7 +3103,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="47" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:9" ht="14.45">
       <c r="A47" s="7" t="s">
         <v>95</v>
       </c>
@@ -3132,7 +3132,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="48" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:9" ht="14.45">
       <c r="A48" s="7" t="s">
         <v>95</v>
       </c>
@@ -3161,7 +3161,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="49" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:9" ht="14.45">
       <c r="A49" s="7" t="s">
         <v>95</v>
       </c>
@@ -3190,7 +3190,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="50" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:9" ht="14.45">
       <c r="A50" s="7" t="s">
         <v>95</v>
       </c>
@@ -3213,7 +3213,7 @@
       <c r="H50" s="12"/>
       <c r="I50" s="12"/>
     </row>
-    <row r="51" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:9" ht="14.45">
       <c r="A51" s="7" t="s">
         <v>95</v>
       </c>
@@ -3236,7 +3236,7 @@
       <c r="H51" s="12"/>
       <c r="I51" s="12"/>
     </row>
-    <row r="52" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:9" ht="14.45">
       <c r="A52" s="7" t="s">
         <v>95</v>
       </c>
@@ -3259,7 +3259,7 @@
       <c r="H52" s="12"/>
       <c r="I52" s="12"/>
     </row>
-    <row r="53" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:9" ht="14.45">
       <c r="A53" s="7" t="s">
         <v>95</v>
       </c>
@@ -3288,7 +3288,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="54" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:9" ht="14.45">
       <c r="A54" s="7" t="s">
         <v>95</v>
       </c>
@@ -3311,7 +3311,7 @@
       <c r="H54" s="12"/>
       <c r="I54" s="12"/>
     </row>
-    <row r="55" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:9" ht="14.45">
       <c r="A55" s="7" t="s">
         <v>95</v>
       </c>
@@ -3340,7 +3340,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="56" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:9" ht="14.45">
       <c r="A56" s="7" t="s">
         <v>95</v>
       </c>
@@ -3369,7 +3369,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="57" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:9" ht="14.45">
       <c r="A57" s="7" t="s">
         <v>95</v>
       </c>
@@ -3398,7 +3398,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="58" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:9" ht="14.45">
       <c r="A58" s="7" t="s">
         <v>95</v>
       </c>
@@ -3421,7 +3421,7 @@
       <c r="H58" s="12"/>
       <c r="I58" s="12"/>
     </row>
-    <row r="59" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:9" ht="14.45">
       <c r="A59" s="7" t="s">
         <v>95</v>
       </c>
@@ -3450,7 +3450,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="60" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:9" ht="14.45">
       <c r="A60" s="7" t="s">
         <v>95</v>
       </c>
@@ -3473,7 +3473,7 @@
       <c r="H60" s="12"/>
       <c r="I60" s="12"/>
     </row>
-    <row r="61" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:9" ht="14.45">
       <c r="A61" s="7" t="s">
         <v>95</v>
       </c>
@@ -3496,7 +3496,7 @@
       <c r="H61" s="12"/>
       <c r="I61" s="12"/>
     </row>
-    <row r="62" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:9" ht="14.45">
       <c r="A62" s="7" t="s">
         <v>149</v>
       </c>
@@ -3519,7 +3519,7 @@
       <c r="H62" s="12"/>
       <c r="I62" s="12"/>
     </row>
-    <row r="63" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:9" ht="14.45">
       <c r="A63" s="7" t="s">
         <v>149</v>
       </c>
@@ -3542,7 +3542,7 @@
       <c r="H63" s="12"/>
       <c r="I63" s="12"/>
     </row>
-    <row r="64" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:9" ht="14.45">
       <c r="A64" s="7" t="s">
         <v>149</v>
       </c>
@@ -3565,7 +3565,7 @@
       <c r="H64" s="12"/>
       <c r="I64" s="12"/>
     </row>
-    <row r="65" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:9" ht="14.45">
       <c r="A65" s="7" t="s">
         <v>149</v>
       </c>
@@ -3594,7 +3594,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="66" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:9" ht="14.45">
       <c r="A66" s="7" t="s">
         <v>149</v>
       </c>
@@ -3623,7 +3623,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="67" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:9" ht="14.45">
       <c r="A67" s="7" t="s">
         <v>149</v>
       </c>
@@ -3652,7 +3652,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="68" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:9" ht="14.45">
       <c r="A68" s="7" t="s">
         <v>149</v>
       </c>
@@ -3675,7 +3675,7 @@
       <c r="H68" s="12"/>
       <c r="I68" s="12"/>
     </row>
-    <row r="69" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:9" ht="14.45">
       <c r="A69" s="7" t="s">
         <v>149</v>
       </c>
@@ -3698,7 +3698,7 @@
       <c r="H69" s="12"/>
       <c r="I69" s="12"/>
     </row>
-    <row r="70" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:9" ht="14.45">
       <c r="A70" s="7" t="s">
         <v>149</v>
       </c>
@@ -3721,7 +3721,7 @@
       <c r="H70" s="12"/>
       <c r="I70" s="12"/>
     </row>
-    <row r="71" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:9" ht="14.45">
       <c r="A71" s="7" t="s">
         <v>149</v>
       </c>
@@ -3744,7 +3744,7 @@
       <c r="H71" s="12"/>
       <c r="I71" s="12"/>
     </row>
-    <row r="72" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:9" ht="14.45">
       <c r="A72" s="7" t="s">
         <v>149</v>
       </c>
@@ -3767,7 +3767,7 @@
       <c r="H72" s="12"/>
       <c r="I72" s="12"/>
     </row>
-    <row r="73" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:9" ht="14.45">
       <c r="A73" s="7" t="s">
         <v>172</v>
       </c>
@@ -3790,7 +3790,7 @@
       <c r="H73" s="12"/>
       <c r="I73" s="12"/>
     </row>
-    <row r="74" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:9" ht="14.45">
       <c r="A74" s="7" t="s">
         <v>172</v>
       </c>
@@ -3813,7 +3813,7 @@
       <c r="H74" s="12"/>
       <c r="I74" s="12"/>
     </row>
-    <row r="75" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:9" ht="14.45">
       <c r="A75" s="7" t="s">
         <v>177</v>
       </c>
@@ -3836,7 +3836,7 @@
       <c r="H75" s="12"/>
       <c r="I75" s="12"/>
     </row>
-    <row r="76" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:9" ht="14.45">
       <c r="A76" s="7" t="s">
         <v>177</v>
       </c>
@@ -3859,7 +3859,7 @@
       <c r="H76" s="12"/>
       <c r="I76" s="12"/>
     </row>
-    <row r="77" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:9" ht="14.45">
       <c r="A77" s="7" t="s">
         <v>177</v>
       </c>
@@ -3882,7 +3882,7 @@
       <c r="H77" s="12"/>
       <c r="I77" s="12"/>
     </row>
-    <row r="78" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:9" ht="14.45">
       <c r="A78" s="7" t="s">
         <v>177</v>
       </c>
@@ -3905,7 +3905,7 @@
       <c r="H78" s="12"/>
       <c r="I78" s="12"/>
     </row>
-    <row r="79" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:9" ht="14.45">
       <c r="A79" s="7" t="s">
         <v>177</v>
       </c>
@@ -3928,7 +3928,7 @@
       <c r="H79" s="12"/>
       <c r="I79" s="12"/>
     </row>
-    <row r="80" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:9" ht="14.45">
       <c r="A80" s="7" t="s">
         <v>177</v>
       </c>
@@ -3951,7 +3951,7 @@
       <c r="H80" s="12"/>
       <c r="I80" s="12"/>
     </row>
-    <row r="81" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:9" ht="14.45">
       <c r="A81" s="7" t="s">
         <v>177</v>
       </c>
@@ -3974,7 +3974,7 @@
       <c r="H81" s="12"/>
       <c r="I81" s="12"/>
     </row>
-    <row r="82" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="82" spans="1:9" ht="14.45">
       <c r="A82" s="7" t="s">
         <v>177</v>
       </c>
@@ -3997,7 +3997,7 @@
       <c r="H82" s="12"/>
       <c r="I82" s="12"/>
     </row>
-    <row r="83" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:9" ht="14.45">
       <c r="A83" s="7" t="s">
         <v>177</v>
       </c>
@@ -4020,7 +4020,7 @@
       <c r="H83" s="12"/>
       <c r="I83" s="12"/>
     </row>
-    <row r="84" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="84" spans="1:9" ht="14.45">
       <c r="A84" s="7" t="s">
         <v>177</v>
       </c>
@@ -4043,7 +4043,7 @@
       <c r="H84" s="12"/>
       <c r="I84" s="12"/>
     </row>
-    <row r="85" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="85" spans="1:9" ht="14.45">
       <c r="A85" s="7" t="s">
         <v>177</v>
       </c>
@@ -4066,7 +4066,7 @@
       <c r="H85" s="12"/>
       <c r="I85" s="12"/>
     </row>
-    <row r="86" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="86" spans="1:9" ht="14.45">
       <c r="A86" s="7" t="s">
         <v>177</v>
       </c>
@@ -4089,7 +4089,7 @@
       <c r="H86" s="12"/>
       <c r="I86" s="12"/>
     </row>
-    <row r="87" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="87" spans="1:9" ht="14.45">
       <c r="A87" s="7" t="s">
         <v>177</v>
       </c>
@@ -4112,7 +4112,7 @@
       <c r="H87" s="12"/>
       <c r="I87" s="12"/>
     </row>
-    <row r="88" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="88" spans="1:9" ht="14.45">
       <c r="A88" s="7" t="s">
         <v>177</v>
       </c>
@@ -4135,7 +4135,7 @@
       <c r="H88" s="12"/>
       <c r="I88" s="12"/>
     </row>
-    <row r="89" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="89" spans="1:9" ht="14.45">
       <c r="A89" s="7" t="s">
         <v>177</v>
       </c>
@@ -4158,7 +4158,7 @@
       <c r="H89" s="12"/>
       <c r="I89" s="12"/>
     </row>
-    <row r="90" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="90" spans="1:9" ht="14.45">
       <c r="A90" s="7" t="s">
         <v>177</v>
       </c>
@@ -4181,7 +4181,7 @@
       <c r="H90" s="12"/>
       <c r="I90" s="12"/>
     </row>
-    <row r="91" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="91" spans="1:9" ht="14.45">
       <c r="A91" s="7" t="s">
         <v>210</v>
       </c>
@@ -4204,7 +4204,7 @@
       <c r="H91" s="12"/>
       <c r="I91" s="12"/>
     </row>
-    <row r="92" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="92" spans="1:9" ht="14.45">
       <c r="A92" s="7" t="s">
         <v>210</v>
       </c>
@@ -4227,7 +4227,7 @@
       <c r="H92" s="12"/>
       <c r="I92" s="12"/>
     </row>
-    <row r="93" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="93" spans="1:9" ht="14.45">
       <c r="A93" s="7" t="s">
         <v>210</v>
       </c>
@@ -4250,7 +4250,7 @@
       <c r="H93" s="12"/>
       <c r="I93" s="12"/>
     </row>
-    <row r="94" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="94" spans="1:9" ht="14.45">
       <c r="A94" s="7" t="s">
         <v>217</v>
       </c>
@@ -4279,7 +4279,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="95" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="95" spans="1:9" ht="14.45">
       <c r="A95" s="7" t="s">
         <v>217</v>
       </c>
@@ -4302,7 +4302,7 @@
       <c r="H95" s="12"/>
       <c r="I95" s="12"/>
     </row>
-    <row r="96" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="96" spans="1:9" ht="14.45">
       <c r="A96" s="7" t="s">
         <v>217</v>
       </c>
@@ -4325,7 +4325,7 @@
       <c r="H96" s="12"/>
       <c r="I96" s="12"/>
     </row>
-    <row r="97" spans="1:10" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="97" spans="1:10" ht="14.45">
       <c r="A97" s="7" t="s">
         <v>217</v>
       </c>
@@ -4348,7 +4348,7 @@
       <c r="H97" s="12"/>
       <c r="I97" s="12"/>
     </row>
-    <row r="98" spans="1:10" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="98" spans="1:10" ht="14.45">
       <c r="A98" s="7" t="s">
         <v>225</v>
       </c>
@@ -4377,7 +4377,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="99" spans="1:10" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="99" spans="1:10" ht="14.45">
       <c r="A99" s="7" t="s">
         <v>225</v>
       </c>
@@ -4400,7 +4400,7 @@
       <c r="H99" s="12"/>
       <c r="I99" s="12"/>
     </row>
-    <row r="100" spans="1:10" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="100" spans="1:10" ht="14.45">
       <c r="A100" s="7" t="s">
         <v>231</v>
       </c>
@@ -4423,7 +4423,7 @@
       <c r="H100" s="12"/>
       <c r="I100" s="12"/>
     </row>
-    <row r="101" spans="1:10" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="101" spans="1:10" ht="14.45">
       <c r="A101" s="7" t="s">
         <v>231</v>
       </c>
@@ -4449,7 +4449,7 @@
         <v>237</v>
       </c>
     </row>
-    <row r="102" spans="1:10" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="102" spans="1:10" ht="14.45">
       <c r="A102" s="7" t="s">
         <v>238</v>
       </c>
@@ -4472,7 +4472,7 @@
       <c r="H102" s="12"/>
       <c r="I102" s="12"/>
     </row>
-    <row r="103" spans="1:10" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="103" spans="1:10" ht="14.45">
       <c r="A103" s="7" t="s">
         <v>238</v>
       </c>
@@ -4495,7 +4495,7 @@
       <c r="H103" s="12"/>
       <c r="I103" s="12"/>
     </row>
-    <row r="104" spans="1:10" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="104" spans="1:10" ht="14.45">
       <c r="A104" s="7" t="s">
         <v>238</v>
       </c>
@@ -4518,7 +4518,7 @@
       <c r="H104" s="12"/>
       <c r="I104" s="12"/>
     </row>
-    <row r="105" spans="1:10" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="105" spans="1:10" ht="14.45">
       <c r="A105" s="7" t="s">
         <v>238</v>
       </c>
@@ -4541,7 +4541,7 @@
       <c r="H105" s="12"/>
       <c r="I105" s="12"/>
     </row>
-    <row r="106" spans="1:10" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="106" spans="1:10" ht="14.45">
       <c r="A106" s="7" t="s">
         <v>238</v>
       </c>
@@ -4564,7 +4564,7 @@
       <c r="H106" s="12"/>
       <c r="I106" s="12"/>
     </row>
-    <row r="107" spans="1:10" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="107" spans="1:10" ht="14.45">
       <c r="A107" s="7" t="s">
         <v>238</v>
       </c>
@@ -4587,7 +4587,7 @@
       <c r="H107" s="12"/>
       <c r="I107" s="12"/>
     </row>
-    <row r="108" spans="1:10" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="108" spans="1:10" ht="14.45">
       <c r="A108" s="7" t="s">
         <v>238</v>
       </c>
@@ -4610,7 +4610,7 @@
       <c r="H108" s="12"/>
       <c r="I108" s="12"/>
     </row>
-    <row r="109" spans="1:10" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="109" spans="1:10" ht="14.45">
       <c r="A109" s="7" t="s">
         <v>238</v>
       </c>
@@ -4633,7 +4633,7 @@
       <c r="H109" s="12"/>
       <c r="I109" s="12"/>
     </row>
-    <row r="110" spans="1:10" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="110" spans="1:10" ht="14.45">
       <c r="A110" s="7" t="s">
         <v>238</v>
       </c>
@@ -4656,7 +4656,7 @@
       <c r="H110" s="12"/>
       <c r="I110" s="12"/>
     </row>
-    <row r="111" spans="1:10" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="111" spans="1:10" ht="14.45">
       <c r="A111" s="7" t="s">
         <v>238</v>
       </c>
@@ -4679,7 +4679,7 @@
       <c r="H111" s="12"/>
       <c r="I111" s="12"/>
     </row>
-    <row r="112" spans="1:10" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="112" spans="1:10" ht="14.45">
       <c r="A112" s="7" t="s">
         <v>238</v>
       </c>
@@ -4702,7 +4702,7 @@
       <c r="H112" s="12"/>
       <c r="I112" s="12"/>
     </row>
-    <row r="113" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="113" spans="1:9" ht="14.45">
       <c r="A113" s="7" t="s">
         <v>238</v>
       </c>
@@ -4725,7 +4725,7 @@
       <c r="H113" s="12"/>
       <c r="I113" s="12"/>
     </row>
-    <row r="114" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="114" spans="1:9" ht="14.45">
       <c r="A114" s="7" t="s">
         <v>238</v>
       </c>
@@ -4748,7 +4748,7 @@
       <c r="H114" s="12"/>
       <c r="I114" s="12"/>
     </row>
-    <row r="115" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="115" spans="1:9" ht="14.45">
       <c r="A115" s="7" t="s">
         <v>238</v>
       </c>
@@ -4771,7 +4771,7 @@
       <c r="H115" s="12"/>
       <c r="I115" s="12"/>
     </row>
-    <row r="116" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="116" spans="1:9" ht="14.45">
       <c r="A116" s="7" t="s">
         <v>238</v>
       </c>
@@ -4794,7 +4794,7 @@
       <c r="H116" s="12"/>
       <c r="I116" s="12"/>
     </row>
-    <row r="117" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="117" spans="1:9" ht="14.45">
       <c r="A117" s="7" t="s">
         <v>238</v>
       </c>
@@ -4817,7 +4817,7 @@
       <c r="H117" s="12"/>
       <c r="I117" s="12"/>
     </row>
-    <row r="118" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="118" spans="1:9" ht="14.45">
       <c r="A118" s="7" t="s">
         <v>238</v>
       </c>
@@ -4840,7 +4840,7 @@
       <c r="H118" s="12"/>
       <c r="I118" s="12"/>
     </row>
-    <row r="119" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="119" spans="1:9" ht="14.45">
       <c r="A119" s="7" t="s">
         <v>238</v>
       </c>
@@ -4863,7 +4863,7 @@
       <c r="H119" s="12"/>
       <c r="I119" s="12"/>
     </row>
-    <row r="120" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="120" spans="1:9" ht="14.45">
       <c r="A120" s="7" t="s">
         <v>276</v>
       </c>
@@ -4886,7 +4886,7 @@
       <c r="H120" s="12"/>
       <c r="I120" s="12"/>
     </row>
-    <row r="121" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="121" spans="1:9" ht="14.45">
       <c r="A121" s="7" t="s">
         <v>276</v>
       </c>
@@ -4909,7 +4909,7 @@
       <c r="H121" s="12"/>
       <c r="I121" s="12"/>
     </row>
-    <row r="122" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="122" spans="1:9" ht="14.45">
       <c r="A122" s="7" t="s">
         <v>276</v>
       </c>
@@ -4932,7 +4932,7 @@
       <c r="H122" s="12"/>
       <c r="I122" s="12"/>
     </row>
-    <row r="123" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="123" spans="1:9" ht="14.45">
       <c r="A123" s="7" t="s">
         <v>284</v>
       </c>
@@ -4955,7 +4955,7 @@
       <c r="H123" s="12"/>
       <c r="I123" s="12"/>
     </row>
-    <row r="124" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="124" spans="1:9" ht="14.45">
       <c r="A124" s="7" t="s">
         <v>287</v>
       </c>
@@ -4978,7 +4978,7 @@
       <c r="H124" s="12"/>
       <c r="I124" s="12"/>
     </row>
-    <row r="125" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="125" spans="1:9" ht="14.45">
       <c r="A125" s="7" t="s">
         <v>287</v>
       </c>
@@ -5001,7 +5001,7 @@
       <c r="H125" s="12"/>
       <c r="I125" s="12"/>
     </row>
-    <row r="126" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="126" spans="1:9" ht="14.45">
       <c r="A126" s="7" t="s">
         <v>287</v>
       </c>
@@ -5024,7 +5024,7 @@
       <c r="H126" s="15"/>
       <c r="I126" s="15"/>
     </row>
-    <row r="127" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="127" spans="1:9" ht="14.45">
       <c r="A127" s="7" t="s">
         <v>294</v>
       </c>
@@ -5047,7 +5047,7 @@
       <c r="H127" s="12"/>
       <c r="I127" s="12"/>
     </row>
-    <row r="128" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="128" spans="1:9" ht="14.45">
       <c r="A128" t="s">
         <v>297</v>
       </c>
@@ -5074,7 +5074,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="129" spans="1:10" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="129" spans="1:10" ht="14.45">
       <c r="A129" t="s">
         <v>297</v>
       </c>
@@ -5099,7 +5099,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="130" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="130" spans="1:10" ht="15" customHeight="1">
       <c r="A130" s="33" t="s">
         <v>303</v>
       </c>
@@ -5124,7 +5124,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="131" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="131" spans="1:10" ht="15" customHeight="1">
       <c r="A131" s="33" t="s">
         <v>307</v>
       </c>
@@ -5149,7 +5149,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="132" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="132" spans="1:10" ht="15" customHeight="1">
       <c r="A132" s="33" t="s">
         <v>65</v>
       </c>
@@ -5174,7 +5174,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="133" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="133" spans="1:10" ht="15" customHeight="1">
       <c r="A133" s="33" t="s">
         <v>313</v>
       </c>
@@ -5199,7 +5199,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="134" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="134" spans="1:10" ht="15" customHeight="1">
       <c r="A134" s="33" t="s">
         <v>313</v>
       </c>
@@ -5224,7 +5224,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="135" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="135" spans="1:10" ht="15" customHeight="1">
       <c r="A135" s="33" t="s">
         <v>276</v>
       </c>
@@ -5249,7 +5249,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="136" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="136" spans="1:10" ht="15" customHeight="1">
       <c r="A136" s="33" t="s">
         <v>320</v>
       </c>
@@ -5275,7 +5275,7 @@
       </c>
       <c r="J136" s="38"/>
     </row>
-    <row r="137" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="137" spans="1:10" ht="15" customHeight="1">
       <c r="A137" s="33" t="s">
         <v>324</v>
       </c>
@@ -5301,7 +5301,7 @@
       </c>
       <c r="J137" s="38"/>
     </row>
-    <row r="138" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="138" spans="1:10" ht="15" customHeight="1">
       <c r="A138" s="7" t="s">
         <v>329</v>
       </c>
@@ -5325,7 +5325,7 @@
       </c>
       <c r="J138" s="37"/>
     </row>
-    <row r="139" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="139" spans="1:10" ht="15" customHeight="1">
       <c r="A139" s="7" t="s">
         <v>329</v>
       </c>
@@ -5349,7 +5349,7 @@
       </c>
       <c r="J139" s="38"/>
     </row>
-    <row r="140" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="140" spans="1:10" ht="15" customHeight="1">
       <c r="A140" s="7" t="s">
         <v>329</v>
       </c>
@@ -5373,7 +5373,7 @@
       </c>
       <c r="J140" s="38"/>
     </row>
-    <row r="141" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="141" spans="1:10" ht="15" customHeight="1">
       <c r="A141" s="33" t="s">
         <v>333</v>
       </c>
@@ -5399,7 +5399,7 @@
       </c>
       <c r="J141" s="38"/>
     </row>
-    <row r="142" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="142" spans="1:10" ht="15" customHeight="1">
       <c r="A142" s="33" t="s">
         <v>313</v>
       </c>
@@ -5424,7 +5424,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="143" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="143" spans="1:10" ht="15" customHeight="1">
       <c r="A143" s="7" t="s">
         <v>336</v>
       </c>
@@ -5449,7 +5449,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="144" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="144" spans="1:10" ht="15" customHeight="1">
       <c r="A144" s="33" t="s">
         <v>339</v>
       </c>
@@ -5474,7 +5474,7 @@
         <v>342</v>
       </c>
     </row>
-    <row r="145" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="145" spans="1:10" ht="15" customHeight="1">
       <c r="A145" s="7" t="s">
         <v>65</v>
       </c>
@@ -5499,11 +5499,11 @@
         <v>79</v>
       </c>
     </row>
-    <row r="146" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="146" spans="1:10" ht="15" customHeight="1">
       <c r="A146" s="7"/>
       <c r="B146" s="8"/>
       <c r="C146" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="D146" s="9"/>
       <c r="E146" s="8"/>
@@ -5515,11 +5515,11 @@
         <v>863457051708251</v>
       </c>
     </row>
-    <row r="147" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="147" spans="1:10" ht="15" customHeight="1">
       <c r="A147" s="7"/>
       <c r="B147" s="8"/>
       <c r="C147" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="D147" s="9"/>
       <c r="E147" s="8"/>
@@ -5528,11 +5528,11 @@
       <c r="H147" s="12"/>
       <c r="I147" s="12"/>
     </row>
-    <row r="148" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="148" spans="1:10" ht="15" customHeight="1">
       <c r="A148" s="7"/>
       <c r="B148" s="8"/>
       <c r="C148" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="D148" s="9"/>
       <c r="E148" s="8"/>
@@ -5541,7 +5541,7 @@
       <c r="H148" s="12"/>
       <c r="I148" s="12"/>
     </row>
-    <row r="149" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="149" spans="1:10" ht="15" customHeight="1">
       <c r="A149" s="7"/>
       <c r="B149" s="8"/>
       <c r="C149" s="40"/>
@@ -5552,7 +5552,7 @@
       <c r="H149" s="12"/>
       <c r="I149" s="12"/>
     </row>
-    <row r="150" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="150" spans="1:10" ht="15" customHeight="1">
       <c r="A150" s="7"/>
       <c r="B150" s="8"/>
       <c r="C150" s="40"/>
@@ -5563,7 +5563,7 @@
       <c r="H150" s="12"/>
       <c r="I150" s="12"/>
     </row>
-    <row r="151" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="151" spans="1:10" ht="15" customHeight="1">
       <c r="A151" s="7"/>
       <c r="B151" s="8"/>
       <c r="C151" s="40"/>
@@ -5574,7 +5574,7 @@
       <c r="H151" s="12"/>
       <c r="I151" s="12"/>
     </row>
-    <row r="152" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="152" spans="1:10" ht="15" customHeight="1">
       <c r="A152" s="7"/>
       <c r="B152" s="8"/>
       <c r="C152" s="40"/>
@@ -5585,7 +5585,7 @@
       <c r="H152" s="12"/>
       <c r="I152" s="12"/>
     </row>
-    <row r="153" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="153" spans="1:10" ht="15" customHeight="1">
       <c r="A153" s="7"/>
       <c r="B153" s="8"/>
       <c r="C153" s="40"/>
@@ -5596,7 +5596,7 @@
       <c r="H153" s="12"/>
       <c r="I153" s="12"/>
     </row>
-    <row r="154" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="154" spans="1:10" ht="15" customHeight="1">
       <c r="A154" s="7"/>
       <c r="B154" s="8"/>
       <c r="C154" s="40"/>
@@ -5607,7 +5607,7 @@
       <c r="H154" s="12"/>
       <c r="I154" s="12"/>
     </row>
-    <row r="155" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="155" spans="1:10" ht="15" customHeight="1">
       <c r="A155" s="7"/>
       <c r="B155" s="8"/>
       <c r="C155" s="40"/>
@@ -5618,7 +5618,7 @@
       <c r="H155" s="12"/>
       <c r="I155" s="12"/>
     </row>
-    <row r="156" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="156" spans="1:10" ht="15" customHeight="1">
       <c r="A156" s="7"/>
       <c r="B156" s="8"/>
       <c r="C156" s="40"/>
@@ -5629,7 +5629,7 @@
       <c r="H156" s="12"/>
       <c r="I156" s="12"/>
     </row>
-    <row r="157" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="157" spans="1:10" ht="15" customHeight="1">
       <c r="A157" s="7"/>
       <c r="B157" s="8"/>
       <c r="C157" s="40"/>
@@ -5640,7 +5640,7 @@
       <c r="H157" s="12"/>
       <c r="I157" s="12"/>
     </row>
-    <row r="158" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="158" spans="1:10" ht="15" customHeight="1">
       <c r="A158" s="7"/>
       <c r="B158" s="8"/>
       <c r="C158" s="40"/>
@@ -5651,7 +5651,7 @@
       <c r="H158" s="12"/>
       <c r="I158" s="12"/>
     </row>
-    <row r="159" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="159" spans="1:10" ht="15" customHeight="1">
       <c r="A159" s="7"/>
       <c r="B159" s="8"/>
       <c r="C159" s="40"/>
@@ -5662,7 +5662,7 @@
       <c r="H159" s="12"/>
       <c r="I159" s="12"/>
     </row>
-    <row r="160" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="160" spans="1:10" ht="15" customHeight="1">
       <c r="A160" s="7"/>
       <c r="B160" s="8"/>
       <c r="C160" s="40"/>
@@ -5673,7 +5673,7 @@
       <c r="H160" s="12"/>
       <c r="I160" s="12"/>
     </row>
-    <row r="161" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="161" spans="1:9" ht="15" customHeight="1">
       <c r="A161" s="7"/>
       <c r="B161" s="8"/>
       <c r="C161" s="40"/>
@@ -5684,7 +5684,7 @@
       <c r="H161" s="12"/>
       <c r="I161" s="12"/>
     </row>
-    <row r="162" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="162" spans="1:9" ht="15" customHeight="1">
       <c r="A162" s="7"/>
       <c r="B162" s="8"/>
       <c r="C162" s="40"/>
@@ -5695,7 +5695,7 @@
       <c r="H162" s="12"/>
       <c r="I162" s="12"/>
     </row>
-    <row r="163" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="163" spans="1:9" ht="15" customHeight="1">
       <c r="A163" s="7"/>
       <c r="B163" s="8"/>
       <c r="C163" s="40"/>
@@ -5706,7 +5706,7 @@
       <c r="H163" s="12"/>
       <c r="I163" s="12"/>
     </row>
-    <row r="164" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="164" spans="1:9" ht="15" customHeight="1">
       <c r="A164" s="7"/>
       <c r="B164" s="8"/>
       <c r="C164" s="40"/>
@@ -5717,7 +5717,7 @@
       <c r="H164" s="12"/>
       <c r="I164" s="12"/>
     </row>
-    <row r="165" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="165" spans="1:9" ht="15" customHeight="1">
       <c r="A165" s="7"/>
       <c r="B165" s="8"/>
       <c r="C165" s="40"/>
@@ -5728,7 +5728,7 @@
       <c r="H165" s="12"/>
       <c r="I165" s="12"/>
     </row>
-    <row r="166" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="166" spans="1:9" ht="15" customHeight="1">
       <c r="A166" s="7"/>
       <c r="B166" s="8"/>
       <c r="C166" s="40"/>
@@ -5739,7 +5739,7 @@
       <c r="H166" s="12"/>
       <c r="I166" s="12"/>
     </row>
-    <row r="167" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="167" spans="1:9" ht="15" customHeight="1">
       <c r="A167" s="7"/>
       <c r="B167" s="8"/>
       <c r="C167" s="40"/>
@@ -5750,7 +5750,7 @@
       <c r="H167" s="12"/>
       <c r="I167" s="12"/>
     </row>
-    <row r="168" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="168" spans="1:9" ht="15" customHeight="1">
       <c r="A168" s="7"/>
       <c r="B168" s="8"/>
       <c r="C168" s="40"/>
@@ -5761,7 +5761,7 @@
       <c r="H168" s="12"/>
       <c r="I168" s="12"/>
     </row>
-    <row r="169" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="169" spans="1:9" ht="15" customHeight="1">
       <c r="A169" s="7"/>
       <c r="B169" s="8"/>
       <c r="C169" s="40"/>
@@ -5772,7 +5772,7 @@
       <c r="H169" s="12"/>
       <c r="I169" s="12"/>
     </row>
-    <row r="170" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="170" spans="1:9" ht="15" customHeight="1">
       <c r="A170" s="7"/>
       <c r="B170" s="8"/>
       <c r="C170" s="40"/>
@@ -5783,7 +5783,7 @@
       <c r="H170" s="12"/>
       <c r="I170" s="12"/>
     </row>
-    <row r="171" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="171" spans="1:9" ht="15" customHeight="1">
       <c r="A171" s="7"/>
       <c r="B171" s="8"/>
       <c r="C171" s="40"/>
@@ -5794,7 +5794,7 @@
       <c r="H171" s="12"/>
       <c r="I171" s="12"/>
     </row>
-    <row r="172" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="172" spans="1:9" ht="15" customHeight="1">
       <c r="A172" s="7"/>
       <c r="B172" s="8"/>
       <c r="C172" s="40"/>
@@ -5805,7 +5805,7 @@
       <c r="H172" s="12"/>
       <c r="I172" s="12"/>
     </row>
-    <row r="173" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="173" spans="1:9" ht="15" customHeight="1">
       <c r="A173" s="7"/>
       <c r="B173" s="8"/>
       <c r="C173" s="40"/>
@@ -5816,7 +5816,7 @@
       <c r="H173" s="12"/>
       <c r="I173" s="12"/>
     </row>
-    <row r="174" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="174" spans="1:9" ht="15" customHeight="1">
       <c r="A174" s="7"/>
       <c r="B174" s="8"/>
       <c r="C174" s="40"/>
@@ -5827,7 +5827,7 @@
       <c r="H174" s="12"/>
       <c r="I174" s="12"/>
     </row>
-    <row r="175" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="175" spans="1:9" ht="15" customHeight="1">
       <c r="A175" s="7"/>
       <c r="B175" s="8"/>
       <c r="C175" s="40"/>
@@ -5838,7 +5838,7 @@
       <c r="H175" s="12"/>
       <c r="I175" s="12"/>
     </row>
-    <row r="176" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="176" spans="1:9" ht="15" customHeight="1">
       <c r="A176" s="7"/>
       <c r="B176" s="8"/>
       <c r="C176" s="40"/>
@@ -5849,7 +5849,7 @@
       <c r="H176" s="12"/>
       <c r="I176" s="12"/>
     </row>
-    <row r="177" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="177" spans="1:9" ht="15" customHeight="1">
       <c r="A177" s="7"/>
       <c r="B177" s="8"/>
       <c r="C177" s="40"/>
@@ -5860,7 +5860,7 @@
       <c r="H177" s="12"/>
       <c r="I177" s="12"/>
     </row>
-    <row r="178" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="178" spans="1:9" ht="15" customHeight="1">
       <c r="A178" s="7"/>
       <c r="B178" s="8"/>
       <c r="C178" s="40"/>
@@ -5871,7 +5871,7 @@
       <c r="H178" s="12"/>
       <c r="I178" s="12"/>
     </row>
-    <row r="179" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="179" spans="1:9" ht="15" customHeight="1">
       <c r="A179" s="7"/>
       <c r="B179" s="8"/>
       <c r="C179" s="40"/>
@@ -5882,7 +5882,7 @@
       <c r="H179" s="12"/>
       <c r="I179" s="12"/>
     </row>
-    <row r="180" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="180" spans="1:9" ht="15" customHeight="1">
       <c r="A180" s="7"/>
       <c r="B180" s="8"/>
       <c r="C180" s="40"/>
@@ -5893,7 +5893,7 @@
       <c r="H180" s="12"/>
       <c r="I180" s="12"/>
     </row>
-    <row r="181" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="181" spans="1:9" ht="15" customHeight="1">
       <c r="A181" s="7"/>
       <c r="B181" s="8"/>
       <c r="C181" s="40"/>
@@ -5904,7 +5904,7 @@
       <c r="H181" s="12"/>
       <c r="I181" s="12"/>
     </row>
-    <row r="182" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="182" spans="1:9" ht="15" customHeight="1">
       <c r="A182" s="7"/>
       <c r="B182" s="8"/>
       <c r="C182" s="40"/>
@@ -5915,7 +5915,7 @@
       <c r="H182" s="12"/>
       <c r="I182" s="12"/>
     </row>
-    <row r="183" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="183" spans="1:9" ht="15" customHeight="1">
       <c r="A183" s="7"/>
       <c r="B183" s="8"/>
       <c r="C183" s="40"/>
@@ -5926,7 +5926,7 @@
       <c r="H183" s="12"/>
       <c r="I183" s="12"/>
     </row>
-    <row r="184" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="184" spans="1:9" ht="15" customHeight="1">
       <c r="A184" s="7"/>
       <c r="B184" s="8"/>
       <c r="C184" s="40"/>
@@ -5937,7 +5937,7 @@
       <c r="H184" s="12"/>
       <c r="I184" s="12"/>
     </row>
-    <row r="185" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="185" spans="1:9" ht="15" customHeight="1">
       <c r="A185" s="7"/>
       <c r="B185" s="8"/>
       <c r="C185" s="40"/>
@@ -5948,7 +5948,7 @@
       <c r="H185" s="12"/>
       <c r="I185" s="12"/>
     </row>
-    <row r="186" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="186" spans="1:9" ht="15" customHeight="1">
       <c r="A186" s="7"/>
       <c r="B186" s="8"/>
       <c r="C186" s="40"/>
@@ -5959,7 +5959,7 @@
       <c r="H186" s="12"/>
       <c r="I186" s="12"/>
     </row>
-    <row r="187" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="187" spans="1:9" ht="15" customHeight="1">
       <c r="A187" s="7"/>
       <c r="B187" s="8"/>
       <c r="C187" s="40"/>
@@ -5970,7 +5970,7 @@
       <c r="H187" s="12"/>
       <c r="I187" s="12"/>
     </row>
-    <row r="188" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="188" spans="1:9" ht="15" customHeight="1">
       <c r="A188" s="7"/>
       <c r="B188" s="8"/>
       <c r="C188" s="40"/>
@@ -5981,7 +5981,7 @@
       <c r="H188" s="12"/>
       <c r="I188" s="12"/>
     </row>
-    <row r="189" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="189" spans="1:9" ht="15" customHeight="1">
       <c r="A189" s="7"/>
       <c r="B189" s="8"/>
       <c r="C189" s="40"/>
@@ -5992,7 +5992,7 @@
       <c r="H189" s="12"/>
       <c r="I189" s="12"/>
     </row>
-    <row r="190" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="190" spans="1:9" ht="15" customHeight="1">
       <c r="A190" s="7"/>
       <c r="B190" s="8"/>
       <c r="C190" s="40"/>
@@ -6003,7 +6003,7 @@
       <c r="H190" s="12"/>
       <c r="I190" s="12"/>
     </row>
-    <row r="191" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="191" spans="1:9" ht="15" customHeight="1">
       <c r="A191" s="7"/>
       <c r="B191" s="8"/>
       <c r="C191" s="40"/>
@@ -6014,7 +6014,7 @@
       <c r="H191" s="12"/>
       <c r="I191" s="12"/>
     </row>
-    <row r="192" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="192" spans="1:9" ht="15" customHeight="1">
       <c r="A192" s="7"/>
       <c r="B192" s="8"/>
       <c r="C192" s="40"/>
@@ -6025,7 +6025,7 @@
       <c r="H192" s="12"/>
       <c r="I192" s="12"/>
     </row>
-    <row r="193" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="193" spans="1:9" ht="15" customHeight="1">
       <c r="A193" s="7"/>
       <c r="B193" s="8"/>
       <c r="C193" s="40"/>
@@ -6036,7 +6036,7 @@
       <c r="H193" s="12"/>
       <c r="I193" s="12"/>
     </row>
-    <row r="194" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="194" spans="1:9" ht="15" customHeight="1">
       <c r="A194" s="7"/>
       <c r="B194" s="8"/>
       <c r="C194" s="40"/>
@@ -6047,7 +6047,7 @@
       <c r="H194" s="12"/>
       <c r="I194" s="12"/>
     </row>
-    <row r="195" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="195" spans="1:9" ht="15" customHeight="1">
       <c r="A195" s="7"/>
       <c r="B195" s="8"/>
       <c r="C195" s="40"/>
@@ -6058,7 +6058,7 @@
       <c r="H195" s="12"/>
       <c r="I195" s="12"/>
     </row>
-    <row r="196" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="196" spans="1:9" ht="15" customHeight="1">
       <c r="A196" s="7"/>
       <c r="B196" s="8"/>
       <c r="C196" s="40"/>
@@ -6069,7 +6069,7 @@
       <c r="H196" s="12"/>
       <c r="I196" s="12"/>
     </row>
-    <row r="197" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="197" spans="1:9" ht="15" customHeight="1">
       <c r="A197" s="7"/>
       <c r="B197" s="8"/>
       <c r="C197" s="40"/>
@@ -6080,7 +6080,7 @@
       <c r="H197" s="12"/>
       <c r="I197" s="12"/>
     </row>
-    <row r="198" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="198" spans="1:9" ht="15" customHeight="1">
       <c r="A198" s="7"/>
       <c r="B198" s="8"/>
       <c r="C198" s="40"/>
@@ -6091,7 +6091,7 @@
       <c r="H198" s="12"/>
       <c r="I198" s="12"/>
     </row>
-    <row r="199" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="199" spans="1:9" ht="15" customHeight="1">
       <c r="A199" s="7"/>
       <c r="B199" s="8"/>
       <c r="C199" s="40"/>
@@ -6102,7 +6102,7 @@
       <c r="H199" s="12"/>
       <c r="I199" s="12"/>
     </row>
-    <row r="200" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="200" spans="1:9" ht="15" customHeight="1">
       <c r="A200" s="7"/>
       <c r="B200" s="8"/>
       <c r="C200" s="40"/>
@@ -6113,7 +6113,7 @@
       <c r="H200" s="12"/>
       <c r="I200" s="12"/>
     </row>
-    <row r="201" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="201" spans="1:9" ht="15" customHeight="1">
       <c r="A201" s="7"/>
       <c r="B201" s="8"/>
       <c r="C201" s="40"/>
@@ -6124,7 +6124,7 @@
       <c r="H201" s="12"/>
       <c r="I201" s="12"/>
     </row>
-    <row r="202" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="202" spans="1:9" ht="15" customHeight="1">
       <c r="A202" s="7"/>
       <c r="B202" s="8"/>
       <c r="C202" s="40"/>
@@ -6135,7 +6135,7 @@
       <c r="H202" s="12"/>
       <c r="I202" s="12"/>
     </row>
-    <row r="203" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="203" spans="1:9" ht="15" customHeight="1">
       <c r="A203" s="7"/>
       <c r="B203" s="8"/>
       <c r="C203" s="40"/>
@@ -6146,7 +6146,7 @@
       <c r="H203" s="12"/>
       <c r="I203" s="12"/>
     </row>
-    <row r="204" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="204" spans="1:9" ht="15" customHeight="1">
       <c r="A204" s="7"/>
       <c r="B204" s="8"/>
       <c r="C204" s="40"/>
@@ -6168,413 +6168,413 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4E144160-55E5-40A6-9A8E-E41DA7F6726D}">
   <dimension ref="D2:N92"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="14.45"/>
   <cols>
     <col min="1" max="1" width="12" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="60.26953125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="58.81640625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="12.54296875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="11.26953125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="60.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="58.85546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.5703125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.28515625" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="16" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="22.54296875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="22.5703125" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="10" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="42" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="54" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="40.26953125" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="35.453125" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="9.453125" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="8.453125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="40.28515625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="35.42578125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="9.42578125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="8.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="4:14" x14ac:dyDescent="0.35">
+    <row r="2" spans="4:14">
       <c r="M2" s="5"/>
       <c r="N2" s="5"/>
     </row>
-    <row r="3" spans="4:14" x14ac:dyDescent="0.35">
+    <row r="3" spans="4:14">
       <c r="D3" s="1">
         <v>868589060374017</v>
       </c>
       <c r="F3" t="s">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="G3" s="2" t="e">
         <f ca="1">VLOOKUP(D3,Hoja2!G:K,5,FALSE)</f>
         <v>#N/A</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="I3" s="4">
         <v>46043</v>
       </c>
     </row>
-    <row r="4" spans="4:14" x14ac:dyDescent="0.35">
+    <row r="4" spans="4:14">
       <c r="D4" s="1">
         <v>868589060674226</v>
       </c>
       <c r="F4" t="s">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="G4" s="2" t="e">
         <f ca="1">VLOOKUP(D4,Hoja2!G:K,5,FALSE)</f>
         <v>#N/A</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="I4" s="4">
         <v>46043</v>
       </c>
     </row>
-    <row r="5" spans="4:14" x14ac:dyDescent="0.35">
+    <row r="5" spans="4:14">
       <c r="M5" s="5"/>
       <c r="N5" s="5"/>
     </row>
-    <row r="6" spans="4:14" x14ac:dyDescent="0.35">
+    <row r="6" spans="4:14">
       <c r="M6" s="5"/>
       <c r="N6" s="5"/>
     </row>
-    <row r="7" spans="4:14" x14ac:dyDescent="0.35">
+    <row r="7" spans="4:14">
       <c r="M7" s="5"/>
       <c r="N7" s="5"/>
     </row>
-    <row r="8" spans="4:14" x14ac:dyDescent="0.35">
+    <row r="8" spans="4:14">
       <c r="M8" s="5"/>
       <c r="N8" s="5"/>
     </row>
-    <row r="9" spans="4:14" x14ac:dyDescent="0.35">
+    <row r="9" spans="4:14">
       <c r="M9" s="5"/>
       <c r="N9" s="5"/>
     </row>
-    <row r="10" spans="4:14" x14ac:dyDescent="0.35">
+    <row r="10" spans="4:14">
       <c r="M10" s="5"/>
       <c r="N10" s="5"/>
     </row>
-    <row r="11" spans="4:14" x14ac:dyDescent="0.35">
+    <row r="11" spans="4:14">
       <c r="M11" s="5"/>
       <c r="N11" s="5"/>
     </row>
-    <row r="12" spans="4:14" x14ac:dyDescent="0.35">
+    <row r="12" spans="4:14">
       <c r="M12" s="5"/>
       <c r="N12" s="5"/>
     </row>
-    <row r="13" spans="4:14" x14ac:dyDescent="0.35">
+    <row r="13" spans="4:14">
       <c r="M13" s="5"/>
       <c r="N13" s="5"/>
     </row>
-    <row r="14" spans="4:14" x14ac:dyDescent="0.35">
+    <row r="14" spans="4:14">
       <c r="M14" s="5"/>
       <c r="N14" s="5"/>
     </row>
-    <row r="15" spans="4:14" x14ac:dyDescent="0.35">
+    <row r="15" spans="4:14">
       <c r="M15" s="5"/>
       <c r="N15" s="5"/>
     </row>
-    <row r="16" spans="4:14" x14ac:dyDescent="0.35">
+    <row r="16" spans="4:14">
       <c r="M16" s="5"/>
       <c r="N16" s="5"/>
     </row>
-    <row r="17" spans="13:14" x14ac:dyDescent="0.35">
+    <row r="17" spans="13:14">
       <c r="M17" s="5"/>
       <c r="N17" s="5"/>
     </row>
-    <row r="18" spans="13:14" x14ac:dyDescent="0.35">
+    <row r="18" spans="13:14">
       <c r="M18" s="5"/>
       <c r="N18" s="5"/>
     </row>
-    <row r="19" spans="13:14" x14ac:dyDescent="0.35">
+    <row r="19" spans="13:14">
       <c r="M19" s="5"/>
       <c r="N19" s="5"/>
     </row>
-    <row r="20" spans="13:14" x14ac:dyDescent="0.35">
+    <row r="20" spans="13:14">
       <c r="M20" s="5"/>
       <c r="N20" s="5"/>
     </row>
-    <row r="21" spans="13:14" x14ac:dyDescent="0.35">
+    <row r="21" spans="13:14">
       <c r="M21" s="5"/>
       <c r="N21" s="5"/>
     </row>
-    <row r="22" spans="13:14" x14ac:dyDescent="0.35">
+    <row r="22" spans="13:14">
       <c r="M22" s="5"/>
       <c r="N22" s="5"/>
     </row>
-    <row r="23" spans="13:14" x14ac:dyDescent="0.35">
+    <row r="23" spans="13:14">
       <c r="M23" s="5"/>
       <c r="N23" s="5"/>
     </row>
-    <row r="24" spans="13:14" x14ac:dyDescent="0.35">
+    <row r="24" spans="13:14">
       <c r="M24" s="5"/>
       <c r="N24" s="5"/>
     </row>
-    <row r="25" spans="13:14" x14ac:dyDescent="0.35">
+    <row r="25" spans="13:14">
       <c r="M25" s="5"/>
       <c r="N25" s="5"/>
     </row>
-    <row r="26" spans="13:14" x14ac:dyDescent="0.35">
+    <row r="26" spans="13:14">
       <c r="M26" s="5"/>
       <c r="N26" s="5"/>
     </row>
-    <row r="27" spans="13:14" x14ac:dyDescent="0.35">
+    <row r="27" spans="13:14">
       <c r="M27" s="5"/>
       <c r="N27" s="5"/>
     </row>
-    <row r="28" spans="13:14" x14ac:dyDescent="0.35">
+    <row r="28" spans="13:14">
       <c r="M28" s="5"/>
       <c r="N28" s="5"/>
     </row>
-    <row r="29" spans="13:14" x14ac:dyDescent="0.35">
+    <row r="29" spans="13:14">
       <c r="M29" s="5"/>
       <c r="N29" s="5"/>
     </row>
-    <row r="30" spans="13:14" x14ac:dyDescent="0.35">
+    <row r="30" spans="13:14">
       <c r="M30" s="5"/>
       <c r="N30" s="5"/>
     </row>
-    <row r="31" spans="13:14" x14ac:dyDescent="0.35">
+    <row r="31" spans="13:14">
       <c r="M31" s="5"/>
       <c r="N31" s="5"/>
     </row>
-    <row r="32" spans="13:14" x14ac:dyDescent="0.35">
+    <row r="32" spans="13:14">
       <c r="M32" s="5"/>
       <c r="N32" s="5"/>
     </row>
-    <row r="33" spans="13:14" x14ac:dyDescent="0.35">
+    <row r="33" spans="13:14">
       <c r="M33" s="5"/>
       <c r="N33" s="5"/>
     </row>
-    <row r="34" spans="13:14" x14ac:dyDescent="0.35">
+    <row r="34" spans="13:14">
       <c r="M34" s="5"/>
       <c r="N34" s="5"/>
     </row>
-    <row r="35" spans="13:14" x14ac:dyDescent="0.35">
+    <row r="35" spans="13:14">
       <c r="M35" s="5"/>
       <c r="N35" s="5"/>
     </row>
-    <row r="36" spans="13:14" x14ac:dyDescent="0.35">
+    <row r="36" spans="13:14">
       <c r="M36" s="5"/>
       <c r="N36" s="5"/>
     </row>
-    <row r="37" spans="13:14" x14ac:dyDescent="0.35">
+    <row r="37" spans="13:14">
       <c r="M37" s="5"/>
       <c r="N37" s="5"/>
     </row>
-    <row r="38" spans="13:14" x14ac:dyDescent="0.35">
+    <row r="38" spans="13:14">
       <c r="M38" s="5"/>
       <c r="N38" s="5"/>
     </row>
-    <row r="39" spans="13:14" x14ac:dyDescent="0.35">
+    <row r="39" spans="13:14">
       <c r="M39" s="5"/>
       <c r="N39" s="5"/>
     </row>
-    <row r="40" spans="13:14" x14ac:dyDescent="0.35">
+    <row r="40" spans="13:14">
       <c r="M40" s="5"/>
       <c r="N40" s="5"/>
     </row>
-    <row r="41" spans="13:14" x14ac:dyDescent="0.35">
+    <row r="41" spans="13:14">
       <c r="M41" s="5"/>
       <c r="N41" s="5"/>
     </row>
-    <row r="42" spans="13:14" x14ac:dyDescent="0.35">
+    <row r="42" spans="13:14">
       <c r="M42" s="5"/>
       <c r="N42" s="5"/>
     </row>
-    <row r="43" spans="13:14" x14ac:dyDescent="0.35">
+    <row r="43" spans="13:14">
       <c r="M43" s="5"/>
       <c r="N43" s="5"/>
     </row>
-    <row r="44" spans="13:14" x14ac:dyDescent="0.35">
+    <row r="44" spans="13:14">
       <c r="M44" s="5"/>
       <c r="N44" s="5"/>
     </row>
-    <row r="45" spans="13:14" x14ac:dyDescent="0.35">
+    <row r="45" spans="13:14">
       <c r="M45" s="5"/>
       <c r="N45" s="5"/>
     </row>
-    <row r="46" spans="13:14" x14ac:dyDescent="0.35">
+    <row r="46" spans="13:14">
       <c r="M46" s="5"/>
       <c r="N46" s="5"/>
     </row>
-    <row r="47" spans="13:14" x14ac:dyDescent="0.35">
+    <row r="47" spans="13:14">
       <c r="M47" s="5"/>
       <c r="N47" s="5"/>
     </row>
-    <row r="48" spans="13:14" x14ac:dyDescent="0.35">
+    <row r="48" spans="13:14">
       <c r="M48" s="5"/>
       <c r="N48" s="5"/>
     </row>
-    <row r="49" spans="13:14" x14ac:dyDescent="0.35">
+    <row r="49" spans="13:14">
       <c r="M49" s="5"/>
       <c r="N49" s="5"/>
     </row>
-    <row r="50" spans="13:14" x14ac:dyDescent="0.35">
+    <row r="50" spans="13:14">
       <c r="M50" s="5"/>
       <c r="N50" s="5"/>
     </row>
-    <row r="51" spans="13:14" x14ac:dyDescent="0.35">
+    <row r="51" spans="13:14">
       <c r="M51" s="5"/>
       <c r="N51" s="5"/>
     </row>
-    <row r="52" spans="13:14" x14ac:dyDescent="0.35">
+    <row r="52" spans="13:14">
       <c r="M52" s="5"/>
       <c r="N52" s="5"/>
     </row>
-    <row r="53" spans="13:14" x14ac:dyDescent="0.35">
+    <row r="53" spans="13:14">
       <c r="M53" s="5"/>
       <c r="N53" s="5"/>
     </row>
-    <row r="54" spans="13:14" x14ac:dyDescent="0.35">
+    <row r="54" spans="13:14">
       <c r="M54" s="5"/>
       <c r="N54" s="5"/>
     </row>
-    <row r="55" spans="13:14" x14ac:dyDescent="0.35">
+    <row r="55" spans="13:14">
       <c r="M55" s="5"/>
       <c r="N55" s="5"/>
     </row>
-    <row r="56" spans="13:14" x14ac:dyDescent="0.35">
+    <row r="56" spans="13:14">
       <c r="M56" s="5"/>
       <c r="N56" s="5"/>
     </row>
-    <row r="57" spans="13:14" x14ac:dyDescent="0.35">
+    <row r="57" spans="13:14">
       <c r="M57" s="5"/>
       <c r="N57" s="5"/>
     </row>
-    <row r="58" spans="13:14" x14ac:dyDescent="0.35">
+    <row r="58" spans="13:14">
       <c r="M58" s="5"/>
       <c r="N58" s="5"/>
     </row>
-    <row r="59" spans="13:14" x14ac:dyDescent="0.35">
+    <row r="59" spans="13:14">
       <c r="M59" s="5"/>
       <c r="N59" s="5"/>
     </row>
-    <row r="60" spans="13:14" x14ac:dyDescent="0.35">
+    <row r="60" spans="13:14">
       <c r="M60" s="5"/>
       <c r="N60" s="5"/>
     </row>
-    <row r="61" spans="13:14" x14ac:dyDescent="0.35">
+    <row r="61" spans="13:14">
       <c r="M61" s="5"/>
       <c r="N61" s="5"/>
     </row>
-    <row r="62" spans="13:14" x14ac:dyDescent="0.35">
+    <row r="62" spans="13:14">
       <c r="M62" s="5"/>
       <c r="N62" s="5"/>
     </row>
-    <row r="63" spans="13:14" x14ac:dyDescent="0.35">
+    <row r="63" spans="13:14">
       <c r="M63" s="5"/>
       <c r="N63" s="5"/>
     </row>
-    <row r="64" spans="13:14" x14ac:dyDescent="0.35">
+    <row r="64" spans="13:14">
       <c r="M64" s="5"/>
       <c r="N64" s="5"/>
     </row>
-    <row r="65" spans="13:14" x14ac:dyDescent="0.35">
+    <row r="65" spans="13:14">
       <c r="M65" s="5"/>
       <c r="N65" s="5"/>
     </row>
-    <row r="66" spans="13:14" x14ac:dyDescent="0.35">
+    <row r="66" spans="13:14">
       <c r="M66" s="5"/>
       <c r="N66" s="5"/>
     </row>
-    <row r="67" spans="13:14" x14ac:dyDescent="0.35">
+    <row r="67" spans="13:14">
       <c r="M67" s="5"/>
       <c r="N67" s="5"/>
     </row>
-    <row r="68" spans="13:14" x14ac:dyDescent="0.35">
+    <row r="68" spans="13:14">
       <c r="M68" s="5"/>
       <c r="N68" s="5"/>
     </row>
-    <row r="69" spans="13:14" x14ac:dyDescent="0.35">
+    <row r="69" spans="13:14">
       <c r="M69" s="5"/>
       <c r="N69" s="5"/>
     </row>
-    <row r="70" spans="13:14" x14ac:dyDescent="0.35">
+    <row r="70" spans="13:14">
       <c r="M70" s="5"/>
       <c r="N70" s="5"/>
     </row>
-    <row r="71" spans="13:14" x14ac:dyDescent="0.35">
+    <row r="71" spans="13:14">
       <c r="M71" s="5"/>
       <c r="N71" s="5"/>
     </row>
-    <row r="72" spans="13:14" x14ac:dyDescent="0.35">
+    <row r="72" spans="13:14">
       <c r="M72" s="5"/>
       <c r="N72" s="5"/>
     </row>
-    <row r="73" spans="13:14" x14ac:dyDescent="0.35">
+    <row r="73" spans="13:14">
       <c r="M73" s="5"/>
       <c r="N73" s="5"/>
     </row>
-    <row r="74" spans="13:14" x14ac:dyDescent="0.35">
+    <row r="74" spans="13:14">
       <c r="M74" s="5"/>
       <c r="N74" s="5"/>
     </row>
-    <row r="75" spans="13:14" x14ac:dyDescent="0.35">
+    <row r="75" spans="13:14">
       <c r="M75" s="5"/>
       <c r="N75" s="5"/>
     </row>
-    <row r="76" spans="13:14" x14ac:dyDescent="0.35">
+    <row r="76" spans="13:14">
       <c r="M76" s="5"/>
       <c r="N76" s="5"/>
     </row>
-    <row r="77" spans="13:14" x14ac:dyDescent="0.35">
+    <row r="77" spans="13:14">
       <c r="M77" s="5"/>
       <c r="N77" s="5"/>
     </row>
-    <row r="78" spans="13:14" x14ac:dyDescent="0.35">
+    <row r="78" spans="13:14">
       <c r="M78" s="5"/>
       <c r="N78" s="5"/>
     </row>
-    <row r="79" spans="13:14" x14ac:dyDescent="0.35">
+    <row r="79" spans="13:14">
       <c r="M79" s="5"/>
       <c r="N79" s="5"/>
     </row>
-    <row r="80" spans="13:14" x14ac:dyDescent="0.35">
+    <row r="80" spans="13:14">
       <c r="M80" s="5"/>
       <c r="N80" s="5"/>
     </row>
-    <row r="81" spans="13:14" x14ac:dyDescent="0.35">
+    <row r="81" spans="13:14">
       <c r="M81" s="5"/>
       <c r="N81" s="5"/>
     </row>
-    <row r="82" spans="13:14" x14ac:dyDescent="0.35">
+    <row r="82" spans="13:14">
       <c r="M82" s="5"/>
       <c r="N82" s="5"/>
     </row>
-    <row r="83" spans="13:14" x14ac:dyDescent="0.35">
+    <row r="83" spans="13:14">
       <c r="M83" s="5"/>
       <c r="N83" s="5"/>
     </row>
-    <row r="84" spans="13:14" x14ac:dyDescent="0.35">
+    <row r="84" spans="13:14">
       <c r="M84" s="5"/>
       <c r="N84" s="5"/>
     </row>
-    <row r="85" spans="13:14" x14ac:dyDescent="0.35">
+    <row r="85" spans="13:14">
       <c r="M85" s="5"/>
       <c r="N85" s="5"/>
     </row>
-    <row r="86" spans="13:14" x14ac:dyDescent="0.35">
+    <row r="86" spans="13:14">
       <c r="M86" s="5"/>
       <c r="N86" s="5"/>
     </row>
-    <row r="87" spans="13:14" x14ac:dyDescent="0.35">
+    <row r="87" spans="13:14">
       <c r="M87" s="5"/>
       <c r="N87" s="5"/>
     </row>
-    <row r="88" spans="13:14" x14ac:dyDescent="0.35">
+    <row r="88" spans="13:14">
       <c r="M88" s="5"/>
       <c r="N88" s="5"/>
     </row>
-    <row r="89" spans="13:14" x14ac:dyDescent="0.35">
+    <row r="89" spans="13:14">
       <c r="M89" s="5"/>
       <c r="N89" s="5"/>
     </row>
-    <row r="90" spans="13:14" x14ac:dyDescent="0.35">
+    <row r="90" spans="13:14">
       <c r="M90" s="5"/>
       <c r="N90" s="5"/>
     </row>
-    <row r="91" spans="13:14" x14ac:dyDescent="0.35">
+    <row r="91" spans="13:14">
       <c r="M91" s="5"/>
       <c r="N91" s="5"/>
     </row>
-    <row r="92" spans="13:14" x14ac:dyDescent="0.35">
+    <row r="92" spans="13:14">
       <c r="M92" s="5"/>
       <c r="N92" s="5"/>
     </row>
@@ -6584,6 +6584,15 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x010100027709BF533FA442AFC4A8B2C0110727" ma:contentTypeVersion="15" ma:contentTypeDescription="Crear nuevo documento." ma:contentTypeScope="" ma:versionID="a37fc0d7c302f7619d355a49e1f175a4">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="3e53c16e-6636-411e-b1c4-e9eeb71b3b2a" xmlns:ns4="bda9c1ec-c4e2-44f9-929c-ca399fe36c88" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="01250a30c504a808427f15ccf149ee4d" ns3:_="" ns4:_="">
     <xsd:import namespace="3e53c16e-6636-411e-b1c4-e9eeb71b3b2a"/>
@@ -6816,15 +6825,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
@@ -6834,38 +6834,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4794C7E6-B89D-4081-9A67-B8D500EF1EE4}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="3e53c16e-6636-411e-b1c4-e9eeb71b3b2a"/>
-    <ds:schemaRef ds:uri="bda9c1ec-c4e2-44f9-929c-ca399fe36c88"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3C8123E5-81FD-4C24-91F1-33BC079967E9}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3C8123E5-81FD-4C24-91F1-33BC079967E9}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4794C7E6-B89D-4081-9A67-B8D500EF1EE4}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D9861A25-610F-425F-BC6A-AC52D4971411}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="3e53c16e-6636-411e-b1c4-e9eeb71b3b2a"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D9861A25-610F-425F-BC6A-AC52D4971411}"/>
 </file>
--- a/data/bitacora.xlsx
+++ b/data/bitacora.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29910"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://grupokaufmann-my.sharepoint.com/personal/samuel_sanchez_grupokaufmann_com/Documents/Documentos/Dev/bitacora_diaria/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="357" documentId="8_{4616FF0F-C10E-4DFE-8F27-869B9C60E0F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D5D1F434-0134-47BB-ACB8-D6A94FE006B9}"/>
+  <xr:revisionPtr revIDLastSave="391" documentId="8_{4616FF0F-C10E-4DFE-8F27-869B9C60E0F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{319077C7-3FD3-4156-8F5E-D4B5E2AA648D}"/>
   <bookViews>
-    <workbookView minimized="1" xWindow="-26520" yWindow="1035" windowWidth="14400" windowHeight="8175" xr2:uid="{A9E3F017-9040-47A2-B586-0486128F3261}"/>
+    <workbookView xWindow="-28920" yWindow="-1155" windowWidth="29040" windowHeight="15720" xr2:uid="{A9E3F017-9040-47A2-B586-0486128F3261}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -19,7 +19,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Hoja1!$A$1:$F$127</definedName>
   </definedNames>
-  <calcPr calcId="191028" calcCompleted="0"/>
+  <calcPr calcId="191028"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="791" uniqueCount="350">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="811" uniqueCount="355">
   <si>
     <t>FLOTA</t>
   </si>
@@ -1090,13 +1090,28 @@
   </si>
   <si>
     <t>Revisado</t>
+  </si>
+  <si>
+    <t>9BM634074RB328609</t>
+  </si>
+  <si>
+    <t>YANGUAS</t>
+  </si>
+  <si>
+    <t>9BM634074RB328594</t>
+  </si>
+  <si>
+    <t>LPCT72</t>
+  </si>
+  <si>
+    <t>Kamaleon Pegado</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1985,21 +2000,21 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EDA66EBA-6B88-4C75-8217-0B7E221D898D}">
   <dimension ref="A1:L204"/>
-  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" customHeight="1"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.453125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="43" style="6" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="22.7109375" style="6" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.28515625" style="43" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="22.7265625" style="6" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.26953125" style="43" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="25" style="6" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="40.28515625" style="6" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="27.5703125" style="6" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="18.85546875" style="16" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="20.140625" style="16" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="40.26953125" style="6" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="27.54296875" style="6" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="18.81640625" style="16" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="20.1796875" style="16" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="79" style="6" bestFit="1" customWidth="1"/>
-    <col min="11" max="16384" width="11.42578125" style="6"/>
+    <col min="11" max="16384" width="11.453125" style="6"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="14.45">
+    <row r="1" spans="1:12" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A1" s="17" t="s">
         <v>0</v>
       </c>
@@ -2031,7 +2046,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:12" ht="14.45">
+    <row r="2" spans="1:12" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A2" s="7" t="s">
         <v>10</v>
       </c>
@@ -2054,7 +2069,7 @@
       <c r="H2" s="12"/>
       <c r="I2" s="12"/>
     </row>
-    <row r="3" spans="1:12" ht="14.45">
+    <row r="3" spans="1:12" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A3" s="7" t="s">
         <v>10</v>
       </c>
@@ -2077,7 +2092,7 @@
       <c r="H3" s="12"/>
       <c r="I3" s="12"/>
     </row>
-    <row r="4" spans="1:12" ht="14.45">
+    <row r="4" spans="1:12" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A4" s="7" t="s">
         <v>10</v>
       </c>
@@ -2100,7 +2115,7 @@
       <c r="H4" s="12"/>
       <c r="I4" s="12"/>
     </row>
-    <row r="5" spans="1:12" ht="14.45">
+    <row r="5" spans="1:12" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A5" s="7" t="s">
         <v>10</v>
       </c>
@@ -2123,7 +2138,7 @@
       <c r="H5" s="12"/>
       <c r="I5" s="12"/>
     </row>
-    <row r="6" spans="1:12" ht="14.45">
+    <row r="6" spans="1:12" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A6" s="7" t="s">
         <v>10</v>
       </c>
@@ -2146,7 +2161,7 @@
       <c r="H6" s="12"/>
       <c r="I6" s="12"/>
     </row>
-    <row r="7" spans="1:12" ht="14.45">
+    <row r="7" spans="1:12" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A7" s="7" t="s">
         <v>10</v>
       </c>
@@ -2169,7 +2184,7 @@
       <c r="H7" s="24"/>
       <c r="I7" s="24"/>
     </row>
-    <row r="8" spans="1:12" ht="14.45">
+    <row r="8" spans="1:12" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A8" s="7" t="s">
         <v>10</v>
       </c>
@@ -2192,7 +2207,7 @@
       <c r="H8" s="24"/>
       <c r="I8" s="24"/>
     </row>
-    <row r="9" spans="1:12" ht="14.45">
+    <row r="9" spans="1:12" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A9" s="7" t="s">
         <v>10</v>
       </c>
@@ -2215,7 +2230,7 @@
       <c r="H9" s="12"/>
       <c r="I9" s="12"/>
     </row>
-    <row r="10" spans="1:12" ht="14.45">
+    <row r="10" spans="1:12" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A10" s="7" t="s">
         <v>10</v>
       </c>
@@ -2238,7 +2253,7 @@
       <c r="H10" s="12"/>
       <c r="I10" s="12"/>
     </row>
-    <row r="11" spans="1:12" ht="14.45">
+    <row r="11" spans="1:12" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A11" s="7" t="s">
         <v>10</v>
       </c>
@@ -2261,7 +2276,7 @@
       <c r="H11" s="12"/>
       <c r="I11" s="12"/>
     </row>
-    <row r="12" spans="1:12" ht="14.45">
+    <row r="12" spans="1:12" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A12" s="7" t="s">
         <v>33</v>
       </c>
@@ -2285,7 +2300,7 @@
       <c r="I12" s="12"/>
       <c r="L12" s="26"/>
     </row>
-    <row r="13" spans="1:12" ht="14.45">
+    <row r="13" spans="1:12" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A13" s="7" t="s">
         <v>33</v>
       </c>
@@ -2308,7 +2323,7 @@
       <c r="H13" s="12"/>
       <c r="I13" s="12"/>
     </row>
-    <row r="14" spans="1:12" ht="14.45">
+    <row r="14" spans="1:12" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A14" s="7" t="s">
         <v>33</v>
       </c>
@@ -2331,7 +2346,7 @@
       <c r="H14" s="12"/>
       <c r="I14" s="12"/>
     </row>
-    <row r="15" spans="1:12" ht="14.45">
+    <row r="15" spans="1:12" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A15" s="7" t="s">
         <v>33</v>
       </c>
@@ -2354,7 +2369,7 @@
       <c r="H15" s="12"/>
       <c r="I15" s="12"/>
     </row>
-    <row r="16" spans="1:12" ht="14.45">
+    <row r="16" spans="1:12" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A16" s="7" t="s">
         <v>33</v>
       </c>
@@ -2377,7 +2392,7 @@
       <c r="H16" s="12"/>
       <c r="I16" s="12"/>
     </row>
-    <row r="17" spans="1:9" ht="14.45">
+    <row r="17" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A17" s="7" t="s">
         <v>33</v>
       </c>
@@ -2400,7 +2415,7 @@
       <c r="H17" s="12"/>
       <c r="I17" s="12"/>
     </row>
-    <row r="18" spans="1:9" ht="14.45">
+    <row r="18" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A18" s="7" t="s">
         <v>33</v>
       </c>
@@ -2423,7 +2438,7 @@
       <c r="H18" s="12"/>
       <c r="I18" s="12"/>
     </row>
-    <row r="19" spans="1:9" ht="14.45">
+    <row r="19" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A19" s="7" t="s">
         <v>33</v>
       </c>
@@ -2446,7 +2461,7 @@
       <c r="H19" s="12"/>
       <c r="I19" s="12"/>
     </row>
-    <row r="20" spans="1:9" ht="14.45">
+    <row r="20" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A20" s="7" t="s">
         <v>51</v>
       </c>
@@ -2469,7 +2484,7 @@
       <c r="H20" s="12"/>
       <c r="I20" s="12"/>
     </row>
-    <row r="21" spans="1:9" ht="14.45">
+    <row r="21" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A21" s="7" t="s">
         <v>51</v>
       </c>
@@ -2492,7 +2507,7 @@
       <c r="H21" s="12"/>
       <c r="I21" s="12"/>
     </row>
-    <row r="22" spans="1:9" ht="14.45">
+    <row r="22" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A22" s="7" t="s">
         <v>51</v>
       </c>
@@ -2515,7 +2530,7 @@
       <c r="H22" s="12"/>
       <c r="I22" s="12"/>
     </row>
-    <row r="23" spans="1:9" ht="14.45">
+    <row r="23" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A23" s="7" t="s">
         <v>59</v>
       </c>
@@ -2538,7 +2553,7 @@
       <c r="H23" s="12"/>
       <c r="I23" s="12"/>
     </row>
-    <row r="24" spans="1:9" ht="14.45">
+    <row r="24" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A24" s="7" t="s">
         <v>59</v>
       </c>
@@ -2561,7 +2576,7 @@
       <c r="H24" s="12"/>
       <c r="I24" s="12"/>
     </row>
-    <row r="25" spans="1:9" ht="14.45">
+    <row r="25" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A25" s="7" t="s">
         <v>65</v>
       </c>
@@ -2584,7 +2599,7 @@
       <c r="H25" s="12"/>
       <c r="I25" s="12"/>
     </row>
-    <row r="26" spans="1:9" ht="14.45">
+    <row r="26" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A26" s="7" t="s">
         <v>65</v>
       </c>
@@ -2607,7 +2622,7 @@
       <c r="H26" s="12"/>
       <c r="I26" s="12"/>
     </row>
-    <row r="27" spans="1:9" ht="14.45">
+    <row r="27" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A27" s="7" t="s">
         <v>65</v>
       </c>
@@ -2630,7 +2645,7 @@
       <c r="H27" s="12"/>
       <c r="I27" s="12"/>
     </row>
-    <row r="28" spans="1:9" ht="14.45">
+    <row r="28" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A28" s="7" t="s">
         <v>65</v>
       </c>
@@ -2653,7 +2668,7 @@
       <c r="H28" s="12"/>
       <c r="I28" s="12"/>
     </row>
-    <row r="29" spans="1:9" ht="14.45">
+    <row r="29" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A29" s="7" t="s">
         <v>65</v>
       </c>
@@ -2682,7 +2697,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="30" spans="1:9" ht="14.45">
+    <row r="30" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A30" s="7" t="s">
         <v>80</v>
       </c>
@@ -2705,7 +2720,7 @@
       <c r="H30" s="12"/>
       <c r="I30" s="12"/>
     </row>
-    <row r="31" spans="1:9" ht="14.45">
+    <row r="31" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A31" s="7" t="s">
         <v>80</v>
       </c>
@@ -2728,7 +2743,7 @@
       <c r="H31" s="12"/>
       <c r="I31" s="12"/>
     </row>
-    <row r="32" spans="1:9" ht="14.45">
+    <row r="32" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A32" s="7" t="s">
         <v>80</v>
       </c>
@@ -2751,7 +2766,7 @@
       <c r="H32" s="12"/>
       <c r="I32" s="12"/>
     </row>
-    <row r="33" spans="1:9" ht="14.45">
+    <row r="33" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A33" s="7" t="s">
         <v>80</v>
       </c>
@@ -2774,7 +2789,7 @@
       <c r="H33" s="12"/>
       <c r="I33" s="12"/>
     </row>
-    <row r="34" spans="1:9" ht="14.45">
+    <row r="34" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A34" s="7" t="s">
         <v>80</v>
       </c>
@@ -2797,7 +2812,7 @@
       <c r="H34" s="12"/>
       <c r="I34" s="12"/>
     </row>
-    <row r="35" spans="1:9" ht="14.45">
+    <row r="35" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A35" s="7" t="s">
         <v>80</v>
       </c>
@@ -2820,7 +2835,7 @@
       <c r="H35" s="12"/>
       <c r="I35" s="12"/>
     </row>
-    <row r="36" spans="1:9" ht="14.45">
+    <row r="36" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A36" s="7" t="s">
         <v>80</v>
       </c>
@@ -2843,7 +2858,7 @@
       <c r="H36" s="12"/>
       <c r="I36" s="12"/>
     </row>
-    <row r="37" spans="1:9" ht="14.45">
+    <row r="37" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A37" s="7" t="s">
         <v>95</v>
       </c>
@@ -2872,7 +2887,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="38" spans="1:9" ht="14.45">
+    <row r="38" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A38" s="7" t="s">
         <v>95</v>
       </c>
@@ -2901,7 +2916,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="39" spans="1:9" ht="14.45">
+    <row r="39" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A39" s="7" t="s">
         <v>95</v>
       </c>
@@ -2924,7 +2939,7 @@
       <c r="H39" s="12"/>
       <c r="I39" s="12"/>
     </row>
-    <row r="40" spans="1:9" ht="14.45">
+    <row r="40" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A40" s="7" t="s">
         <v>95</v>
       </c>
@@ -2953,7 +2968,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="41" spans="1:9" ht="14.45">
+    <row r="41" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A41" s="7" t="s">
         <v>95</v>
       </c>
@@ -2982,7 +2997,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="42" spans="1:9" ht="14.45">
+    <row r="42" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A42" s="7" t="s">
         <v>95</v>
       </c>
@@ -3005,7 +3020,7 @@
       <c r="H42" s="12"/>
       <c r="I42" s="12"/>
     </row>
-    <row r="43" spans="1:9" ht="14.45">
+    <row r="43" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A43" s="7" t="s">
         <v>95</v>
       </c>
@@ -3028,7 +3043,7 @@
       <c r="H43" s="12"/>
       <c r="I43" s="12"/>
     </row>
-    <row r="44" spans="1:9" ht="14.45">
+    <row r="44" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A44" s="7" t="s">
         <v>95</v>
       </c>
@@ -3051,7 +3066,7 @@
       <c r="H44" s="12"/>
       <c r="I44" s="12"/>
     </row>
-    <row r="45" spans="1:9" ht="14.45">
+    <row r="45" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A45" s="7" t="s">
         <v>95</v>
       </c>
@@ -3074,7 +3089,7 @@
       <c r="H45" s="12"/>
       <c r="I45" s="12"/>
     </row>
-    <row r="46" spans="1:9" ht="14.45">
+    <row r="46" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A46" s="7" t="s">
         <v>95</v>
       </c>
@@ -3103,7 +3118,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="47" spans="1:9" ht="14.45">
+    <row r="47" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A47" s="7" t="s">
         <v>95</v>
       </c>
@@ -3132,7 +3147,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="48" spans="1:9" ht="14.45">
+    <row r="48" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A48" s="7" t="s">
         <v>95</v>
       </c>
@@ -3161,7 +3176,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="49" spans="1:9" ht="14.45">
+    <row r="49" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A49" s="7" t="s">
         <v>95</v>
       </c>
@@ -3190,7 +3205,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="50" spans="1:9" ht="14.45">
+    <row r="50" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A50" s="7" t="s">
         <v>95</v>
       </c>
@@ -3213,7 +3228,7 @@
       <c r="H50" s="12"/>
       <c r="I50" s="12"/>
     </row>
-    <row r="51" spans="1:9" ht="14.45">
+    <row r="51" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A51" s="7" t="s">
         <v>95</v>
       </c>
@@ -3236,7 +3251,7 @@
       <c r="H51" s="12"/>
       <c r="I51" s="12"/>
     </row>
-    <row r="52" spans="1:9" ht="14.45">
+    <row r="52" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A52" s="7" t="s">
         <v>95</v>
       </c>
@@ -3259,7 +3274,7 @@
       <c r="H52" s="12"/>
       <c r="I52" s="12"/>
     </row>
-    <row r="53" spans="1:9" ht="14.45">
+    <row r="53" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A53" s="7" t="s">
         <v>95</v>
       </c>
@@ -3288,7 +3303,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="54" spans="1:9" ht="14.45">
+    <row r="54" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A54" s="7" t="s">
         <v>95</v>
       </c>
@@ -3311,7 +3326,7 @@
       <c r="H54" s="12"/>
       <c r="I54" s="12"/>
     </row>
-    <row r="55" spans="1:9" ht="14.45">
+    <row r="55" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A55" s="7" t="s">
         <v>95</v>
       </c>
@@ -3340,7 +3355,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="56" spans="1:9" ht="14.45">
+    <row r="56" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A56" s="7" t="s">
         <v>95</v>
       </c>
@@ -3369,7 +3384,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="57" spans="1:9" ht="14.45">
+    <row r="57" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A57" s="7" t="s">
         <v>95</v>
       </c>
@@ -3398,7 +3413,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="58" spans="1:9" ht="14.45">
+    <row r="58" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A58" s="7" t="s">
         <v>95</v>
       </c>
@@ -3421,7 +3436,7 @@
       <c r="H58" s="12"/>
       <c r="I58" s="12"/>
     </row>
-    <row r="59" spans="1:9" ht="14.45">
+    <row r="59" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A59" s="7" t="s">
         <v>95</v>
       </c>
@@ -3450,7 +3465,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="60" spans="1:9" ht="14.45">
+    <row r="60" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A60" s="7" t="s">
         <v>95</v>
       </c>
@@ -3473,7 +3488,7 @@
       <c r="H60" s="12"/>
       <c r="I60" s="12"/>
     </row>
-    <row r="61" spans="1:9" ht="14.45">
+    <row r="61" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A61" s="7" t="s">
         <v>95</v>
       </c>
@@ -3496,7 +3511,7 @@
       <c r="H61" s="12"/>
       <c r="I61" s="12"/>
     </row>
-    <row r="62" spans="1:9" ht="14.45">
+    <row r="62" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A62" s="7" t="s">
         <v>149</v>
       </c>
@@ -3519,7 +3534,7 @@
       <c r="H62" s="12"/>
       <c r="I62" s="12"/>
     </row>
-    <row r="63" spans="1:9" ht="14.45">
+    <row r="63" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A63" s="7" t="s">
         <v>149</v>
       </c>
@@ -3542,7 +3557,7 @@
       <c r="H63" s="12"/>
       <c r="I63" s="12"/>
     </row>
-    <row r="64" spans="1:9" ht="14.45">
+    <row r="64" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A64" s="7" t="s">
         <v>149</v>
       </c>
@@ -3565,7 +3580,7 @@
       <c r="H64" s="12"/>
       <c r="I64" s="12"/>
     </row>
-    <row r="65" spans="1:9" ht="14.45">
+    <row r="65" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A65" s="7" t="s">
         <v>149</v>
       </c>
@@ -3594,7 +3609,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="66" spans="1:9" ht="14.45">
+    <row r="66" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A66" s="7" t="s">
         <v>149</v>
       </c>
@@ -3623,7 +3638,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="67" spans="1:9" ht="14.45">
+    <row r="67" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A67" s="7" t="s">
         <v>149</v>
       </c>
@@ -3652,7 +3667,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="68" spans="1:9" ht="14.45">
+    <row r="68" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A68" s="7" t="s">
         <v>149</v>
       </c>
@@ -3675,7 +3690,7 @@
       <c r="H68" s="12"/>
       <c r="I68" s="12"/>
     </row>
-    <row r="69" spans="1:9" ht="14.45">
+    <row r="69" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A69" s="7" t="s">
         <v>149</v>
       </c>
@@ -3698,7 +3713,7 @@
       <c r="H69" s="12"/>
       <c r="I69" s="12"/>
     </row>
-    <row r="70" spans="1:9" ht="14.45">
+    <row r="70" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A70" s="7" t="s">
         <v>149</v>
       </c>
@@ -3721,7 +3736,7 @@
       <c r="H70" s="12"/>
       <c r="I70" s="12"/>
     </row>
-    <row r="71" spans="1:9" ht="14.45">
+    <row r="71" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A71" s="7" t="s">
         <v>149</v>
       </c>
@@ -3744,7 +3759,7 @@
       <c r="H71" s="12"/>
       <c r="I71" s="12"/>
     </row>
-    <row r="72" spans="1:9" ht="14.45">
+    <row r="72" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A72" s="7" t="s">
         <v>149</v>
       </c>
@@ -3767,7 +3782,7 @@
       <c r="H72" s="12"/>
       <c r="I72" s="12"/>
     </row>
-    <row r="73" spans="1:9" ht="14.45">
+    <row r="73" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A73" s="7" t="s">
         <v>172</v>
       </c>
@@ -3790,7 +3805,7 @@
       <c r="H73" s="12"/>
       <c r="I73" s="12"/>
     </row>
-    <row r="74" spans="1:9" ht="14.45">
+    <row r="74" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A74" s="7" t="s">
         <v>172</v>
       </c>
@@ -3813,7 +3828,7 @@
       <c r="H74" s="12"/>
       <c r="I74" s="12"/>
     </row>
-    <row r="75" spans="1:9" ht="14.45">
+    <row r="75" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A75" s="7" t="s">
         <v>177</v>
       </c>
@@ -3836,7 +3851,7 @@
       <c r="H75" s="12"/>
       <c r="I75" s="12"/>
     </row>
-    <row r="76" spans="1:9" ht="14.45">
+    <row r="76" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A76" s="7" t="s">
         <v>177</v>
       </c>
@@ -3859,7 +3874,7 @@
       <c r="H76" s="12"/>
       <c r="I76" s="12"/>
     </row>
-    <row r="77" spans="1:9" ht="14.45">
+    <row r="77" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A77" s="7" t="s">
         <v>177</v>
       </c>
@@ -3882,7 +3897,7 @@
       <c r="H77" s="12"/>
       <c r="I77" s="12"/>
     </row>
-    <row r="78" spans="1:9" ht="14.45">
+    <row r="78" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A78" s="7" t="s">
         <v>177</v>
       </c>
@@ -3905,7 +3920,7 @@
       <c r="H78" s="12"/>
       <c r="I78" s="12"/>
     </row>
-    <row r="79" spans="1:9" ht="14.45">
+    <row r="79" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A79" s="7" t="s">
         <v>177</v>
       </c>
@@ -3928,7 +3943,7 @@
       <c r="H79" s="12"/>
       <c r="I79" s="12"/>
     </row>
-    <row r="80" spans="1:9" ht="14.45">
+    <row r="80" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A80" s="7" t="s">
         <v>177</v>
       </c>
@@ -3951,7 +3966,7 @@
       <c r="H80" s="12"/>
       <c r="I80" s="12"/>
     </row>
-    <row r="81" spans="1:9" ht="14.45">
+    <row r="81" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A81" s="7" t="s">
         <v>177</v>
       </c>
@@ -3974,7 +3989,7 @@
       <c r="H81" s="12"/>
       <c r="I81" s="12"/>
     </row>
-    <row r="82" spans="1:9" ht="14.45">
+    <row r="82" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A82" s="7" t="s">
         <v>177</v>
       </c>
@@ -3997,7 +4012,7 @@
       <c r="H82" s="12"/>
       <c r="I82" s="12"/>
     </row>
-    <row r="83" spans="1:9" ht="14.45">
+    <row r="83" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A83" s="7" t="s">
         <v>177</v>
       </c>
@@ -4020,7 +4035,7 @@
       <c r="H83" s="12"/>
       <c r="I83" s="12"/>
     </row>
-    <row r="84" spans="1:9" ht="14.45">
+    <row r="84" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A84" s="7" t="s">
         <v>177</v>
       </c>
@@ -4043,7 +4058,7 @@
       <c r="H84" s="12"/>
       <c r="I84" s="12"/>
     </row>
-    <row r="85" spans="1:9" ht="14.45">
+    <row r="85" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A85" s="7" t="s">
         <v>177</v>
       </c>
@@ -4066,7 +4081,7 @@
       <c r="H85" s="12"/>
       <c r="I85" s="12"/>
     </row>
-    <row r="86" spans="1:9" ht="14.45">
+    <row r="86" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A86" s="7" t="s">
         <v>177</v>
       </c>
@@ -4089,7 +4104,7 @@
       <c r="H86" s="12"/>
       <c r="I86" s="12"/>
     </row>
-    <row r="87" spans="1:9" ht="14.45">
+    <row r="87" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A87" s="7" t="s">
         <v>177</v>
       </c>
@@ -4112,7 +4127,7 @@
       <c r="H87" s="12"/>
       <c r="I87" s="12"/>
     </row>
-    <row r="88" spans="1:9" ht="14.45">
+    <row r="88" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A88" s="7" t="s">
         <v>177</v>
       </c>
@@ -4135,7 +4150,7 @@
       <c r="H88" s="12"/>
       <c r="I88" s="12"/>
     </row>
-    <row r="89" spans="1:9" ht="14.45">
+    <row r="89" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A89" s="7" t="s">
         <v>177</v>
       </c>
@@ -4158,7 +4173,7 @@
       <c r="H89" s="12"/>
       <c r="I89" s="12"/>
     </row>
-    <row r="90" spans="1:9" ht="14.45">
+    <row r="90" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A90" s="7" t="s">
         <v>177</v>
       </c>
@@ -4181,7 +4196,7 @@
       <c r="H90" s="12"/>
       <c r="I90" s="12"/>
     </row>
-    <row r="91" spans="1:9" ht="14.45">
+    <row r="91" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A91" s="7" t="s">
         <v>210</v>
       </c>
@@ -4204,7 +4219,7 @@
       <c r="H91" s="12"/>
       <c r="I91" s="12"/>
     </row>
-    <row r="92" spans="1:9" ht="14.45">
+    <row r="92" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A92" s="7" t="s">
         <v>210</v>
       </c>
@@ -4227,7 +4242,7 @@
       <c r="H92" s="12"/>
       <c r="I92" s="12"/>
     </row>
-    <row r="93" spans="1:9" ht="14.45">
+    <row r="93" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A93" s="7" t="s">
         <v>210</v>
       </c>
@@ -4250,7 +4265,7 @@
       <c r="H93" s="12"/>
       <c r="I93" s="12"/>
     </row>
-    <row r="94" spans="1:9" ht="14.45">
+    <row r="94" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A94" s="7" t="s">
         <v>217</v>
       </c>
@@ -4279,7 +4294,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="95" spans="1:9" ht="14.45">
+    <row r="95" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A95" s="7" t="s">
         <v>217</v>
       </c>
@@ -4302,7 +4317,7 @@
       <c r="H95" s="12"/>
       <c r="I95" s="12"/>
     </row>
-    <row r="96" spans="1:9" ht="14.45">
+    <row r="96" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A96" s="7" t="s">
         <v>217</v>
       </c>
@@ -4325,7 +4340,7 @@
       <c r="H96" s="12"/>
       <c r="I96" s="12"/>
     </row>
-    <row r="97" spans="1:10" ht="14.45">
+    <row r="97" spans="1:10" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A97" s="7" t="s">
         <v>217</v>
       </c>
@@ -4348,7 +4363,7 @@
       <c r="H97" s="12"/>
       <c r="I97" s="12"/>
     </row>
-    <row r="98" spans="1:10" ht="14.45">
+    <row r="98" spans="1:10" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A98" s="7" t="s">
         <v>225</v>
       </c>
@@ -4377,7 +4392,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="99" spans="1:10" ht="14.45">
+    <row r="99" spans="1:10" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A99" s="7" t="s">
         <v>225</v>
       </c>
@@ -4400,7 +4415,7 @@
       <c r="H99" s="12"/>
       <c r="I99" s="12"/>
     </row>
-    <row r="100" spans="1:10" ht="14.45">
+    <row r="100" spans="1:10" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A100" s="7" t="s">
         <v>231</v>
       </c>
@@ -4423,7 +4438,7 @@
       <c r="H100" s="12"/>
       <c r="I100" s="12"/>
     </row>
-    <row r="101" spans="1:10" ht="14.45">
+    <row r="101" spans="1:10" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A101" s="7" t="s">
         <v>231</v>
       </c>
@@ -4449,7 +4464,7 @@
         <v>237</v>
       </c>
     </row>
-    <row r="102" spans="1:10" ht="14.45">
+    <row r="102" spans="1:10" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A102" s="7" t="s">
         <v>238</v>
       </c>
@@ -4472,7 +4487,7 @@
       <c r="H102" s="12"/>
       <c r="I102" s="12"/>
     </row>
-    <row r="103" spans="1:10" ht="14.45">
+    <row r="103" spans="1:10" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A103" s="7" t="s">
         <v>238</v>
       </c>
@@ -4495,7 +4510,7 @@
       <c r="H103" s="12"/>
       <c r="I103" s="12"/>
     </row>
-    <row r="104" spans="1:10" ht="14.45">
+    <row r="104" spans="1:10" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A104" s="7" t="s">
         <v>238</v>
       </c>
@@ -4518,7 +4533,7 @@
       <c r="H104" s="12"/>
       <c r="I104" s="12"/>
     </row>
-    <row r="105" spans="1:10" ht="14.45">
+    <row r="105" spans="1:10" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A105" s="7" t="s">
         <v>238</v>
       </c>
@@ -4541,7 +4556,7 @@
       <c r="H105" s="12"/>
       <c r="I105" s="12"/>
     </row>
-    <row r="106" spans="1:10" ht="14.45">
+    <row r="106" spans="1:10" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A106" s="7" t="s">
         <v>238</v>
       </c>
@@ -4564,7 +4579,7 @@
       <c r="H106" s="12"/>
       <c r="I106" s="12"/>
     </row>
-    <row r="107" spans="1:10" ht="14.45">
+    <row r="107" spans="1:10" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A107" s="7" t="s">
         <v>238</v>
       </c>
@@ -4587,7 +4602,7 @@
       <c r="H107" s="12"/>
       <c r="I107" s="12"/>
     </row>
-    <row r="108" spans="1:10" ht="14.45">
+    <row r="108" spans="1:10" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A108" s="7" t="s">
         <v>238</v>
       </c>
@@ -4610,7 +4625,7 @@
       <c r="H108" s="12"/>
       <c r="I108" s="12"/>
     </row>
-    <row r="109" spans="1:10" ht="14.45">
+    <row r="109" spans="1:10" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A109" s="7" t="s">
         <v>238</v>
       </c>
@@ -4633,7 +4648,7 @@
       <c r="H109" s="12"/>
       <c r="I109" s="12"/>
     </row>
-    <row r="110" spans="1:10" ht="14.45">
+    <row r="110" spans="1:10" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A110" s="7" t="s">
         <v>238</v>
       </c>
@@ -4656,7 +4671,7 @@
       <c r="H110" s="12"/>
       <c r="I110" s="12"/>
     </row>
-    <row r="111" spans="1:10" ht="14.45">
+    <row r="111" spans="1:10" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A111" s="7" t="s">
         <v>238</v>
       </c>
@@ -4679,7 +4694,7 @@
       <c r="H111" s="12"/>
       <c r="I111" s="12"/>
     </row>
-    <row r="112" spans="1:10" ht="14.45">
+    <row r="112" spans="1:10" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A112" s="7" t="s">
         <v>238</v>
       </c>
@@ -4702,7 +4717,7 @@
       <c r="H112" s="12"/>
       <c r="I112" s="12"/>
     </row>
-    <row r="113" spans="1:9" ht="14.45">
+    <row r="113" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A113" s="7" t="s">
         <v>238</v>
       </c>
@@ -4725,7 +4740,7 @@
       <c r="H113" s="12"/>
       <c r="I113" s="12"/>
     </row>
-    <row r="114" spans="1:9" ht="14.45">
+    <row r="114" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A114" s="7" t="s">
         <v>238</v>
       </c>
@@ -4748,7 +4763,7 @@
       <c r="H114" s="12"/>
       <c r="I114" s="12"/>
     </row>
-    <row r="115" spans="1:9" ht="14.45">
+    <row r="115" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A115" s="7" t="s">
         <v>238</v>
       </c>
@@ -4771,7 +4786,7 @@
       <c r="H115" s="12"/>
       <c r="I115" s="12"/>
     </row>
-    <row r="116" spans="1:9" ht="14.45">
+    <row r="116" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A116" s="7" t="s">
         <v>238</v>
       </c>
@@ -4794,7 +4809,7 @@
       <c r="H116" s="12"/>
       <c r="I116" s="12"/>
     </row>
-    <row r="117" spans="1:9" ht="14.45">
+    <row r="117" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A117" s="7" t="s">
         <v>238</v>
       </c>
@@ -4817,7 +4832,7 @@
       <c r="H117" s="12"/>
       <c r="I117" s="12"/>
     </row>
-    <row r="118" spans="1:9" ht="14.45">
+    <row r="118" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A118" s="7" t="s">
         <v>238</v>
       </c>
@@ -4840,7 +4855,7 @@
       <c r="H118" s="12"/>
       <c r="I118" s="12"/>
     </row>
-    <row r="119" spans="1:9" ht="14.45">
+    <row r="119" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A119" s="7" t="s">
         <v>238</v>
       </c>
@@ -4863,7 +4878,7 @@
       <c r="H119" s="12"/>
       <c r="I119" s="12"/>
     </row>
-    <row r="120" spans="1:9" ht="14.45">
+    <row r="120" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A120" s="7" t="s">
         <v>276</v>
       </c>
@@ -4886,7 +4901,7 @@
       <c r="H120" s="12"/>
       <c r="I120" s="12"/>
     </row>
-    <row r="121" spans="1:9" ht="14.45">
+    <row r="121" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A121" s="7" t="s">
         <v>276</v>
       </c>
@@ -4909,7 +4924,7 @@
       <c r="H121" s="12"/>
       <c r="I121" s="12"/>
     </row>
-    <row r="122" spans="1:9" ht="14.45">
+    <row r="122" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A122" s="7" t="s">
         <v>276</v>
       </c>
@@ -4932,7 +4947,7 @@
       <c r="H122" s="12"/>
       <c r="I122" s="12"/>
     </row>
-    <row r="123" spans="1:9" ht="14.45">
+    <row r="123" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A123" s="7" t="s">
         <v>284</v>
       </c>
@@ -4955,7 +4970,7 @@
       <c r="H123" s="12"/>
       <c r="I123" s="12"/>
     </row>
-    <row r="124" spans="1:9" ht="14.45">
+    <row r="124" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A124" s="7" t="s">
         <v>287</v>
       </c>
@@ -4978,7 +4993,7 @@
       <c r="H124" s="12"/>
       <c r="I124" s="12"/>
     </row>
-    <row r="125" spans="1:9" ht="14.45">
+    <row r="125" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A125" s="7" t="s">
         <v>287</v>
       </c>
@@ -5001,7 +5016,7 @@
       <c r="H125" s="12"/>
       <c r="I125" s="12"/>
     </row>
-    <row r="126" spans="1:9" ht="14.45">
+    <row r="126" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A126" s="7" t="s">
         <v>287</v>
       </c>
@@ -5024,7 +5039,7 @@
       <c r="H126" s="15"/>
       <c r="I126" s="15"/>
     </row>
-    <row r="127" spans="1:9" ht="14.45">
+    <row r="127" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A127" s="7" t="s">
         <v>294</v>
       </c>
@@ -5047,7 +5062,7 @@
       <c r="H127" s="12"/>
       <c r="I127" s="12"/>
     </row>
-    <row r="128" spans="1:9" ht="14.45">
+    <row r="128" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A128" t="s">
         <v>297</v>
       </c>
@@ -5074,7 +5089,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="129" spans="1:10" ht="14.45">
+    <row r="129" spans="1:10" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A129" t="s">
         <v>297</v>
       </c>
@@ -5099,7 +5114,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="130" spans="1:10" ht="15" customHeight="1">
+    <row r="130" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A130" s="33" t="s">
         <v>303</v>
       </c>
@@ -5124,7 +5139,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="131" spans="1:10" ht="15" customHeight="1">
+    <row r="131" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A131" s="33" t="s">
         <v>307</v>
       </c>
@@ -5149,7 +5164,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="132" spans="1:10" ht="15" customHeight="1">
+    <row r="132" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A132" s="33" t="s">
         <v>65</v>
       </c>
@@ -5174,7 +5189,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="133" spans="1:10" ht="15" customHeight="1">
+    <row r="133" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A133" s="33" t="s">
         <v>313</v>
       </c>
@@ -5199,7 +5214,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="134" spans="1:10" ht="15" customHeight="1">
+    <row r="134" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A134" s="33" t="s">
         <v>313</v>
       </c>
@@ -5224,7 +5239,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="135" spans="1:10" ht="15" customHeight="1">
+    <row r="135" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A135" s="33" t="s">
         <v>276</v>
       </c>
@@ -5249,7 +5264,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="136" spans="1:10" ht="15" customHeight="1">
+    <row r="136" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A136" s="33" t="s">
         <v>320</v>
       </c>
@@ -5275,7 +5290,7 @@
       </c>
       <c r="J136" s="38"/>
     </row>
-    <row r="137" spans="1:10" ht="15" customHeight="1">
+    <row r="137" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A137" s="33" t="s">
         <v>324</v>
       </c>
@@ -5301,7 +5316,7 @@
       </c>
       <c r="J137" s="38"/>
     </row>
-    <row r="138" spans="1:10" ht="15" customHeight="1">
+    <row r="138" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A138" s="7" t="s">
         <v>329</v>
       </c>
@@ -5325,7 +5340,7 @@
       </c>
       <c r="J138" s="37"/>
     </row>
-    <row r="139" spans="1:10" ht="15" customHeight="1">
+    <row r="139" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A139" s="7" t="s">
         <v>329</v>
       </c>
@@ -5349,7 +5364,7 @@
       </c>
       <c r="J139" s="38"/>
     </row>
-    <row r="140" spans="1:10" ht="15" customHeight="1">
+    <row r="140" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A140" s="7" t="s">
         <v>329</v>
       </c>
@@ -5373,7 +5388,7 @@
       </c>
       <c r="J140" s="38"/>
     </row>
-    <row r="141" spans="1:10" ht="15" customHeight="1">
+    <row r="141" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A141" s="33" t="s">
         <v>333</v>
       </c>
@@ -5399,7 +5414,7 @@
       </c>
       <c r="J141" s="38"/>
     </row>
-    <row r="142" spans="1:10" ht="15" customHeight="1">
+    <row r="142" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A142" s="33" t="s">
         <v>313</v>
       </c>
@@ -5424,7 +5439,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="143" spans="1:10" ht="15" customHeight="1">
+    <row r="143" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A143" s="7" t="s">
         <v>336</v>
       </c>
@@ -5449,7 +5464,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="144" spans="1:10" ht="15" customHeight="1">
+    <row r="144" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A144" s="33" t="s">
         <v>339</v>
       </c>
@@ -5474,7 +5489,7 @@
         <v>342</v>
       </c>
     </row>
-    <row r="145" spans="1:10" ht="15" customHeight="1">
+    <row r="145" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A145" s="7" t="s">
         <v>65</v>
       </c>
@@ -5499,60 +5514,108 @@
         <v>79</v>
       </c>
     </row>
-    <row r="146" spans="1:10" ht="15" customHeight="1">
-      <c r="A146" s="7"/>
-      <c r="B146" s="8"/>
+    <row r="146" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A146" s="7" t="s">
+        <v>351</v>
+      </c>
+      <c r="B146" s="8" t="s">
+        <v>350</v>
+      </c>
       <c r="C146" t="s">
         <v>345</v>
       </c>
       <c r="D146" s="9"/>
       <c r="E146" s="8"/>
-      <c r="F146" s="10"/>
-      <c r="G146" s="13"/>
-      <c r="H146" s="12"/>
-      <c r="I146" s="12"/>
+      <c r="F146" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="G146" s="13">
+        <v>46092</v>
+      </c>
+      <c r="H146" s="12" t="s">
+        <v>327</v>
+      </c>
+      <c r="I146" s="15" t="s">
+        <v>79</v>
+      </c>
       <c r="J146" s="6">
         <v>863457051708251</v>
       </c>
     </row>
-    <row r="147" spans="1:10" ht="15" customHeight="1">
-      <c r="A147" s="7"/>
+    <row r="147" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A147" s="7" t="s">
+        <v>333</v>
+      </c>
       <c r="B147" s="8"/>
       <c r="C147" t="s">
         <v>346</v>
       </c>
       <c r="D147" s="9"/>
       <c r="E147" s="8"/>
-      <c r="F147" s="10"/>
-      <c r="G147" s="13"/>
-      <c r="H147" s="12"/>
-      <c r="I147" s="12"/>
-    </row>
-    <row r="148" spans="1:10" ht="15" customHeight="1">
-      <c r="A148" s="7"/>
-      <c r="B148" s="8"/>
+      <c r="F147" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="G147" s="13">
+        <v>46092</v>
+      </c>
+      <c r="H147" s="12" t="s">
+        <v>327</v>
+      </c>
+      <c r="I147" s="15" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="148" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A148" s="7" t="s">
+        <v>333</v>
+      </c>
+      <c r="B148" s="8" t="s">
+        <v>352</v>
+      </c>
       <c r="C148" t="s">
         <v>347</v>
       </c>
       <c r="D148" s="9"/>
       <c r="E148" s="8"/>
-      <c r="F148" s="10"/>
-      <c r="G148" s="13"/>
-      <c r="H148" s="12"/>
-      <c r="I148" s="12"/>
-    </row>
-    <row r="149" spans="1:10" ht="15" customHeight="1">
-      <c r="A149" s="7"/>
-      <c r="B149" s="8"/>
-      <c r="C149" s="40"/>
+      <c r="F148" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="G148" s="13">
+        <v>46093</v>
+      </c>
+      <c r="H148" s="12" t="s">
+        <v>323</v>
+      </c>
+      <c r="I148" s="15" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="149" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A149" s="7" t="s">
+        <v>149</v>
+      </c>
+      <c r="B149" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="C149" s="40" t="s">
+        <v>353</v>
+      </c>
       <c r="D149" s="9"/>
       <c r="E149" s="8"/>
-      <c r="F149" s="10"/>
-      <c r="G149" s="13"/>
-      <c r="H149" s="12"/>
-      <c r="I149" s="12"/>
-    </row>
-    <row r="150" spans="1:10" ht="15" customHeight="1">
+      <c r="F149" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="G149" s="13">
+        <v>46284</v>
+      </c>
+      <c r="H149" s="12" t="s">
+        <v>354</v>
+      </c>
+      <c r="I149" s="15" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="150" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A150" s="7"/>
       <c r="B150" s="8"/>
       <c r="C150" s="40"/>
@@ -5563,7 +5626,7 @@
       <c r="H150" s="12"/>
       <c r="I150" s="12"/>
     </row>
-    <row r="151" spans="1:10" ht="15" customHeight="1">
+    <row r="151" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A151" s="7"/>
       <c r="B151" s="8"/>
       <c r="C151" s="40"/>
@@ -5574,7 +5637,7 @@
       <c r="H151" s="12"/>
       <c r="I151" s="12"/>
     </row>
-    <row r="152" spans="1:10" ht="15" customHeight="1">
+    <row r="152" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A152" s="7"/>
       <c r="B152" s="8"/>
       <c r="C152" s="40"/>
@@ -5585,7 +5648,7 @@
       <c r="H152" s="12"/>
       <c r="I152" s="12"/>
     </row>
-    <row r="153" spans="1:10" ht="15" customHeight="1">
+    <row r="153" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A153" s="7"/>
       <c r="B153" s="8"/>
       <c r="C153" s="40"/>
@@ -5596,7 +5659,7 @@
       <c r="H153" s="12"/>
       <c r="I153" s="12"/>
     </row>
-    <row r="154" spans="1:10" ht="15" customHeight="1">
+    <row r="154" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A154" s="7"/>
       <c r="B154" s="8"/>
       <c r="C154" s="40"/>
@@ -5607,7 +5670,7 @@
       <c r="H154" s="12"/>
       <c r="I154" s="12"/>
     </row>
-    <row r="155" spans="1:10" ht="15" customHeight="1">
+    <row r="155" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A155" s="7"/>
       <c r="B155" s="8"/>
       <c r="C155" s="40"/>
@@ -5618,7 +5681,7 @@
       <c r="H155" s="12"/>
       <c r="I155" s="12"/>
     </row>
-    <row r="156" spans="1:10" ht="15" customHeight="1">
+    <row r="156" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A156" s="7"/>
       <c r="B156" s="8"/>
       <c r="C156" s="40"/>
@@ -5629,7 +5692,7 @@
       <c r="H156" s="12"/>
       <c r="I156" s="12"/>
     </row>
-    <row r="157" spans="1:10" ht="15" customHeight="1">
+    <row r="157" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A157" s="7"/>
       <c r="B157" s="8"/>
       <c r="C157" s="40"/>
@@ -5640,7 +5703,7 @@
       <c r="H157" s="12"/>
       <c r="I157" s="12"/>
     </row>
-    <row r="158" spans="1:10" ht="15" customHeight="1">
+    <row r="158" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A158" s="7"/>
       <c r="B158" s="8"/>
       <c r="C158" s="40"/>
@@ -5651,7 +5714,7 @@
       <c r="H158" s="12"/>
       <c r="I158" s="12"/>
     </row>
-    <row r="159" spans="1:10" ht="15" customHeight="1">
+    <row r="159" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A159" s="7"/>
       <c r="B159" s="8"/>
       <c r="C159" s="40"/>
@@ -5662,7 +5725,7 @@
       <c r="H159" s="12"/>
       <c r="I159" s="12"/>
     </row>
-    <row r="160" spans="1:10" ht="15" customHeight="1">
+    <row r="160" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A160" s="7"/>
       <c r="B160" s="8"/>
       <c r="C160" s="40"/>
@@ -5673,7 +5736,7 @@
       <c r="H160" s="12"/>
       <c r="I160" s="12"/>
     </row>
-    <row r="161" spans="1:9" ht="15" customHeight="1">
+    <row r="161" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A161" s="7"/>
       <c r="B161" s="8"/>
       <c r="C161" s="40"/>
@@ -5684,7 +5747,7 @@
       <c r="H161" s="12"/>
       <c r="I161" s="12"/>
     </row>
-    <row r="162" spans="1:9" ht="15" customHeight="1">
+    <row r="162" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A162" s="7"/>
       <c r="B162" s="8"/>
       <c r="C162" s="40"/>
@@ -5695,7 +5758,7 @@
       <c r="H162" s="12"/>
       <c r="I162" s="12"/>
     </row>
-    <row r="163" spans="1:9" ht="15" customHeight="1">
+    <row r="163" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A163" s="7"/>
       <c r="B163" s="8"/>
       <c r="C163" s="40"/>
@@ -5706,7 +5769,7 @@
       <c r="H163" s="12"/>
       <c r="I163" s="12"/>
     </row>
-    <row r="164" spans="1:9" ht="15" customHeight="1">
+    <row r="164" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A164" s="7"/>
       <c r="B164" s="8"/>
       <c r="C164" s="40"/>
@@ -5717,7 +5780,7 @@
       <c r="H164" s="12"/>
       <c r="I164" s="12"/>
     </row>
-    <row r="165" spans="1:9" ht="15" customHeight="1">
+    <row r="165" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A165" s="7"/>
       <c r="B165" s="8"/>
       <c r="C165" s="40"/>
@@ -5728,7 +5791,7 @@
       <c r="H165" s="12"/>
       <c r="I165" s="12"/>
     </row>
-    <row r="166" spans="1:9" ht="15" customHeight="1">
+    <row r="166" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A166" s="7"/>
       <c r="B166" s="8"/>
       <c r="C166" s="40"/>
@@ -5739,7 +5802,7 @@
       <c r="H166" s="12"/>
       <c r="I166" s="12"/>
     </row>
-    <row r="167" spans="1:9" ht="15" customHeight="1">
+    <row r="167" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A167" s="7"/>
       <c r="B167" s="8"/>
       <c r="C167" s="40"/>
@@ -5750,7 +5813,7 @@
       <c r="H167" s="12"/>
       <c r="I167" s="12"/>
     </row>
-    <row r="168" spans="1:9" ht="15" customHeight="1">
+    <row r="168" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A168" s="7"/>
       <c r="B168" s="8"/>
       <c r="C168" s="40"/>
@@ -5761,7 +5824,7 @@
       <c r="H168" s="12"/>
       <c r="I168" s="12"/>
     </row>
-    <row r="169" spans="1:9" ht="15" customHeight="1">
+    <row r="169" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A169" s="7"/>
       <c r="B169" s="8"/>
       <c r="C169" s="40"/>
@@ -5772,7 +5835,7 @@
       <c r="H169" s="12"/>
       <c r="I169" s="12"/>
     </row>
-    <row r="170" spans="1:9" ht="15" customHeight="1">
+    <row r="170" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A170" s="7"/>
       <c r="B170" s="8"/>
       <c r="C170" s="40"/>
@@ -5783,7 +5846,7 @@
       <c r="H170" s="12"/>
       <c r="I170" s="12"/>
     </row>
-    <row r="171" spans="1:9" ht="15" customHeight="1">
+    <row r="171" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A171" s="7"/>
       <c r="B171" s="8"/>
       <c r="C171" s="40"/>
@@ -5794,7 +5857,7 @@
       <c r="H171" s="12"/>
       <c r="I171" s="12"/>
     </row>
-    <row r="172" spans="1:9" ht="15" customHeight="1">
+    <row r="172" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A172" s="7"/>
       <c r="B172" s="8"/>
       <c r="C172" s="40"/>
@@ -5805,7 +5868,7 @@
       <c r="H172" s="12"/>
       <c r="I172" s="12"/>
     </row>
-    <row r="173" spans="1:9" ht="15" customHeight="1">
+    <row r="173" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A173" s="7"/>
       <c r="B173" s="8"/>
       <c r="C173" s="40"/>
@@ -5816,7 +5879,7 @@
       <c r="H173" s="12"/>
       <c r="I173" s="12"/>
     </row>
-    <row r="174" spans="1:9" ht="15" customHeight="1">
+    <row r="174" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A174" s="7"/>
       <c r="B174" s="8"/>
       <c r="C174" s="40"/>
@@ -5827,7 +5890,7 @@
       <c r="H174" s="12"/>
       <c r="I174" s="12"/>
     </row>
-    <row r="175" spans="1:9" ht="15" customHeight="1">
+    <row r="175" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A175" s="7"/>
       <c r="B175" s="8"/>
       <c r="C175" s="40"/>
@@ -5838,7 +5901,7 @@
       <c r="H175" s="12"/>
       <c r="I175" s="12"/>
     </row>
-    <row r="176" spans="1:9" ht="15" customHeight="1">
+    <row r="176" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A176" s="7"/>
       <c r="B176" s="8"/>
       <c r="C176" s="40"/>
@@ -5849,7 +5912,7 @@
       <c r="H176" s="12"/>
       <c r="I176" s="12"/>
     </row>
-    <row r="177" spans="1:9" ht="15" customHeight="1">
+    <row r="177" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A177" s="7"/>
       <c r="B177" s="8"/>
       <c r="C177" s="40"/>
@@ -5860,7 +5923,7 @@
       <c r="H177" s="12"/>
       <c r="I177" s="12"/>
     </row>
-    <row r="178" spans="1:9" ht="15" customHeight="1">
+    <row r="178" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A178" s="7"/>
       <c r="B178" s="8"/>
       <c r="C178" s="40"/>
@@ -5871,7 +5934,7 @@
       <c r="H178" s="12"/>
       <c r="I178" s="12"/>
     </row>
-    <row r="179" spans="1:9" ht="15" customHeight="1">
+    <row r="179" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A179" s="7"/>
       <c r="B179" s="8"/>
       <c r="C179" s="40"/>
@@ -5882,7 +5945,7 @@
       <c r="H179" s="12"/>
       <c r="I179" s="12"/>
     </row>
-    <row r="180" spans="1:9" ht="15" customHeight="1">
+    <row r="180" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A180" s="7"/>
       <c r="B180" s="8"/>
       <c r="C180" s="40"/>
@@ -5893,7 +5956,7 @@
       <c r="H180" s="12"/>
       <c r="I180" s="12"/>
     </row>
-    <row r="181" spans="1:9" ht="15" customHeight="1">
+    <row r="181" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A181" s="7"/>
       <c r="B181" s="8"/>
       <c r="C181" s="40"/>
@@ -5904,7 +5967,7 @@
       <c r="H181" s="12"/>
       <c r="I181" s="12"/>
     </row>
-    <row r="182" spans="1:9" ht="15" customHeight="1">
+    <row r="182" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A182" s="7"/>
       <c r="B182" s="8"/>
       <c r="C182" s="40"/>
@@ -5915,7 +5978,7 @@
       <c r="H182" s="12"/>
       <c r="I182" s="12"/>
     </row>
-    <row r="183" spans="1:9" ht="15" customHeight="1">
+    <row r="183" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A183" s="7"/>
       <c r="B183" s="8"/>
       <c r="C183" s="40"/>
@@ -5926,7 +5989,7 @@
       <c r="H183" s="12"/>
       <c r="I183" s="12"/>
     </row>
-    <row r="184" spans="1:9" ht="15" customHeight="1">
+    <row r="184" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A184" s="7"/>
       <c r="B184" s="8"/>
       <c r="C184" s="40"/>
@@ -5937,7 +6000,7 @@
       <c r="H184" s="12"/>
       <c r="I184" s="12"/>
     </row>
-    <row r="185" spans="1:9" ht="15" customHeight="1">
+    <row r="185" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A185" s="7"/>
       <c r="B185" s="8"/>
       <c r="C185" s="40"/>
@@ -5948,7 +6011,7 @@
       <c r="H185" s="12"/>
       <c r="I185" s="12"/>
     </row>
-    <row r="186" spans="1:9" ht="15" customHeight="1">
+    <row r="186" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A186" s="7"/>
       <c r="B186" s="8"/>
       <c r="C186" s="40"/>
@@ -5959,7 +6022,7 @@
       <c r="H186" s="12"/>
       <c r="I186" s="12"/>
     </row>
-    <row r="187" spans="1:9" ht="15" customHeight="1">
+    <row r="187" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A187" s="7"/>
       <c r="B187" s="8"/>
       <c r="C187" s="40"/>
@@ -5970,7 +6033,7 @@
       <c r="H187" s="12"/>
       <c r="I187" s="12"/>
     </row>
-    <row r="188" spans="1:9" ht="15" customHeight="1">
+    <row r="188" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A188" s="7"/>
       <c r="B188" s="8"/>
       <c r="C188" s="40"/>
@@ -5981,7 +6044,7 @@
       <c r="H188" s="12"/>
       <c r="I188" s="12"/>
     </row>
-    <row r="189" spans="1:9" ht="15" customHeight="1">
+    <row r="189" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A189" s="7"/>
       <c r="B189" s="8"/>
       <c r="C189" s="40"/>
@@ -5992,7 +6055,7 @@
       <c r="H189" s="12"/>
       <c r="I189" s="12"/>
     </row>
-    <row r="190" spans="1:9" ht="15" customHeight="1">
+    <row r="190" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A190" s="7"/>
       <c r="B190" s="8"/>
       <c r="C190" s="40"/>
@@ -6003,7 +6066,7 @@
       <c r="H190" s="12"/>
       <c r="I190" s="12"/>
     </row>
-    <row r="191" spans="1:9" ht="15" customHeight="1">
+    <row r="191" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A191" s="7"/>
       <c r="B191" s="8"/>
       <c r="C191" s="40"/>
@@ -6014,7 +6077,7 @@
       <c r="H191" s="12"/>
       <c r="I191" s="12"/>
     </row>
-    <row r="192" spans="1:9" ht="15" customHeight="1">
+    <row r="192" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A192" s="7"/>
       <c r="B192" s="8"/>
       <c r="C192" s="40"/>
@@ -6025,7 +6088,7 @@
       <c r="H192" s="12"/>
       <c r="I192" s="12"/>
     </row>
-    <row r="193" spans="1:9" ht="15" customHeight="1">
+    <row r="193" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A193" s="7"/>
       <c r="B193" s="8"/>
       <c r="C193" s="40"/>
@@ -6036,7 +6099,7 @@
       <c r="H193" s="12"/>
       <c r="I193" s="12"/>
     </row>
-    <row r="194" spans="1:9" ht="15" customHeight="1">
+    <row r="194" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A194" s="7"/>
       <c r="B194" s="8"/>
       <c r="C194" s="40"/>
@@ -6047,7 +6110,7 @@
       <c r="H194" s="12"/>
       <c r="I194" s="12"/>
     </row>
-    <row r="195" spans="1:9" ht="15" customHeight="1">
+    <row r="195" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A195" s="7"/>
       <c r="B195" s="8"/>
       <c r="C195" s="40"/>
@@ -6058,7 +6121,7 @@
       <c r="H195" s="12"/>
       <c r="I195" s="12"/>
     </row>
-    <row r="196" spans="1:9" ht="15" customHeight="1">
+    <row r="196" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A196" s="7"/>
       <c r="B196" s="8"/>
       <c r="C196" s="40"/>
@@ -6069,7 +6132,7 @@
       <c r="H196" s="12"/>
       <c r="I196" s="12"/>
     </row>
-    <row r="197" spans="1:9" ht="15" customHeight="1">
+    <row r="197" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A197" s="7"/>
       <c r="B197" s="8"/>
       <c r="C197" s="40"/>
@@ -6080,7 +6143,7 @@
       <c r="H197" s="12"/>
       <c r="I197" s="12"/>
     </row>
-    <row r="198" spans="1:9" ht="15" customHeight="1">
+    <row r="198" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A198" s="7"/>
       <c r="B198" s="8"/>
       <c r="C198" s="40"/>
@@ -6091,7 +6154,7 @@
       <c r="H198" s="12"/>
       <c r="I198" s="12"/>
     </row>
-    <row r="199" spans="1:9" ht="15" customHeight="1">
+    <row r="199" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A199" s="7"/>
       <c r="B199" s="8"/>
       <c r="C199" s="40"/>
@@ -6102,7 +6165,7 @@
       <c r="H199" s="12"/>
       <c r="I199" s="12"/>
     </row>
-    <row r="200" spans="1:9" ht="15" customHeight="1">
+    <row r="200" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A200" s="7"/>
       <c r="B200" s="8"/>
       <c r="C200" s="40"/>
@@ -6113,7 +6176,7 @@
       <c r="H200" s="12"/>
       <c r="I200" s="12"/>
     </row>
-    <row r="201" spans="1:9" ht="15" customHeight="1">
+    <row r="201" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A201" s="7"/>
       <c r="B201" s="8"/>
       <c r="C201" s="40"/>
@@ -6124,7 +6187,7 @@
       <c r="H201" s="12"/>
       <c r="I201" s="12"/>
     </row>
-    <row r="202" spans="1:9" ht="15" customHeight="1">
+    <row r="202" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A202" s="7"/>
       <c r="B202" s="8"/>
       <c r="C202" s="40"/>
@@ -6135,7 +6198,7 @@
       <c r="H202" s="12"/>
       <c r="I202" s="12"/>
     </row>
-    <row r="203" spans="1:9" ht="15" customHeight="1">
+    <row r="203" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A203" s="7"/>
       <c r="B203" s="8"/>
       <c r="C203" s="40"/>
@@ -6146,7 +6209,7 @@
       <c r="H203" s="12"/>
       <c r="I203" s="12"/>
     </row>
-    <row r="204" spans="1:9" ht="15" customHeight="1">
+    <row r="204" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A204" s="7"/>
       <c r="B204" s="8"/>
       <c r="C204" s="40"/>
@@ -6168,29 +6231,29 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4E144160-55E5-40A6-9A8E-E41DA7F6726D}">
   <dimension ref="D2:N92"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="14.45"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="12" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="60.28515625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="58.85546875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="12.5703125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="11.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="60.26953125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="58.81640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.54296875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.26953125" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="16" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="22.5703125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="22.54296875" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="10" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="42" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="54" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="40.28515625" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="35.42578125" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="9.42578125" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="8.42578125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="40.26953125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="35.453125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="9.453125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="8.453125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="4:14">
+    <row r="2" spans="4:14" x14ac:dyDescent="0.35">
       <c r="M2" s="5"/>
       <c r="N2" s="5"/>
     </row>
-    <row r="3" spans="4:14">
+    <row r="3" spans="4:14" x14ac:dyDescent="0.35">
       <c r="D3" s="1">
         <v>868589060374017</v>
       </c>
@@ -6208,7 +6271,7 @@
         <v>46043</v>
       </c>
     </row>
-    <row r="4" spans="4:14">
+    <row r="4" spans="4:14" x14ac:dyDescent="0.35">
       <c r="D4" s="1">
         <v>868589060674226</v>
       </c>
@@ -6226,355 +6289,355 @@
         <v>46043</v>
       </c>
     </row>
-    <row r="5" spans="4:14">
+    <row r="5" spans="4:14" x14ac:dyDescent="0.35">
       <c r="M5" s="5"/>
       <c r="N5" s="5"/>
     </row>
-    <row r="6" spans="4:14">
+    <row r="6" spans="4:14" x14ac:dyDescent="0.35">
       <c r="M6" s="5"/>
       <c r="N6" s="5"/>
     </row>
-    <row r="7" spans="4:14">
+    <row r="7" spans="4:14" x14ac:dyDescent="0.35">
       <c r="M7" s="5"/>
       <c r="N7" s="5"/>
     </row>
-    <row r="8" spans="4:14">
+    <row r="8" spans="4:14" x14ac:dyDescent="0.35">
       <c r="M8" s="5"/>
       <c r="N8" s="5"/>
     </row>
-    <row r="9" spans="4:14">
+    <row r="9" spans="4:14" x14ac:dyDescent="0.35">
       <c r="M9" s="5"/>
       <c r="N9" s="5"/>
     </row>
-    <row r="10" spans="4:14">
+    <row r="10" spans="4:14" x14ac:dyDescent="0.35">
       <c r="M10" s="5"/>
       <c r="N10" s="5"/>
     </row>
-    <row r="11" spans="4:14">
+    <row r="11" spans="4:14" x14ac:dyDescent="0.35">
       <c r="M11" s="5"/>
       <c r="N11" s="5"/>
     </row>
-    <row r="12" spans="4:14">
+    <row r="12" spans="4:14" x14ac:dyDescent="0.35">
       <c r="M12" s="5"/>
       <c r="N12" s="5"/>
     </row>
-    <row r="13" spans="4:14">
+    <row r="13" spans="4:14" x14ac:dyDescent="0.35">
       <c r="M13" s="5"/>
       <c r="N13" s="5"/>
     </row>
-    <row r="14" spans="4:14">
+    <row r="14" spans="4:14" x14ac:dyDescent="0.35">
       <c r="M14" s="5"/>
       <c r="N14" s="5"/>
     </row>
-    <row r="15" spans="4:14">
+    <row r="15" spans="4:14" x14ac:dyDescent="0.35">
       <c r="M15" s="5"/>
       <c r="N15" s="5"/>
     </row>
-    <row r="16" spans="4:14">
+    <row r="16" spans="4:14" x14ac:dyDescent="0.35">
       <c r="M16" s="5"/>
       <c r="N16" s="5"/>
     </row>
-    <row r="17" spans="13:14">
+    <row r="17" spans="13:14" x14ac:dyDescent="0.35">
       <c r="M17" s="5"/>
       <c r="N17" s="5"/>
     </row>
-    <row r="18" spans="13:14">
+    <row r="18" spans="13:14" x14ac:dyDescent="0.35">
       <c r="M18" s="5"/>
       <c r="N18" s="5"/>
     </row>
-    <row r="19" spans="13:14">
+    <row r="19" spans="13:14" x14ac:dyDescent="0.35">
       <c r="M19" s="5"/>
       <c r="N19" s="5"/>
     </row>
-    <row r="20" spans="13:14">
+    <row r="20" spans="13:14" x14ac:dyDescent="0.35">
       <c r="M20" s="5"/>
       <c r="N20" s="5"/>
     </row>
-    <row r="21" spans="13:14">
+    <row r="21" spans="13:14" x14ac:dyDescent="0.35">
       <c r="M21" s="5"/>
       <c r="N21" s="5"/>
     </row>
-    <row r="22" spans="13:14">
+    <row r="22" spans="13:14" x14ac:dyDescent="0.35">
       <c r="M22" s="5"/>
       <c r="N22" s="5"/>
     </row>
-    <row r="23" spans="13:14">
+    <row r="23" spans="13:14" x14ac:dyDescent="0.35">
       <c r="M23" s="5"/>
       <c r="N23" s="5"/>
     </row>
-    <row r="24" spans="13:14">
+    <row r="24" spans="13:14" x14ac:dyDescent="0.35">
       <c r="M24" s="5"/>
       <c r="N24" s="5"/>
     </row>
-    <row r="25" spans="13:14">
+    <row r="25" spans="13:14" x14ac:dyDescent="0.35">
       <c r="M25" s="5"/>
       <c r="N25" s="5"/>
     </row>
-    <row r="26" spans="13:14">
+    <row r="26" spans="13:14" x14ac:dyDescent="0.35">
       <c r="M26" s="5"/>
       <c r="N26" s="5"/>
     </row>
-    <row r="27" spans="13:14">
+    <row r="27" spans="13:14" x14ac:dyDescent="0.35">
       <c r="M27" s="5"/>
       <c r="N27" s="5"/>
     </row>
-    <row r="28" spans="13:14">
+    <row r="28" spans="13:14" x14ac:dyDescent="0.35">
       <c r="M28" s="5"/>
       <c r="N28" s="5"/>
     </row>
-    <row r="29" spans="13:14">
+    <row r="29" spans="13:14" x14ac:dyDescent="0.35">
       <c r="M29" s="5"/>
       <c r="N29" s="5"/>
     </row>
-    <row r="30" spans="13:14">
+    <row r="30" spans="13:14" x14ac:dyDescent="0.35">
       <c r="M30" s="5"/>
       <c r="N30" s="5"/>
     </row>
-    <row r="31" spans="13:14">
+    <row r="31" spans="13:14" x14ac:dyDescent="0.35">
       <c r="M31" s="5"/>
       <c r="N31" s="5"/>
     </row>
-    <row r="32" spans="13:14">
+    <row r="32" spans="13:14" x14ac:dyDescent="0.35">
       <c r="M32" s="5"/>
       <c r="N32" s="5"/>
     </row>
-    <row r="33" spans="13:14">
+    <row r="33" spans="13:14" x14ac:dyDescent="0.35">
       <c r="M33" s="5"/>
       <c r="N33" s="5"/>
     </row>
-    <row r="34" spans="13:14">
+    <row r="34" spans="13:14" x14ac:dyDescent="0.35">
       <c r="M34" s="5"/>
       <c r="N34" s="5"/>
     </row>
-    <row r="35" spans="13:14">
+    <row r="35" spans="13:14" x14ac:dyDescent="0.35">
       <c r="M35" s="5"/>
       <c r="N35" s="5"/>
     </row>
-    <row r="36" spans="13:14">
+    <row r="36" spans="13:14" x14ac:dyDescent="0.35">
       <c r="M36" s="5"/>
       <c r="N36" s="5"/>
     </row>
-    <row r="37" spans="13:14">
+    <row r="37" spans="13:14" x14ac:dyDescent="0.35">
       <c r="M37" s="5"/>
       <c r="N37" s="5"/>
     </row>
-    <row r="38" spans="13:14">
+    <row r="38" spans="13:14" x14ac:dyDescent="0.35">
       <c r="M38" s="5"/>
       <c r="N38" s="5"/>
     </row>
-    <row r="39" spans="13:14">
+    <row r="39" spans="13:14" x14ac:dyDescent="0.35">
       <c r="M39" s="5"/>
       <c r="N39" s="5"/>
     </row>
-    <row r="40" spans="13:14">
+    <row r="40" spans="13:14" x14ac:dyDescent="0.35">
       <c r="M40" s="5"/>
       <c r="N40" s="5"/>
     </row>
-    <row r="41" spans="13:14">
+    <row r="41" spans="13:14" x14ac:dyDescent="0.35">
       <c r="M41" s="5"/>
       <c r="N41" s="5"/>
     </row>
-    <row r="42" spans="13:14">
+    <row r="42" spans="13:14" x14ac:dyDescent="0.35">
       <c r="M42" s="5"/>
       <c r="N42" s="5"/>
     </row>
-    <row r="43" spans="13:14">
+    <row r="43" spans="13:14" x14ac:dyDescent="0.35">
       <c r="M43" s="5"/>
       <c r="N43" s="5"/>
     </row>
-    <row r="44" spans="13:14">
+    <row r="44" spans="13:14" x14ac:dyDescent="0.35">
       <c r="M44" s="5"/>
       <c r="N44" s="5"/>
     </row>
-    <row r="45" spans="13:14">
+    <row r="45" spans="13:14" x14ac:dyDescent="0.35">
       <c r="M45" s="5"/>
       <c r="N45" s="5"/>
     </row>
-    <row r="46" spans="13:14">
+    <row r="46" spans="13:14" x14ac:dyDescent="0.35">
       <c r="M46" s="5"/>
       <c r="N46" s="5"/>
     </row>
-    <row r="47" spans="13:14">
+    <row r="47" spans="13:14" x14ac:dyDescent="0.35">
       <c r="M47" s="5"/>
       <c r="N47" s="5"/>
     </row>
-    <row r="48" spans="13:14">
+    <row r="48" spans="13:14" x14ac:dyDescent="0.35">
       <c r="M48" s="5"/>
       <c r="N48" s="5"/>
     </row>
-    <row r="49" spans="13:14">
+    <row r="49" spans="13:14" x14ac:dyDescent="0.35">
       <c r="M49" s="5"/>
       <c r="N49" s="5"/>
     </row>
-    <row r="50" spans="13:14">
+    <row r="50" spans="13:14" x14ac:dyDescent="0.35">
       <c r="M50" s="5"/>
       <c r="N50" s="5"/>
     </row>
-    <row r="51" spans="13:14">
+    <row r="51" spans="13:14" x14ac:dyDescent="0.35">
       <c r="M51" s="5"/>
       <c r="N51" s="5"/>
     </row>
-    <row r="52" spans="13:14">
+    <row r="52" spans="13:14" x14ac:dyDescent="0.35">
       <c r="M52" s="5"/>
       <c r="N52" s="5"/>
     </row>
-    <row r="53" spans="13:14">
+    <row r="53" spans="13:14" x14ac:dyDescent="0.35">
       <c r="M53" s="5"/>
       <c r="N53" s="5"/>
     </row>
-    <row r="54" spans="13:14">
+    <row r="54" spans="13:14" x14ac:dyDescent="0.35">
       <c r="M54" s="5"/>
       <c r="N54" s="5"/>
     </row>
-    <row r="55" spans="13:14">
+    <row r="55" spans="13:14" x14ac:dyDescent="0.35">
       <c r="M55" s="5"/>
       <c r="N55" s="5"/>
     </row>
-    <row r="56" spans="13:14">
+    <row r="56" spans="13:14" x14ac:dyDescent="0.35">
       <c r="M56" s="5"/>
       <c r="N56" s="5"/>
     </row>
-    <row r="57" spans="13:14">
+    <row r="57" spans="13:14" x14ac:dyDescent="0.35">
       <c r="M57" s="5"/>
       <c r="N57" s="5"/>
     </row>
-    <row r="58" spans="13:14">
+    <row r="58" spans="13:14" x14ac:dyDescent="0.35">
       <c r="M58" s="5"/>
       <c r="N58" s="5"/>
     </row>
-    <row r="59" spans="13:14">
+    <row r="59" spans="13:14" x14ac:dyDescent="0.35">
       <c r="M59" s="5"/>
       <c r="N59" s="5"/>
     </row>
-    <row r="60" spans="13:14">
+    <row r="60" spans="13:14" x14ac:dyDescent="0.35">
       <c r="M60" s="5"/>
       <c r="N60" s="5"/>
     </row>
-    <row r="61" spans="13:14">
+    <row r="61" spans="13:14" x14ac:dyDescent="0.35">
       <c r="M61" s="5"/>
       <c r="N61" s="5"/>
     </row>
-    <row r="62" spans="13:14">
+    <row r="62" spans="13:14" x14ac:dyDescent="0.35">
       <c r="M62" s="5"/>
       <c r="N62" s="5"/>
     </row>
-    <row r="63" spans="13:14">
+    <row r="63" spans="13:14" x14ac:dyDescent="0.35">
       <c r="M63" s="5"/>
       <c r="N63" s="5"/>
     </row>
-    <row r="64" spans="13:14">
+    <row r="64" spans="13:14" x14ac:dyDescent="0.35">
       <c r="M64" s="5"/>
       <c r="N64" s="5"/>
     </row>
-    <row r="65" spans="13:14">
+    <row r="65" spans="13:14" x14ac:dyDescent="0.35">
       <c r="M65" s="5"/>
       <c r="N65" s="5"/>
     </row>
-    <row r="66" spans="13:14">
+    <row r="66" spans="13:14" x14ac:dyDescent="0.35">
       <c r="M66" s="5"/>
       <c r="N66" s="5"/>
     </row>
-    <row r="67" spans="13:14">
+    <row r="67" spans="13:14" x14ac:dyDescent="0.35">
       <c r="M67" s="5"/>
       <c r="N67" s="5"/>
     </row>
-    <row r="68" spans="13:14">
+    <row r="68" spans="13:14" x14ac:dyDescent="0.35">
       <c r="M68" s="5"/>
       <c r="N68" s="5"/>
     </row>
-    <row r="69" spans="13:14">
+    <row r="69" spans="13:14" x14ac:dyDescent="0.35">
       <c r="M69" s="5"/>
       <c r="N69" s="5"/>
     </row>
-    <row r="70" spans="13:14">
+    <row r="70" spans="13:14" x14ac:dyDescent="0.35">
       <c r="M70" s="5"/>
       <c r="N70" s="5"/>
     </row>
-    <row r="71" spans="13:14">
+    <row r="71" spans="13:14" x14ac:dyDescent="0.35">
       <c r="M71" s="5"/>
       <c r="N71" s="5"/>
     </row>
-    <row r="72" spans="13:14">
+    <row r="72" spans="13:14" x14ac:dyDescent="0.35">
       <c r="M72" s="5"/>
       <c r="N72" s="5"/>
     </row>
-    <row r="73" spans="13:14">
+    <row r="73" spans="13:14" x14ac:dyDescent="0.35">
       <c r="M73" s="5"/>
       <c r="N73" s="5"/>
     </row>
-    <row r="74" spans="13:14">
+    <row r="74" spans="13:14" x14ac:dyDescent="0.35">
       <c r="M74" s="5"/>
       <c r="N74" s="5"/>
     </row>
-    <row r="75" spans="13:14">
+    <row r="75" spans="13:14" x14ac:dyDescent="0.35">
       <c r="M75" s="5"/>
       <c r="N75" s="5"/>
     </row>
-    <row r="76" spans="13:14">
+    <row r="76" spans="13:14" x14ac:dyDescent="0.35">
       <c r="M76" s="5"/>
       <c r="N76" s="5"/>
     </row>
-    <row r="77" spans="13:14">
+    <row r="77" spans="13:14" x14ac:dyDescent="0.35">
       <c r="M77" s="5"/>
       <c r="N77" s="5"/>
     </row>
-    <row r="78" spans="13:14">
+    <row r="78" spans="13:14" x14ac:dyDescent="0.35">
       <c r="M78" s="5"/>
       <c r="N78" s="5"/>
     </row>
-    <row r="79" spans="13:14">
+    <row r="79" spans="13:14" x14ac:dyDescent="0.35">
       <c r="M79" s="5"/>
       <c r="N79" s="5"/>
     </row>
-    <row r="80" spans="13:14">
+    <row r="80" spans="13:14" x14ac:dyDescent="0.35">
       <c r="M80" s="5"/>
       <c r="N80" s="5"/>
     </row>
-    <row r="81" spans="13:14">
+    <row r="81" spans="13:14" x14ac:dyDescent="0.35">
       <c r="M81" s="5"/>
       <c r="N81" s="5"/>
     </row>
-    <row r="82" spans="13:14">
+    <row r="82" spans="13:14" x14ac:dyDescent="0.35">
       <c r="M82" s="5"/>
       <c r="N82" s="5"/>
     </row>
-    <row r="83" spans="13:14">
+    <row r="83" spans="13:14" x14ac:dyDescent="0.35">
       <c r="M83" s="5"/>
       <c r="N83" s="5"/>
     </row>
-    <row r="84" spans="13:14">
+    <row r="84" spans="13:14" x14ac:dyDescent="0.35">
       <c r="M84" s="5"/>
       <c r="N84" s="5"/>
     </row>
-    <row r="85" spans="13:14">
+    <row r="85" spans="13:14" x14ac:dyDescent="0.35">
       <c r="M85" s="5"/>
       <c r="N85" s="5"/>
     </row>
-    <row r="86" spans="13:14">
+    <row r="86" spans="13:14" x14ac:dyDescent="0.35">
       <c r="M86" s="5"/>
       <c r="N86" s="5"/>
     </row>
-    <row r="87" spans="13:14">
+    <row r="87" spans="13:14" x14ac:dyDescent="0.35">
       <c r="M87" s="5"/>
       <c r="N87" s="5"/>
     </row>
-    <row r="88" spans="13:14">
+    <row r="88" spans="13:14" x14ac:dyDescent="0.35">
       <c r="M88" s="5"/>
       <c r="N88" s="5"/>
     </row>
-    <row r="89" spans="13:14">
+    <row r="89" spans="13:14" x14ac:dyDescent="0.35">
       <c r="M89" s="5"/>
       <c r="N89" s="5"/>
     </row>
-    <row r="90" spans="13:14">
+    <row r="90" spans="13:14" x14ac:dyDescent="0.35">
       <c r="M90" s="5"/>
       <c r="N90" s="5"/>
     </row>
-    <row r="91" spans="13:14">
+    <row r="91" spans="13:14" x14ac:dyDescent="0.35">
       <c r="M91" s="5"/>
       <c r="N91" s="5"/>
     </row>
-    <row r="92" spans="13:14">
+    <row r="92" spans="13:14" x14ac:dyDescent="0.35">
       <c r="M92" s="5"/>
       <c r="N92" s="5"/>
     </row>
@@ -6584,12 +6647,11 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_activity xmlns="3e53c16e-6636-411e-b1c4-e9eeb71b3b2a" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -6826,21 +6888,47 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_activity xmlns="3e53c16e-6636-411e-b1c4-e9eeb71b3b2a" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3C8123E5-81FD-4C24-91F1-33BC079967E9}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D9861A25-610F-425F-BC6A-AC52D4971411}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="3e53c16e-6636-411e-b1c4-e9eeb71b3b2a"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4794C7E6-B89D-4081-9A67-B8D500EF1EE4}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4794C7E6-B89D-4081-9A67-B8D500EF1EE4}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="3e53c16e-6636-411e-b1c4-e9eeb71b3b2a"/>
+    <ds:schemaRef ds:uri="bda9c1ec-c4e2-44f9-929c-ca399fe36c88"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D9861A25-610F-425F-BC6A-AC52D4971411}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3C8123E5-81FD-4C24-91F1-33BC079967E9}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/data/bitacora.xlsx
+++ b/data/bitacora.xlsx
@@ -6655,6 +6655,15 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x010100027709BF533FA442AFC4A8B2C0110727" ma:contentTypeVersion="15" ma:contentTypeDescription="Crear nuevo documento." ma:contentTypeScope="" ma:versionID="a37fc0d7c302f7619d355a49e1f175a4">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="3e53c16e-6636-411e-b1c4-e9eeb71b3b2a" xmlns:ns4="bda9c1ec-c4e2-44f9-929c-ca399fe36c88" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="01250a30c504a808427f15ccf149ee4d" ns3:_="" ns4:_="">
     <xsd:import namespace="3e53c16e-6636-411e-b1c4-e9eeb71b3b2a"/>
@@ -6887,15 +6896,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D9861A25-610F-425F-BC6A-AC52D4971411}">
   <ds:schemaRefs>
@@ -6907,6 +6907,14 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3C8123E5-81FD-4C24-91F1-33BC079967E9}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4794C7E6-B89D-4081-9A67-B8D500EF1EE4}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -6923,12 +6931,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3C8123E5-81FD-4C24-91F1-33BC079967E9}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/data/bitacora.xlsx
+++ b/data/bitacora.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://grupokaufmann-my.sharepoint.com/personal/samuel_sanchez_grupokaufmann_com/Documents/Documentos/Dev/bitacora_diaria/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="391" documentId="8_{4616FF0F-C10E-4DFE-8F27-869B9C60E0F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{319077C7-3FD3-4156-8F5E-D4B5E2AA648D}"/>
+  <xr:revisionPtr revIDLastSave="452" documentId="8_{4616FF0F-C10E-4DFE-8F27-869B9C60E0F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C6702C49-8E3D-4DA8-B4CD-16B6C302CDE0}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-1155" windowWidth="29040" windowHeight="15720" xr2:uid="{A9E3F017-9040-47A2-B586-0486128F3261}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="811" uniqueCount="355">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="813" uniqueCount="355">
   <si>
     <t>FLOTA</t>
   </si>
@@ -1136,7 +1136,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="11">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1176,6 +1176,24 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFF0000"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC00000"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1340,7 +1358,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="44">
+  <cellXfs count="67">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -1392,9 +1410,6 @@
     <xf numFmtId="0" fontId="2" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="14" fontId="0" fillId="5" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1435,6 +1450,54 @@
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="8" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="9" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="10" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1665,7 +1728,13 @@
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{40364ABC-409D-4532-8E14-9D155F80C509}" name="Tabla1" displayName="Tabla1" ref="A1:J205" totalsRowShown="0">
-  <autoFilter ref="A1:J205" xr:uid="{40364ABC-409D-4532-8E14-9D155F80C509}"/>
+  <autoFilter ref="A1:J205" xr:uid="{40364ABC-409D-4532-8E14-9D155F80C509}">
+    <filterColumn colId="5">
+      <filters>
+        <filter val="Reparado"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <tableColumns count="10">
     <tableColumn id="1" xr3:uid="{0A7C6585-5C8B-46BF-ABA0-2DA806D161DC}" name="FLOTA" dataDxfId="9"/>
     <tableColumn id="2" xr3:uid="{EB7792BB-219D-496F-9F16-84F6805E0CB0}" name="VIN CON PROBLEMAS" dataDxfId="8"/>
@@ -1999,12 +2068,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EDA66EBA-6B88-4C75-8217-0B7E221D898D}">
-  <dimension ref="A1:L204"/>
+  <dimension ref="A1:L205"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.453125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="43" style="6" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="22.7265625" style="6" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.26953125" style="43" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.26953125" style="42" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="25" style="6" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="40.26953125" style="6" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="27.54296875" style="6" bestFit="1" customWidth="1"/>
@@ -2021,7 +2090,7 @@
       <c r="B1" s="18" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="39" t="s">
+      <c r="C1" s="38" t="s">
         <v>2</v>
       </c>
       <c r="D1" s="19" t="s">
@@ -2046,14 +2115,14 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:12" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:12" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A2" s="7" t="s">
         <v>10</v>
       </c>
       <c r="B2" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="C2" s="40" t="s">
+      <c r="C2" s="39" t="s">
         <v>12</v>
       </c>
       <c r="D2" s="9">
@@ -2069,14 +2138,14 @@
       <c r="H2" s="12"/>
       <c r="I2" s="12"/>
     </row>
-    <row r="3" spans="1:12" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:12" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A3" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="B3" s="8" t="s">
+      <c r="B3" s="43" t="s">
         <v>15</v>
       </c>
-      <c r="C3" s="40" t="s">
+      <c r="C3" s="39" t="s">
         <v>16</v>
       </c>
       <c r="D3" s="9">
@@ -2099,7 +2168,7 @@
       <c r="B4" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="C4" s="40" t="s">
+      <c r="C4" s="39" t="s">
         <v>18</v>
       </c>
       <c r="D4" s="9">
@@ -2109,9 +2178,11 @@
         <v>13</v>
       </c>
       <c r="F4" s="10" t="s">
-        <v>14</v>
-      </c>
-      <c r="G4" s="11"/>
+        <v>77</v>
+      </c>
+      <c r="G4" s="13">
+        <v>46099</v>
+      </c>
       <c r="H4" s="12"/>
       <c r="I4" s="12"/>
     </row>
@@ -2122,7 +2193,7 @@
       <c r="B5" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="C5" s="40" t="s">
+      <c r="C5" s="39" t="s">
         <v>20</v>
       </c>
       <c r="D5" s="9">
@@ -2132,9 +2203,11 @@
         <v>13</v>
       </c>
       <c r="F5" s="10" t="s">
-        <v>14</v>
-      </c>
-      <c r="G5" s="11"/>
+        <v>77</v>
+      </c>
+      <c r="G5" s="13">
+        <v>46104</v>
+      </c>
       <c r="H5" s="12"/>
       <c r="I5" s="12"/>
     </row>
@@ -2145,7 +2218,7 @@
       <c r="B6" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="C6" s="40" t="s">
+      <c r="C6" s="39" t="s">
         <v>22</v>
       </c>
       <c r="D6" s="9">
@@ -2155,20 +2228,22 @@
         <v>13</v>
       </c>
       <c r="F6" s="10" t="s">
-        <v>14</v>
-      </c>
-      <c r="G6" s="11"/>
+        <v>77</v>
+      </c>
+      <c r="G6" s="13">
+        <v>46099</v>
+      </c>
       <c r="H6" s="12"/>
       <c r="I6" s="12"/>
     </row>
-    <row r="7" spans="1:12" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:12" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A7" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="B7" s="8" t="s">
+      <c r="B7" s="43" t="s">
         <v>23</v>
       </c>
-      <c r="C7" s="40" t="s">
+      <c r="C7" s="39" t="s">
         <v>24</v>
       </c>
       <c r="D7" s="9">
@@ -2191,7 +2266,7 @@
       <c r="B8" s="8" t="s">
         <v>25</v>
       </c>
-      <c r="C8" s="40" t="s">
+      <c r="C8" s="39" t="s">
         <v>26</v>
       </c>
       <c r="D8" s="9">
@@ -2201,20 +2276,22 @@
         <v>13</v>
       </c>
       <c r="F8" s="10" t="s">
-        <v>14</v>
-      </c>
-      <c r="G8" s="25"/>
+        <v>77</v>
+      </c>
+      <c r="G8" s="23">
+        <v>46091</v>
+      </c>
       <c r="H8" s="24"/>
       <c r="I8" s="24"/>
     </row>
-    <row r="9" spans="1:12" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:12" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A9" s="7" t="s">
         <v>10</v>
       </c>
       <c r="B9" s="8" t="s">
         <v>27</v>
       </c>
-      <c r="C9" s="40" t="s">
+      <c r="C9" s="39" t="s">
         <v>28</v>
       </c>
       <c r="D9" s="9">
@@ -2230,14 +2307,14 @@
       <c r="H9" s="12"/>
       <c r="I9" s="12"/>
     </row>
-    <row r="10" spans="1:12" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:12" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A10" s="7" t="s">
         <v>10</v>
       </c>
       <c r="B10" s="8" t="s">
         <v>29</v>
       </c>
-      <c r="C10" s="40" t="s">
+      <c r="C10" s="39" t="s">
         <v>30</v>
       </c>
       <c r="D10" s="9">
@@ -2260,7 +2337,7 @@
       <c r="B11" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="C11" s="40" t="s">
+      <c r="C11" s="39" t="s">
         <v>32</v>
       </c>
       <c r="D11" s="9">
@@ -2270,20 +2347,22 @@
         <v>13</v>
       </c>
       <c r="F11" s="10" t="s">
-        <v>14</v>
-      </c>
-      <c r="G11" s="11"/>
+        <v>77</v>
+      </c>
+      <c r="G11" s="13">
+        <v>46099</v>
+      </c>
       <c r="H11" s="12"/>
       <c r="I11" s="12"/>
     </row>
-    <row r="12" spans="1:12" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:12" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A12" s="7" t="s">
         <v>33</v>
       </c>
       <c r="B12" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="C12" s="40" t="s">
+      <c r="C12" s="39" t="s">
         <v>35</v>
       </c>
       <c r="D12" s="9">
@@ -2298,16 +2377,16 @@
       <c r="G12" s="11"/>
       <c r="H12" s="12"/>
       <c r="I12" s="12"/>
-      <c r="L12" s="26"/>
-    </row>
-    <row r="13" spans="1:12" ht="14.5" x14ac:dyDescent="0.35">
+      <c r="L12" s="25"/>
+    </row>
+    <row r="13" spans="1:12" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A13" s="7" t="s">
         <v>33</v>
       </c>
       <c r="B13" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="C13" s="40" t="s">
+      <c r="C13" s="39" t="s">
         <v>38</v>
       </c>
       <c r="D13" s="9">
@@ -2323,14 +2402,14 @@
       <c r="H13" s="12"/>
       <c r="I13" s="12"/>
     </row>
-    <row r="14" spans="1:12" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:12" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A14" s="7" t="s">
         <v>33</v>
       </c>
       <c r="B14" s="8" t="s">
         <v>39</v>
       </c>
-      <c r="C14" s="40" t="s">
+      <c r="C14" s="39" t="s">
         <v>40</v>
       </c>
       <c r="D14" s="9">
@@ -2346,14 +2425,14 @@
       <c r="H14" s="12"/>
       <c r="I14" s="12"/>
     </row>
-    <row r="15" spans="1:12" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:12" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A15" s="7" t="s">
         <v>33</v>
       </c>
       <c r="B15" s="8" t="s">
         <v>41</v>
       </c>
-      <c r="C15" s="40" t="s">
+      <c r="C15" s="39" t="s">
         <v>42</v>
       </c>
       <c r="D15" s="9">
@@ -2369,37 +2448,37 @@
       <c r="H15" s="12"/>
       <c r="I15" s="12"/>
     </row>
-    <row r="16" spans="1:12" ht="14.5" x14ac:dyDescent="0.35">
-      <c r="A16" s="7" t="s">
+    <row r="16" spans="1:12" s="50" customFormat="1" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A16" s="44" t="s">
         <v>33</v>
       </c>
-      <c r="B16" s="8" t="s">
+      <c r="B16" s="43" t="s">
         <v>43</v>
       </c>
-      <c r="C16" s="40" t="s">
+      <c r="C16" s="45" t="s">
         <v>44</v>
       </c>
-      <c r="D16" s="9">
+      <c r="D16" s="46">
         <v>46112</v>
       </c>
-      <c r="E16" s="8" t="s">
+      <c r="E16" s="43" t="s">
         <v>36</v>
       </c>
-      <c r="F16" s="10" t="s">
+      <c r="F16" s="47" t="s">
         <v>14</v>
       </c>
-      <c r="G16" s="11"/>
-      <c r="H16" s="12"/>
-      <c r="I16" s="12"/>
-    </row>
-    <row r="17" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
+      <c r="G16" s="48"/>
+      <c r="H16" s="49"/>
+      <c r="I16" s="49"/>
+    </row>
+    <row r="17" spans="1:9" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A17" s="7" t="s">
         <v>33</v>
       </c>
       <c r="B17" s="8" t="s">
         <v>45</v>
       </c>
-      <c r="C17" s="40" t="s">
+      <c r="C17" s="39" t="s">
         <v>46</v>
       </c>
       <c r="D17" s="9">
@@ -2415,14 +2494,14 @@
       <c r="H17" s="12"/>
       <c r="I17" s="12"/>
     </row>
-    <row r="18" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:9" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A18" s="7" t="s">
         <v>33</v>
       </c>
       <c r="B18" s="8" t="s">
         <v>47</v>
       </c>
-      <c r="C18" s="40" t="s">
+      <c r="C18" s="39" t="s">
         <v>48</v>
       </c>
       <c r="D18" s="9">
@@ -2438,14 +2517,14 @@
       <c r="H18" s="12"/>
       <c r="I18" s="12"/>
     </row>
-    <row r="19" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:9" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A19" s="7" t="s">
         <v>33</v>
       </c>
       <c r="B19" s="8" t="s">
         <v>49</v>
       </c>
-      <c r="C19" s="40" t="s">
+      <c r="C19" s="39" t="s">
         <v>50</v>
       </c>
       <c r="D19" s="9">
@@ -2461,14 +2540,14 @@
       <c r="H19" s="12"/>
       <c r="I19" s="12"/>
     </row>
-    <row r="20" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:9" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A20" s="7" t="s">
         <v>51</v>
       </c>
       <c r="B20" s="8" t="s">
         <v>52</v>
       </c>
-      <c r="C20" s="40" t="s">
+      <c r="C20" s="39" t="s">
         <v>53</v>
       </c>
       <c r="D20" s="9">
@@ -2484,14 +2563,14 @@
       <c r="H20" s="12"/>
       <c r="I20" s="12"/>
     </row>
-    <row r="21" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:9" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A21" s="7" t="s">
         <v>51</v>
       </c>
       <c r="B21" s="8" t="s">
         <v>55</v>
       </c>
-      <c r="C21" s="40" t="s">
+      <c r="C21" s="39" t="s">
         <v>56</v>
       </c>
       <c r="D21" s="9">
@@ -2507,14 +2586,14 @@
       <c r="H21" s="12"/>
       <c r="I21" s="12"/>
     </row>
-    <row r="22" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:9" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A22" s="7" t="s">
         <v>51</v>
       </c>
       <c r="B22" s="8" t="s">
         <v>57</v>
       </c>
-      <c r="C22" s="40" t="s">
+      <c r="C22" s="39" t="s">
         <v>58</v>
       </c>
       <c r="D22" s="9">
@@ -2530,14 +2609,14 @@
       <c r="H22" s="12"/>
       <c r="I22" s="12"/>
     </row>
-    <row r="23" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:9" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A23" s="7" t="s">
         <v>59</v>
       </c>
       <c r="B23" s="8" t="s">
         <v>60</v>
       </c>
-      <c r="C23" s="40" t="s">
+      <c r="C23" s="39" t="s">
         <v>61</v>
       </c>
       <c r="D23" s="9">
@@ -2553,14 +2632,14 @@
       <c r="H23" s="12"/>
       <c r="I23" s="12"/>
     </row>
-    <row r="24" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:9" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A24" s="7" t="s">
         <v>59</v>
       </c>
       <c r="B24" s="8" t="s">
         <v>63</v>
       </c>
-      <c r="C24" s="40" t="s">
+      <c r="C24" s="39" t="s">
         <v>64</v>
       </c>
       <c r="D24" s="9">
@@ -2576,14 +2655,14 @@
       <c r="H24" s="12"/>
       <c r="I24" s="12"/>
     </row>
-    <row r="25" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:9" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A25" s="7" t="s">
         <v>65</v>
       </c>
       <c r="B25" s="8" t="s">
         <v>66</v>
       </c>
-      <c r="C25" s="40" t="s">
+      <c r="C25" s="39" t="s">
         <v>67</v>
       </c>
       <c r="D25" s="9">
@@ -2599,14 +2678,14 @@
       <c r="H25" s="12"/>
       <c r="I25" s="12"/>
     </row>
-    <row r="26" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:9" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A26" s="7" t="s">
         <v>65</v>
       </c>
       <c r="B26" s="8" t="s">
         <v>68</v>
       </c>
-      <c r="C26" s="40" t="s">
+      <c r="C26" s="39" t="s">
         <v>69</v>
       </c>
       <c r="D26" s="9">
@@ -2622,14 +2701,14 @@
       <c r="H26" s="12"/>
       <c r="I26" s="12"/>
     </row>
-    <row r="27" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:9" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A27" s="7" t="s">
         <v>65</v>
       </c>
       <c r="B27" s="8" t="s">
         <v>71</v>
       </c>
-      <c r="C27" s="40" t="s">
+      <c r="C27" s="39" t="s">
         <v>72</v>
       </c>
       <c r="D27" s="9">
@@ -2645,14 +2724,14 @@
       <c r="H27" s="12"/>
       <c r="I27" s="12"/>
     </row>
-    <row r="28" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:9" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A28" s="7" t="s">
         <v>65</v>
       </c>
       <c r="B28" s="8" t="s">
         <v>73</v>
       </c>
-      <c r="C28" s="40" t="s">
+      <c r="C28" s="39" t="s">
         <v>74</v>
       </c>
       <c r="D28" s="9">
@@ -2675,7 +2754,7 @@
       <c r="B29" s="8" t="s">
         <v>75</v>
       </c>
-      <c r="C29" s="40" t="s">
+      <c r="C29" s="39" t="s">
         <v>76</v>
       </c>
       <c r="D29" s="9">
@@ -2697,14 +2776,14 @@
         <v>79</v>
       </c>
     </row>
-    <row r="30" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:9" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A30" s="7" t="s">
         <v>80</v>
       </c>
       <c r="B30" s="8" t="s">
         <v>81</v>
       </c>
-      <c r="C30" s="40" t="s">
+      <c r="C30" s="39" t="s">
         <v>82</v>
       </c>
       <c r="D30" s="9">
@@ -2720,14 +2799,14 @@
       <c r="H30" s="12"/>
       <c r="I30" s="12"/>
     </row>
-    <row r="31" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:9" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A31" s="7" t="s">
         <v>80</v>
       </c>
       <c r="B31" s="8" t="s">
         <v>83</v>
       </c>
-      <c r="C31" s="40" t="s">
+      <c r="C31" s="39" t="s">
         <v>84</v>
       </c>
       <c r="D31" s="9">
@@ -2743,14 +2822,14 @@
       <c r="H31" s="12"/>
       <c r="I31" s="12"/>
     </row>
-    <row r="32" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:9" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A32" s="7" t="s">
         <v>80</v>
       </c>
       <c r="B32" s="8" t="s">
         <v>85</v>
       </c>
-      <c r="C32" s="40" t="s">
+      <c r="C32" s="39" t="s">
         <v>86</v>
       </c>
       <c r="D32" s="9">
@@ -2766,14 +2845,14 @@
       <c r="H32" s="12"/>
       <c r="I32" s="12"/>
     </row>
-    <row r="33" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:9" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A33" s="7" t="s">
         <v>80</v>
       </c>
       <c r="B33" s="8" t="s">
         <v>87</v>
       </c>
-      <c r="C33" s="40" t="s">
+      <c r="C33" s="39" t="s">
         <v>88</v>
       </c>
       <c r="D33" s="9">
@@ -2789,14 +2868,14 @@
       <c r="H33" s="12"/>
       <c r="I33" s="12"/>
     </row>
-    <row r="34" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:9" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A34" s="7" t="s">
         <v>80</v>
       </c>
       <c r="B34" s="8" t="s">
         <v>89</v>
       </c>
-      <c r="C34" s="40" t="s">
+      <c r="C34" s="39" t="s">
         <v>90</v>
       </c>
       <c r="D34" s="9">
@@ -2812,37 +2891,37 @@
       <c r="H34" s="12"/>
       <c r="I34" s="12"/>
     </row>
-    <row r="35" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
-      <c r="A35" s="7" t="s">
+    <row r="35" spans="1:9" s="50" customFormat="1" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A35" s="44" t="s">
         <v>80</v>
       </c>
-      <c r="B35" s="8" t="s">
+      <c r="B35" s="43" t="s">
         <v>91</v>
       </c>
-      <c r="C35" s="40" t="s">
+      <c r="C35" s="45" t="s">
         <v>92</v>
       </c>
-      <c r="D35" s="9">
+      <c r="D35" s="46">
         <v>46204</v>
       </c>
-      <c r="E35" s="8" t="s">
+      <c r="E35" s="43" t="s">
         <v>13</v>
       </c>
-      <c r="F35" s="10" t="s">
+      <c r="F35" s="47" t="s">
         <v>14</v>
       </c>
-      <c r="G35" s="11"/>
-      <c r="H35" s="12"/>
-      <c r="I35" s="12"/>
-    </row>
-    <row r="36" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
+      <c r="G35" s="48"/>
+      <c r="H35" s="49"/>
+      <c r="I35" s="49"/>
+    </row>
+    <row r="36" spans="1:9" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A36" s="7" t="s">
         <v>80</v>
       </c>
       <c r="B36" s="8" t="s">
         <v>93</v>
       </c>
-      <c r="C36" s="40" t="s">
+      <c r="C36" s="39" t="s">
         <v>94</v>
       </c>
       <c r="D36" s="9">
@@ -2865,7 +2944,7 @@
       <c r="B37" s="8" t="s">
         <v>96</v>
       </c>
-      <c r="C37" s="40" t="s">
+      <c r="C37" s="39" t="s">
         <v>97</v>
       </c>
       <c r="D37" s="9">
@@ -2894,7 +2973,7 @@
       <c r="B38" s="8" t="s">
         <v>100</v>
       </c>
-      <c r="C38" s="40" t="s">
+      <c r="C38" s="39" t="s">
         <v>101</v>
       </c>
       <c r="D38" s="9">
@@ -2916,14 +2995,14 @@
         <v>79</v>
       </c>
     </row>
-    <row r="39" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:9" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A39" s="7" t="s">
         <v>95</v>
       </c>
-      <c r="B39" s="32" t="s">
+      <c r="B39" s="31" t="s">
         <v>102</v>
       </c>
-      <c r="C39" s="40" t="s">
+      <c r="C39" s="39" t="s">
         <v>103</v>
       </c>
       <c r="D39" s="9">
@@ -2946,7 +3025,7 @@
       <c r="B40" s="8" t="s">
         <v>104</v>
       </c>
-      <c r="C40" s="40" t="s">
+      <c r="C40" s="39" t="s">
         <v>105</v>
       </c>
       <c r="D40" s="9">
@@ -2975,7 +3054,7 @@
       <c r="B41" s="8" t="s">
         <v>106</v>
       </c>
-      <c r="C41" s="40" t="s">
+      <c r="C41" s="39" t="s">
         <v>107</v>
       </c>
       <c r="D41" s="9">
@@ -2997,14 +3076,14 @@
         <v>79</v>
       </c>
     </row>
-    <row r="42" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:9" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A42" s="7" t="s">
         <v>95</v>
       </c>
       <c r="B42" s="8" t="s">
         <v>108</v>
       </c>
-      <c r="C42" s="40" t="s">
+      <c r="C42" s="39" t="s">
         <v>109</v>
       </c>
       <c r="D42" s="9">
@@ -3020,14 +3099,14 @@
       <c r="H42" s="12"/>
       <c r="I42" s="12"/>
     </row>
-    <row r="43" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:9" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A43" s="7" t="s">
         <v>95</v>
       </c>
       <c r="B43" s="8" t="s">
         <v>110</v>
       </c>
-      <c r="C43" s="40" t="s">
+      <c r="C43" s="39" t="s">
         <v>111</v>
       </c>
       <c r="D43" s="9">
@@ -3043,14 +3122,14 @@
       <c r="H43" s="12"/>
       <c r="I43" s="12"/>
     </row>
-    <row r="44" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:9" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A44" s="7" t="s">
         <v>95</v>
       </c>
       <c r="B44" s="8" t="s">
         <v>112</v>
       </c>
-      <c r="C44" s="40" t="s">
+      <c r="C44" s="39" t="s">
         <v>113</v>
       </c>
       <c r="D44" s="9">
@@ -3066,14 +3145,14 @@
       <c r="H44" s="12"/>
       <c r="I44" s="12"/>
     </row>
-    <row r="45" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:9" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A45" s="7" t="s">
         <v>95</v>
       </c>
       <c r="B45" s="8" t="s">
         <v>114</v>
       </c>
-      <c r="C45" s="40" t="s">
+      <c r="C45" s="39" t="s">
         <v>115</v>
       </c>
       <c r="D45" s="9">
@@ -3096,7 +3175,7 @@
       <c r="B46" s="8" t="s">
         <v>116</v>
       </c>
-      <c r="C46" s="40" t="s">
+      <c r="C46" s="39" t="s">
         <v>117</v>
       </c>
       <c r="D46" s="9">
@@ -3125,7 +3204,7 @@
       <c r="B47" s="8" t="s">
         <v>118</v>
       </c>
-      <c r="C47" s="40" t="s">
+      <c r="C47" s="39" t="s">
         <v>119</v>
       </c>
       <c r="D47" s="9">
@@ -3137,13 +3216,13 @@
       <c r="F47" s="10" t="s">
         <v>77</v>
       </c>
-      <c r="G47" s="27">
+      <c r="G47" s="26">
         <v>46043</v>
       </c>
-      <c r="H47" s="28" t="s">
+      <c r="H47" s="27" t="s">
         <v>99</v>
       </c>
-      <c r="I47" s="28" t="s">
+      <c r="I47" s="27" t="s">
         <v>79</v>
       </c>
     </row>
@@ -3154,7 +3233,7 @@
       <c r="B48" s="8" t="s">
         <v>120</v>
       </c>
-      <c r="C48" s="40" t="s">
+      <c r="C48" s="39" t="s">
         <v>121</v>
       </c>
       <c r="D48" s="9">
@@ -3169,7 +3248,7 @@
       <c r="G48" s="14">
         <v>46052</v>
       </c>
-      <c r="H48" s="31" t="s">
+      <c r="H48" s="30" t="s">
         <v>122</v>
       </c>
       <c r="I48" s="12" t="s">
@@ -3183,7 +3262,7 @@
       <c r="B49" s="8" t="s">
         <v>123</v>
       </c>
-      <c r="C49" s="40" t="s">
+      <c r="C49" s="39" t="s">
         <v>124</v>
       </c>
       <c r="D49" s="9">
@@ -3195,24 +3274,24 @@
       <c r="F49" s="10" t="s">
         <v>77</v>
       </c>
-      <c r="G49" s="29">
+      <c r="G49" s="28">
         <v>46049</v>
       </c>
-      <c r="H49" s="30" t="s">
+      <c r="H49" s="29" t="s">
         <v>99</v>
       </c>
-      <c r="I49" s="30" t="s">
+      <c r="I49" s="29" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="50" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:9" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A50" s="7" t="s">
         <v>95</v>
       </c>
       <c r="B50" s="8" t="s">
         <v>125</v>
       </c>
-      <c r="C50" s="40" t="s">
+      <c r="C50" s="39" t="s">
         <v>126</v>
       </c>
       <c r="D50" s="9">
@@ -3228,14 +3307,14 @@
       <c r="H50" s="12"/>
       <c r="I50" s="12"/>
     </row>
-    <row r="51" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:9" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A51" s="7" t="s">
         <v>95</v>
       </c>
       <c r="B51" s="8" t="s">
         <v>127</v>
       </c>
-      <c r="C51" s="40" t="s">
+      <c r="C51" s="39" t="s">
         <v>128</v>
       </c>
       <c r="D51" s="9">
@@ -3245,7 +3324,7 @@
         <v>98</v>
       </c>
       <c r="F51" s="10" t="s">
-        <v>14</v>
+        <v>236</v>
       </c>
       <c r="G51" s="11"/>
       <c r="H51" s="12"/>
@@ -3258,7 +3337,7 @@
       <c r="B52" s="8" t="s">
         <v>129</v>
       </c>
-      <c r="C52" s="40" t="s">
+      <c r="C52" s="39" t="s">
         <v>130</v>
       </c>
       <c r="D52" s="9">
@@ -3268,9 +3347,11 @@
         <v>98</v>
       </c>
       <c r="F52" s="10" t="s">
-        <v>14</v>
-      </c>
-      <c r="G52" s="11"/>
+        <v>77</v>
+      </c>
+      <c r="G52" s="13">
+        <v>46099</v>
+      </c>
       <c r="H52" s="12"/>
       <c r="I52" s="12"/>
     </row>
@@ -3281,7 +3362,7 @@
       <c r="B53" s="8" t="s">
         <v>131</v>
       </c>
-      <c r="C53" s="40" t="s">
+      <c r="C53" s="39" t="s">
         <v>132</v>
       </c>
       <c r="D53" s="9">
@@ -3303,14 +3384,14 @@
         <v>79</v>
       </c>
     </row>
-    <row r="54" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:9" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A54" s="7" t="s">
         <v>95</v>
       </c>
       <c r="B54" s="8" t="s">
         <v>133</v>
       </c>
-      <c r="C54" s="40" t="s">
+      <c r="C54" s="39" t="s">
         <v>134</v>
       </c>
       <c r="D54" s="9">
@@ -3333,7 +3414,7 @@
       <c r="B55" s="8" t="s">
         <v>135</v>
       </c>
-      <c r="C55" s="40" t="s">
+      <c r="C55" s="39" t="s">
         <v>136</v>
       </c>
       <c r="D55" s="9">
@@ -3362,7 +3443,7 @@
       <c r="B56" s="8" t="s">
         <v>137</v>
       </c>
-      <c r="C56" s="40" t="s">
+      <c r="C56" s="39" t="s">
         <v>138</v>
       </c>
       <c r="D56" s="9">
@@ -3391,7 +3472,7 @@
       <c r="B57" s="8" t="s">
         <v>139</v>
       </c>
-      <c r="C57" s="40" t="s">
+      <c r="C57" s="39" t="s">
         <v>140</v>
       </c>
       <c r="D57" s="9">
@@ -3413,14 +3494,14 @@
         <v>79</v>
       </c>
     </row>
-    <row r="58" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:9" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A58" s="7" t="s">
         <v>95</v>
       </c>
       <c r="B58" s="8" t="s">
         <v>141</v>
       </c>
-      <c r="C58" s="40" t="s">
+      <c r="C58" s="39" t="s">
         <v>142</v>
       </c>
       <c r="D58" s="9">
@@ -3443,7 +3524,7 @@
       <c r="B59" s="8" t="s">
         <v>143</v>
       </c>
-      <c r="C59" s="40" t="s">
+      <c r="C59" s="39" t="s">
         <v>144</v>
       </c>
       <c r="D59" s="9">
@@ -3472,7 +3553,7 @@
       <c r="B60" s="8" t="s">
         <v>145</v>
       </c>
-      <c r="C60" s="40" t="s">
+      <c r="C60" s="39" t="s">
         <v>146</v>
       </c>
       <c r="D60" s="9">
@@ -3482,20 +3563,22 @@
         <v>98</v>
       </c>
       <c r="F60" s="10" t="s">
-        <v>14</v>
-      </c>
-      <c r="G60" s="11"/>
+        <v>77</v>
+      </c>
+      <c r="G60" s="13">
+        <v>46104</v>
+      </c>
       <c r="H60" s="12"/>
       <c r="I60" s="12"/>
     </row>
-    <row r="61" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:9" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A61" s="7" t="s">
         <v>95</v>
       </c>
       <c r="B61" s="8" t="s">
         <v>147</v>
       </c>
-      <c r="C61" s="40" t="s">
+      <c r="C61" s="39" t="s">
         <v>148</v>
       </c>
       <c r="D61" s="9">
@@ -3511,37 +3594,37 @@
       <c r="H61" s="12"/>
       <c r="I61" s="12"/>
     </row>
-    <row r="62" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
-      <c r="A62" s="7" t="s">
+    <row r="62" spans="1:9" s="50" customFormat="1" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A62" s="44" t="s">
         <v>149</v>
       </c>
-      <c r="B62" s="8" t="s">
+      <c r="B62" s="43" t="s">
         <v>150</v>
       </c>
-      <c r="C62" s="40" t="s">
+      <c r="C62" s="45" t="s">
         <v>151</v>
       </c>
-      <c r="D62" s="9">
+      <c r="D62" s="46">
         <v>46387</v>
       </c>
-      <c r="E62" s="8" t="s">
+      <c r="E62" s="43" t="s">
         <v>62</v>
       </c>
-      <c r="F62" s="10" t="s">
+      <c r="F62" s="47" t="s">
         <v>14</v>
       </c>
-      <c r="G62" s="11"/>
-      <c r="H62" s="12"/>
-      <c r="I62" s="12"/>
-    </row>
-    <row r="63" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
+      <c r="G62" s="48"/>
+      <c r="H62" s="49"/>
+      <c r="I62" s="49"/>
+    </row>
+    <row r="63" spans="1:9" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A63" s="7" t="s">
         <v>149</v>
       </c>
       <c r="B63" s="8" t="s">
         <v>152</v>
       </c>
-      <c r="C63" s="40" t="s">
+      <c r="C63" s="39" t="s">
         <v>153</v>
       </c>
       <c r="D63" s="9">
@@ -3557,14 +3640,14 @@
       <c r="H63" s="12"/>
       <c r="I63" s="12"/>
     </row>
-    <row r="64" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:9" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A64" s="7" t="s">
         <v>149</v>
       </c>
       <c r="B64" s="8" t="s">
         <v>154</v>
       </c>
-      <c r="C64" s="40" t="s">
+      <c r="C64" s="39" t="s">
         <v>155</v>
       </c>
       <c r="D64" s="9">
@@ -3587,7 +3670,7 @@
       <c r="B65" s="8" t="s">
         <v>156</v>
       </c>
-      <c r="C65" s="40" t="s">
+      <c r="C65" s="39" t="s">
         <v>157</v>
       </c>
       <c r="D65" s="9">
@@ -3616,7 +3699,7 @@
       <c r="B66" s="8" t="s">
         <v>158</v>
       </c>
-      <c r="C66" s="40" t="s">
+      <c r="C66" s="39" t="s">
         <v>159</v>
       </c>
       <c r="D66" s="9">
@@ -3645,7 +3728,7 @@
       <c r="B67" s="8" t="s">
         <v>160</v>
       </c>
-      <c r="C67" s="40" t="s">
+      <c r="C67" s="39" t="s">
         <v>161</v>
       </c>
       <c r="D67" s="9">
@@ -3667,60 +3750,60 @@
         <v>79</v>
       </c>
     </row>
-    <row r="68" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
-      <c r="A68" s="7" t="s">
+    <row r="68" spans="1:9" s="50" customFormat="1" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A68" s="44" t="s">
         <v>149</v>
       </c>
-      <c r="B68" s="8" t="s">
+      <c r="B68" s="43" t="s">
         <v>162</v>
       </c>
-      <c r="C68" s="40" t="s">
+      <c r="C68" s="45" t="s">
         <v>163</v>
       </c>
-      <c r="D68" s="9">
+      <c r="D68" s="46">
         <v>46387</v>
       </c>
-      <c r="E68" s="8" t="s">
+      <c r="E68" s="43" t="s">
         <v>62</v>
       </c>
-      <c r="F68" s="10" t="s">
+      <c r="F68" s="47" t="s">
         <v>14</v>
       </c>
-      <c r="G68" s="11"/>
-      <c r="H68" s="12"/>
-      <c r="I68" s="12"/>
-    </row>
-    <row r="69" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
-      <c r="A69" s="7" t="s">
+      <c r="G68" s="48"/>
+      <c r="H68" s="49"/>
+      <c r="I68" s="49"/>
+    </row>
+    <row r="69" spans="1:9" s="50" customFormat="1" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A69" s="44" t="s">
         <v>149</v>
       </c>
-      <c r="B69" s="8" t="s">
+      <c r="B69" s="43" t="s">
         <v>164</v>
       </c>
-      <c r="C69" s="40" t="s">
+      <c r="C69" s="45" t="s">
         <v>165</v>
       </c>
-      <c r="D69" s="9">
+      <c r="D69" s="46">
         <v>46387</v>
       </c>
-      <c r="E69" s="8" t="s">
+      <c r="E69" s="43" t="s">
         <v>62</v>
       </c>
-      <c r="F69" s="10" t="s">
+      <c r="F69" s="47" t="s">
         <v>14</v>
       </c>
-      <c r="G69" s="11"/>
-      <c r="H69" s="12"/>
-      <c r="I69" s="12"/>
-    </row>
-    <row r="70" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
+      <c r="G69" s="48"/>
+      <c r="H69" s="49"/>
+      <c r="I69" s="49"/>
+    </row>
+    <row r="70" spans="1:9" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A70" s="7" t="s">
         <v>149</v>
       </c>
       <c r="B70" s="8" t="s">
         <v>166</v>
       </c>
-      <c r="C70" s="40" t="s">
+      <c r="C70" s="39" t="s">
         <v>167</v>
       </c>
       <c r="D70" s="9">
@@ -3736,74 +3819,74 @@
       <c r="H70" s="12"/>
       <c r="I70" s="12"/>
     </row>
-    <row r="71" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
-      <c r="A71" s="7" t="s">
+    <row r="71" spans="1:9" s="50" customFormat="1" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A71" s="44" t="s">
         <v>149</v>
       </c>
-      <c r="B71" s="8" t="s">
+      <c r="B71" s="43" t="s">
         <v>168</v>
       </c>
-      <c r="C71" s="40" t="s">
+      <c r="C71" s="45" t="s">
         <v>169</v>
       </c>
-      <c r="D71" s="9">
+      <c r="D71" s="46">
         <v>46387</v>
       </c>
-      <c r="E71" s="8" t="s">
+      <c r="E71" s="43" t="s">
         <v>62</v>
       </c>
-      <c r="F71" s="10" t="s">
+      <c r="F71" s="47" t="s">
         <v>14</v>
       </c>
-      <c r="G71" s="11"/>
-      <c r="H71" s="12"/>
-      <c r="I71" s="12"/>
-    </row>
-    <row r="72" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
-      <c r="A72" s="7" t="s">
+      <c r="G71" s="48"/>
+      <c r="H71" s="49"/>
+      <c r="I71" s="49"/>
+    </row>
+    <row r="72" spans="1:9" s="50" customFormat="1" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A72" s="44" t="s">
         <v>149</v>
       </c>
-      <c r="B72" s="8" t="s">
+      <c r="B72" s="43" t="s">
         <v>170</v>
       </c>
-      <c r="C72" s="40" t="s">
+      <c r="C72" s="45" t="s">
         <v>171</v>
       </c>
-      <c r="D72" s="9">
+      <c r="D72" s="46">
         <v>46387</v>
       </c>
-      <c r="E72" s="8" t="s">
+      <c r="E72" s="43" t="s">
         <v>62</v>
       </c>
-      <c r="F72" s="10" t="s">
+      <c r="F72" s="47" t="s">
         <v>14</v>
       </c>
-      <c r="G72" s="11"/>
-      <c r="H72" s="12"/>
-      <c r="I72" s="12"/>
-    </row>
-    <row r="73" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
-      <c r="A73" s="7" t="s">
+      <c r="G72" s="48"/>
+      <c r="H72" s="49"/>
+      <c r="I72" s="49"/>
+    </row>
+    <row r="73" spans="1:9" s="50" customFormat="1" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A73" s="44" t="s">
         <v>172</v>
       </c>
-      <c r="B73" s="8" t="s">
+      <c r="B73" s="43" t="s">
         <v>173</v>
       </c>
-      <c r="C73" s="40" t="s">
+      <c r="C73" s="45" t="s">
         <v>174</v>
       </c>
-      <c r="D73" s="9">
+      <c r="D73" s="46">
         <v>46053</v>
       </c>
-      <c r="E73" s="8" t="s">
+      <c r="E73" s="43" t="s">
         <v>13</v>
       </c>
-      <c r="F73" s="10" t="s">
+      <c r="F73" s="47" t="s">
         <v>14</v>
       </c>
-      <c r="G73" s="11"/>
-      <c r="H73" s="12"/>
-      <c r="I73" s="12"/>
+      <c r="G73" s="48"/>
+      <c r="H73" s="49"/>
+      <c r="I73" s="49"/>
     </row>
     <row r="74" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A74" s="7" t="s">
@@ -3812,7 +3895,7 @@
       <c r="B74" s="8" t="s">
         <v>175</v>
       </c>
-      <c r="C74" s="40" t="s">
+      <c r="C74" s="39" t="s">
         <v>176</v>
       </c>
       <c r="D74" s="9">
@@ -3822,57 +3905,59 @@
         <v>13</v>
       </c>
       <c r="F74" s="10" t="s">
-        <v>14</v>
-      </c>
-      <c r="G74" s="11"/>
+        <v>77</v>
+      </c>
+      <c r="G74" s="13">
+        <v>46092</v>
+      </c>
       <c r="H74" s="12"/>
       <c r="I74" s="12"/>
     </row>
-    <row r="75" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
-      <c r="A75" s="7" t="s">
+    <row r="75" spans="1:9" s="58" customFormat="1" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A75" s="51" t="s">
         <v>177</v>
       </c>
-      <c r="B75" s="8" t="s">
+      <c r="B75" s="52" t="s">
         <v>178</v>
       </c>
-      <c r="C75" s="40" t="s">
+      <c r="C75" s="53" t="s">
         <v>179</v>
       </c>
-      <c r="D75" s="9">
+      <c r="D75" s="54">
         <v>46081</v>
       </c>
-      <c r="E75" s="8" t="s">
+      <c r="E75" s="52" t="s">
         <v>36</v>
       </c>
-      <c r="F75" s="10" t="s">
+      <c r="F75" s="55" t="s">
         <v>14</v>
       </c>
-      <c r="G75" s="11"/>
-      <c r="H75" s="12"/>
-      <c r="I75" s="12"/>
-    </row>
-    <row r="76" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
-      <c r="A76" s="7" t="s">
+      <c r="G75" s="56"/>
+      <c r="H75" s="57"/>
+      <c r="I75" s="57"/>
+    </row>
+    <row r="76" spans="1:9" s="66" customFormat="1" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A76" s="59" t="s">
         <v>177</v>
       </c>
-      <c r="B76" s="8" t="s">
+      <c r="B76" s="60" t="s">
         <v>180</v>
       </c>
-      <c r="C76" s="40" t="s">
+      <c r="C76" s="61" t="s">
         <v>181</v>
       </c>
-      <c r="D76" s="9">
+      <c r="D76" s="62">
         <v>46081</v>
       </c>
-      <c r="E76" s="8" t="s">
+      <c r="E76" s="60" t="s">
         <v>36</v>
       </c>
-      <c r="F76" s="10" t="s">
+      <c r="F76" s="63" t="s">
         <v>14</v>
       </c>
-      <c r="G76" s="11"/>
-      <c r="H76" s="12"/>
-      <c r="I76" s="12"/>
+      <c r="G76" s="64"/>
+      <c r="H76" s="65"/>
+      <c r="I76" s="65"/>
     </row>
     <row r="77" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A77" s="7" t="s">
@@ -3881,7 +3966,7 @@
       <c r="B77" s="8" t="s">
         <v>182</v>
       </c>
-      <c r="C77" s="40" t="s">
+      <c r="C77" s="39" t="s">
         <v>183</v>
       </c>
       <c r="D77" s="9">
@@ -3891,20 +3976,22 @@
         <v>36</v>
       </c>
       <c r="F77" s="10" t="s">
-        <v>14</v>
-      </c>
-      <c r="G77" s="11"/>
+        <v>77</v>
+      </c>
+      <c r="G77" s="13">
+        <v>46092</v>
+      </c>
       <c r="H77" s="12"/>
       <c r="I77" s="12"/>
     </row>
-    <row r="78" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:9" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A78" s="7" t="s">
         <v>177</v>
       </c>
       <c r="B78" s="8" t="s">
         <v>184</v>
       </c>
-      <c r="C78" s="40" t="s">
+      <c r="C78" s="39" t="s">
         <v>185</v>
       </c>
       <c r="D78" s="9">
@@ -3920,14 +4007,14 @@
       <c r="H78" s="12"/>
       <c r="I78" s="12"/>
     </row>
-    <row r="79" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:9" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A79" s="7" t="s">
         <v>177</v>
       </c>
       <c r="B79" s="8" t="s">
         <v>186</v>
       </c>
-      <c r="C79" s="40" t="s">
+      <c r="C79" s="39" t="s">
         <v>187</v>
       </c>
       <c r="D79" s="9">
@@ -3943,14 +4030,14 @@
       <c r="H79" s="12"/>
       <c r="I79" s="12"/>
     </row>
-    <row r="80" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:9" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A80" s="7" t="s">
         <v>177</v>
       </c>
       <c r="B80" s="8" t="s">
         <v>188</v>
       </c>
-      <c r="C80" s="40" t="s">
+      <c r="C80" s="39" t="s">
         <v>189</v>
       </c>
       <c r="D80" s="9">
@@ -3973,7 +4060,7 @@
       <c r="B81" s="8" t="s">
         <v>190</v>
       </c>
-      <c r="C81" s="40" t="s">
+      <c r="C81" s="39" t="s">
         <v>191</v>
       </c>
       <c r="D81" s="9">
@@ -3983,9 +4070,11 @@
         <v>36</v>
       </c>
       <c r="F81" s="10" t="s">
-        <v>14</v>
-      </c>
-      <c r="G81" s="11"/>
+        <v>77</v>
+      </c>
+      <c r="G81" s="13">
+        <v>46091</v>
+      </c>
       <c r="H81" s="12"/>
       <c r="I81" s="12"/>
     </row>
@@ -3996,7 +4085,7 @@
       <c r="B82" s="8" t="s">
         <v>192</v>
       </c>
-      <c r="C82" s="40" t="s">
+      <c r="C82" s="39" t="s">
         <v>193</v>
       </c>
       <c r="D82" s="9">
@@ -4006,9 +4095,11 @@
         <v>36</v>
       </c>
       <c r="F82" s="10" t="s">
-        <v>14</v>
-      </c>
-      <c r="G82" s="11"/>
+        <v>77</v>
+      </c>
+      <c r="G82" s="13">
+        <v>46086</v>
+      </c>
       <c r="H82" s="12"/>
       <c r="I82" s="12"/>
     </row>
@@ -4019,7 +4110,7 @@
       <c r="B83" s="8" t="s">
         <v>194</v>
       </c>
-      <c r="C83" s="40" t="s">
+      <c r="C83" s="39" t="s">
         <v>195</v>
       </c>
       <c r="D83" s="9">
@@ -4029,20 +4120,22 @@
         <v>36</v>
       </c>
       <c r="F83" s="10" t="s">
-        <v>14</v>
-      </c>
-      <c r="G83" s="11"/>
+        <v>77</v>
+      </c>
+      <c r="G83" s="13">
+        <v>46086</v>
+      </c>
       <c r="H83" s="12"/>
       <c r="I83" s="12"/>
     </row>
-    <row r="84" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="84" spans="1:9" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A84" s="7" t="s">
         <v>177</v>
       </c>
       <c r="B84" s="8" t="s">
         <v>196</v>
       </c>
-      <c r="C84" s="40" t="s">
+      <c r="C84" s="39" t="s">
         <v>197</v>
       </c>
       <c r="D84" s="9">
@@ -4065,7 +4158,7 @@
       <c r="B85" s="8" t="s">
         <v>198</v>
       </c>
-      <c r="C85" s="40" t="s">
+      <c r="C85" s="39" t="s">
         <v>199</v>
       </c>
       <c r="D85" s="9">
@@ -4075,9 +4168,11 @@
         <v>36</v>
       </c>
       <c r="F85" s="10" t="s">
-        <v>14</v>
-      </c>
-      <c r="G85" s="11"/>
+        <v>77</v>
+      </c>
+      <c r="G85" s="13">
+        <v>46078</v>
+      </c>
       <c r="H85" s="12"/>
       <c r="I85" s="12"/>
     </row>
@@ -4088,7 +4183,7 @@
       <c r="B86" s="8" t="s">
         <v>200</v>
       </c>
-      <c r="C86" s="40" t="s">
+      <c r="C86" s="39" t="s">
         <v>201</v>
       </c>
       <c r="D86" s="9">
@@ -4098,9 +4193,11 @@
         <v>36</v>
       </c>
       <c r="F86" s="10" t="s">
-        <v>14</v>
-      </c>
-      <c r="G86" s="11"/>
+        <v>77</v>
+      </c>
+      <c r="G86" s="13">
+        <v>46077</v>
+      </c>
       <c r="H86" s="12"/>
       <c r="I86" s="12"/>
     </row>
@@ -4111,7 +4208,7 @@
       <c r="B87" s="8" t="s">
         <v>202</v>
       </c>
-      <c r="C87" s="40" t="s">
+      <c r="C87" s="39" t="s">
         <v>203</v>
       </c>
       <c r="D87" s="9">
@@ -4121,20 +4218,22 @@
         <v>36</v>
       </c>
       <c r="F87" s="10" t="s">
-        <v>14</v>
-      </c>
-      <c r="G87" s="11"/>
+        <v>77</v>
+      </c>
+      <c r="G87" s="13">
+        <v>46099</v>
+      </c>
       <c r="H87" s="12"/>
       <c r="I87" s="12"/>
     </row>
-    <row r="88" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="88" spans="1:9" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A88" s="7" t="s">
         <v>177</v>
       </c>
       <c r="B88" s="8" t="s">
         <v>204</v>
       </c>
-      <c r="C88" s="40" t="s">
+      <c r="C88" s="39" t="s">
         <v>205</v>
       </c>
       <c r="D88" s="9">
@@ -4150,14 +4249,14 @@
       <c r="H88" s="12"/>
       <c r="I88" s="12"/>
     </row>
-    <row r="89" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="89" spans="1:9" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A89" s="7" t="s">
         <v>177</v>
       </c>
       <c r="B89" s="8" t="s">
         <v>206</v>
       </c>
-      <c r="C89" s="40" t="s">
+      <c r="C89" s="39" t="s">
         <v>207</v>
       </c>
       <c r="D89" s="9">
@@ -4173,14 +4272,14 @@
       <c r="H89" s="12"/>
       <c r="I89" s="12"/>
     </row>
-    <row r="90" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="90" spans="1:9" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A90" s="7" t="s">
         <v>177</v>
       </c>
       <c r="B90" s="8" t="s">
         <v>208</v>
       </c>
-      <c r="C90" s="40" t="s">
+      <c r="C90" s="39" t="s">
         <v>209</v>
       </c>
       <c r="D90" s="9">
@@ -4196,14 +4295,14 @@
       <c r="H90" s="12"/>
       <c r="I90" s="12"/>
     </row>
-    <row r="91" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="91" spans="1:9" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A91" s="7" t="s">
         <v>210</v>
       </c>
       <c r="B91" s="8" t="s">
         <v>211</v>
       </c>
-      <c r="C91" s="40" t="s">
+      <c r="C91" s="39" t="s">
         <v>212</v>
       </c>
       <c r="D91" s="9">
@@ -4219,14 +4318,14 @@
       <c r="H91" s="12"/>
       <c r="I91" s="12"/>
     </row>
-    <row r="92" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="92" spans="1:9" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A92" s="7" t="s">
         <v>210</v>
       </c>
       <c r="B92" s="8" t="s">
         <v>213</v>
       </c>
-      <c r="C92" s="40" t="s">
+      <c r="C92" s="39" t="s">
         <v>214</v>
       </c>
       <c r="D92" s="9">
@@ -4242,14 +4341,14 @@
       <c r="H92" s="12"/>
       <c r="I92" s="12"/>
     </row>
-    <row r="93" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="93" spans="1:9" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A93" s="7" t="s">
         <v>210</v>
       </c>
       <c r="B93" s="8" t="s">
         <v>215</v>
       </c>
-      <c r="C93" s="40" t="s">
+      <c r="C93" s="39" t="s">
         <v>216</v>
       </c>
       <c r="D93" s="9">
@@ -4272,7 +4371,7 @@
       <c r="B94" s="8" t="s">
         <v>218</v>
       </c>
-      <c r="C94" s="40" t="s">
+      <c r="C94" s="39" t="s">
         <v>219</v>
       </c>
       <c r="D94" s="9">
@@ -4294,14 +4393,14 @@
         <v>79</v>
       </c>
     </row>
-    <row r="95" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="95" spans="1:9" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A95" s="7" t="s">
         <v>217</v>
       </c>
       <c r="B95" s="8" t="s">
         <v>220</v>
       </c>
-      <c r="C95" s="40" t="s">
+      <c r="C95" s="39" t="s">
         <v>221</v>
       </c>
       <c r="D95" s="9">
@@ -4317,14 +4416,14 @@
       <c r="H95" s="12"/>
       <c r="I95" s="12"/>
     </row>
-    <row r="96" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="96" spans="1:9" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A96" s="7" t="s">
         <v>217</v>
       </c>
       <c r="B96" s="8" t="s">
         <v>222</v>
       </c>
-      <c r="C96" s="40" t="s">
+      <c r="C96" s="39" t="s">
         <v>223</v>
       </c>
       <c r="D96" s="9">
@@ -4340,14 +4439,14 @@
       <c r="H96" s="12"/>
       <c r="I96" s="12"/>
     </row>
-    <row r="97" spans="1:10" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="97" spans="1:10" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A97" s="7" t="s">
         <v>217</v>
       </c>
       <c r="B97" s="8" t="s">
         <v>224</v>
       </c>
-      <c r="C97" s="40">
+      <c r="C97" s="39">
         <v>65153</v>
       </c>
       <c r="D97" s="9">
@@ -4370,7 +4469,7 @@
       <c r="B98" s="8" t="s">
         <v>226</v>
       </c>
-      <c r="C98" s="40" t="s">
+      <c r="C98" s="39" t="s">
         <v>227</v>
       </c>
       <c r="D98" s="9">
@@ -4399,7 +4498,7 @@
       <c r="B99" s="8" t="s">
         <v>229</v>
       </c>
-      <c r="C99" s="40" t="s">
+      <c r="C99" s="39" t="s">
         <v>230</v>
       </c>
       <c r="D99" s="9">
@@ -4409,20 +4508,26 @@
         <v>228</v>
       </c>
       <c r="F99" s="10" t="s">
-        <v>14</v>
-      </c>
-      <c r="G99" s="11"/>
-      <c r="H99" s="12"/>
-      <c r="I99" s="12"/>
-    </row>
-    <row r="100" spans="1:10" ht="14.5" x14ac:dyDescent="0.35">
+        <v>77</v>
+      </c>
+      <c r="G99" s="13">
+        <v>46099</v>
+      </c>
+      <c r="H99" s="12" t="s">
+        <v>99</v>
+      </c>
+      <c r="I99" s="12" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="100" spans="1:10" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A100" s="7" t="s">
         <v>231</v>
       </c>
       <c r="B100" s="8" t="s">
         <v>232</v>
       </c>
-      <c r="C100" s="40" t="s">
+      <c r="C100" s="39" t="s">
         <v>233</v>
       </c>
       <c r="D100" s="9">
@@ -4438,14 +4543,14 @@
       <c r="H100" s="12"/>
       <c r="I100" s="12"/>
     </row>
-    <row r="101" spans="1:10" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="101" spans="1:10" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A101" s="7" t="s">
         <v>231</v>
       </c>
       <c r="B101" s="8" t="s">
         <v>234</v>
       </c>
-      <c r="C101" s="40" t="s">
+      <c r="C101" s="39" t="s">
         <v>235</v>
       </c>
       <c r="D101" s="9">
@@ -4464,14 +4569,14 @@
         <v>237</v>
       </c>
     </row>
-    <row r="102" spans="1:10" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="102" spans="1:10" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A102" s="7" t="s">
         <v>238</v>
       </c>
       <c r="B102" s="8" t="s">
         <v>239</v>
       </c>
-      <c r="C102" s="40" t="s">
+      <c r="C102" s="39" t="s">
         <v>240</v>
       </c>
       <c r="D102" s="9">
@@ -4487,14 +4592,14 @@
       <c r="H102" s="12"/>
       <c r="I102" s="12"/>
     </row>
-    <row r="103" spans="1:10" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="103" spans="1:10" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A103" s="7" t="s">
         <v>238</v>
       </c>
       <c r="B103" s="8" t="s">
         <v>242</v>
       </c>
-      <c r="C103" s="40" t="s">
+      <c r="C103" s="39" t="s">
         <v>243</v>
       </c>
       <c r="D103" s="9">
@@ -4510,14 +4615,14 @@
       <c r="H103" s="12"/>
       <c r="I103" s="12"/>
     </row>
-    <row r="104" spans="1:10" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="104" spans="1:10" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A104" s="7" t="s">
         <v>238</v>
       </c>
       <c r="B104" s="8" t="s">
         <v>244</v>
       </c>
-      <c r="C104" s="40" t="s">
+      <c r="C104" s="39" t="s">
         <v>245</v>
       </c>
       <c r="D104" s="9">
@@ -4533,14 +4638,14 @@
       <c r="H104" s="12"/>
       <c r="I104" s="12"/>
     </row>
-    <row r="105" spans="1:10" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="105" spans="1:10" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A105" s="7" t="s">
         <v>238</v>
       </c>
       <c r="B105" s="8" t="s">
         <v>246</v>
       </c>
-      <c r="C105" s="40" t="s">
+      <c r="C105" s="39" t="s">
         <v>247</v>
       </c>
       <c r="D105" s="9">
@@ -4556,14 +4661,14 @@
       <c r="H105" s="12"/>
       <c r="I105" s="12"/>
     </row>
-    <row r="106" spans="1:10" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="106" spans="1:10" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A106" s="7" t="s">
         <v>238</v>
       </c>
       <c r="B106" s="8" t="s">
         <v>248</v>
       </c>
-      <c r="C106" s="40" t="s">
+      <c r="C106" s="39" t="s">
         <v>249</v>
       </c>
       <c r="D106" s="9">
@@ -4579,14 +4684,14 @@
       <c r="H106" s="12"/>
       <c r="I106" s="12"/>
     </row>
-    <row r="107" spans="1:10" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="107" spans="1:10" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A107" s="7" t="s">
         <v>238</v>
       </c>
       <c r="B107" s="8" t="s">
         <v>250</v>
       </c>
-      <c r="C107" s="40" t="s">
+      <c r="C107" s="39" t="s">
         <v>251</v>
       </c>
       <c r="D107" s="9">
@@ -4602,14 +4707,14 @@
       <c r="H107" s="12"/>
       <c r="I107" s="12"/>
     </row>
-    <row r="108" spans="1:10" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="108" spans="1:10" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A108" s="7" t="s">
         <v>238</v>
       </c>
       <c r="B108" s="8" t="s">
         <v>252</v>
       </c>
-      <c r="C108" s="40" t="s">
+      <c r="C108" s="39" t="s">
         <v>253</v>
       </c>
       <c r="D108" s="9">
@@ -4625,14 +4730,14 @@
       <c r="H108" s="12"/>
       <c r="I108" s="12"/>
     </row>
-    <row r="109" spans="1:10" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="109" spans="1:10" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A109" s="7" t="s">
         <v>238</v>
       </c>
       <c r="B109" s="8" t="s">
         <v>254</v>
       </c>
-      <c r="C109" s="40" t="s">
+      <c r="C109" s="39" t="s">
         <v>255</v>
       </c>
       <c r="D109" s="9">
@@ -4648,14 +4753,14 @@
       <c r="H109" s="12"/>
       <c r="I109" s="12"/>
     </row>
-    <row r="110" spans="1:10" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="110" spans="1:10" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A110" s="7" t="s">
         <v>238</v>
       </c>
       <c r="B110" s="8" t="s">
         <v>256</v>
       </c>
-      <c r="C110" s="40" t="s">
+      <c r="C110" s="39" t="s">
         <v>257</v>
       </c>
       <c r="D110" s="9">
@@ -4671,14 +4776,14 @@
       <c r="H110" s="12"/>
       <c r="I110" s="12"/>
     </row>
-    <row r="111" spans="1:10" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="111" spans="1:10" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A111" s="7" t="s">
         <v>238</v>
       </c>
       <c r="B111" s="8" t="s">
         <v>258</v>
       </c>
-      <c r="C111" s="40" t="s">
+      <c r="C111" s="39" t="s">
         <v>259</v>
       </c>
       <c r="D111" s="9">
@@ -4694,14 +4799,14 @@
       <c r="H111" s="12"/>
       <c r="I111" s="12"/>
     </row>
-    <row r="112" spans="1:10" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="112" spans="1:10" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A112" s="7" t="s">
         <v>238</v>
       </c>
       <c r="B112" s="8" t="s">
         <v>260</v>
       </c>
-      <c r="C112" s="40" t="s">
+      <c r="C112" s="39" t="s">
         <v>261</v>
       </c>
       <c r="D112" s="9">
@@ -4717,14 +4822,14 @@
       <c r="H112" s="12"/>
       <c r="I112" s="12"/>
     </row>
-    <row r="113" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="113" spans="1:9" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A113" s="7" t="s">
         <v>238</v>
       </c>
       <c r="B113" s="8" t="s">
         <v>262</v>
       </c>
-      <c r="C113" s="40" t="s">
+      <c r="C113" s="39" t="s">
         <v>263</v>
       </c>
       <c r="D113" s="9">
@@ -4740,14 +4845,14 @@
       <c r="H113" s="12"/>
       <c r="I113" s="12"/>
     </row>
-    <row r="114" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="114" spans="1:9" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A114" s="7" t="s">
         <v>238</v>
       </c>
       <c r="B114" s="8" t="s">
         <v>264</v>
       </c>
-      <c r="C114" s="40" t="s">
+      <c r="C114" s="39" t="s">
         <v>265</v>
       </c>
       <c r="D114" s="9">
@@ -4763,14 +4868,14 @@
       <c r="H114" s="12"/>
       <c r="I114" s="12"/>
     </row>
-    <row r="115" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="115" spans="1:9" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A115" s="7" t="s">
         <v>238</v>
       </c>
       <c r="B115" s="8" t="s">
         <v>266</v>
       </c>
-      <c r="C115" s="40" t="s">
+      <c r="C115" s="39" t="s">
         <v>267</v>
       </c>
       <c r="D115" s="9">
@@ -4786,14 +4891,14 @@
       <c r="H115" s="12"/>
       <c r="I115" s="12"/>
     </row>
-    <row r="116" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="116" spans="1:9" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A116" s="7" t="s">
         <v>238</v>
       </c>
       <c r="B116" s="8" t="s">
         <v>268</v>
       </c>
-      <c r="C116" s="40" t="s">
+      <c r="C116" s="39" t="s">
         <v>269</v>
       </c>
       <c r="D116" s="9">
@@ -4809,14 +4914,14 @@
       <c r="H116" s="12"/>
       <c r="I116" s="12"/>
     </row>
-    <row r="117" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="117" spans="1:9" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A117" s="7" t="s">
         <v>238</v>
       </c>
       <c r="B117" s="8" t="s">
         <v>270</v>
       </c>
-      <c r="C117" s="40" t="s">
+      <c r="C117" s="39" t="s">
         <v>271</v>
       </c>
       <c r="D117" s="9">
@@ -4832,14 +4937,14 @@
       <c r="H117" s="12"/>
       <c r="I117" s="12"/>
     </row>
-    <row r="118" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="118" spans="1:9" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A118" s="7" t="s">
         <v>238</v>
       </c>
       <c r="B118" s="8" t="s">
         <v>272</v>
       </c>
-      <c r="C118" s="40" t="s">
+      <c r="C118" s="39" t="s">
         <v>273</v>
       </c>
       <c r="D118" s="9">
@@ -4855,14 +4960,14 @@
       <c r="H118" s="12"/>
       <c r="I118" s="12"/>
     </row>
-    <row r="119" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="119" spans="1:9" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A119" s="7" t="s">
         <v>238</v>
       </c>
       <c r="B119" s="8" t="s">
         <v>274</v>
       </c>
-      <c r="C119" s="40" t="s">
+      <c r="C119" s="39" t="s">
         <v>275</v>
       </c>
       <c r="D119" s="9">
@@ -4878,14 +4983,14 @@
       <c r="H119" s="12"/>
       <c r="I119" s="12"/>
     </row>
-    <row r="120" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="120" spans="1:9" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A120" s="7" t="s">
         <v>276</v>
       </c>
       <c r="B120" s="8" t="s">
         <v>277</v>
       </c>
-      <c r="C120" s="40" t="s">
+      <c r="C120" s="39" t="s">
         <v>278</v>
       </c>
       <c r="D120" s="9">
@@ -4901,14 +5006,14 @@
       <c r="H120" s="12"/>
       <c r="I120" s="12"/>
     </row>
-    <row r="121" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="121" spans="1:9" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A121" s="7" t="s">
         <v>276</v>
       </c>
       <c r="B121" s="8" t="s">
         <v>279</v>
       </c>
-      <c r="C121" s="40" t="s">
+      <c r="C121" s="39" t="s">
         <v>280</v>
       </c>
       <c r="D121" s="9">
@@ -4924,14 +5029,14 @@
       <c r="H121" s="12"/>
       <c r="I121" s="12"/>
     </row>
-    <row r="122" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="122" spans="1:9" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A122" s="7" t="s">
         <v>276</v>
       </c>
       <c r="B122" s="8" t="s">
         <v>281</v>
       </c>
-      <c r="C122" s="40" t="s">
+      <c r="C122" s="39" t="s">
         <v>282</v>
       </c>
       <c r="D122" s="9">
@@ -4947,14 +5052,14 @@
       <c r="H122" s="12"/>
       <c r="I122" s="12"/>
     </row>
-    <row r="123" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="123" spans="1:9" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A123" s="7" t="s">
         <v>284</v>
       </c>
       <c r="B123" s="8" t="s">
         <v>285</v>
       </c>
-      <c r="C123" s="40" t="s">
+      <c r="C123" s="39" t="s">
         <v>286</v>
       </c>
       <c r="D123" s="9">
@@ -4970,60 +5075,60 @@
       <c r="H123" s="12"/>
       <c r="I123" s="12"/>
     </row>
-    <row r="124" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
-      <c r="A124" s="7" t="s">
+    <row r="124" spans="1:9" s="50" customFormat="1" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A124" s="44" t="s">
         <v>287</v>
       </c>
-      <c r="B124" s="8" t="s">
+      <c r="B124" s="43" t="s">
         <v>288</v>
       </c>
-      <c r="C124" s="40" t="s">
+      <c r="C124" s="45" t="s">
         <v>289</v>
       </c>
-      <c r="D124" s="9">
+      <c r="D124" s="46">
         <v>46507</v>
       </c>
-      <c r="E124" s="8" t="s">
+      <c r="E124" s="43" t="s">
         <v>13</v>
       </c>
-      <c r="F124" s="10" t="s">
+      <c r="F124" s="47" t="s">
         <v>14</v>
       </c>
-      <c r="G124" s="11"/>
-      <c r="H124" s="12"/>
-      <c r="I124" s="12"/>
-    </row>
-    <row r="125" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
-      <c r="A125" s="7" t="s">
+      <c r="G124" s="48"/>
+      <c r="H124" s="49"/>
+      <c r="I124" s="49"/>
+    </row>
+    <row r="125" spans="1:9" s="50" customFormat="1" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A125" s="44" t="s">
         <v>287</v>
       </c>
-      <c r="B125" s="8" t="s">
+      <c r="B125" s="43" t="s">
         <v>290</v>
       </c>
-      <c r="C125" s="40" t="s">
+      <c r="C125" s="45" t="s">
         <v>291</v>
       </c>
-      <c r="D125" s="9">
+      <c r="D125" s="46">
         <v>46507</v>
       </c>
-      <c r="E125" s="8" t="s">
+      <c r="E125" s="43" t="s">
         <v>13</v>
       </c>
-      <c r="F125" s="10" t="s">
+      <c r="F125" s="47" t="s">
         <v>14</v>
       </c>
-      <c r="G125" s="11"/>
-      <c r="H125" s="12"/>
-      <c r="I125" s="12"/>
-    </row>
-    <row r="126" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
+      <c r="G125" s="48"/>
+      <c r="H125" s="49"/>
+      <c r="I125" s="49"/>
+    </row>
+    <row r="126" spans="1:9" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A126" s="7" t="s">
         <v>287</v>
       </c>
       <c r="B126" s="8" t="s">
         <v>292</v>
       </c>
-      <c r="C126" s="40" t="s">
+      <c r="C126" s="39" t="s">
         <v>293</v>
       </c>
       <c r="D126" s="9">
@@ -5039,14 +5144,14 @@
       <c r="H126" s="15"/>
       <c r="I126" s="15"/>
     </row>
-    <row r="127" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="127" spans="1:9" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A127" s="7" t="s">
         <v>294</v>
       </c>
       <c r="B127" s="8" t="s">
         <v>295</v>
       </c>
-      <c r="C127" s="40" t="s">
+      <c r="C127" s="39" t="s">
         <v>296</v>
       </c>
       <c r="D127" s="9">
@@ -5069,7 +5174,7 @@
       <c r="B128" t="s">
         <v>298</v>
       </c>
-      <c r="C128" s="40" t="s">
+      <c r="C128" s="39" t="s">
         <v>299</v>
       </c>
       <c r="D128" s="9" t="s">
@@ -5096,7 +5201,7 @@
       <c r="B129" s="8" t="s">
         <v>301</v>
       </c>
-      <c r="C129" s="40" t="s">
+      <c r="C129" s="39" t="s">
         <v>302</v>
       </c>
       <c r="D129" s="9"/>
@@ -5115,17 +5220,17 @@
       </c>
     </row>
     <row r="130" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A130" s="33" t="s">
+      <c r="A130" s="32" t="s">
         <v>303</v>
       </c>
-      <c r="B130" s="34" t="s">
+      <c r="B130" s="33" t="s">
         <v>304</v>
       </c>
-      <c r="C130" s="41" t="s">
+      <c r="C130" s="40" t="s">
         <v>305</v>
       </c>
-      <c r="D130" s="35"/>
-      <c r="E130" s="34"/>
+      <c r="D130" s="34"/>
+      <c r="E130" s="33"/>
       <c r="F130" s="10" t="s">
         <v>77</v>
       </c>
@@ -5140,21 +5245,21 @@
       </c>
     </row>
     <row r="131" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A131" s="33" t="s">
+      <c r="A131" s="32" t="s">
         <v>307</v>
       </c>
-      <c r="B131" s="34" t="s">
+      <c r="B131" s="33" t="s">
         <v>308</v>
       </c>
-      <c r="C131" s="41" t="s">
+      <c r="C131" s="40" t="s">
         <v>309</v>
       </c>
-      <c r="D131" s="35"/>
-      <c r="E131" s="34"/>
+      <c r="D131" s="34"/>
+      <c r="E131" s="33"/>
       <c r="F131" s="10" t="s">
         <v>77</v>
       </c>
-      <c r="G131" s="27">
+      <c r="G131" s="26">
         <v>46065</v>
       </c>
       <c r="H131" s="15" t="s">
@@ -5165,21 +5270,21 @@
       </c>
     </row>
     <row r="132" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A132" s="33" t="s">
+      <c r="A132" s="32" t="s">
         <v>65</v>
       </c>
-      <c r="B132" s="34" t="s">
+      <c r="B132" s="33" t="s">
         <v>311</v>
       </c>
-      <c r="C132" s="41" t="s">
+      <c r="C132" s="40" t="s">
         <v>312</v>
       </c>
-      <c r="D132" s="35"/>
-      <c r="E132" s="34"/>
+      <c r="D132" s="34"/>
+      <c r="E132" s="33"/>
       <c r="F132" s="10" t="s">
         <v>77</v>
       </c>
-      <c r="G132" s="27">
+      <c r="G132" s="26">
         <v>46065</v>
       </c>
       <c r="H132" s="15" t="s">
@@ -5190,21 +5295,21 @@
       </c>
     </row>
     <row r="133" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A133" s="33" t="s">
+      <c r="A133" s="32" t="s">
         <v>313</v>
       </c>
-      <c r="B133" s="34" t="s">
+      <c r="B133" s="33" t="s">
         <v>314</v>
       </c>
-      <c r="C133" s="41" t="s">
+      <c r="C133" s="40" t="s">
         <v>315</v>
       </c>
-      <c r="D133" s="35"/>
-      <c r="E133" s="34"/>
-      <c r="F133" s="36" t="s">
+      <c r="D133" s="34"/>
+      <c r="E133" s="33"/>
+      <c r="F133" s="35" t="s">
         <v>77</v>
       </c>
-      <c r="G133" s="27">
+      <c r="G133" s="26">
         <v>46065</v>
       </c>
       <c r="H133" s="15" t="s">
@@ -5215,21 +5320,21 @@
       </c>
     </row>
     <row r="134" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A134" s="33" t="s">
+      <c r="A134" s="32" t="s">
         <v>313</v>
       </c>
-      <c r="B134" s="34" t="s">
+      <c r="B134" s="33" t="s">
         <v>316</v>
       </c>
-      <c r="C134" s="41" t="s">
+      <c r="C134" s="40" t="s">
         <v>317</v>
       </c>
-      <c r="D134" s="35"/>
-      <c r="E134" s="34"/>
-      <c r="F134" s="36" t="s">
+      <c r="D134" s="34"/>
+      <c r="E134" s="33"/>
+      <c r="F134" s="35" t="s">
         <v>77</v>
       </c>
-      <c r="G134" s="27">
+      <c r="G134" s="26">
         <v>46065</v>
       </c>
       <c r="H134" s="15" t="s">
@@ -5240,46 +5345,46 @@
       </c>
     </row>
     <row r="135" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A135" s="33" t="s">
+      <c r="A135" s="32" t="s">
         <v>276</v>
       </c>
-      <c r="B135" s="34" t="s">
+      <c r="B135" s="33" t="s">
         <v>318</v>
       </c>
-      <c r="C135" s="41" t="s">
+      <c r="C135" s="40" t="s">
         <v>319</v>
       </c>
-      <c r="D135" s="35"/>
-      <c r="E135" s="34"/>
-      <c r="F135" s="36" t="s">
+      <c r="D135" s="34"/>
+      <c r="E135" s="33"/>
+      <c r="F135" s="35" t="s">
         <v>77</v>
       </c>
-      <c r="G135" s="27">
+      <c r="G135" s="26">
         <v>46065</v>
       </c>
       <c r="H135" s="15" t="s">
         <v>310</v>
       </c>
-      <c r="I135" s="28" t="s">
+      <c r="I135" s="27" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="136" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A136" s="33" t="s">
+      <c r="A136" s="32" t="s">
         <v>320</v>
       </c>
-      <c r="B136" s="34" t="s">
+      <c r="B136" s="33" t="s">
         <v>321</v>
       </c>
-      <c r="C136" s="42" t="s">
+      <c r="C136" s="41" t="s">
         <v>322</v>
       </c>
-      <c r="D136" s="35"/>
-      <c r="E136" s="34"/>
-      <c r="F136" s="36" t="s">
+      <c r="D136" s="34"/>
+      <c r="E136" s="33"/>
+      <c r="F136" s="35" t="s">
         <v>77</v>
       </c>
-      <c r="G136" s="27">
+      <c r="G136" s="26">
         <v>46071</v>
       </c>
       <c r="H136" s="15" t="s">
@@ -5288,24 +5393,24 @@
       <c r="I136" s="15" t="s">
         <v>79</v>
       </c>
-      <c r="J136" s="38"/>
+      <c r="J136" s="37"/>
     </row>
     <row r="137" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A137" s="33" t="s">
+      <c r="A137" s="32" t="s">
         <v>324</v>
       </c>
-      <c r="B137" s="34" t="s">
+      <c r="B137" s="33" t="s">
         <v>325</v>
       </c>
-      <c r="C137" s="41" t="s">
+      <c r="C137" s="40" t="s">
         <v>326</v>
       </c>
-      <c r="D137" s="35"/>
-      <c r="E137" s="34"/>
-      <c r="F137" s="36" t="s">
+      <c r="D137" s="34"/>
+      <c r="E137" s="33"/>
+      <c r="F137" s="35" t="s">
         <v>77</v>
       </c>
-      <c r="G137" s="27">
+      <c r="G137" s="26">
         <v>46071</v>
       </c>
       <c r="H137" s="15" t="s">
@@ -5314,7 +5419,7 @@
       <c r="I137" s="15" t="s">
         <v>328</v>
       </c>
-      <c r="J137" s="38"/>
+      <c r="J137" s="37"/>
     </row>
     <row r="138" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A138" s="7" t="s">
@@ -5323,13 +5428,13 @@
       <c r="B138" s="8" t="s">
         <v>330</v>
       </c>
-      <c r="C138" s="40"/>
+      <c r="C138" s="39"/>
       <c r="D138" s="9"/>
       <c r="E138" s="8"/>
       <c r="F138" s="10" t="s">
         <v>77</v>
       </c>
-      <c r="G138" s="27">
+      <c r="G138" s="26">
         <v>46071</v>
       </c>
       <c r="H138" s="15" t="s">
@@ -5338,22 +5443,22 @@
       <c r="I138" s="15" t="s">
         <v>328</v>
       </c>
-      <c r="J138" s="37"/>
+      <c r="J138" s="36"/>
     </row>
     <row r="139" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A139" s="7" t="s">
         <v>329</v>
       </c>
-      <c r="B139" s="34" t="s">
+      <c r="B139" s="33" t="s">
         <v>331</v>
       </c>
-      <c r="C139" s="41"/>
-      <c r="D139" s="35"/>
-      <c r="E139" s="34"/>
+      <c r="C139" s="40"/>
+      <c r="D139" s="34"/>
+      <c r="E139" s="33"/>
       <c r="F139" s="10" t="s">
         <v>77</v>
       </c>
-      <c r="G139" s="27">
+      <c r="G139" s="26">
         <v>46071</v>
       </c>
       <c r="H139" s="15" t="s">
@@ -5362,22 +5467,22 @@
       <c r="I139" s="15" t="s">
         <v>328</v>
       </c>
-      <c r="J139" s="38"/>
+      <c r="J139" s="37"/>
     </row>
     <row r="140" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A140" s="7" t="s">
         <v>329</v>
       </c>
-      <c r="B140" s="34" t="s">
+      <c r="B140" s="33" t="s">
         <v>332</v>
       </c>
-      <c r="C140" s="41"/>
-      <c r="D140" s="35"/>
-      <c r="E140" s="34"/>
+      <c r="C140" s="40"/>
+      <c r="D140" s="34"/>
+      <c r="E140" s="33"/>
       <c r="F140" s="10" t="s">
         <v>77</v>
       </c>
-      <c r="G140" s="27">
+      <c r="G140" s="26">
         <v>46071</v>
       </c>
       <c r="H140" s="15" t="s">
@@ -5386,24 +5491,24 @@
       <c r="I140" s="15" t="s">
         <v>328</v>
       </c>
-      <c r="J140" s="38"/>
+      <c r="J140" s="37"/>
     </row>
     <row r="141" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A141" s="33" t="s">
+      <c r="A141" s="32" t="s">
         <v>333</v>
       </c>
-      <c r="B141" s="34" t="s">
+      <c r="B141" s="33" t="s">
         <v>334</v>
       </c>
-      <c r="C141" s="41" t="s">
+      <c r="C141" s="40" t="s">
         <v>335</v>
       </c>
-      <c r="D141" s="35"/>
-      <c r="E141" s="34"/>
+      <c r="D141" s="34"/>
+      <c r="E141" s="33"/>
       <c r="F141" s="10" t="s">
         <v>77</v>
       </c>
-      <c r="G141" s="27">
+      <c r="G141" s="26">
         <v>46072</v>
       </c>
       <c r="H141" s="12" t="s">
@@ -5412,16 +5517,16 @@
       <c r="I141" s="15" t="s">
         <v>79</v>
       </c>
-      <c r="J141" s="38"/>
+      <c r="J141" s="37"/>
     </row>
     <row r="142" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A142" s="33" t="s">
+      <c r="A142" s="32" t="s">
         <v>313</v>
       </c>
       <c r="B142" s="8" t="s">
         <v>206</v>
       </c>
-      <c r="C142" s="40" t="s">
+      <c r="C142" s="39" t="s">
         <v>207</v>
       </c>
       <c r="D142" s="9"/>
@@ -5429,7 +5534,7 @@
       <c r="F142" s="10" t="s">
         <v>77</v>
       </c>
-      <c r="G142" s="27">
+      <c r="G142" s="26">
         <v>46072</v>
       </c>
       <c r="H142" s="14" t="s">
@@ -5446,7 +5551,7 @@
       <c r="B143" s="8" t="s">
         <v>337</v>
       </c>
-      <c r="C143" s="40" t="s">
+      <c r="C143" s="39" t="s">
         <v>338</v>
       </c>
       <c r="D143" s="9"/>
@@ -5454,7 +5559,7 @@
       <c r="F143" s="10" t="s">
         <v>77</v>
       </c>
-      <c r="G143" s="27">
+      <c r="G143" s="26">
         <v>46072</v>
       </c>
       <c r="H143" s="15" t="s">
@@ -5465,13 +5570,13 @@
       </c>
     </row>
     <row r="144" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A144" s="33" t="s">
+      <c r="A144" s="32" t="s">
         <v>339</v>
       </c>
       <c r="B144" s="8" t="s">
         <v>340</v>
       </c>
-      <c r="C144" s="40" t="s">
+      <c r="C144" s="39" t="s">
         <v>341</v>
       </c>
       <c r="D144" s="9"/>
@@ -5496,7 +5601,7 @@
       <c r="B145" s="8" t="s">
         <v>343</v>
       </c>
-      <c r="C145" s="40" t="s">
+      <c r="C145" s="39" t="s">
         <v>344</v>
       </c>
       <c r="D145" s="9"/>
@@ -5597,7 +5702,7 @@
       <c r="B149" s="8" t="s">
         <v>60</v>
       </c>
-      <c r="C149" s="40" t="s">
+      <c r="C149" s="39" t="s">
         <v>353</v>
       </c>
       <c r="D149" s="9"/>
@@ -5615,10 +5720,10 @@
         <v>79</v>
       </c>
     </row>
-    <row r="150" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="150" spans="1:10" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A150" s="7"/>
       <c r="B150" s="8"/>
-      <c r="C150" s="40"/>
+      <c r="C150" s="39"/>
       <c r="D150" s="9"/>
       <c r="E150" s="8"/>
       <c r="F150" s="10"/>
@@ -5626,10 +5731,10 @@
       <c r="H150" s="12"/>
       <c r="I150" s="12"/>
     </row>
-    <row r="151" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="151" spans="1:10" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A151" s="7"/>
       <c r="B151" s="8"/>
-      <c r="C151" s="40"/>
+      <c r="C151" s="39"/>
       <c r="D151" s="9"/>
       <c r="E151" s="8"/>
       <c r="F151" s="10"/>
@@ -5637,10 +5742,10 @@
       <c r="H151" s="12"/>
       <c r="I151" s="12"/>
     </row>
-    <row r="152" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="152" spans="1:10" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A152" s="7"/>
       <c r="B152" s="8"/>
-      <c r="C152" s="40"/>
+      <c r="C152" s="39"/>
       <c r="D152" s="9"/>
       <c r="E152" s="8"/>
       <c r="F152" s="10"/>
@@ -5648,10 +5753,10 @@
       <c r="H152" s="12"/>
       <c r="I152" s="12"/>
     </row>
-    <row r="153" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="153" spans="1:10" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A153" s="7"/>
       <c r="B153" s="8"/>
-      <c r="C153" s="40"/>
+      <c r="C153" s="39"/>
       <c r="D153" s="9"/>
       <c r="E153" s="8"/>
       <c r="F153" s="10"/>
@@ -5659,10 +5764,10 @@
       <c r="H153" s="12"/>
       <c r="I153" s="12"/>
     </row>
-    <row r="154" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="154" spans="1:10" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A154" s="7"/>
       <c r="B154" s="8"/>
-      <c r="C154" s="40"/>
+      <c r="C154" s="39"/>
       <c r="D154" s="9"/>
       <c r="E154" s="8"/>
       <c r="F154" s="10"/>
@@ -5670,10 +5775,10 @@
       <c r="H154" s="12"/>
       <c r="I154" s="12"/>
     </row>
-    <row r="155" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="155" spans="1:10" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A155" s="7"/>
       <c r="B155" s="8"/>
-      <c r="C155" s="40"/>
+      <c r="C155" s="39"/>
       <c r="D155" s="9"/>
       <c r="E155" s="8"/>
       <c r="F155" s="10"/>
@@ -5681,10 +5786,10 @@
       <c r="H155" s="12"/>
       <c r="I155" s="12"/>
     </row>
-    <row r="156" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="156" spans="1:10" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A156" s="7"/>
       <c r="B156" s="8"/>
-      <c r="C156" s="40"/>
+      <c r="C156" s="39"/>
       <c r="D156" s="9"/>
       <c r="E156" s="8"/>
       <c r="F156" s="10"/>
@@ -5692,10 +5797,10 @@
       <c r="H156" s="12"/>
       <c r="I156" s="12"/>
     </row>
-    <row r="157" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="157" spans="1:10" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A157" s="7"/>
       <c r="B157" s="8"/>
-      <c r="C157" s="40"/>
+      <c r="C157" s="39"/>
       <c r="D157" s="9"/>
       <c r="E157" s="8"/>
       <c r="F157" s="10"/>
@@ -5703,10 +5808,10 @@
       <c r="H157" s="12"/>
       <c r="I157" s="12"/>
     </row>
-    <row r="158" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="158" spans="1:10" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A158" s="7"/>
       <c r="B158" s="8"/>
-      <c r="C158" s="40"/>
+      <c r="C158" s="39"/>
       <c r="D158" s="9"/>
       <c r="E158" s="8"/>
       <c r="F158" s="10"/>
@@ -5714,10 +5819,10 @@
       <c r="H158" s="12"/>
       <c r="I158" s="12"/>
     </row>
-    <row r="159" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="159" spans="1:10" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A159" s="7"/>
       <c r="B159" s="8"/>
-      <c r="C159" s="40"/>
+      <c r="C159" s="39"/>
       <c r="D159" s="9"/>
       <c r="E159" s="8"/>
       <c r="F159" s="10"/>
@@ -5725,10 +5830,10 @@
       <c r="H159" s="12"/>
       <c r="I159" s="12"/>
     </row>
-    <row r="160" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="160" spans="1:10" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A160" s="7"/>
       <c r="B160" s="8"/>
-      <c r="C160" s="40"/>
+      <c r="C160" s="39"/>
       <c r="D160" s="9"/>
       <c r="E160" s="8"/>
       <c r="F160" s="10"/>
@@ -5736,10 +5841,10 @@
       <c r="H160" s="12"/>
       <c r="I160" s="12"/>
     </row>
-    <row r="161" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="161" spans="1:9" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A161" s="7"/>
       <c r="B161" s="8"/>
-      <c r="C161" s="40"/>
+      <c r="C161" s="39"/>
       <c r="D161" s="9"/>
       <c r="E161" s="8"/>
       <c r="F161" s="10"/>
@@ -5747,10 +5852,10 @@
       <c r="H161" s="12"/>
       <c r="I161" s="12"/>
     </row>
-    <row r="162" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="162" spans="1:9" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A162" s="7"/>
       <c r="B162" s="8"/>
-      <c r="C162" s="40"/>
+      <c r="C162" s="39"/>
       <c r="D162" s="9"/>
       <c r="E162" s="8"/>
       <c r="F162" s="10"/>
@@ -5758,10 +5863,10 @@
       <c r="H162" s="12"/>
       <c r="I162" s="12"/>
     </row>
-    <row r="163" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="163" spans="1:9" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A163" s="7"/>
       <c r="B163" s="8"/>
-      <c r="C163" s="40"/>
+      <c r="C163" s="39"/>
       <c r="D163" s="9"/>
       <c r="E163" s="8"/>
       <c r="F163" s="10"/>
@@ -5769,10 +5874,10 @@
       <c r="H163" s="12"/>
       <c r="I163" s="12"/>
     </row>
-    <row r="164" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="164" spans="1:9" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A164" s="7"/>
       <c r="B164" s="8"/>
-      <c r="C164" s="40"/>
+      <c r="C164" s="39"/>
       <c r="D164" s="9"/>
       <c r="E164" s="8"/>
       <c r="F164" s="10"/>
@@ -5780,10 +5885,10 @@
       <c r="H164" s="12"/>
       <c r="I164" s="12"/>
     </row>
-    <row r="165" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="165" spans="1:9" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A165" s="7"/>
       <c r="B165" s="8"/>
-      <c r="C165" s="40"/>
+      <c r="C165" s="39"/>
       <c r="D165" s="9"/>
       <c r="E165" s="8"/>
       <c r="F165" s="10"/>
@@ -5791,10 +5896,10 @@
       <c r="H165" s="12"/>
       <c r="I165" s="12"/>
     </row>
-    <row r="166" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="166" spans="1:9" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A166" s="7"/>
       <c r="B166" s="8"/>
-      <c r="C166" s="40"/>
+      <c r="C166" s="39"/>
       <c r="D166" s="9"/>
       <c r="E166" s="8"/>
       <c r="F166" s="10"/>
@@ -5802,10 +5907,10 @@
       <c r="H166" s="12"/>
       <c r="I166" s="12"/>
     </row>
-    <row r="167" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="167" spans="1:9" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A167" s="7"/>
       <c r="B167" s="8"/>
-      <c r="C167" s="40"/>
+      <c r="C167" s="39"/>
       <c r="D167" s="9"/>
       <c r="E167" s="8"/>
       <c r="F167" s="10"/>
@@ -5813,10 +5918,10 @@
       <c r="H167" s="12"/>
       <c r="I167" s="12"/>
     </row>
-    <row r="168" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="168" spans="1:9" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A168" s="7"/>
       <c r="B168" s="8"/>
-      <c r="C168" s="40"/>
+      <c r="C168" s="39"/>
       <c r="D168" s="9"/>
       <c r="E168" s="8"/>
       <c r="F168" s="10"/>
@@ -5824,10 +5929,10 @@
       <c r="H168" s="12"/>
       <c r="I168" s="12"/>
     </row>
-    <row r="169" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="169" spans="1:9" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A169" s="7"/>
       <c r="B169" s="8"/>
-      <c r="C169" s="40"/>
+      <c r="C169" s="39"/>
       <c r="D169" s="9"/>
       <c r="E169" s="8"/>
       <c r="F169" s="10"/>
@@ -5835,10 +5940,10 @@
       <c r="H169" s="12"/>
       <c r="I169" s="12"/>
     </row>
-    <row r="170" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="170" spans="1:9" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A170" s="7"/>
       <c r="B170" s="8"/>
-      <c r="C170" s="40"/>
+      <c r="C170" s="39"/>
       <c r="D170" s="9"/>
       <c r="E170" s="8"/>
       <c r="F170" s="10"/>
@@ -5846,10 +5951,10 @@
       <c r="H170" s="12"/>
       <c r="I170" s="12"/>
     </row>
-    <row r="171" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="171" spans="1:9" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A171" s="7"/>
       <c r="B171" s="8"/>
-      <c r="C171" s="40"/>
+      <c r="C171" s="39"/>
       <c r="D171" s="9"/>
       <c r="E171" s="8"/>
       <c r="F171" s="10"/>
@@ -5857,10 +5962,10 @@
       <c r="H171" s="12"/>
       <c r="I171" s="12"/>
     </row>
-    <row r="172" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="172" spans="1:9" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A172" s="7"/>
       <c r="B172" s="8"/>
-      <c r="C172" s="40"/>
+      <c r="C172" s="39"/>
       <c r="D172" s="9"/>
       <c r="E172" s="8"/>
       <c r="F172" s="10"/>
@@ -5868,10 +5973,10 @@
       <c r="H172" s="12"/>
       <c r="I172" s="12"/>
     </row>
-    <row r="173" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="173" spans="1:9" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A173" s="7"/>
       <c r="B173" s="8"/>
-      <c r="C173" s="40"/>
+      <c r="C173" s="39"/>
       <c r="D173" s="9"/>
       <c r="E173" s="8"/>
       <c r="F173" s="10"/>
@@ -5879,10 +5984,10 @@
       <c r="H173" s="12"/>
       <c r="I173" s="12"/>
     </row>
-    <row r="174" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="174" spans="1:9" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A174" s="7"/>
       <c r="B174" s="8"/>
-      <c r="C174" s="40"/>
+      <c r="C174" s="39"/>
       <c r="D174" s="9"/>
       <c r="E174" s="8"/>
       <c r="F174" s="10"/>
@@ -5890,10 +5995,10 @@
       <c r="H174" s="12"/>
       <c r="I174" s="12"/>
     </row>
-    <row r="175" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="175" spans="1:9" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A175" s="7"/>
       <c r="B175" s="8"/>
-      <c r="C175" s="40"/>
+      <c r="C175" s="39"/>
       <c r="D175" s="9"/>
       <c r="E175" s="8"/>
       <c r="F175" s="10"/>
@@ -5901,10 +6006,10 @@
       <c r="H175" s="12"/>
       <c r="I175" s="12"/>
     </row>
-    <row r="176" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="176" spans="1:9" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A176" s="7"/>
       <c r="B176" s="8"/>
-      <c r="C176" s="40"/>
+      <c r="C176" s="39"/>
       <c r="D176" s="9"/>
       <c r="E176" s="8"/>
       <c r="F176" s="10"/>
@@ -5912,10 +6017,10 @@
       <c r="H176" s="12"/>
       <c r="I176" s="12"/>
     </row>
-    <row r="177" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="177" spans="1:9" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A177" s="7"/>
       <c r="B177" s="8"/>
-      <c r="C177" s="40"/>
+      <c r="C177" s="39"/>
       <c r="D177" s="9"/>
       <c r="E177" s="8"/>
       <c r="F177" s="10"/>
@@ -5923,10 +6028,10 @@
       <c r="H177" s="12"/>
       <c r="I177" s="12"/>
     </row>
-    <row r="178" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="178" spans="1:9" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A178" s="7"/>
       <c r="B178" s="8"/>
-      <c r="C178" s="40"/>
+      <c r="C178" s="39"/>
       <c r="D178" s="9"/>
       <c r="E178" s="8"/>
       <c r="F178" s="10"/>
@@ -5934,10 +6039,10 @@
       <c r="H178" s="12"/>
       <c r="I178" s="12"/>
     </row>
-    <row r="179" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="179" spans="1:9" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A179" s="7"/>
       <c r="B179" s="8"/>
-      <c r="C179" s="40"/>
+      <c r="C179" s="39"/>
       <c r="D179" s="9"/>
       <c r="E179" s="8"/>
       <c r="F179" s="10"/>
@@ -5945,10 +6050,10 @@
       <c r="H179" s="12"/>
       <c r="I179" s="12"/>
     </row>
-    <row r="180" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="180" spans="1:9" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A180" s="7"/>
       <c r="B180" s="8"/>
-      <c r="C180" s="40"/>
+      <c r="C180" s="39"/>
       <c r="D180" s="9"/>
       <c r="E180" s="8"/>
       <c r="F180" s="10"/>
@@ -5956,10 +6061,10 @@
       <c r="H180" s="12"/>
       <c r="I180" s="12"/>
     </row>
-    <row r="181" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="181" spans="1:9" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A181" s="7"/>
       <c r="B181" s="8"/>
-      <c r="C181" s="40"/>
+      <c r="C181" s="39"/>
       <c r="D181" s="9"/>
       <c r="E181" s="8"/>
       <c r="F181" s="10"/>
@@ -5967,10 +6072,10 @@
       <c r="H181" s="12"/>
       <c r="I181" s="12"/>
     </row>
-    <row r="182" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="182" spans="1:9" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A182" s="7"/>
       <c r="B182" s="8"/>
-      <c r="C182" s="40"/>
+      <c r="C182" s="39"/>
       <c r="D182" s="9"/>
       <c r="E182" s="8"/>
       <c r="F182" s="10"/>
@@ -5978,10 +6083,10 @@
       <c r="H182" s="12"/>
       <c r="I182" s="12"/>
     </row>
-    <row r="183" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="183" spans="1:9" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A183" s="7"/>
       <c r="B183" s="8"/>
-      <c r="C183" s="40"/>
+      <c r="C183" s="39"/>
       <c r="D183" s="9"/>
       <c r="E183" s="8"/>
       <c r="F183" s="10"/>
@@ -5989,10 +6094,10 @@
       <c r="H183" s="12"/>
       <c r="I183" s="12"/>
     </row>
-    <row r="184" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="184" spans="1:9" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A184" s="7"/>
       <c r="B184" s="8"/>
-      <c r="C184" s="40"/>
+      <c r="C184" s="39"/>
       <c r="D184" s="9"/>
       <c r="E184" s="8"/>
       <c r="F184" s="10"/>
@@ -6000,10 +6105,10 @@
       <c r="H184" s="12"/>
       <c r="I184" s="12"/>
     </row>
-    <row r="185" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="185" spans="1:9" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A185" s="7"/>
       <c r="B185" s="8"/>
-      <c r="C185" s="40"/>
+      <c r="C185" s="39"/>
       <c r="D185" s="9"/>
       <c r="E185" s="8"/>
       <c r="F185" s="10"/>
@@ -6011,10 +6116,10 @@
       <c r="H185" s="12"/>
       <c r="I185" s="12"/>
     </row>
-    <row r="186" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="186" spans="1:9" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A186" s="7"/>
       <c r="B186" s="8"/>
-      <c r="C186" s="40"/>
+      <c r="C186" s="39"/>
       <c r="D186" s="9"/>
       <c r="E186" s="8"/>
       <c r="F186" s="10"/>
@@ -6022,10 +6127,10 @@
       <c r="H186" s="12"/>
       <c r="I186" s="12"/>
     </row>
-    <row r="187" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="187" spans="1:9" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A187" s="7"/>
       <c r="B187" s="8"/>
-      <c r="C187" s="40"/>
+      <c r="C187" s="39"/>
       <c r="D187" s="9"/>
       <c r="E187" s="8"/>
       <c r="F187" s="10"/>
@@ -6033,10 +6138,10 @@
       <c r="H187" s="12"/>
       <c r="I187" s="12"/>
     </row>
-    <row r="188" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="188" spans="1:9" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A188" s="7"/>
       <c r="B188" s="8"/>
-      <c r="C188" s="40"/>
+      <c r="C188" s="39"/>
       <c r="D188" s="9"/>
       <c r="E188" s="8"/>
       <c r="F188" s="10"/>
@@ -6044,10 +6149,10 @@
       <c r="H188" s="12"/>
       <c r="I188" s="12"/>
     </row>
-    <row r="189" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="189" spans="1:9" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A189" s="7"/>
       <c r="B189" s="8"/>
-      <c r="C189" s="40"/>
+      <c r="C189" s="39"/>
       <c r="D189" s="9"/>
       <c r="E189" s="8"/>
       <c r="F189" s="10"/>
@@ -6055,10 +6160,10 @@
       <c r="H189" s="12"/>
       <c r="I189" s="12"/>
     </row>
-    <row r="190" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="190" spans="1:9" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A190" s="7"/>
       <c r="B190" s="8"/>
-      <c r="C190" s="40"/>
+      <c r="C190" s="39"/>
       <c r="D190" s="9"/>
       <c r="E190" s="8"/>
       <c r="F190" s="10"/>
@@ -6066,10 +6171,10 @@
       <c r="H190" s="12"/>
       <c r="I190" s="12"/>
     </row>
-    <row r="191" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="191" spans="1:9" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A191" s="7"/>
       <c r="B191" s="8"/>
-      <c r="C191" s="40"/>
+      <c r="C191" s="39"/>
       <c r="D191" s="9"/>
       <c r="E191" s="8"/>
       <c r="F191" s="10"/>
@@ -6077,10 +6182,10 @@
       <c r="H191" s="12"/>
       <c r="I191" s="12"/>
     </row>
-    <row r="192" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="192" spans="1:9" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A192" s="7"/>
       <c r="B192" s="8"/>
-      <c r="C192" s="40"/>
+      <c r="C192" s="39"/>
       <c r="D192" s="9"/>
       <c r="E192" s="8"/>
       <c r="F192" s="10"/>
@@ -6088,10 +6193,10 @@
       <c r="H192" s="12"/>
       <c r="I192" s="12"/>
     </row>
-    <row r="193" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="193" spans="1:9" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A193" s="7"/>
       <c r="B193" s="8"/>
-      <c r="C193" s="40"/>
+      <c r="C193" s="39"/>
       <c r="D193" s="9"/>
       <c r="E193" s="8"/>
       <c r="F193" s="10"/>
@@ -6099,10 +6204,10 @@
       <c r="H193" s="12"/>
       <c r="I193" s="12"/>
     </row>
-    <row r="194" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="194" spans="1:9" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A194" s="7"/>
       <c r="B194" s="8"/>
-      <c r="C194" s="40"/>
+      <c r="C194" s="39"/>
       <c r="D194" s="9"/>
       <c r="E194" s="8"/>
       <c r="F194" s="10"/>
@@ -6110,10 +6215,10 @@
       <c r="H194" s="12"/>
       <c r="I194" s="12"/>
     </row>
-    <row r="195" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="195" spans="1:9" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A195" s="7"/>
       <c r="B195" s="8"/>
-      <c r="C195" s="40"/>
+      <c r="C195" s="39"/>
       <c r="D195" s="9"/>
       <c r="E195" s="8"/>
       <c r="F195" s="10"/>
@@ -6121,10 +6226,10 @@
       <c r="H195" s="12"/>
       <c r="I195" s="12"/>
     </row>
-    <row r="196" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="196" spans="1:9" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A196" s="7"/>
       <c r="B196" s="8"/>
-      <c r="C196" s="40"/>
+      <c r="C196" s="39"/>
       <c r="D196" s="9"/>
       <c r="E196" s="8"/>
       <c r="F196" s="10"/>
@@ -6132,10 +6237,10 @@
       <c r="H196" s="12"/>
       <c r="I196" s="12"/>
     </row>
-    <row r="197" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="197" spans="1:9" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A197" s="7"/>
       <c r="B197" s="8"/>
-      <c r="C197" s="40"/>
+      <c r="C197" s="39"/>
       <c r="D197" s="9"/>
       <c r="E197" s="8"/>
       <c r="F197" s="10"/>
@@ -6143,10 +6248,10 @@
       <c r="H197" s="12"/>
       <c r="I197" s="12"/>
     </row>
-    <row r="198" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="198" spans="1:9" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A198" s="7"/>
       <c r="B198" s="8"/>
-      <c r="C198" s="40"/>
+      <c r="C198" s="39"/>
       <c r="D198" s="9"/>
       <c r="E198" s="8"/>
       <c r="F198" s="10"/>
@@ -6154,10 +6259,10 @@
       <c r="H198" s="12"/>
       <c r="I198" s="12"/>
     </row>
-    <row r="199" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="199" spans="1:9" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A199" s="7"/>
       <c r="B199" s="8"/>
-      <c r="C199" s="40"/>
+      <c r="C199" s="39"/>
       <c r="D199" s="9"/>
       <c r="E199" s="8"/>
       <c r="F199" s="10"/>
@@ -6165,10 +6270,10 @@
       <c r="H199" s="12"/>
       <c r="I199" s="12"/>
     </row>
-    <row r="200" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="200" spans="1:9" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A200" s="7"/>
       <c r="B200" s="8"/>
-      <c r="C200" s="40"/>
+      <c r="C200" s="39"/>
       <c r="D200" s="9"/>
       <c r="E200" s="8"/>
       <c r="F200" s="10"/>
@@ -6176,10 +6281,10 @@
       <c r="H200" s="12"/>
       <c r="I200" s="12"/>
     </row>
-    <row r="201" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="201" spans="1:9" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A201" s="7"/>
       <c r="B201" s="8"/>
-      <c r="C201" s="40"/>
+      <c r="C201" s="39"/>
       <c r="D201" s="9"/>
       <c r="E201" s="8"/>
       <c r="F201" s="10"/>
@@ -6187,10 +6292,10 @@
       <c r="H201" s="12"/>
       <c r="I201" s="12"/>
     </row>
-    <row r="202" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="202" spans="1:9" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A202" s="7"/>
       <c r="B202" s="8"/>
-      <c r="C202" s="40"/>
+      <c r="C202" s="39"/>
       <c r="D202" s="9"/>
       <c r="E202" s="8"/>
       <c r="F202" s="10"/>
@@ -6198,10 +6303,10 @@
       <c r="H202" s="12"/>
       <c r="I202" s="12"/>
     </row>
-    <row r="203" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="203" spans="1:9" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A203" s="7"/>
       <c r="B203" s="8"/>
-      <c r="C203" s="40"/>
+      <c r="C203" s="39"/>
       <c r="D203" s="9"/>
       <c r="E203" s="8"/>
       <c r="F203" s="10"/>
@@ -6209,10 +6314,10 @@
       <c r="H203" s="12"/>
       <c r="I203" s="12"/>
     </row>
-    <row r="204" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="204" spans="1:9" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A204" s="7"/>
       <c r="B204" s="8"/>
-      <c r="C204" s="40"/>
+      <c r="C204" s="39"/>
       <c r="D204" s="9"/>
       <c r="E204" s="8"/>
       <c r="F204" s="10"/>
@@ -6220,6 +6325,7 @@
       <c r="H204" s="12"/>
       <c r="I204" s="12"/>
     </row>
+    <row r="205" spans="1:9" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
@@ -6655,15 +6761,6 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x010100027709BF533FA442AFC4A8B2C0110727" ma:contentTypeVersion="15" ma:contentTypeDescription="Crear nuevo documento." ma:contentTypeScope="" ma:versionID="a37fc0d7c302f7619d355a49e1f175a4">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="3e53c16e-6636-411e-b1c4-e9eeb71b3b2a" xmlns:ns4="bda9c1ec-c4e2-44f9-929c-ca399fe36c88" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="01250a30c504a808427f15ccf149ee4d" ns3:_="" ns4:_="">
     <xsd:import namespace="3e53c16e-6636-411e-b1c4-e9eeb71b3b2a"/>
@@ -6896,6 +6993,15 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D9861A25-610F-425F-BC6A-AC52D4971411}">
   <ds:schemaRefs>
@@ -6907,14 +7013,6 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3C8123E5-81FD-4C24-91F1-33BC079967E9}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4794C7E6-B89D-4081-9A67-B8D500EF1EE4}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -6931,4 +7029,12 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3C8123E5-81FD-4C24-91F1-33BC079967E9}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/data/bitacora.xlsx
+++ b/data/bitacora.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://grupokaufmann-my.sharepoint.com/personal/samuel_sanchez_grupokaufmann_com/Documents/Documentos/Dev/bitacora_diaria/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="452" documentId="8_{4616FF0F-C10E-4DFE-8F27-869B9C60E0F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C6702C49-8E3D-4DA8-B4CD-16B6C302CDE0}"/>
+  <xr:revisionPtr revIDLastSave="466" documentId="8_{4616FF0F-C10E-4DFE-8F27-869B9C60E0F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4D2E51A4-9A2E-450F-94B9-28F1672981F0}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-1155" windowWidth="29040" windowHeight="15720" xr2:uid="{A9E3F017-9040-47A2-B586-0486128F3261}"/>
   </bookViews>
@@ -1728,13 +1728,7 @@
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{40364ABC-409D-4532-8E14-9D155F80C509}" name="Tabla1" displayName="Tabla1" ref="A1:J205" totalsRowShown="0">
-  <autoFilter ref="A1:J205" xr:uid="{40364ABC-409D-4532-8E14-9D155F80C509}">
-    <filterColumn colId="5">
-      <filters>
-        <filter val="Reparado"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
+  <autoFilter ref="A1:J205" xr:uid="{40364ABC-409D-4532-8E14-9D155F80C509}"/>
   <tableColumns count="10">
     <tableColumn id="1" xr3:uid="{0A7C6585-5C8B-46BF-ABA0-2DA806D161DC}" name="FLOTA" dataDxfId="9"/>
     <tableColumn id="2" xr3:uid="{EB7792BB-219D-496F-9F16-84F6805E0CB0}" name="VIN CON PROBLEMAS" dataDxfId="8"/>
@@ -2068,7 +2062,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EDA66EBA-6B88-4C75-8217-0B7E221D898D}">
-  <dimension ref="A1:L205"/>
+  <dimension ref="A1:L203"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.453125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="43" style="6" bestFit="1" customWidth="1"/>
@@ -2115,7 +2109,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:12" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:12" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A2" s="7" t="s">
         <v>10</v>
       </c>
@@ -2138,7 +2132,7 @@
       <c r="H2" s="12"/>
       <c r="I2" s="12"/>
     </row>
-    <row r="3" spans="1:12" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:12" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A3" s="7" t="s">
         <v>10</v>
       </c>
@@ -2236,7 +2230,7 @@
       <c r="H6" s="12"/>
       <c r="I6" s="12"/>
     </row>
-    <row r="7" spans="1:12" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:12" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A7" s="7" t="s">
         <v>10</v>
       </c>
@@ -2284,7 +2278,7 @@
       <c r="H8" s="24"/>
       <c r="I8" s="24"/>
     </row>
-    <row r="9" spans="1:12" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:12" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A9" s="7" t="s">
         <v>10</v>
       </c>
@@ -2307,7 +2301,7 @@
       <c r="H9" s="12"/>
       <c r="I9" s="12"/>
     </row>
-    <row r="10" spans="1:12" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:12" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A10" s="7" t="s">
         <v>10</v>
       </c>
@@ -2355,7 +2349,7 @@
       <c r="H11" s="12"/>
       <c r="I11" s="12"/>
     </row>
-    <row r="12" spans="1:12" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:12" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A12" s="7" t="s">
         <v>33</v>
       </c>
@@ -2379,7 +2373,7 @@
       <c r="I12" s="12"/>
       <c r="L12" s="25"/>
     </row>
-    <row r="13" spans="1:12" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:12" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A13" s="7" t="s">
         <v>33</v>
       </c>
@@ -2402,7 +2396,7 @@
       <c r="H13" s="12"/>
       <c r="I13" s="12"/>
     </row>
-    <row r="14" spans="1:12" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:12" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A14" s="7" t="s">
         <v>33</v>
       </c>
@@ -2425,7 +2419,7 @@
       <c r="H14" s="12"/>
       <c r="I14" s="12"/>
     </row>
-    <row r="15" spans="1:12" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:12" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A15" s="7" t="s">
         <v>33</v>
       </c>
@@ -2448,7 +2442,7 @@
       <c r="H15" s="12"/>
       <c r="I15" s="12"/>
     </row>
-    <row r="16" spans="1:12" s="50" customFormat="1" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:12" s="50" customFormat="1" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A16" s="44" t="s">
         <v>33</v>
       </c>
@@ -2471,7 +2465,7 @@
       <c r="H16" s="49"/>
       <c r="I16" s="49"/>
     </row>
-    <row r="17" spans="1:9" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A17" s="7" t="s">
         <v>33</v>
       </c>
@@ -2494,7 +2488,7 @@
       <c r="H17" s="12"/>
       <c r="I17" s="12"/>
     </row>
-    <row r="18" spans="1:9" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A18" s="7" t="s">
         <v>33</v>
       </c>
@@ -2517,7 +2511,7 @@
       <c r="H18" s="12"/>
       <c r="I18" s="12"/>
     </row>
-    <row r="19" spans="1:9" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A19" s="7" t="s">
         <v>33</v>
       </c>
@@ -2540,7 +2534,7 @@
       <c r="H19" s="12"/>
       <c r="I19" s="12"/>
     </row>
-    <row r="20" spans="1:9" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A20" s="7" t="s">
         <v>51</v>
       </c>
@@ -2563,7 +2557,7 @@
       <c r="H20" s="12"/>
       <c r="I20" s="12"/>
     </row>
-    <row r="21" spans="1:9" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A21" s="7" t="s">
         <v>51</v>
       </c>
@@ -2586,7 +2580,7 @@
       <c r="H21" s="12"/>
       <c r="I21" s="12"/>
     </row>
-    <row r="22" spans="1:9" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A22" s="7" t="s">
         <v>51</v>
       </c>
@@ -2609,7 +2603,7 @@
       <c r="H22" s="12"/>
       <c r="I22" s="12"/>
     </row>
-    <row r="23" spans="1:9" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A23" s="7" t="s">
         <v>59</v>
       </c>
@@ -2632,7 +2626,7 @@
       <c r="H23" s="12"/>
       <c r="I23" s="12"/>
     </row>
-    <row r="24" spans="1:9" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A24" s="7" t="s">
         <v>59</v>
       </c>
@@ -2655,7 +2649,7 @@
       <c r="H24" s="12"/>
       <c r="I24" s="12"/>
     </row>
-    <row r="25" spans="1:9" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A25" s="7" t="s">
         <v>65</v>
       </c>
@@ -2678,7 +2672,7 @@
       <c r="H25" s="12"/>
       <c r="I25" s="12"/>
     </row>
-    <row r="26" spans="1:9" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A26" s="7" t="s">
         <v>65</v>
       </c>
@@ -2701,7 +2695,7 @@
       <c r="H26" s="12"/>
       <c r="I26" s="12"/>
     </row>
-    <row r="27" spans="1:9" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A27" s="7" t="s">
         <v>65</v>
       </c>
@@ -2724,7 +2718,7 @@
       <c r="H27" s="12"/>
       <c r="I27" s="12"/>
     </row>
-    <row r="28" spans="1:9" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A28" s="7" t="s">
         <v>65</v>
       </c>
@@ -2776,7 +2770,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="30" spans="1:9" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A30" s="7" t="s">
         <v>80</v>
       </c>
@@ -2799,7 +2793,7 @@
       <c r="H30" s="12"/>
       <c r="I30" s="12"/>
     </row>
-    <row r="31" spans="1:9" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A31" s="7" t="s">
         <v>80</v>
       </c>
@@ -2822,7 +2816,7 @@
       <c r="H31" s="12"/>
       <c r="I31" s="12"/>
     </row>
-    <row r="32" spans="1:9" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A32" s="7" t="s">
         <v>80</v>
       </c>
@@ -2845,7 +2839,7 @@
       <c r="H32" s="12"/>
       <c r="I32" s="12"/>
     </row>
-    <row r="33" spans="1:9" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A33" s="7" t="s">
         <v>80</v>
       </c>
@@ -2868,7 +2862,7 @@
       <c r="H33" s="12"/>
       <c r="I33" s="12"/>
     </row>
-    <row r="34" spans="1:9" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A34" s="7" t="s">
         <v>80</v>
       </c>
@@ -2891,7 +2885,7 @@
       <c r="H34" s="12"/>
       <c r="I34" s="12"/>
     </row>
-    <row r="35" spans="1:9" s="50" customFormat="1" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:9" s="50" customFormat="1" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A35" s="44" t="s">
         <v>80</v>
       </c>
@@ -2914,7 +2908,7 @@
       <c r="H35" s="49"/>
       <c r="I35" s="49"/>
     </row>
-    <row r="36" spans="1:9" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A36" s="7" t="s">
         <v>80</v>
       </c>
@@ -2995,7 +2989,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="39" spans="1:9" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A39" s="7" t="s">
         <v>95</v>
       </c>
@@ -3076,7 +3070,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="42" spans="1:9" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A42" s="7" t="s">
         <v>95</v>
       </c>
@@ -3099,7 +3093,7 @@
       <c r="H42" s="12"/>
       <c r="I42" s="12"/>
     </row>
-    <row r="43" spans="1:9" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A43" s="7" t="s">
         <v>95</v>
       </c>
@@ -3122,7 +3116,7 @@
       <c r="H43" s="12"/>
       <c r="I43" s="12"/>
     </row>
-    <row r="44" spans="1:9" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A44" s="7" t="s">
         <v>95</v>
       </c>
@@ -3145,7 +3139,7 @@
       <c r="H44" s="12"/>
       <c r="I44" s="12"/>
     </row>
-    <row r="45" spans="1:9" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A45" s="7" t="s">
         <v>95</v>
       </c>
@@ -3284,7 +3278,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="50" spans="1:9" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A50" s="7" t="s">
         <v>95</v>
       </c>
@@ -3307,7 +3301,7 @@
       <c r="H50" s="12"/>
       <c r="I50" s="12"/>
     </row>
-    <row r="51" spans="1:9" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A51" s="7" t="s">
         <v>95</v>
       </c>
@@ -3384,7 +3378,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="54" spans="1:9" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A54" s="7" t="s">
         <v>95</v>
       </c>
@@ -3494,7 +3488,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="58" spans="1:9" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A58" s="7" t="s">
         <v>95</v>
       </c>
@@ -3571,7 +3565,7 @@
       <c r="H60" s="12"/>
       <c r="I60" s="12"/>
     </row>
-    <row r="61" spans="1:9" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A61" s="7" t="s">
         <v>95</v>
       </c>
@@ -3594,7 +3588,7 @@
       <c r="H61" s="12"/>
       <c r="I61" s="12"/>
     </row>
-    <row r="62" spans="1:9" s="50" customFormat="1" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:9" s="50" customFormat="1" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A62" s="44" t="s">
         <v>149</v>
       </c>
@@ -3617,7 +3611,7 @@
       <c r="H62" s="49"/>
       <c r="I62" s="49"/>
     </row>
-    <row r="63" spans="1:9" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A63" s="7" t="s">
         <v>149</v>
       </c>
@@ -3640,7 +3634,7 @@
       <c r="H63" s="12"/>
       <c r="I63" s="12"/>
     </row>
-    <row r="64" spans="1:9" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A64" s="7" t="s">
         <v>149</v>
       </c>
@@ -3750,7 +3744,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="68" spans="1:9" s="50" customFormat="1" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:9" s="50" customFormat="1" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A68" s="44" t="s">
         <v>149</v>
       </c>
@@ -3773,7 +3767,7 @@
       <c r="H68" s="49"/>
       <c r="I68" s="49"/>
     </row>
-    <row r="69" spans="1:9" s="50" customFormat="1" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:9" s="50" customFormat="1" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A69" s="44" t="s">
         <v>149</v>
       </c>
@@ -3796,7 +3790,7 @@
       <c r="H69" s="49"/>
       <c r="I69" s="49"/>
     </row>
-    <row r="70" spans="1:9" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A70" s="7" t="s">
         <v>149</v>
       </c>
@@ -3819,7 +3813,7 @@
       <c r="H70" s="12"/>
       <c r="I70" s="12"/>
     </row>
-    <row r="71" spans="1:9" s="50" customFormat="1" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:9" s="50" customFormat="1" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A71" s="44" t="s">
         <v>149</v>
       </c>
@@ -3842,7 +3836,7 @@
       <c r="H71" s="49"/>
       <c r="I71" s="49"/>
     </row>
-    <row r="72" spans="1:9" s="50" customFormat="1" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:9" s="50" customFormat="1" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A72" s="44" t="s">
         <v>149</v>
       </c>
@@ -3865,7 +3859,7 @@
       <c r="H72" s="49"/>
       <c r="I72" s="49"/>
     </row>
-    <row r="73" spans="1:9" s="50" customFormat="1" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:9" s="50" customFormat="1" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A73" s="44" t="s">
         <v>172</v>
       </c>
@@ -3913,7 +3907,7 @@
       <c r="H74" s="12"/>
       <c r="I74" s="12"/>
     </row>
-    <row r="75" spans="1:9" s="58" customFormat="1" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:9" s="58" customFormat="1" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A75" s="51" t="s">
         <v>177</v>
       </c>
@@ -3936,7 +3930,7 @@
       <c r="H75" s="57"/>
       <c r="I75" s="57"/>
     </row>
-    <row r="76" spans="1:9" s="66" customFormat="1" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:9" s="66" customFormat="1" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A76" s="59" t="s">
         <v>177</v>
       </c>
@@ -3984,7 +3978,7 @@
       <c r="H77" s="12"/>
       <c r="I77" s="12"/>
     </row>
-    <row r="78" spans="1:9" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A78" s="7" t="s">
         <v>177</v>
       </c>
@@ -4007,7 +4001,7 @@
       <c r="H78" s="12"/>
       <c r="I78" s="12"/>
     </row>
-    <row r="79" spans="1:9" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A79" s="7" t="s">
         <v>177</v>
       </c>
@@ -4030,7 +4024,7 @@
       <c r="H79" s="12"/>
       <c r="I79" s="12"/>
     </row>
-    <row r="80" spans="1:9" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A80" s="7" t="s">
         <v>177</v>
       </c>
@@ -4128,7 +4122,7 @@
       <c r="H83" s="12"/>
       <c r="I83" s="12"/>
     </row>
-    <row r="84" spans="1:9" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="84" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A84" s="7" t="s">
         <v>177</v>
       </c>
@@ -4226,7 +4220,7 @@
       <c r="H87" s="12"/>
       <c r="I87" s="12"/>
     </row>
-    <row r="88" spans="1:9" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="88" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A88" s="7" t="s">
         <v>177</v>
       </c>
@@ -4249,7 +4243,7 @@
       <c r="H88" s="12"/>
       <c r="I88" s="12"/>
     </row>
-    <row r="89" spans="1:9" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="89" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A89" s="7" t="s">
         <v>177</v>
       </c>
@@ -4272,7 +4266,7 @@
       <c r="H89" s="12"/>
       <c r="I89" s="12"/>
     </row>
-    <row r="90" spans="1:9" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="90" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A90" s="7" t="s">
         <v>177</v>
       </c>
@@ -4295,7 +4289,7 @@
       <c r="H90" s="12"/>
       <c r="I90" s="12"/>
     </row>
-    <row r="91" spans="1:9" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="91" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A91" s="7" t="s">
         <v>210</v>
       </c>
@@ -4318,7 +4312,7 @@
       <c r="H91" s="12"/>
       <c r="I91" s="12"/>
     </row>
-    <row r="92" spans="1:9" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="92" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A92" s="7" t="s">
         <v>210</v>
       </c>
@@ -4341,7 +4335,7 @@
       <c r="H92" s="12"/>
       <c r="I92" s="12"/>
     </row>
-    <row r="93" spans="1:9" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="93" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A93" s="7" t="s">
         <v>210</v>
       </c>
@@ -4393,7 +4387,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="95" spans="1:9" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="95" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A95" s="7" t="s">
         <v>217</v>
       </c>
@@ -4416,7 +4410,7 @@
       <c r="H95" s="12"/>
       <c r="I95" s="12"/>
     </row>
-    <row r="96" spans="1:9" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="96" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A96" s="7" t="s">
         <v>217</v>
       </c>
@@ -4439,7 +4433,7 @@
       <c r="H96" s="12"/>
       <c r="I96" s="12"/>
     </row>
-    <row r="97" spans="1:10" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="97" spans="1:10" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A97" s="7" t="s">
         <v>217</v>
       </c>
@@ -4520,7 +4514,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="100" spans="1:10" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="100" spans="1:10" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A100" s="7" t="s">
         <v>231</v>
       </c>
@@ -4543,7 +4537,7 @@
       <c r="H100" s="12"/>
       <c r="I100" s="12"/>
     </row>
-    <row r="101" spans="1:10" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="101" spans="1:10" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A101" s="7" t="s">
         <v>231</v>
       </c>
@@ -4569,7 +4563,7 @@
         <v>237</v>
       </c>
     </row>
-    <row r="102" spans="1:10" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="102" spans="1:10" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A102" s="7" t="s">
         <v>238</v>
       </c>
@@ -4592,7 +4586,7 @@
       <c r="H102" s="12"/>
       <c r="I102" s="12"/>
     </row>
-    <row r="103" spans="1:10" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="103" spans="1:10" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A103" s="7" t="s">
         <v>238</v>
       </c>
@@ -4615,7 +4609,7 @@
       <c r="H103" s="12"/>
       <c r="I103" s="12"/>
     </row>
-    <row r="104" spans="1:10" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="104" spans="1:10" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A104" s="7" t="s">
         <v>238</v>
       </c>
@@ -4638,7 +4632,7 @@
       <c r="H104" s="12"/>
       <c r="I104" s="12"/>
     </row>
-    <row r="105" spans="1:10" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="105" spans="1:10" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A105" s="7" t="s">
         <v>238</v>
       </c>
@@ -4661,7 +4655,7 @@
       <c r="H105" s="12"/>
       <c r="I105" s="12"/>
     </row>
-    <row r="106" spans="1:10" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="106" spans="1:10" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A106" s="7" t="s">
         <v>238</v>
       </c>
@@ -4684,7 +4678,7 @@
       <c r="H106" s="12"/>
       <c r="I106" s="12"/>
     </row>
-    <row r="107" spans="1:10" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="107" spans="1:10" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A107" s="7" t="s">
         <v>238</v>
       </c>
@@ -4707,7 +4701,7 @@
       <c r="H107" s="12"/>
       <c r="I107" s="12"/>
     </row>
-    <row r="108" spans="1:10" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="108" spans="1:10" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A108" s="7" t="s">
         <v>238</v>
       </c>
@@ -4730,7 +4724,7 @@
       <c r="H108" s="12"/>
       <c r="I108" s="12"/>
     </row>
-    <row r="109" spans="1:10" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="109" spans="1:10" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A109" s="7" t="s">
         <v>238</v>
       </c>
@@ -4753,7 +4747,7 @@
       <c r="H109" s="12"/>
       <c r="I109" s="12"/>
     </row>
-    <row r="110" spans="1:10" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="110" spans="1:10" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A110" s="7" t="s">
         <v>238</v>
       </c>
@@ -4776,7 +4770,7 @@
       <c r="H110" s="12"/>
       <c r="I110" s="12"/>
     </row>
-    <row r="111" spans="1:10" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="111" spans="1:10" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A111" s="7" t="s">
         <v>238</v>
       </c>
@@ -4799,7 +4793,7 @@
       <c r="H111" s="12"/>
       <c r="I111" s="12"/>
     </row>
-    <row r="112" spans="1:10" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="112" spans="1:10" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A112" s="7" t="s">
         <v>238</v>
       </c>
@@ -4822,7 +4816,7 @@
       <c r="H112" s="12"/>
       <c r="I112" s="12"/>
     </row>
-    <row r="113" spans="1:9" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="113" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A113" s="7" t="s">
         <v>238</v>
       </c>
@@ -4845,7 +4839,7 @@
       <c r="H113" s="12"/>
       <c r="I113" s="12"/>
     </row>
-    <row r="114" spans="1:9" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="114" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A114" s="7" t="s">
         <v>238</v>
       </c>
@@ -4868,7 +4862,7 @@
       <c r="H114" s="12"/>
       <c r="I114" s="12"/>
     </row>
-    <row r="115" spans="1:9" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="115" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A115" s="7" t="s">
         <v>238</v>
       </c>
@@ -4891,7 +4885,7 @@
       <c r="H115" s="12"/>
       <c r="I115" s="12"/>
     </row>
-    <row r="116" spans="1:9" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="116" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A116" s="7" t="s">
         <v>238</v>
       </c>
@@ -4914,7 +4908,7 @@
       <c r="H116" s="12"/>
       <c r="I116" s="12"/>
     </row>
-    <row r="117" spans="1:9" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="117" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A117" s="7" t="s">
         <v>238</v>
       </c>
@@ -4937,7 +4931,7 @@
       <c r="H117" s="12"/>
       <c r="I117" s="12"/>
     </row>
-    <row r="118" spans="1:9" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="118" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A118" s="7" t="s">
         <v>238</v>
       </c>
@@ -4960,7 +4954,7 @@
       <c r="H118" s="12"/>
       <c r="I118" s="12"/>
     </row>
-    <row r="119" spans="1:9" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="119" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A119" s="7" t="s">
         <v>238</v>
       </c>
@@ -4983,7 +4977,7 @@
       <c r="H119" s="12"/>
       <c r="I119" s="12"/>
     </row>
-    <row r="120" spans="1:9" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="120" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A120" s="7" t="s">
         <v>276</v>
       </c>
@@ -5006,7 +5000,7 @@
       <c r="H120" s="12"/>
       <c r="I120" s="12"/>
     </row>
-    <row r="121" spans="1:9" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="121" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A121" s="7" t="s">
         <v>276</v>
       </c>
@@ -5029,7 +5023,7 @@
       <c r="H121" s="12"/>
       <c r="I121" s="12"/>
     </row>
-    <row r="122" spans="1:9" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="122" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A122" s="7" t="s">
         <v>276</v>
       </c>
@@ -5052,7 +5046,7 @@
       <c r="H122" s="12"/>
       <c r="I122" s="12"/>
     </row>
-    <row r="123" spans="1:9" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="123" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A123" s="7" t="s">
         <v>284</v>
       </c>
@@ -5075,7 +5069,7 @@
       <c r="H123" s="12"/>
       <c r="I123" s="12"/>
     </row>
-    <row r="124" spans="1:9" s="50" customFormat="1" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="124" spans="1:9" s="50" customFormat="1" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A124" s="44" t="s">
         <v>287</v>
       </c>
@@ -5098,7 +5092,7 @@
       <c r="H124" s="49"/>
       <c r="I124" s="49"/>
     </row>
-    <row r="125" spans="1:9" s="50" customFormat="1" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="125" spans="1:9" s="50" customFormat="1" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A125" s="44" t="s">
         <v>287</v>
       </c>
@@ -5121,7 +5115,7 @@
       <c r="H125" s="49"/>
       <c r="I125" s="49"/>
     </row>
-    <row r="126" spans="1:9" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="126" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A126" s="7" t="s">
         <v>287</v>
       </c>
@@ -5144,7 +5138,7 @@
       <c r="H126" s="15"/>
       <c r="I126" s="15"/>
     </row>
-    <row r="127" spans="1:9" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="127" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A127" s="7" t="s">
         <v>294</v>
       </c>
@@ -5711,7 +5705,7 @@
         <v>77</v>
       </c>
       <c r="G149" s="13">
-        <v>46284</v>
+        <v>46100</v>
       </c>
       <c r="H149" s="12" t="s">
         <v>354</v>
@@ -5720,7 +5714,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="150" spans="1:10" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="150" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A150" s="7"/>
       <c r="B150" s="8"/>
       <c r="C150" s="39"/>
@@ -5731,7 +5725,7 @@
       <c r="H150" s="12"/>
       <c r="I150" s="12"/>
     </row>
-    <row r="151" spans="1:10" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="151" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A151" s="7"/>
       <c r="B151" s="8"/>
       <c r="C151" s="39"/>
@@ -5742,7 +5736,7 @@
       <c r="H151" s="12"/>
       <c r="I151" s="12"/>
     </row>
-    <row r="152" spans="1:10" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="152" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A152" s="7"/>
       <c r="B152" s="8"/>
       <c r="C152" s="39"/>
@@ -5753,7 +5747,7 @@
       <c r="H152" s="12"/>
       <c r="I152" s="12"/>
     </row>
-    <row r="153" spans="1:10" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="153" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A153" s="7"/>
       <c r="B153" s="8"/>
       <c r="C153" s="39"/>
@@ -5764,7 +5758,7 @@
       <c r="H153" s="12"/>
       <c r="I153" s="12"/>
     </row>
-    <row r="154" spans="1:10" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="154" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A154" s="7"/>
       <c r="B154" s="8"/>
       <c r="C154" s="39"/>
@@ -5775,7 +5769,7 @@
       <c r="H154" s="12"/>
       <c r="I154" s="12"/>
     </row>
-    <row r="155" spans="1:10" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="155" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A155" s="7"/>
       <c r="B155" s="8"/>
       <c r="C155" s="39"/>
@@ -5786,7 +5780,7 @@
       <c r="H155" s="12"/>
       <c r="I155" s="12"/>
     </row>
-    <row r="156" spans="1:10" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="156" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A156" s="7"/>
       <c r="B156" s="8"/>
       <c r="C156" s="39"/>
@@ -5797,7 +5791,7 @@
       <c r="H156" s="12"/>
       <c r="I156" s="12"/>
     </row>
-    <row r="157" spans="1:10" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="157" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A157" s="7"/>
       <c r="B157" s="8"/>
       <c r="C157" s="39"/>
@@ -5808,7 +5802,7 @@
       <c r="H157" s="12"/>
       <c r="I157" s="12"/>
     </row>
-    <row r="158" spans="1:10" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="158" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A158" s="7"/>
       <c r="B158" s="8"/>
       <c r="C158" s="39"/>
@@ -5819,7 +5813,7 @@
       <c r="H158" s="12"/>
       <c r="I158" s="12"/>
     </row>
-    <row r="159" spans="1:10" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="159" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A159" s="7"/>
       <c r="B159" s="8"/>
       <c r="C159" s="39"/>
@@ -5830,7 +5824,7 @@
       <c r="H159" s="12"/>
       <c r="I159" s="12"/>
     </row>
-    <row r="160" spans="1:10" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="160" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A160" s="7"/>
       <c r="B160" s="8"/>
       <c r="C160" s="39"/>
@@ -5841,7 +5835,7 @@
       <c r="H160" s="12"/>
       <c r="I160" s="12"/>
     </row>
-    <row r="161" spans="1:9" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="161" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A161" s="7"/>
       <c r="B161" s="8"/>
       <c r="C161" s="39"/>
@@ -5852,7 +5846,7 @@
       <c r="H161" s="12"/>
       <c r="I161" s="12"/>
     </row>
-    <row r="162" spans="1:9" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="162" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A162" s="7"/>
       <c r="B162" s="8"/>
       <c r="C162" s="39"/>
@@ -5863,7 +5857,7 @@
       <c r="H162" s="12"/>
       <c r="I162" s="12"/>
     </row>
-    <row r="163" spans="1:9" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="163" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A163" s="7"/>
       <c r="B163" s="8"/>
       <c r="C163" s="39"/>
@@ -5874,7 +5868,7 @@
       <c r="H163" s="12"/>
       <c r="I163" s="12"/>
     </row>
-    <row r="164" spans="1:9" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="164" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A164" s="7"/>
       <c r="B164" s="8"/>
       <c r="C164" s="39"/>
@@ -5885,7 +5879,7 @@
       <c r="H164" s="12"/>
       <c r="I164" s="12"/>
     </row>
-    <row r="165" spans="1:9" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="165" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A165" s="7"/>
       <c r="B165" s="8"/>
       <c r="C165" s="39"/>
@@ -5896,7 +5890,7 @@
       <c r="H165" s="12"/>
       <c r="I165" s="12"/>
     </row>
-    <row r="166" spans="1:9" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="166" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A166" s="7"/>
       <c r="B166" s="8"/>
       <c r="C166" s="39"/>
@@ -5907,7 +5901,7 @@
       <c r="H166" s="12"/>
       <c r="I166" s="12"/>
     </row>
-    <row r="167" spans="1:9" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="167" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A167" s="7"/>
       <c r="B167" s="8"/>
       <c r="C167" s="39"/>
@@ -5918,7 +5912,7 @@
       <c r="H167" s="12"/>
       <c r="I167" s="12"/>
     </row>
-    <row r="168" spans="1:9" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="168" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A168" s="7"/>
       <c r="B168" s="8"/>
       <c r="C168" s="39"/>
@@ -5929,7 +5923,7 @@
       <c r="H168" s="12"/>
       <c r="I168" s="12"/>
     </row>
-    <row r="169" spans="1:9" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="169" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A169" s="7"/>
       <c r="B169" s="8"/>
       <c r="C169" s="39"/>
@@ -5940,7 +5934,7 @@
       <c r="H169" s="12"/>
       <c r="I169" s="12"/>
     </row>
-    <row r="170" spans="1:9" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="170" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A170" s="7"/>
       <c r="B170" s="8"/>
       <c r="C170" s="39"/>
@@ -5951,7 +5945,7 @@
       <c r="H170" s="12"/>
       <c r="I170" s="12"/>
     </row>
-    <row r="171" spans="1:9" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="171" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A171" s="7"/>
       <c r="B171" s="8"/>
       <c r="C171" s="39"/>
@@ -5962,7 +5956,7 @@
       <c r="H171" s="12"/>
       <c r="I171" s="12"/>
     </row>
-    <row r="172" spans="1:9" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="172" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A172" s="7"/>
       <c r="B172" s="8"/>
       <c r="C172" s="39"/>
@@ -5973,7 +5967,7 @@
       <c r="H172" s="12"/>
       <c r="I172" s="12"/>
     </row>
-    <row r="173" spans="1:9" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="173" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A173" s="7"/>
       <c r="B173" s="8"/>
       <c r="C173" s="39"/>
@@ -5984,7 +5978,7 @@
       <c r="H173" s="12"/>
       <c r="I173" s="12"/>
     </row>
-    <row r="174" spans="1:9" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="174" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A174" s="7"/>
       <c r="B174" s="8"/>
       <c r="C174" s="39"/>
@@ -5995,7 +5989,7 @@
       <c r="H174" s="12"/>
       <c r="I174" s="12"/>
     </row>
-    <row r="175" spans="1:9" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="175" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A175" s="7"/>
       <c r="B175" s="8"/>
       <c r="C175" s="39"/>
@@ -6006,7 +6000,7 @@
       <c r="H175" s="12"/>
       <c r="I175" s="12"/>
     </row>
-    <row r="176" spans="1:9" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="176" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A176" s="7"/>
       <c r="B176" s="8"/>
       <c r="C176" s="39"/>
@@ -6017,7 +6011,7 @@
       <c r="H176" s="12"/>
       <c r="I176" s="12"/>
     </row>
-    <row r="177" spans="1:9" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="177" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A177" s="7"/>
       <c r="B177" s="8"/>
       <c r="C177" s="39"/>
@@ -6028,7 +6022,7 @@
       <c r="H177" s="12"/>
       <c r="I177" s="12"/>
     </row>
-    <row r="178" spans="1:9" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="178" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A178" s="7"/>
       <c r="B178" s="8"/>
       <c r="C178" s="39"/>
@@ -6039,7 +6033,7 @@
       <c r="H178" s="12"/>
       <c r="I178" s="12"/>
     </row>
-    <row r="179" spans="1:9" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="179" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A179" s="7"/>
       <c r="B179" s="8"/>
       <c r="C179" s="39"/>
@@ -6050,7 +6044,7 @@
       <c r="H179" s="12"/>
       <c r="I179" s="12"/>
     </row>
-    <row r="180" spans="1:9" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="180" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A180" s="7"/>
       <c r="B180" s="8"/>
       <c r="C180" s="39"/>
@@ -6061,7 +6055,7 @@
       <c r="H180" s="12"/>
       <c r="I180" s="12"/>
     </row>
-    <row r="181" spans="1:9" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="181" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A181" s="7"/>
       <c r="B181" s="8"/>
       <c r="C181" s="39"/>
@@ -6072,7 +6066,7 @@
       <c r="H181" s="12"/>
       <c r="I181" s="12"/>
     </row>
-    <row r="182" spans="1:9" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="182" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A182" s="7"/>
       <c r="B182" s="8"/>
       <c r="C182" s="39"/>
@@ -6083,7 +6077,7 @@
       <c r="H182" s="12"/>
       <c r="I182" s="12"/>
     </row>
-    <row r="183" spans="1:9" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="183" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A183" s="7"/>
       <c r="B183" s="8"/>
       <c r="C183" s="39"/>
@@ -6094,7 +6088,7 @@
       <c r="H183" s="12"/>
       <c r="I183" s="12"/>
     </row>
-    <row r="184" spans="1:9" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="184" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A184" s="7"/>
       <c r="B184" s="8"/>
       <c r="C184" s="39"/>
@@ -6105,7 +6099,7 @@
       <c r="H184" s="12"/>
       <c r="I184" s="12"/>
     </row>
-    <row r="185" spans="1:9" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="185" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A185" s="7"/>
       <c r="B185" s="8"/>
       <c r="C185" s="39"/>
@@ -6116,7 +6110,7 @@
       <c r="H185" s="12"/>
       <c r="I185" s="12"/>
     </row>
-    <row r="186" spans="1:9" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="186" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A186" s="7"/>
       <c r="B186" s="8"/>
       <c r="C186" s="39"/>
@@ -6127,7 +6121,7 @@
       <c r="H186" s="12"/>
       <c r="I186" s="12"/>
     </row>
-    <row r="187" spans="1:9" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="187" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A187" s="7"/>
       <c r="B187" s="8"/>
       <c r="C187" s="39"/>
@@ -6138,7 +6132,7 @@
       <c r="H187" s="12"/>
       <c r="I187" s="12"/>
     </row>
-    <row r="188" spans="1:9" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="188" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A188" s="7"/>
       <c r="B188" s="8"/>
       <c r="C188" s="39"/>
@@ -6149,7 +6143,7 @@
       <c r="H188" s="12"/>
       <c r="I188" s="12"/>
     </row>
-    <row r="189" spans="1:9" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="189" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A189" s="7"/>
       <c r="B189" s="8"/>
       <c r="C189" s="39"/>
@@ -6160,7 +6154,7 @@
       <c r="H189" s="12"/>
       <c r="I189" s="12"/>
     </row>
-    <row r="190" spans="1:9" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="190" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A190" s="7"/>
       <c r="B190" s="8"/>
       <c r="C190" s="39"/>
@@ -6171,7 +6165,7 @@
       <c r="H190" s="12"/>
       <c r="I190" s="12"/>
     </row>
-    <row r="191" spans="1:9" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="191" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A191" s="7"/>
       <c r="B191" s="8"/>
       <c r="C191" s="39"/>
@@ -6182,7 +6176,7 @@
       <c r="H191" s="12"/>
       <c r="I191" s="12"/>
     </row>
-    <row r="192" spans="1:9" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="192" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A192" s="7"/>
       <c r="B192" s="8"/>
       <c r="C192" s="39"/>
@@ -6193,7 +6187,7 @@
       <c r="H192" s="12"/>
       <c r="I192" s="12"/>
     </row>
-    <row r="193" spans="1:9" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="193" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A193" s="7"/>
       <c r="B193" s="8"/>
       <c r="C193" s="39"/>
@@ -6204,7 +6198,7 @@
       <c r="H193" s="12"/>
       <c r="I193" s="12"/>
     </row>
-    <row r="194" spans="1:9" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="194" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A194" s="7"/>
       <c r="B194" s="8"/>
       <c r="C194" s="39"/>
@@ -6215,7 +6209,7 @@
       <c r="H194" s="12"/>
       <c r="I194" s="12"/>
     </row>
-    <row r="195" spans="1:9" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="195" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A195" s="7"/>
       <c r="B195" s="8"/>
       <c r="C195" s="39"/>
@@ -6226,7 +6220,7 @@
       <c r="H195" s="12"/>
       <c r="I195" s="12"/>
     </row>
-    <row r="196" spans="1:9" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="196" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A196" s="7"/>
       <c r="B196" s="8"/>
       <c r="C196" s="39"/>
@@ -6237,7 +6231,7 @@
       <c r="H196" s="12"/>
       <c r="I196" s="12"/>
     </row>
-    <row r="197" spans="1:9" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="197" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A197" s="7"/>
       <c r="B197" s="8"/>
       <c r="C197" s="39"/>
@@ -6248,7 +6242,7 @@
       <c r="H197" s="12"/>
       <c r="I197" s="12"/>
     </row>
-    <row r="198" spans="1:9" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="198" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A198" s="7"/>
       <c r="B198" s="8"/>
       <c r="C198" s="39"/>
@@ -6259,7 +6253,7 @@
       <c r="H198" s="12"/>
       <c r="I198" s="12"/>
     </row>
-    <row r="199" spans="1:9" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="199" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A199" s="7"/>
       <c r="B199" s="8"/>
       <c r="C199" s="39"/>
@@ -6270,7 +6264,7 @@
       <c r="H199" s="12"/>
       <c r="I199" s="12"/>
     </row>
-    <row r="200" spans="1:9" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="200" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A200" s="7"/>
       <c r="B200" s="8"/>
       <c r="C200" s="39"/>
@@ -6281,7 +6275,7 @@
       <c r="H200" s="12"/>
       <c r="I200" s="12"/>
     </row>
-    <row r="201" spans="1:9" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="201" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A201" s="7"/>
       <c r="B201" s="8"/>
       <c r="C201" s="39"/>
@@ -6292,7 +6286,7 @@
       <c r="H201" s="12"/>
       <c r="I201" s="12"/>
     </row>
-    <row r="202" spans="1:9" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="202" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A202" s="7"/>
       <c r="B202" s="8"/>
       <c r="C202" s="39"/>
@@ -6303,7 +6297,7 @@
       <c r="H202" s="12"/>
       <c r="I202" s="12"/>
     </row>
-    <row r="203" spans="1:9" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="203" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A203" s="7"/>
       <c r="B203" s="8"/>
       <c r="C203" s="39"/>
@@ -6314,22 +6308,11 @@
       <c r="H203" s="12"/>
       <c r="I203" s="12"/>
     </row>
-    <row r="204" spans="1:9" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A204" s="7"/>
-      <c r="B204" s="8"/>
-      <c r="C204" s="39"/>
-      <c r="D204" s="9"/>
-      <c r="E204" s="8"/>
-      <c r="F204" s="10"/>
-      <c r="G204" s="13"/>
-      <c r="H204" s="12"/>
-      <c r="I204" s="12"/>
-    </row>
-    <row r="205" spans="1:9" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
   <tableParts count="1">
-    <tablePart r:id="rId1"/>
+    <tablePart r:id="rId2"/>
   </tableParts>
 </worksheet>
 </file>
@@ -6753,14 +6736,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_activity xmlns="3e53c16e-6636-411e-b1c4-e9eeb71b3b2a" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x010100027709BF533FA442AFC4A8B2C0110727" ma:contentTypeVersion="15" ma:contentTypeDescription="Crear nuevo documento." ma:contentTypeScope="" ma:versionID="a37fc0d7c302f7619d355a49e1f175a4">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="3e53c16e-6636-411e-b1c4-e9eeb71b3b2a" xmlns:ns4="bda9c1ec-c4e2-44f9-929c-ca399fe36c88" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="01250a30c504a808427f15ccf149ee4d" ns3:_="" ns4:_="">
     <xsd:import namespace="3e53c16e-6636-411e-b1c4-e9eeb71b3b2a"/>
@@ -6993,6 +6968,14 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_activity xmlns="3e53c16e-6636-411e-b1c4-e9eeb71b3b2a" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
@@ -7003,16 +6986,6 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D9861A25-610F-425F-BC6A-AC52D4971411}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="3e53c16e-6636-411e-b1c4-e9eeb71b3b2a"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4794C7E6-B89D-4081-9A67-B8D500EF1EE4}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -7031,6 +7004,16 @@
 </ds:datastoreItem>
 </file>
 
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D9861A25-610F-425F-BC6A-AC52D4971411}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="3e53c16e-6636-411e-b1c4-e9eeb71b3b2a"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3C8123E5-81FD-4C24-91F1-33BC079967E9}">
   <ds:schemaRefs>

--- a/data/bitacora.xlsx
+++ b/data/bitacora.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://grupokaufmann-my.sharepoint.com/personal/samuel_sanchez_grupokaufmann_com/Documents/Documentos/Dev/bitacora_diaria/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="466" documentId="8_{4616FF0F-C10E-4DFE-8F27-869B9C60E0F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4D2E51A4-9A2E-450F-94B9-28F1672981F0}"/>
+  <xr:revisionPtr revIDLastSave="467" documentId="8_{4616FF0F-C10E-4DFE-8F27-869B9C60E0F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9ED67F72-22B1-4A8E-8901-AFC6A7894AC6}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-1155" windowWidth="29040" windowHeight="15720" xr2:uid="{A9E3F017-9040-47A2-B586-0486128F3261}"/>
   </bookViews>
@@ -19,7 +19,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Hoja1!$A$1:$F$127</definedName>
   </definedNames>
-  <calcPr calcId="191028"/>
+  <calcPr calcId="191028" calcCompleted="0"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -1728,7 +1728,13 @@
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{40364ABC-409D-4532-8E14-9D155F80C509}" name="Tabla1" displayName="Tabla1" ref="A1:J205" totalsRowShown="0">
-  <autoFilter ref="A1:J205" xr:uid="{40364ABC-409D-4532-8E14-9D155F80C509}"/>
+  <autoFilter ref="A1:J205" xr:uid="{40364ABC-409D-4532-8E14-9D155F80C509}">
+    <filterColumn colId="5">
+      <filters>
+        <filter val="No revisada"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <tableColumns count="10">
     <tableColumn id="1" xr3:uid="{0A7C6585-5C8B-46BF-ABA0-2DA806D161DC}" name="FLOTA" dataDxfId="9"/>
     <tableColumn id="2" xr3:uid="{EB7792BB-219D-496F-9F16-84F6805E0CB0}" name="VIN CON PROBLEMAS" dataDxfId="8"/>
@@ -2062,7 +2068,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EDA66EBA-6B88-4C75-8217-0B7E221D898D}">
-  <dimension ref="A1:L203"/>
+  <dimension ref="A1:L205"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.453125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="43" style="6" bestFit="1" customWidth="1"/>
@@ -2155,7 +2161,7 @@
       <c r="H3" s="12"/>
       <c r="I3" s="12"/>
     </row>
-    <row r="4" spans="1:12" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:12" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A4" s="7" t="s">
         <v>10</v>
       </c>
@@ -2180,7 +2186,7 @@
       <c r="H4" s="12"/>
       <c r="I4" s="12"/>
     </row>
-    <row r="5" spans="1:12" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:12" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A5" s="7" t="s">
         <v>10</v>
       </c>
@@ -2205,7 +2211,7 @@
       <c r="H5" s="12"/>
       <c r="I5" s="12"/>
     </row>
-    <row r="6" spans="1:12" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:12" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A6" s="7" t="s">
         <v>10</v>
       </c>
@@ -2253,7 +2259,7 @@
       <c r="H7" s="24"/>
       <c r="I7" s="24"/>
     </row>
-    <row r="8" spans="1:12" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:12" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A8" s="7" t="s">
         <v>10</v>
       </c>
@@ -2324,7 +2330,7 @@
       <c r="H10" s="12"/>
       <c r="I10" s="12"/>
     </row>
-    <row r="11" spans="1:12" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:12" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A11" s="7" t="s">
         <v>10</v>
       </c>
@@ -2672,7 +2678,7 @@
       <c r="H25" s="12"/>
       <c r="I25" s="12"/>
     </row>
-    <row r="26" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:9" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A26" s="7" t="s">
         <v>65</v>
       </c>
@@ -2695,7 +2701,7 @@
       <c r="H26" s="12"/>
       <c r="I26" s="12"/>
     </row>
-    <row r="27" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:9" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A27" s="7" t="s">
         <v>65</v>
       </c>
@@ -2718,7 +2724,7 @@
       <c r="H27" s="12"/>
       <c r="I27" s="12"/>
     </row>
-    <row r="28" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:9" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A28" s="7" t="s">
         <v>65</v>
       </c>
@@ -2741,7 +2747,7 @@
       <c r="H28" s="12"/>
       <c r="I28" s="12"/>
     </row>
-    <row r="29" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:9" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A29" s="7" t="s">
         <v>65</v>
       </c>
@@ -2931,7 +2937,7 @@
       <c r="H36" s="12"/>
       <c r="I36" s="12"/>
     </row>
-    <row r="37" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:9" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A37" s="7" t="s">
         <v>95</v>
       </c>
@@ -2960,7 +2966,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="38" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:9" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A38" s="7" t="s">
         <v>95</v>
       </c>
@@ -3012,7 +3018,7 @@
       <c r="H39" s="12"/>
       <c r="I39" s="12"/>
     </row>
-    <row r="40" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:9" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A40" s="7" t="s">
         <v>95</v>
       </c>
@@ -3041,7 +3047,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="41" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:9" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A41" s="7" t="s">
         <v>95</v>
       </c>
@@ -3162,7 +3168,7 @@
       <c r="H45" s="12"/>
       <c r="I45" s="12"/>
     </row>
-    <row r="46" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:9" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A46" s="7" t="s">
         <v>95</v>
       </c>
@@ -3191,7 +3197,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="47" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:9" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A47" s="7" t="s">
         <v>95</v>
       </c>
@@ -3220,7 +3226,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="48" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:9" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A48" s="7" t="s">
         <v>95</v>
       </c>
@@ -3249,7 +3255,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="49" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:9" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A49" s="7" t="s">
         <v>95</v>
       </c>
@@ -3324,7 +3330,7 @@
       <c r="H51" s="12"/>
       <c r="I51" s="12"/>
     </row>
-    <row r="52" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:9" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A52" s="7" t="s">
         <v>95</v>
       </c>
@@ -3349,7 +3355,7 @@
       <c r="H52" s="12"/>
       <c r="I52" s="12"/>
     </row>
-    <row r="53" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:9" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A53" s="7" t="s">
         <v>95</v>
       </c>
@@ -3401,7 +3407,7 @@
       <c r="H54" s="12"/>
       <c r="I54" s="12"/>
     </row>
-    <row r="55" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:9" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A55" s="7" t="s">
         <v>95</v>
       </c>
@@ -3430,7 +3436,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="56" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:9" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A56" s="7" t="s">
         <v>95</v>
       </c>
@@ -3459,7 +3465,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="57" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:9" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A57" s="7" t="s">
         <v>95</v>
       </c>
@@ -3511,7 +3517,7 @@
       <c r="H58" s="12"/>
       <c r="I58" s="12"/>
     </row>
-    <row r="59" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:9" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A59" s="7" t="s">
         <v>95</v>
       </c>
@@ -3540,7 +3546,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="60" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:9" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A60" s="7" t="s">
         <v>95</v>
       </c>
@@ -3657,7 +3663,7 @@
       <c r="H64" s="12"/>
       <c r="I64" s="12"/>
     </row>
-    <row r="65" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:9" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A65" s="7" t="s">
         <v>149</v>
       </c>
@@ -3686,7 +3692,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="66" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:9" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A66" s="7" t="s">
         <v>149</v>
       </c>
@@ -3715,7 +3721,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="67" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:9" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A67" s="7" t="s">
         <v>149</v>
       </c>
@@ -3882,7 +3888,7 @@
       <c r="H73" s="49"/>
       <c r="I73" s="49"/>
     </row>
-    <row r="74" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:9" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A74" s="7" t="s">
         <v>172</v>
       </c>
@@ -3953,7 +3959,7 @@
       <c r="H76" s="65"/>
       <c r="I76" s="65"/>
     </row>
-    <row r="77" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:9" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A77" s="7" t="s">
         <v>177</v>
       </c>
@@ -4047,7 +4053,7 @@
       <c r="H80" s="12"/>
       <c r="I80" s="12"/>
     </row>
-    <row r="81" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:9" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A81" s="7" t="s">
         <v>177</v>
       </c>
@@ -4072,7 +4078,7 @@
       <c r="H81" s="12"/>
       <c r="I81" s="12"/>
     </row>
-    <row r="82" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="82" spans="1:9" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A82" s="7" t="s">
         <v>177</v>
       </c>
@@ -4097,7 +4103,7 @@
       <c r="H82" s="12"/>
       <c r="I82" s="12"/>
     </row>
-    <row r="83" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:9" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A83" s="7" t="s">
         <v>177</v>
       </c>
@@ -4145,7 +4151,7 @@
       <c r="H84" s="12"/>
       <c r="I84" s="12"/>
     </row>
-    <row r="85" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="85" spans="1:9" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A85" s="7" t="s">
         <v>177</v>
       </c>
@@ -4170,7 +4176,7 @@
       <c r="H85" s="12"/>
       <c r="I85" s="12"/>
     </row>
-    <row r="86" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="86" spans="1:9" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A86" s="7" t="s">
         <v>177</v>
       </c>
@@ -4195,7 +4201,7 @@
       <c r="H86" s="12"/>
       <c r="I86" s="12"/>
     </row>
-    <row r="87" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="87" spans="1:9" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A87" s="7" t="s">
         <v>177</v>
       </c>
@@ -4358,7 +4364,7 @@
       <c r="H93" s="12"/>
       <c r="I93" s="12"/>
     </row>
-    <row r="94" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="94" spans="1:9" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A94" s="7" t="s">
         <v>217</v>
       </c>
@@ -4456,7 +4462,7 @@
       <c r="H97" s="12"/>
       <c r="I97" s="12"/>
     </row>
-    <row r="98" spans="1:10" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="98" spans="1:10" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A98" s="7" t="s">
         <v>225</v>
       </c>
@@ -4485,7 +4491,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="99" spans="1:10" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="99" spans="1:10" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A99" s="7" t="s">
         <v>225</v>
       </c>
@@ -4563,7 +4569,7 @@
         <v>237</v>
       </c>
     </row>
-    <row r="102" spans="1:10" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="102" spans="1:10" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A102" s="7" t="s">
         <v>238</v>
       </c>
@@ -4586,7 +4592,7 @@
       <c r="H102" s="12"/>
       <c r="I102" s="12"/>
     </row>
-    <row r="103" spans="1:10" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="103" spans="1:10" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A103" s="7" t="s">
         <v>238</v>
       </c>
@@ -4609,7 +4615,7 @@
       <c r="H103" s="12"/>
       <c r="I103" s="12"/>
     </row>
-    <row r="104" spans="1:10" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="104" spans="1:10" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A104" s="7" t="s">
         <v>238</v>
       </c>
@@ -4632,7 +4638,7 @@
       <c r="H104" s="12"/>
       <c r="I104" s="12"/>
     </row>
-    <row r="105" spans="1:10" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="105" spans="1:10" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A105" s="7" t="s">
         <v>238</v>
       </c>
@@ -4655,7 +4661,7 @@
       <c r="H105" s="12"/>
       <c r="I105" s="12"/>
     </row>
-    <row r="106" spans="1:10" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="106" spans="1:10" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A106" s="7" t="s">
         <v>238</v>
       </c>
@@ -4678,7 +4684,7 @@
       <c r="H106" s="12"/>
       <c r="I106" s="12"/>
     </row>
-    <row r="107" spans="1:10" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="107" spans="1:10" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A107" s="7" t="s">
         <v>238</v>
       </c>
@@ -4701,7 +4707,7 @@
       <c r="H107" s="12"/>
       <c r="I107" s="12"/>
     </row>
-    <row r="108" spans="1:10" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="108" spans="1:10" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A108" s="7" t="s">
         <v>238</v>
       </c>
@@ -4724,7 +4730,7 @@
       <c r="H108" s="12"/>
       <c r="I108" s="12"/>
     </row>
-    <row r="109" spans="1:10" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="109" spans="1:10" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A109" s="7" t="s">
         <v>238</v>
       </c>
@@ -4747,7 +4753,7 @@
       <c r="H109" s="12"/>
       <c r="I109" s="12"/>
     </row>
-    <row r="110" spans="1:10" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="110" spans="1:10" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A110" s="7" t="s">
         <v>238</v>
       </c>
@@ -4770,7 +4776,7 @@
       <c r="H110" s="12"/>
       <c r="I110" s="12"/>
     </row>
-    <row r="111" spans="1:10" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="111" spans="1:10" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A111" s="7" t="s">
         <v>238</v>
       </c>
@@ -4793,7 +4799,7 @@
       <c r="H111" s="12"/>
       <c r="I111" s="12"/>
     </row>
-    <row r="112" spans="1:10" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="112" spans="1:10" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A112" s="7" t="s">
         <v>238</v>
       </c>
@@ -4816,7 +4822,7 @@
       <c r="H112" s="12"/>
       <c r="I112" s="12"/>
     </row>
-    <row r="113" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="113" spans="1:9" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A113" s="7" t="s">
         <v>238</v>
       </c>
@@ -4839,7 +4845,7 @@
       <c r="H113" s="12"/>
       <c r="I113" s="12"/>
     </row>
-    <row r="114" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="114" spans="1:9" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A114" s="7" t="s">
         <v>238</v>
       </c>
@@ -4862,7 +4868,7 @@
       <c r="H114" s="12"/>
       <c r="I114" s="12"/>
     </row>
-    <row r="115" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="115" spans="1:9" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A115" s="7" t="s">
         <v>238</v>
       </c>
@@ -4885,7 +4891,7 @@
       <c r="H115" s="12"/>
       <c r="I115" s="12"/>
     </row>
-    <row r="116" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="116" spans="1:9" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A116" s="7" t="s">
         <v>238</v>
       </c>
@@ -4908,7 +4914,7 @@
       <c r="H116" s="12"/>
       <c r="I116" s="12"/>
     </row>
-    <row r="117" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="117" spans="1:9" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A117" s="7" t="s">
         <v>238</v>
       </c>
@@ -4931,7 +4937,7 @@
       <c r="H117" s="12"/>
       <c r="I117" s="12"/>
     </row>
-    <row r="118" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="118" spans="1:9" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A118" s="7" t="s">
         <v>238</v>
       </c>
@@ -4954,7 +4960,7 @@
       <c r="H118" s="12"/>
       <c r="I118" s="12"/>
     </row>
-    <row r="119" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="119" spans="1:9" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A119" s="7" t="s">
         <v>238</v>
       </c>
@@ -5023,7 +5029,7 @@
       <c r="H121" s="12"/>
       <c r="I121" s="12"/>
     </row>
-    <row r="122" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="122" spans="1:9" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A122" s="7" t="s">
         <v>276</v>
       </c>
@@ -5161,7 +5167,7 @@
       <c r="H127" s="12"/>
       <c r="I127" s="12"/>
     </row>
-    <row r="128" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="128" spans="1:9" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A128" t="s">
         <v>297</v>
       </c>
@@ -5188,7 +5194,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="129" spans="1:10" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="129" spans="1:10" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A129" t="s">
         <v>297</v>
       </c>
@@ -5213,7 +5219,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="130" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="130" spans="1:10" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A130" s="32" t="s">
         <v>303</v>
       </c>
@@ -5238,7 +5244,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="131" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="131" spans="1:10" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A131" s="32" t="s">
         <v>307</v>
       </c>
@@ -5263,7 +5269,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="132" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="132" spans="1:10" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A132" s="32" t="s">
         <v>65</v>
       </c>
@@ -5288,7 +5294,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="133" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="133" spans="1:10" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A133" s="32" t="s">
         <v>313</v>
       </c>
@@ -5313,7 +5319,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="134" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="134" spans="1:10" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A134" s="32" t="s">
         <v>313</v>
       </c>
@@ -5338,7 +5344,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="135" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="135" spans="1:10" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A135" s="32" t="s">
         <v>276</v>
       </c>
@@ -5363,7 +5369,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="136" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="136" spans="1:10" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A136" s="32" t="s">
         <v>320</v>
       </c>
@@ -5389,7 +5395,7 @@
       </c>
       <c r="J136" s="37"/>
     </row>
-    <row r="137" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="137" spans="1:10" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A137" s="32" t="s">
         <v>324</v>
       </c>
@@ -5415,7 +5421,7 @@
       </c>
       <c r="J137" s="37"/>
     </row>
-    <row r="138" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="138" spans="1:10" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A138" s="7" t="s">
         <v>329</v>
       </c>
@@ -5439,7 +5445,7 @@
       </c>
       <c r="J138" s="36"/>
     </row>
-    <row r="139" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="139" spans="1:10" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A139" s="7" t="s">
         <v>329</v>
       </c>
@@ -5463,7 +5469,7 @@
       </c>
       <c r="J139" s="37"/>
     </row>
-    <row r="140" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="140" spans="1:10" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A140" s="7" t="s">
         <v>329</v>
       </c>
@@ -5487,7 +5493,7 @@
       </c>
       <c r="J140" s="37"/>
     </row>
-    <row r="141" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="141" spans="1:10" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A141" s="32" t="s">
         <v>333</v>
       </c>
@@ -5513,7 +5519,7 @@
       </c>
       <c r="J141" s="37"/>
     </row>
-    <row r="142" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="142" spans="1:10" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A142" s="32" t="s">
         <v>313</v>
       </c>
@@ -5538,7 +5544,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="143" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="143" spans="1:10" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A143" s="7" t="s">
         <v>336</v>
       </c>
@@ -5563,7 +5569,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="144" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="144" spans="1:10" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A144" s="32" t="s">
         <v>339</v>
       </c>
@@ -5588,7 +5594,7 @@
         <v>342</v>
       </c>
     </row>
-    <row r="145" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="145" spans="1:10" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A145" s="7" t="s">
         <v>65</v>
       </c>
@@ -5613,7 +5619,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="146" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="146" spans="1:10" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A146" s="7" t="s">
         <v>351</v>
       </c>
@@ -5641,7 +5647,7 @@
         <v>863457051708251</v>
       </c>
     </row>
-    <row r="147" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="147" spans="1:10" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A147" s="7" t="s">
         <v>333</v>
       </c>
@@ -5664,7 +5670,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="148" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="148" spans="1:10" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A148" s="7" t="s">
         <v>333</v>
       </c>
@@ -5689,7 +5695,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="149" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="149" spans="1:10" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A149" s="7" t="s">
         <v>149</v>
       </c>
@@ -5714,7 +5720,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="150" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="150" spans="1:10" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A150" s="7"/>
       <c r="B150" s="8"/>
       <c r="C150" s="39"/>
@@ -5725,7 +5731,7 @@
       <c r="H150" s="12"/>
       <c r="I150" s="12"/>
     </row>
-    <row r="151" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="151" spans="1:10" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A151" s="7"/>
       <c r="B151" s="8"/>
       <c r="C151" s="39"/>
@@ -5736,7 +5742,7 @@
       <c r="H151" s="12"/>
       <c r="I151" s="12"/>
     </row>
-    <row r="152" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="152" spans="1:10" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A152" s="7"/>
       <c r="B152" s="8"/>
       <c r="C152" s="39"/>
@@ -5747,7 +5753,7 @@
       <c r="H152" s="12"/>
       <c r="I152" s="12"/>
     </row>
-    <row r="153" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="153" spans="1:10" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A153" s="7"/>
       <c r="B153" s="8"/>
       <c r="C153" s="39"/>
@@ -5758,7 +5764,7 @@
       <c r="H153" s="12"/>
       <c r="I153" s="12"/>
     </row>
-    <row r="154" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="154" spans="1:10" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A154" s="7"/>
       <c r="B154" s="8"/>
       <c r="C154" s="39"/>
@@ -5769,7 +5775,7 @@
       <c r="H154" s="12"/>
       <c r="I154" s="12"/>
     </row>
-    <row r="155" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="155" spans="1:10" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A155" s="7"/>
       <c r="B155" s="8"/>
       <c r="C155" s="39"/>
@@ -5780,7 +5786,7 @@
       <c r="H155" s="12"/>
       <c r="I155" s="12"/>
     </row>
-    <row r="156" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="156" spans="1:10" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A156" s="7"/>
       <c r="B156" s="8"/>
       <c r="C156" s="39"/>
@@ -5791,7 +5797,7 @@
       <c r="H156" s="12"/>
       <c r="I156" s="12"/>
     </row>
-    <row r="157" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="157" spans="1:10" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A157" s="7"/>
       <c r="B157" s="8"/>
       <c r="C157" s="39"/>
@@ -5802,7 +5808,7 @@
       <c r="H157" s="12"/>
       <c r="I157" s="12"/>
     </row>
-    <row r="158" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="158" spans="1:10" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A158" s="7"/>
       <c r="B158" s="8"/>
       <c r="C158" s="39"/>
@@ -5813,7 +5819,7 @@
       <c r="H158" s="12"/>
       <c r="I158" s="12"/>
     </row>
-    <row r="159" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="159" spans="1:10" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A159" s="7"/>
       <c r="B159" s="8"/>
       <c r="C159" s="39"/>
@@ -5824,7 +5830,7 @@
       <c r="H159" s="12"/>
       <c r="I159" s="12"/>
     </row>
-    <row r="160" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="160" spans="1:10" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A160" s="7"/>
       <c r="B160" s="8"/>
       <c r="C160" s="39"/>
@@ -5835,7 +5841,7 @@
       <c r="H160" s="12"/>
       <c r="I160" s="12"/>
     </row>
-    <row r="161" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="161" spans="1:9" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A161" s="7"/>
       <c r="B161" s="8"/>
       <c r="C161" s="39"/>
@@ -5846,7 +5852,7 @@
       <c r="H161" s="12"/>
       <c r="I161" s="12"/>
     </row>
-    <row r="162" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="162" spans="1:9" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A162" s="7"/>
       <c r="B162" s="8"/>
       <c r="C162" s="39"/>
@@ -5857,7 +5863,7 @@
       <c r="H162" s="12"/>
       <c r="I162" s="12"/>
     </row>
-    <row r="163" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="163" spans="1:9" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A163" s="7"/>
       <c r="B163" s="8"/>
       <c r="C163" s="39"/>
@@ -5868,7 +5874,7 @@
       <c r="H163" s="12"/>
       <c r="I163" s="12"/>
     </row>
-    <row r="164" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="164" spans="1:9" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A164" s="7"/>
       <c r="B164" s="8"/>
       <c r="C164" s="39"/>
@@ -5879,7 +5885,7 @@
       <c r="H164" s="12"/>
       <c r="I164" s="12"/>
     </row>
-    <row r="165" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="165" spans="1:9" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A165" s="7"/>
       <c r="B165" s="8"/>
       <c r="C165" s="39"/>
@@ -5890,7 +5896,7 @@
       <c r="H165" s="12"/>
       <c r="I165" s="12"/>
     </row>
-    <row r="166" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="166" spans="1:9" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A166" s="7"/>
       <c r="B166" s="8"/>
       <c r="C166" s="39"/>
@@ -5901,7 +5907,7 @@
       <c r="H166" s="12"/>
       <c r="I166" s="12"/>
     </row>
-    <row r="167" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="167" spans="1:9" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A167" s="7"/>
       <c r="B167" s="8"/>
       <c r="C167" s="39"/>
@@ -5912,7 +5918,7 @@
       <c r="H167" s="12"/>
       <c r="I167" s="12"/>
     </row>
-    <row r="168" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="168" spans="1:9" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A168" s="7"/>
       <c r="B168" s="8"/>
       <c r="C168" s="39"/>
@@ -5923,7 +5929,7 @@
       <c r="H168" s="12"/>
       <c r="I168" s="12"/>
     </row>
-    <row r="169" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="169" spans="1:9" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A169" s="7"/>
       <c r="B169" s="8"/>
       <c r="C169" s="39"/>
@@ -5934,7 +5940,7 @@
       <c r="H169" s="12"/>
       <c r="I169" s="12"/>
     </row>
-    <row r="170" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="170" spans="1:9" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A170" s="7"/>
       <c r="B170" s="8"/>
       <c r="C170" s="39"/>
@@ -5945,7 +5951,7 @@
       <c r="H170" s="12"/>
       <c r="I170" s="12"/>
     </row>
-    <row r="171" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="171" spans="1:9" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A171" s="7"/>
       <c r="B171" s="8"/>
       <c r="C171" s="39"/>
@@ -5956,7 +5962,7 @@
       <c r="H171" s="12"/>
       <c r="I171" s="12"/>
     </row>
-    <row r="172" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="172" spans="1:9" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A172" s="7"/>
       <c r="B172" s="8"/>
       <c r="C172" s="39"/>
@@ -5967,7 +5973,7 @@
       <c r="H172" s="12"/>
       <c r="I172" s="12"/>
     </row>
-    <row r="173" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="173" spans="1:9" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A173" s="7"/>
       <c r="B173" s="8"/>
       <c r="C173" s="39"/>
@@ -5978,7 +5984,7 @@
       <c r="H173" s="12"/>
       <c r="I173" s="12"/>
     </row>
-    <row r="174" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="174" spans="1:9" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A174" s="7"/>
       <c r="B174" s="8"/>
       <c r="C174" s="39"/>
@@ -5989,7 +5995,7 @@
       <c r="H174" s="12"/>
       <c r="I174" s="12"/>
     </row>
-    <row r="175" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="175" spans="1:9" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A175" s="7"/>
       <c r="B175" s="8"/>
       <c r="C175" s="39"/>
@@ -6000,7 +6006,7 @@
       <c r="H175" s="12"/>
       <c r="I175" s="12"/>
     </row>
-    <row r="176" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="176" spans="1:9" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A176" s="7"/>
       <c r="B176" s="8"/>
       <c r="C176" s="39"/>
@@ -6011,7 +6017,7 @@
       <c r="H176" s="12"/>
       <c r="I176" s="12"/>
     </row>
-    <row r="177" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="177" spans="1:9" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A177" s="7"/>
       <c r="B177" s="8"/>
       <c r="C177" s="39"/>
@@ -6022,7 +6028,7 @@
       <c r="H177" s="12"/>
       <c r="I177" s="12"/>
     </row>
-    <row r="178" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="178" spans="1:9" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A178" s="7"/>
       <c r="B178" s="8"/>
       <c r="C178" s="39"/>
@@ -6033,7 +6039,7 @@
       <c r="H178" s="12"/>
       <c r="I178" s="12"/>
     </row>
-    <row r="179" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="179" spans="1:9" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A179" s="7"/>
       <c r="B179" s="8"/>
       <c r="C179" s="39"/>
@@ -6044,7 +6050,7 @@
       <c r="H179" s="12"/>
       <c r="I179" s="12"/>
     </row>
-    <row r="180" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="180" spans="1:9" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A180" s="7"/>
       <c r="B180" s="8"/>
       <c r="C180" s="39"/>
@@ -6055,7 +6061,7 @@
       <c r="H180" s="12"/>
       <c r="I180" s="12"/>
     </row>
-    <row r="181" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="181" spans="1:9" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A181" s="7"/>
       <c r="B181" s="8"/>
       <c r="C181" s="39"/>
@@ -6066,7 +6072,7 @@
       <c r="H181" s="12"/>
       <c r="I181" s="12"/>
     </row>
-    <row r="182" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="182" spans="1:9" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A182" s="7"/>
       <c r="B182" s="8"/>
       <c r="C182" s="39"/>
@@ -6077,7 +6083,7 @@
       <c r="H182" s="12"/>
       <c r="I182" s="12"/>
     </row>
-    <row r="183" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="183" spans="1:9" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A183" s="7"/>
       <c r="B183" s="8"/>
       <c r="C183" s="39"/>
@@ -6088,7 +6094,7 @@
       <c r="H183" s="12"/>
       <c r="I183" s="12"/>
     </row>
-    <row r="184" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="184" spans="1:9" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A184" s="7"/>
       <c r="B184" s="8"/>
       <c r="C184" s="39"/>
@@ -6099,7 +6105,7 @@
       <c r="H184" s="12"/>
       <c r="I184" s="12"/>
     </row>
-    <row r="185" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="185" spans="1:9" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A185" s="7"/>
       <c r="B185" s="8"/>
       <c r="C185" s="39"/>
@@ -6110,7 +6116,7 @@
       <c r="H185" s="12"/>
       <c r="I185" s="12"/>
     </row>
-    <row r="186" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="186" spans="1:9" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A186" s="7"/>
       <c r="B186" s="8"/>
       <c r="C186" s="39"/>
@@ -6121,7 +6127,7 @@
       <c r="H186" s="12"/>
       <c r="I186" s="12"/>
     </row>
-    <row r="187" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="187" spans="1:9" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A187" s="7"/>
       <c r="B187" s="8"/>
       <c r="C187" s="39"/>
@@ -6132,7 +6138,7 @@
       <c r="H187" s="12"/>
       <c r="I187" s="12"/>
     </row>
-    <row r="188" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="188" spans="1:9" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A188" s="7"/>
       <c r="B188" s="8"/>
       <c r="C188" s="39"/>
@@ -6143,7 +6149,7 @@
       <c r="H188" s="12"/>
       <c r="I188" s="12"/>
     </row>
-    <row r="189" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="189" spans="1:9" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A189" s="7"/>
       <c r="B189" s="8"/>
       <c r="C189" s="39"/>
@@ -6154,7 +6160,7 @@
       <c r="H189" s="12"/>
       <c r="I189" s="12"/>
     </row>
-    <row r="190" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="190" spans="1:9" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A190" s="7"/>
       <c r="B190" s="8"/>
       <c r="C190" s="39"/>
@@ -6165,7 +6171,7 @@
       <c r="H190" s="12"/>
       <c r="I190" s="12"/>
     </row>
-    <row r="191" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="191" spans="1:9" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A191" s="7"/>
       <c r="B191" s="8"/>
       <c r="C191" s="39"/>
@@ -6176,7 +6182,7 @@
       <c r="H191" s="12"/>
       <c r="I191" s="12"/>
     </row>
-    <row r="192" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="192" spans="1:9" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A192" s="7"/>
       <c r="B192" s="8"/>
       <c r="C192" s="39"/>
@@ -6187,7 +6193,7 @@
       <c r="H192" s="12"/>
       <c r="I192" s="12"/>
     </row>
-    <row r="193" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="193" spans="1:9" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A193" s="7"/>
       <c r="B193" s="8"/>
       <c r="C193" s="39"/>
@@ -6198,7 +6204,7 @@
       <c r="H193" s="12"/>
       <c r="I193" s="12"/>
     </row>
-    <row r="194" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="194" spans="1:9" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A194" s="7"/>
       <c r="B194" s="8"/>
       <c r="C194" s="39"/>
@@ -6209,7 +6215,7 @@
       <c r="H194" s="12"/>
       <c r="I194" s="12"/>
     </row>
-    <row r="195" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="195" spans="1:9" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A195" s="7"/>
       <c r="B195" s="8"/>
       <c r="C195" s="39"/>
@@ -6220,7 +6226,7 @@
       <c r="H195" s="12"/>
       <c r="I195" s="12"/>
     </row>
-    <row r="196" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="196" spans="1:9" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A196" s="7"/>
       <c r="B196" s="8"/>
       <c r="C196" s="39"/>
@@ -6231,7 +6237,7 @@
       <c r="H196" s="12"/>
       <c r="I196" s="12"/>
     </row>
-    <row r="197" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="197" spans="1:9" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A197" s="7"/>
       <c r="B197" s="8"/>
       <c r="C197" s="39"/>
@@ -6242,7 +6248,7 @@
       <c r="H197" s="12"/>
       <c r="I197" s="12"/>
     </row>
-    <row r="198" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="198" spans="1:9" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A198" s="7"/>
       <c r="B198" s="8"/>
       <c r="C198" s="39"/>
@@ -6253,7 +6259,7 @@
       <c r="H198" s="12"/>
       <c r="I198" s="12"/>
     </row>
-    <row r="199" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="199" spans="1:9" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A199" s="7"/>
       <c r="B199" s="8"/>
       <c r="C199" s="39"/>
@@ -6264,7 +6270,7 @@
       <c r="H199" s="12"/>
       <c r="I199" s="12"/>
     </row>
-    <row r="200" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="200" spans="1:9" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A200" s="7"/>
       <c r="B200" s="8"/>
       <c r="C200" s="39"/>
@@ -6275,7 +6281,7 @@
       <c r="H200" s="12"/>
       <c r="I200" s="12"/>
     </row>
-    <row r="201" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="201" spans="1:9" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A201" s="7"/>
       <c r="B201" s="8"/>
       <c r="C201" s="39"/>
@@ -6286,7 +6292,7 @@
       <c r="H201" s="12"/>
       <c r="I201" s="12"/>
     </row>
-    <row r="202" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="202" spans="1:9" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A202" s="7"/>
       <c r="B202" s="8"/>
       <c r="C202" s="39"/>
@@ -6297,7 +6303,7 @@
       <c r="H202" s="12"/>
       <c r="I202" s="12"/>
     </row>
-    <row r="203" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="203" spans="1:9" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A203" s="7"/>
       <c r="B203" s="8"/>
       <c r="C203" s="39"/>
@@ -6308,6 +6314,8 @@
       <c r="H203" s="12"/>
       <c r="I203" s="12"/>
     </row>
+    <row r="204" spans="1:9" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="205" spans="1:9" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>

--- a/data/bitacora.xlsx
+++ b/data/bitacora.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://grupokaufmann-my.sharepoint.com/personal/samuel_sanchez_grupokaufmann_com/Documents/Documentos/Dev/bitacora_diaria/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="467" documentId="8_{4616FF0F-C10E-4DFE-8F27-869B9C60E0F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9ED67F72-22B1-4A8E-8901-AFC6A7894AC6}"/>
+  <xr:revisionPtr revIDLastSave="482" documentId="8_{4616FF0F-C10E-4DFE-8F27-869B9C60E0F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F3F2B27D-67A4-40E5-AE7F-EAD633B6E13E}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-1155" windowWidth="29040" windowHeight="15720" xr2:uid="{A9E3F017-9040-47A2-B586-0486128F3261}"/>
   </bookViews>
@@ -19,7 +19,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Hoja1!$A$1:$F$127</definedName>
   </definedNames>
-  <calcPr calcId="191028" calcCompleted="0"/>
+  <calcPr calcId="191028"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="813" uniqueCount="355">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="819" uniqueCount="357">
   <si>
     <t>FLOTA</t>
   </si>
@@ -1105,6 +1105,12 @@
   </si>
   <si>
     <t>Kamaleon Pegado</t>
+  </si>
+  <si>
+    <t>TFLF 71</t>
+  </si>
+  <si>
+    <t>9BM634074RB328601</t>
   </si>
 </sst>
 </file>
@@ -1728,13 +1734,7 @@
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{40364ABC-409D-4532-8E14-9D155F80C509}" name="Tabla1" displayName="Tabla1" ref="A1:J205" totalsRowShown="0">
-  <autoFilter ref="A1:J205" xr:uid="{40364ABC-409D-4532-8E14-9D155F80C509}">
-    <filterColumn colId="5">
-      <filters>
-        <filter val="No revisada"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
+  <autoFilter ref="A1:J205" xr:uid="{40364ABC-409D-4532-8E14-9D155F80C509}"/>
   <tableColumns count="10">
     <tableColumn id="1" xr3:uid="{0A7C6585-5C8B-46BF-ABA0-2DA806D161DC}" name="FLOTA" dataDxfId="9"/>
     <tableColumn id="2" xr3:uid="{EB7792BB-219D-496F-9F16-84F6805E0CB0}" name="VIN CON PROBLEMAS" dataDxfId="8"/>
@@ -2068,7 +2068,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EDA66EBA-6B88-4C75-8217-0B7E221D898D}">
-  <dimension ref="A1:L205"/>
+  <dimension ref="A1:L203"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.453125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="43" style="6" bestFit="1" customWidth="1"/>
@@ -2161,7 +2161,7 @@
       <c r="H3" s="12"/>
       <c r="I3" s="12"/>
     </row>
-    <row r="4" spans="1:12" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:12" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A4" s="7" t="s">
         <v>10</v>
       </c>
@@ -2186,7 +2186,7 @@
       <c r="H4" s="12"/>
       <c r="I4" s="12"/>
     </row>
-    <row r="5" spans="1:12" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:12" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A5" s="7" t="s">
         <v>10</v>
       </c>
@@ -2211,7 +2211,7 @@
       <c r="H5" s="12"/>
       <c r="I5" s="12"/>
     </row>
-    <row r="6" spans="1:12" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:12" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A6" s="7" t="s">
         <v>10</v>
       </c>
@@ -2259,7 +2259,7 @@
       <c r="H7" s="24"/>
       <c r="I7" s="24"/>
     </row>
-    <row r="8" spans="1:12" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:12" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A8" s="7" t="s">
         <v>10</v>
       </c>
@@ -2330,7 +2330,7 @@
       <c r="H10" s="12"/>
       <c r="I10" s="12"/>
     </row>
-    <row r="11" spans="1:12" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:12" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A11" s="7" t="s">
         <v>10</v>
       </c>
@@ -2678,7 +2678,7 @@
       <c r="H25" s="12"/>
       <c r="I25" s="12"/>
     </row>
-    <row r="26" spans="1:9" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A26" s="7" t="s">
         <v>65</v>
       </c>
@@ -2701,7 +2701,7 @@
       <c r="H26" s="12"/>
       <c r="I26" s="12"/>
     </row>
-    <row r="27" spans="1:9" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A27" s="7" t="s">
         <v>65</v>
       </c>
@@ -2724,7 +2724,7 @@
       <c r="H27" s="12"/>
       <c r="I27" s="12"/>
     </row>
-    <row r="28" spans="1:9" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A28" s="7" t="s">
         <v>65</v>
       </c>
@@ -2747,7 +2747,7 @@
       <c r="H28" s="12"/>
       <c r="I28" s="12"/>
     </row>
-    <row r="29" spans="1:9" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A29" s="7" t="s">
         <v>65</v>
       </c>
@@ -2937,7 +2937,7 @@
       <c r="H36" s="12"/>
       <c r="I36" s="12"/>
     </row>
-    <row r="37" spans="1:9" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A37" s="7" t="s">
         <v>95</v>
       </c>
@@ -2966,7 +2966,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="38" spans="1:9" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A38" s="7" t="s">
         <v>95</v>
       </c>
@@ -3018,7 +3018,7 @@
       <c r="H39" s="12"/>
       <c r="I39" s="12"/>
     </row>
-    <row r="40" spans="1:9" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A40" s="7" t="s">
         <v>95</v>
       </c>
@@ -3047,7 +3047,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="41" spans="1:9" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A41" s="7" t="s">
         <v>95</v>
       </c>
@@ -3168,7 +3168,7 @@
       <c r="H45" s="12"/>
       <c r="I45" s="12"/>
     </row>
-    <row r="46" spans="1:9" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A46" s="7" t="s">
         <v>95</v>
       </c>
@@ -3197,7 +3197,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="47" spans="1:9" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A47" s="7" t="s">
         <v>95</v>
       </c>
@@ -3226,7 +3226,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="48" spans="1:9" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A48" s="7" t="s">
         <v>95</v>
       </c>
@@ -3255,7 +3255,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="49" spans="1:9" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A49" s="7" t="s">
         <v>95</v>
       </c>
@@ -3330,7 +3330,7 @@
       <c r="H51" s="12"/>
       <c r="I51" s="12"/>
     </row>
-    <row r="52" spans="1:9" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A52" s="7" t="s">
         <v>95</v>
       </c>
@@ -3355,7 +3355,7 @@
       <c r="H52" s="12"/>
       <c r="I52" s="12"/>
     </row>
-    <row r="53" spans="1:9" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A53" s="7" t="s">
         <v>95</v>
       </c>
@@ -3407,7 +3407,7 @@
       <c r="H54" s="12"/>
       <c r="I54" s="12"/>
     </row>
-    <row r="55" spans="1:9" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A55" s="7" t="s">
         <v>95</v>
       </c>
@@ -3436,7 +3436,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="56" spans="1:9" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A56" s="7" t="s">
         <v>95</v>
       </c>
@@ -3465,7 +3465,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="57" spans="1:9" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A57" s="7" t="s">
         <v>95</v>
       </c>
@@ -3517,7 +3517,7 @@
       <c r="H58" s="12"/>
       <c r="I58" s="12"/>
     </row>
-    <row r="59" spans="1:9" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A59" s="7" t="s">
         <v>95</v>
       </c>
@@ -3546,7 +3546,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="60" spans="1:9" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A60" s="7" t="s">
         <v>95</v>
       </c>
@@ -3663,7 +3663,7 @@
       <c r="H64" s="12"/>
       <c r="I64" s="12"/>
     </row>
-    <row r="65" spans="1:9" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A65" s="7" t="s">
         <v>149</v>
       </c>
@@ -3692,7 +3692,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="66" spans="1:9" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A66" s="7" t="s">
         <v>149</v>
       </c>
@@ -3721,7 +3721,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="67" spans="1:9" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A67" s="7" t="s">
         <v>149</v>
       </c>
@@ -3888,7 +3888,7 @@
       <c r="H73" s="49"/>
       <c r="I73" s="49"/>
     </row>
-    <row r="74" spans="1:9" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A74" s="7" t="s">
         <v>172</v>
       </c>
@@ -3959,7 +3959,7 @@
       <c r="H76" s="65"/>
       <c r="I76" s="65"/>
     </row>
-    <row r="77" spans="1:9" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A77" s="7" t="s">
         <v>177</v>
       </c>
@@ -4053,7 +4053,7 @@
       <c r="H80" s="12"/>
       <c r="I80" s="12"/>
     </row>
-    <row r="81" spans="1:9" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A81" s="7" t="s">
         <v>177</v>
       </c>
@@ -4078,7 +4078,7 @@
       <c r="H81" s="12"/>
       <c r="I81" s="12"/>
     </row>
-    <row r="82" spans="1:9" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="82" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A82" s="7" t="s">
         <v>177</v>
       </c>
@@ -4103,7 +4103,7 @@
       <c r="H82" s="12"/>
       <c r="I82" s="12"/>
     </row>
-    <row r="83" spans="1:9" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A83" s="7" t="s">
         <v>177</v>
       </c>
@@ -4151,7 +4151,7 @@
       <c r="H84" s="12"/>
       <c r="I84" s="12"/>
     </row>
-    <row r="85" spans="1:9" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="85" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A85" s="7" t="s">
         <v>177</v>
       </c>
@@ -4176,7 +4176,7 @@
       <c r="H85" s="12"/>
       <c r="I85" s="12"/>
     </row>
-    <row r="86" spans="1:9" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="86" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A86" s="7" t="s">
         <v>177</v>
       </c>
@@ -4201,7 +4201,7 @@
       <c r="H86" s="12"/>
       <c r="I86" s="12"/>
     </row>
-    <row r="87" spans="1:9" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="87" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A87" s="7" t="s">
         <v>177</v>
       </c>
@@ -4364,7 +4364,7 @@
       <c r="H93" s="12"/>
       <c r="I93" s="12"/>
     </row>
-    <row r="94" spans="1:9" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="94" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A94" s="7" t="s">
         <v>217</v>
       </c>
@@ -4462,7 +4462,7 @@
       <c r="H97" s="12"/>
       <c r="I97" s="12"/>
     </row>
-    <row r="98" spans="1:10" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="98" spans="1:10" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A98" s="7" t="s">
         <v>225</v>
       </c>
@@ -4491,7 +4491,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="99" spans="1:10" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="99" spans="1:10" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A99" s="7" t="s">
         <v>225</v>
       </c>
@@ -4569,7 +4569,7 @@
         <v>237</v>
       </c>
     </row>
-    <row r="102" spans="1:10" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="102" spans="1:10" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A102" s="7" t="s">
         <v>238</v>
       </c>
@@ -4592,7 +4592,7 @@
       <c r="H102" s="12"/>
       <c r="I102" s="12"/>
     </row>
-    <row r="103" spans="1:10" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="103" spans="1:10" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A103" s="7" t="s">
         <v>238</v>
       </c>
@@ -4615,7 +4615,7 @@
       <c r="H103" s="12"/>
       <c r="I103" s="12"/>
     </row>
-    <row r="104" spans="1:10" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="104" spans="1:10" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A104" s="7" t="s">
         <v>238</v>
       </c>
@@ -4638,7 +4638,7 @@
       <c r="H104" s="12"/>
       <c r="I104" s="12"/>
     </row>
-    <row r="105" spans="1:10" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="105" spans="1:10" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A105" s="7" t="s">
         <v>238</v>
       </c>
@@ -4661,7 +4661,7 @@
       <c r="H105" s="12"/>
       <c r="I105" s="12"/>
     </row>
-    <row r="106" spans="1:10" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="106" spans="1:10" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A106" s="7" t="s">
         <v>238</v>
       </c>
@@ -4684,7 +4684,7 @@
       <c r="H106" s="12"/>
       <c r="I106" s="12"/>
     </row>
-    <row r="107" spans="1:10" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="107" spans="1:10" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A107" s="7" t="s">
         <v>238</v>
       </c>
@@ -4707,7 +4707,7 @@
       <c r="H107" s="12"/>
       <c r="I107" s="12"/>
     </row>
-    <row r="108" spans="1:10" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="108" spans="1:10" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A108" s="7" t="s">
         <v>238</v>
       </c>
@@ -4730,7 +4730,7 @@
       <c r="H108" s="12"/>
       <c r="I108" s="12"/>
     </row>
-    <row r="109" spans="1:10" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="109" spans="1:10" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A109" s="7" t="s">
         <v>238</v>
       </c>
@@ -4753,7 +4753,7 @@
       <c r="H109" s="12"/>
       <c r="I109" s="12"/>
     </row>
-    <row r="110" spans="1:10" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="110" spans="1:10" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A110" s="7" t="s">
         <v>238</v>
       </c>
@@ -4776,7 +4776,7 @@
       <c r="H110" s="12"/>
       <c r="I110" s="12"/>
     </row>
-    <row r="111" spans="1:10" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="111" spans="1:10" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A111" s="7" t="s">
         <v>238</v>
       </c>
@@ -4799,7 +4799,7 @@
       <c r="H111" s="12"/>
       <c r="I111" s="12"/>
     </row>
-    <row r="112" spans="1:10" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="112" spans="1:10" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A112" s="7" t="s">
         <v>238</v>
       </c>
@@ -4822,7 +4822,7 @@
       <c r="H112" s="12"/>
       <c r="I112" s="12"/>
     </row>
-    <row r="113" spans="1:9" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="113" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A113" s="7" t="s">
         <v>238</v>
       </c>
@@ -4845,7 +4845,7 @@
       <c r="H113" s="12"/>
       <c r="I113" s="12"/>
     </row>
-    <row r="114" spans="1:9" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="114" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A114" s="7" t="s">
         <v>238</v>
       </c>
@@ -4868,7 +4868,7 @@
       <c r="H114" s="12"/>
       <c r="I114" s="12"/>
     </row>
-    <row r="115" spans="1:9" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="115" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A115" s="7" t="s">
         <v>238</v>
       </c>
@@ -4891,7 +4891,7 @@
       <c r="H115" s="12"/>
       <c r="I115" s="12"/>
     </row>
-    <row r="116" spans="1:9" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="116" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A116" s="7" t="s">
         <v>238</v>
       </c>
@@ -4914,7 +4914,7 @@
       <c r="H116" s="12"/>
       <c r="I116" s="12"/>
     </row>
-    <row r="117" spans="1:9" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="117" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A117" s="7" t="s">
         <v>238</v>
       </c>
@@ -4937,7 +4937,7 @@
       <c r="H117" s="12"/>
       <c r="I117" s="12"/>
     </row>
-    <row r="118" spans="1:9" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="118" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A118" s="7" t="s">
         <v>238</v>
       </c>
@@ -4960,7 +4960,7 @@
       <c r="H118" s="12"/>
       <c r="I118" s="12"/>
     </row>
-    <row r="119" spans="1:9" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="119" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A119" s="7" t="s">
         <v>238</v>
       </c>
@@ -5029,7 +5029,7 @@
       <c r="H121" s="12"/>
       <c r="I121" s="12"/>
     </row>
-    <row r="122" spans="1:9" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="122" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A122" s="7" t="s">
         <v>276</v>
       </c>
@@ -5167,7 +5167,7 @@
       <c r="H127" s="12"/>
       <c r="I127" s="12"/>
     </row>
-    <row r="128" spans="1:9" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="128" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A128" t="s">
         <v>297</v>
       </c>
@@ -5194,7 +5194,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="129" spans="1:10" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="129" spans="1:10" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A129" t="s">
         <v>297</v>
       </c>
@@ -5219,7 +5219,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="130" spans="1:10" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="130" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A130" s="32" t="s">
         <v>303</v>
       </c>
@@ -5244,7 +5244,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="131" spans="1:10" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="131" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A131" s="32" t="s">
         <v>307</v>
       </c>
@@ -5269,7 +5269,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="132" spans="1:10" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="132" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A132" s="32" t="s">
         <v>65</v>
       </c>
@@ -5294,7 +5294,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="133" spans="1:10" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="133" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A133" s="32" t="s">
         <v>313</v>
       </c>
@@ -5319,7 +5319,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="134" spans="1:10" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="134" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A134" s="32" t="s">
         <v>313</v>
       </c>
@@ -5344,7 +5344,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="135" spans="1:10" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="135" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A135" s="32" t="s">
         <v>276</v>
       </c>
@@ -5369,7 +5369,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="136" spans="1:10" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="136" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A136" s="32" t="s">
         <v>320</v>
       </c>
@@ -5395,7 +5395,7 @@
       </c>
       <c r="J136" s="37"/>
     </row>
-    <row r="137" spans="1:10" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="137" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A137" s="32" t="s">
         <v>324</v>
       </c>
@@ -5421,7 +5421,7 @@
       </c>
       <c r="J137" s="37"/>
     </row>
-    <row r="138" spans="1:10" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="138" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A138" s="7" t="s">
         <v>329</v>
       </c>
@@ -5445,7 +5445,7 @@
       </c>
       <c r="J138" s="36"/>
     </row>
-    <row r="139" spans="1:10" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="139" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A139" s="7" t="s">
         <v>329</v>
       </c>
@@ -5469,7 +5469,7 @@
       </c>
       <c r="J139" s="37"/>
     </row>
-    <row r="140" spans="1:10" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="140" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A140" s="7" t="s">
         <v>329</v>
       </c>
@@ -5493,7 +5493,7 @@
       </c>
       <c r="J140" s="37"/>
     </row>
-    <row r="141" spans="1:10" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="141" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A141" s="32" t="s">
         <v>333</v>
       </c>
@@ -5519,7 +5519,7 @@
       </c>
       <c r="J141" s="37"/>
     </row>
-    <row r="142" spans="1:10" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="142" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A142" s="32" t="s">
         <v>313</v>
       </c>
@@ -5544,7 +5544,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="143" spans="1:10" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="143" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A143" s="7" t="s">
         <v>336</v>
       </c>
@@ -5569,7 +5569,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="144" spans="1:10" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="144" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A144" s="32" t="s">
         <v>339</v>
       </c>
@@ -5594,7 +5594,7 @@
         <v>342</v>
       </c>
     </row>
-    <row r="145" spans="1:10" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="145" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A145" s="7" t="s">
         <v>65</v>
       </c>
@@ -5619,7 +5619,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="146" spans="1:10" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="146" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A146" s="7" t="s">
         <v>351</v>
       </c>
@@ -5647,7 +5647,7 @@
         <v>863457051708251</v>
       </c>
     </row>
-    <row r="147" spans="1:10" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="147" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A147" s="7" t="s">
         <v>333</v>
       </c>
@@ -5670,7 +5670,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="148" spans="1:10" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="148" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A148" s="7" t="s">
         <v>333</v>
       </c>
@@ -5695,7 +5695,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="149" spans="1:10" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="149" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A149" s="7" t="s">
         <v>149</v>
       </c>
@@ -5720,18 +5720,32 @@
         <v>79</v>
       </c>
     </row>
-    <row r="150" spans="1:10" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A150" s="7"/>
-      <c r="B150" s="8"/>
-      <c r="C150" s="39"/>
+    <row r="150" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A150" s="7" t="s">
+        <v>351</v>
+      </c>
+      <c r="B150" s="8" t="s">
+        <v>356</v>
+      </c>
+      <c r="C150" s="39" t="s">
+        <v>355</v>
+      </c>
       <c r="D150" s="9"/>
       <c r="E150" s="8"/>
-      <c r="F150" s="10"/>
-      <c r="G150" s="13"/>
-      <c r="H150" s="12"/>
-      <c r="I150" s="12"/>
-    </row>
-    <row r="151" spans="1:10" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="F150" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="G150" s="13">
+        <v>46119</v>
+      </c>
+      <c r="H150" s="24" t="s">
+        <v>327</v>
+      </c>
+      <c r="I150" s="15" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="151" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A151" s="7"/>
       <c r="B151" s="8"/>
       <c r="C151" s="39"/>
@@ -5742,7 +5756,7 @@
       <c r="H151" s="12"/>
       <c r="I151" s="12"/>
     </row>
-    <row r="152" spans="1:10" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="152" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A152" s="7"/>
       <c r="B152" s="8"/>
       <c r="C152" s="39"/>
@@ -5753,7 +5767,7 @@
       <c r="H152" s="12"/>
       <c r="I152" s="12"/>
     </row>
-    <row r="153" spans="1:10" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="153" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A153" s="7"/>
       <c r="B153" s="8"/>
       <c r="C153" s="39"/>
@@ -5764,7 +5778,7 @@
       <c r="H153" s="12"/>
       <c r="I153" s="12"/>
     </row>
-    <row r="154" spans="1:10" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="154" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A154" s="7"/>
       <c r="B154" s="8"/>
       <c r="C154" s="39"/>
@@ -5775,7 +5789,7 @@
       <c r="H154" s="12"/>
       <c r="I154" s="12"/>
     </row>
-    <row r="155" spans="1:10" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="155" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A155" s="7"/>
       <c r="B155" s="8"/>
       <c r="C155" s="39"/>
@@ -5786,7 +5800,7 @@
       <c r="H155" s="12"/>
       <c r="I155" s="12"/>
     </row>
-    <row r="156" spans="1:10" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="156" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A156" s="7"/>
       <c r="B156" s="8"/>
       <c r="C156" s="39"/>
@@ -5797,7 +5811,7 @@
       <c r="H156" s="12"/>
       <c r="I156" s="12"/>
     </row>
-    <row r="157" spans="1:10" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="157" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A157" s="7"/>
       <c r="B157" s="8"/>
       <c r="C157" s="39"/>
@@ -5808,7 +5822,7 @@
       <c r="H157" s="12"/>
       <c r="I157" s="12"/>
     </row>
-    <row r="158" spans="1:10" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="158" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A158" s="7"/>
       <c r="B158" s="8"/>
       <c r="C158" s="39"/>
@@ -5819,7 +5833,7 @@
       <c r="H158" s="12"/>
       <c r="I158" s="12"/>
     </row>
-    <row r="159" spans="1:10" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="159" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A159" s="7"/>
       <c r="B159" s="8"/>
       <c r="C159" s="39"/>
@@ -5830,7 +5844,7 @@
       <c r="H159" s="12"/>
       <c r="I159" s="12"/>
     </row>
-    <row r="160" spans="1:10" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="160" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A160" s="7"/>
       <c r="B160" s="8"/>
       <c r="C160" s="39"/>
@@ -5841,7 +5855,7 @@
       <c r="H160" s="12"/>
       <c r="I160" s="12"/>
     </row>
-    <row r="161" spans="1:9" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="161" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A161" s="7"/>
       <c r="B161" s="8"/>
       <c r="C161" s="39"/>
@@ -5852,7 +5866,7 @@
       <c r="H161" s="12"/>
       <c r="I161" s="12"/>
     </row>
-    <row r="162" spans="1:9" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="162" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A162" s="7"/>
       <c r="B162" s="8"/>
       <c r="C162" s="39"/>
@@ -5863,7 +5877,7 @@
       <c r="H162" s="12"/>
       <c r="I162" s="12"/>
     </row>
-    <row r="163" spans="1:9" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="163" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A163" s="7"/>
       <c r="B163" s="8"/>
       <c r="C163" s="39"/>
@@ -5874,7 +5888,7 @@
       <c r="H163" s="12"/>
       <c r="I163" s="12"/>
     </row>
-    <row r="164" spans="1:9" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="164" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A164" s="7"/>
       <c r="B164" s="8"/>
       <c r="C164" s="39"/>
@@ -5885,7 +5899,7 @@
       <c r="H164" s="12"/>
       <c r="I164" s="12"/>
     </row>
-    <row r="165" spans="1:9" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="165" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A165" s="7"/>
       <c r="B165" s="8"/>
       <c r="C165" s="39"/>
@@ -5896,7 +5910,7 @@
       <c r="H165" s="12"/>
       <c r="I165" s="12"/>
     </row>
-    <row r="166" spans="1:9" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="166" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A166" s="7"/>
       <c r="B166" s="8"/>
       <c r="C166" s="39"/>
@@ -5907,7 +5921,7 @@
       <c r="H166" s="12"/>
       <c r="I166" s="12"/>
     </row>
-    <row r="167" spans="1:9" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="167" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A167" s="7"/>
       <c r="B167" s="8"/>
       <c r="C167" s="39"/>
@@ -5918,7 +5932,7 @@
       <c r="H167" s="12"/>
       <c r="I167" s="12"/>
     </row>
-    <row r="168" spans="1:9" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="168" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A168" s="7"/>
       <c r="B168" s="8"/>
       <c r="C168" s="39"/>
@@ -5929,7 +5943,7 @@
       <c r="H168" s="12"/>
       <c r="I168" s="12"/>
     </row>
-    <row r="169" spans="1:9" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="169" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A169" s="7"/>
       <c r="B169" s="8"/>
       <c r="C169" s="39"/>
@@ -5940,7 +5954,7 @@
       <c r="H169" s="12"/>
       <c r="I169" s="12"/>
     </row>
-    <row r="170" spans="1:9" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="170" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A170" s="7"/>
       <c r="B170" s="8"/>
       <c r="C170" s="39"/>
@@ -5951,7 +5965,7 @@
       <c r="H170" s="12"/>
       <c r="I170" s="12"/>
     </row>
-    <row r="171" spans="1:9" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="171" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A171" s="7"/>
       <c r="B171" s="8"/>
       <c r="C171" s="39"/>
@@ -5962,7 +5976,7 @@
       <c r="H171" s="12"/>
       <c r="I171" s="12"/>
     </row>
-    <row r="172" spans="1:9" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="172" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A172" s="7"/>
       <c r="B172" s="8"/>
       <c r="C172" s="39"/>
@@ -5973,7 +5987,7 @@
       <c r="H172" s="12"/>
       <c r="I172" s="12"/>
     </row>
-    <row r="173" spans="1:9" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="173" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A173" s="7"/>
       <c r="B173" s="8"/>
       <c r="C173" s="39"/>
@@ -5984,7 +5998,7 @@
       <c r="H173" s="12"/>
       <c r="I173" s="12"/>
     </row>
-    <row r="174" spans="1:9" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="174" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A174" s="7"/>
       <c r="B174" s="8"/>
       <c r="C174" s="39"/>
@@ -5995,7 +6009,7 @@
       <c r="H174" s="12"/>
       <c r="I174" s="12"/>
     </row>
-    <row r="175" spans="1:9" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="175" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A175" s="7"/>
       <c r="B175" s="8"/>
       <c r="C175" s="39"/>
@@ -6006,7 +6020,7 @@
       <c r="H175" s="12"/>
       <c r="I175" s="12"/>
     </row>
-    <row r="176" spans="1:9" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="176" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A176" s="7"/>
       <c r="B176" s="8"/>
       <c r="C176" s="39"/>
@@ -6017,7 +6031,7 @@
       <c r="H176" s="12"/>
       <c r="I176" s="12"/>
     </row>
-    <row r="177" spans="1:9" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="177" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A177" s="7"/>
       <c r="B177" s="8"/>
       <c r="C177" s="39"/>
@@ -6028,7 +6042,7 @@
       <c r="H177" s="12"/>
       <c r="I177" s="12"/>
     </row>
-    <row r="178" spans="1:9" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="178" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A178" s="7"/>
       <c r="B178" s="8"/>
       <c r="C178" s="39"/>
@@ -6039,7 +6053,7 @@
       <c r="H178" s="12"/>
       <c r="I178" s="12"/>
     </row>
-    <row r="179" spans="1:9" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="179" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A179" s="7"/>
       <c r="B179" s="8"/>
       <c r="C179" s="39"/>
@@ -6050,7 +6064,7 @@
       <c r="H179" s="12"/>
       <c r="I179" s="12"/>
     </row>
-    <row r="180" spans="1:9" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="180" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A180" s="7"/>
       <c r="B180" s="8"/>
       <c r="C180" s="39"/>
@@ -6061,7 +6075,7 @@
       <c r="H180" s="12"/>
       <c r="I180" s="12"/>
     </row>
-    <row r="181" spans="1:9" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="181" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A181" s="7"/>
       <c r="B181" s="8"/>
       <c r="C181" s="39"/>
@@ -6072,7 +6086,7 @@
       <c r="H181" s="12"/>
       <c r="I181" s="12"/>
     </row>
-    <row r="182" spans="1:9" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="182" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A182" s="7"/>
       <c r="B182" s="8"/>
       <c r="C182" s="39"/>
@@ -6083,7 +6097,7 @@
       <c r="H182" s="12"/>
       <c r="I182" s="12"/>
     </row>
-    <row r="183" spans="1:9" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="183" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A183" s="7"/>
       <c r="B183" s="8"/>
       <c r="C183" s="39"/>
@@ -6094,7 +6108,7 @@
       <c r="H183" s="12"/>
       <c r="I183" s="12"/>
     </row>
-    <row r="184" spans="1:9" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="184" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A184" s="7"/>
       <c r="B184" s="8"/>
       <c r="C184" s="39"/>
@@ -6105,7 +6119,7 @@
       <c r="H184" s="12"/>
       <c r="I184" s="12"/>
     </row>
-    <row r="185" spans="1:9" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="185" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A185" s="7"/>
       <c r="B185" s="8"/>
       <c r="C185" s="39"/>
@@ -6116,7 +6130,7 @@
       <c r="H185" s="12"/>
       <c r="I185" s="12"/>
     </row>
-    <row r="186" spans="1:9" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="186" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A186" s="7"/>
       <c r="B186" s="8"/>
       <c r="C186" s="39"/>
@@ -6127,7 +6141,7 @@
       <c r="H186" s="12"/>
       <c r="I186" s="12"/>
     </row>
-    <row r="187" spans="1:9" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="187" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A187" s="7"/>
       <c r="B187" s="8"/>
       <c r="C187" s="39"/>
@@ -6138,7 +6152,7 @@
       <c r="H187" s="12"/>
       <c r="I187" s="12"/>
     </row>
-    <row r="188" spans="1:9" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="188" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A188" s="7"/>
       <c r="B188" s="8"/>
       <c r="C188" s="39"/>
@@ -6149,7 +6163,7 @@
       <c r="H188" s="12"/>
       <c r="I188" s="12"/>
     </row>
-    <row r="189" spans="1:9" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="189" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A189" s="7"/>
       <c r="B189" s="8"/>
       <c r="C189" s="39"/>
@@ -6160,7 +6174,7 @@
       <c r="H189" s="12"/>
       <c r="I189" s="12"/>
     </row>
-    <row r="190" spans="1:9" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="190" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A190" s="7"/>
       <c r="B190" s="8"/>
       <c r="C190" s="39"/>
@@ -6171,7 +6185,7 @@
       <c r="H190" s="12"/>
       <c r="I190" s="12"/>
     </row>
-    <row r="191" spans="1:9" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="191" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A191" s="7"/>
       <c r="B191" s="8"/>
       <c r="C191" s="39"/>
@@ -6182,7 +6196,7 @@
       <c r="H191" s="12"/>
       <c r="I191" s="12"/>
     </row>
-    <row r="192" spans="1:9" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="192" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A192" s="7"/>
       <c r="B192" s="8"/>
       <c r="C192" s="39"/>
@@ -6193,7 +6207,7 @@
       <c r="H192" s="12"/>
       <c r="I192" s="12"/>
     </row>
-    <row r="193" spans="1:9" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="193" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A193" s="7"/>
       <c r="B193" s="8"/>
       <c r="C193" s="39"/>
@@ -6204,7 +6218,7 @@
       <c r="H193" s="12"/>
       <c r="I193" s="12"/>
     </row>
-    <row r="194" spans="1:9" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="194" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A194" s="7"/>
       <c r="B194" s="8"/>
       <c r="C194" s="39"/>
@@ -6215,7 +6229,7 @@
       <c r="H194" s="12"/>
       <c r="I194" s="12"/>
     </row>
-    <row r="195" spans="1:9" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="195" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A195" s="7"/>
       <c r="B195" s="8"/>
       <c r="C195" s="39"/>
@@ -6226,7 +6240,7 @@
       <c r="H195" s="12"/>
       <c r="I195" s="12"/>
     </row>
-    <row r="196" spans="1:9" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="196" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A196" s="7"/>
       <c r="B196" s="8"/>
       <c r="C196" s="39"/>
@@ -6237,7 +6251,7 @@
       <c r="H196" s="12"/>
       <c r="I196" s="12"/>
     </row>
-    <row r="197" spans="1:9" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="197" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A197" s="7"/>
       <c r="B197" s="8"/>
       <c r="C197" s="39"/>
@@ -6248,7 +6262,7 @@
       <c r="H197" s="12"/>
       <c r="I197" s="12"/>
     </row>
-    <row r="198" spans="1:9" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="198" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A198" s="7"/>
       <c r="B198" s="8"/>
       <c r="C198" s="39"/>
@@ -6259,7 +6273,7 @@
       <c r="H198" s="12"/>
       <c r="I198" s="12"/>
     </row>
-    <row r="199" spans="1:9" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="199" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A199" s="7"/>
       <c r="B199" s="8"/>
       <c r="C199" s="39"/>
@@ -6270,7 +6284,7 @@
       <c r="H199" s="12"/>
       <c r="I199" s="12"/>
     </row>
-    <row r="200" spans="1:9" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="200" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A200" s="7"/>
       <c r="B200" s="8"/>
       <c r="C200" s="39"/>
@@ -6281,7 +6295,7 @@
       <c r="H200" s="12"/>
       <c r="I200" s="12"/>
     </row>
-    <row r="201" spans="1:9" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="201" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A201" s="7"/>
       <c r="B201" s="8"/>
       <c r="C201" s="39"/>
@@ -6292,7 +6306,7 @@
       <c r="H201" s="12"/>
       <c r="I201" s="12"/>
     </row>
-    <row r="202" spans="1:9" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="202" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A202" s="7"/>
       <c r="B202" s="8"/>
       <c r="C202" s="39"/>
@@ -6303,7 +6317,7 @@
       <c r="H202" s="12"/>
       <c r="I202" s="12"/>
     </row>
-    <row r="203" spans="1:9" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="203" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A203" s="7"/>
       <c r="B203" s="8"/>
       <c r="C203" s="39"/>
@@ -6314,8 +6328,6 @@
       <c r="H203" s="12"/>
       <c r="I203" s="12"/>
     </row>
-    <row r="204" spans="1:9" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="205" spans="1:9" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -6744,6 +6756,23 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_activity xmlns="3e53c16e-6636-411e-b1c4-e9eeb71b3b2a" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x010100027709BF533FA442AFC4A8B2C0110727" ma:contentTypeVersion="15" ma:contentTypeDescription="Crear nuevo documento." ma:contentTypeScope="" ma:versionID="a37fc0d7c302f7619d355a49e1f175a4">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="3e53c16e-6636-411e-b1c4-e9eeb71b3b2a" xmlns:ns4="bda9c1ec-c4e2-44f9-929c-ca399fe36c88" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="01250a30c504a808427f15ccf149ee4d" ns3:_="" ns4:_="">
     <xsd:import namespace="3e53c16e-6636-411e-b1c4-e9eeb71b3b2a"/>
@@ -6976,24 +7005,25 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_activity xmlns="3e53c16e-6636-411e-b1c4-e9eeb71b3b2a" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3C8123E5-81FD-4C24-91F1-33BC079967E9}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D9861A25-610F-425F-BC6A-AC52D4971411}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="3e53c16e-6636-411e-b1c4-e9eeb71b3b2a"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4794C7E6-B89D-4081-9A67-B8D500EF1EE4}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -7010,22 +7040,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D9861A25-610F-425F-BC6A-AC52D4971411}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="3e53c16e-6636-411e-b1c4-e9eeb71b3b2a"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3C8123E5-81FD-4C24-91F1-33BC079967E9}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>